--- a/hmm_regime_results_monthly.xlsx
+++ b/hmm_regime_results_monthly.xlsx
@@ -491,7 +491,7 @@
         <v>-2.915567756089579</v>
       </c>
       <c r="F2" t="n">
-        <v>7.948783884085062</v>
+        <v>7.94878388408506</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5231463948411231</v>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.948783884085062</v>
+        <v>7.94878388408506</v>
       </c>
       <c r="C10" t="n">
         <v>5.037871764325111</v>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8913880599458675</v>
+        <v>0.8913880599458304</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003881296848967605</v>
+        <v>0.003881296849025836</v>
       </c>
       <c r="D22" t="n">
-        <v>0.104730643205165</v>
+        <v>0.1047306432051439</v>
       </c>
     </row>
     <row r="23">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0166161876612837</v>
+        <v>0.01661618766126477</v>
       </c>
       <c r="C23" t="n">
-        <v>0.940673540716451</v>
+        <v>0.9406735407165159</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04271027162226536</v>
+        <v>0.04271027162221921</v>
       </c>
     </row>
     <row r="24">
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.485350796670785e-08</v>
+        <v>4.485350796600124e-08</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04973435529075192</v>
+        <v>0.04973435529074275</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9502655998557402</v>
+        <v>0.9502655998557493</v>
       </c>
     </row>
     <row r="27">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8913880599458675</v>
+        <v>0.8913880599458304</v>
       </c>
       <c r="C28" t="n">
-        <v>9.207090854850735</v>
+        <v>9.207090854847591</v>
       </c>
     </row>
     <row r="29">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.940673540716451</v>
+        <v>0.9406735407165159</v>
       </c>
       <c r="C29" t="n">
-        <v>16.85588541902579</v>
+        <v>16.85588541904421</v>
       </c>
     </row>
     <row r="30">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9502655998557402</v>
+        <v>0.9502655998557493</v>
       </c>
       <c r="C30" t="n">
-        <v>20.10680730237816</v>
+        <v>20.10680730238184</v>
       </c>
     </row>
     <row r="33">
@@ -1158,7 +1158,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>1445.788715168305</v>
+        <v>1445.788715168303</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -1184,7 +1184,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>1444.53547122711</v>
+        <v>1444.535471227111</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1210,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1444.534569317037</v>
+        <v>1444.534569317038</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1262,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>1442.925003415813</v>
+        <v>1442.925003415807</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -1288,7 +1288,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>1440.262283589452</v>
+        <v>1440.262283589453</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -1314,7 +1314,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>1440.224319393109</v>
+        <v>1440.224319393116</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -1366,7 +1366,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>1439.914657167446</v>
+        <v>1439.914657167448</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -1392,7 +1392,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>1439.068577161559</v>
+        <v>1439.068577161563</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
@@ -1418,7 +1418,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="n">
-        <v>1438.64816039359</v>
+        <v>1438.648160393587</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
@@ -1444,7 +1444,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>1438.481325457338</v>
+        <v>1438.481325457343</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -1470,7 +1470,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>1438.257985253289</v>
+        <v>1438.257985253284</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
@@ -1496,7 +1496,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>1438.257974771667</v>
+        <v>1438.257974771671</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1522,7 +1522,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>1437.950053028634</v>
+        <v>1437.950053028632</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="n">
-        <v>1437.549368362985</v>
+        <v>1437.549368362972</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
@@ -1574,7 +1574,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1437.51786052341</v>
+        <v>1437.517860523411</v>
       </c>
       <c r="C18" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1432.264318100705</v>
+        <v>1432.264318100713</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -1652,7 +1652,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>1432.159907672288</v>
+        <v>1432.159907672292</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>1429.271115507528</v>
+        <v>1429.27111550752</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -1704,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="n">
-        <v>1429.227096908194</v>
+        <v>1429.227096908193</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -1730,7 +1730,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="n">
-        <v>1428.661687114702</v>
+        <v>1428.661687114704</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -1756,7 +1756,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="n">
-        <v>1422.695318049565</v>
+        <v>1422.695318049556</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
@@ -1782,7 +1782,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="n">
-        <v>1420.959985288543</v>
+        <v>1420.959985288537</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
@@ -1857,16 +1857,16 @@
         <v>0.03746962579352606</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008686003136073352</v>
+        <v>0.0008686003136073347</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1.822856416171981e-150</v>
+        <v>1.822856416200579e-150</v>
       </c>
       <c r="F2" t="n">
-        <v>8.797567933541798e-87</v>
+        <v>8.797567933629813e-87</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1886,10 +1886,10 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1.259713813972069e-08</v>
+        <v>1.259713813952306e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00316090685345764</v>
+        <v>0.003160906853459077</v>
       </c>
       <c r="G3" t="n">
         <v>0.9968390805494566</v>
@@ -1909,10 +1909,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3.537756398709743e-06</v>
+        <v>3.537756398705721e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01962311378487605</v>
+        <v>0.01962311378488497</v>
       </c>
       <c r="G4" t="n">
         <v>0.9803733484588154</v>
@@ -1932,10 +1932,10 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.959218544953181e-05</v>
+        <v>1.959218544951844e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04503615748764486</v>
+        <v>0.04503615748766535</v>
       </c>
       <c r="G5" t="n">
         <v>0.9549442503269683</v>
@@ -1955,10 +1955,10 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>7.84744196262289e-05</v>
+        <v>7.847441962621107e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08740437739243172</v>
+        <v>0.08740437739247146</v>
       </c>
       <c r="G6" t="n">
         <v>0.9125171481879744</v>
@@ -1978,13 +1978,13 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>6.161816837181579e-05</v>
+        <v>6.161816837180178e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1897170413199841</v>
+        <v>0.1897170413200703</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8102213405117272</v>
+        <v>0.8102213405115429</v>
       </c>
     </row>
     <row r="8">
@@ -2001,10 +2001,10 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001498340439795939</v>
+        <v>0.000149834043979628</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2929818593957344</v>
+        <v>0.2929818593958676</v>
       </c>
       <c r="G8" t="n">
         <v>0.7068683065602283</v>
@@ -2027,10 +2027,10 @@
         <v>0.0001186262957228101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3739390329165496</v>
+        <v>0.3739390329166346</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6259423407878051</v>
+        <v>0.6259423407876629</v>
       </c>
     </row>
     <row r="10">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001919811178947498</v>
+        <v>0.0001919811178946188</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5209401592071969</v>
+        <v>0.5209401592073154</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4788678596750031</v>
+        <v>0.4788678596746764</v>
       </c>
     </row>
     <row r="11">
@@ -2070,13 +2070,13 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0002360692610641242</v>
+        <v>0.0002360692610640169</v>
       </c>
       <c r="F11" t="n">
-        <v>0.577289631843341</v>
+        <v>0.5772896318436036</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4224742988955056</v>
+        <v>0.4224742988953135</v>
       </c>
     </row>
     <row r="12">
@@ -2093,13 +2093,13 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000247444227557482</v>
+        <v>0.0002474442275575945</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6221819812200822</v>
+        <v>0.6221819812203651</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3775705745522567</v>
+        <v>0.377570574552085</v>
       </c>
     </row>
     <row r="13">
@@ -2119,10 +2119,10 @@
         <v>0.0006394049830491329</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7364270562108969</v>
+        <v>0.7364270562112317</v>
       </c>
       <c r="G13" t="n">
-        <v>0.262933538805998</v>
+        <v>0.2629335388057588</v>
       </c>
     </row>
     <row r="14">
@@ -2139,13 +2139,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001942487279819148</v>
+        <v>0.001942487279818264</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8222438154345801</v>
+        <v>0.8222438154347671</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1758136972856756</v>
+        <v>0.1758136972855157</v>
       </c>
     </row>
     <row r="15">
@@ -2162,13 +2162,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002295234634897844</v>
+        <v>0.002295234634897322</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8466025836446517</v>
+        <v>0.8466025836448442</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1511021817204858</v>
+        <v>0.151102181720314</v>
       </c>
     </row>
     <row r="16">
@@ -2185,13 +2185,13 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.004557637629761906</v>
+        <v>0.004557637629760871</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8539614955688367</v>
+        <v>0.8539614955690308</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1414808668013194</v>
+        <v>0.1414808668011264</v>
       </c>
     </row>
     <row r="17">
@@ -2208,13 +2208,13 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002725585641747992</v>
+        <v>0.002725585641748611</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8572385664423727</v>
+        <v>0.8572385664425676</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1400358479158901</v>
+        <v>0.1400358479157309</v>
       </c>
     </row>
     <row r="18">
@@ -2231,13 +2231,13 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00113035993303486</v>
+        <v>0.001130359933035374</v>
       </c>
       <c r="F18" t="n">
-        <v>0.865920749296071</v>
+        <v>0.8659207492962679</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1329488907707972</v>
+        <v>0.1329488907706763</v>
       </c>
     </row>
     <row r="19">
@@ -2254,13 +2254,13 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000349602852841993</v>
+        <v>0.0003496028528428674</v>
       </c>
       <c r="F19" t="n">
         <v>0.8741493193380432</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1255010778091448</v>
+        <v>0.1255010778090021</v>
       </c>
     </row>
     <row r="20">
@@ -2271,19 +2271,19 @@
         <v>-0.02054671670874412</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002590752718941235</v>
+        <v>0.002590752718941236</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0002069109463842847</v>
+        <v>0.0002069109463851315</v>
       </c>
       <c r="F20" t="n">
         <v>0.9063597636783753</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09343332537525939</v>
+        <v>0.09343332537513192</v>
       </c>
     </row>
     <row r="21">
@@ -2300,13 +2300,13 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0001880533632507184</v>
+        <v>0.0001880533632518729</v>
       </c>
       <c r="F21" t="n">
         <v>0.9365742602204776</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06323768641634914</v>
+        <v>0.06323768641627725</v>
       </c>
     </row>
     <row r="22">
@@ -2323,13 +2323,13 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0003117600593350977</v>
+        <v>0.0003117600593365154</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9857752032191869</v>
+        <v>0.985775203219411</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01391303672137754</v>
+        <v>0.01391303672136173</v>
       </c>
     </row>
     <row r="23">
@@ -2337,22 +2337,22 @@
         <v>36830</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.009817373019298678</v>
+        <v>-0.00981737301929868</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0035647155073691</v>
+        <v>0.003564715507369099</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0002075823107723243</v>
+        <v>0.0002075823107732683</v>
       </c>
       <c r="F23" t="n">
         <v>0.9892334094044088</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01055900828492359</v>
+        <v>0.01055900828491158</v>
       </c>
     </row>
     <row r="24">
@@ -2369,13 +2369,13 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0004453946856024954</v>
+        <v>0.0004453946856033056</v>
       </c>
       <c r="F24" t="n">
         <v>0.9995014964064887</v>
       </c>
       <c r="G24" t="n">
-        <v>5.310890788491587e-05</v>
+        <v>5.310890788480719e-05</v>
       </c>
     </row>
     <row r="25">
@@ -2392,13 +2392,13 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0002429273396503306</v>
+        <v>0.0002429273396511591</v>
       </c>
       <c r="F25" t="n">
         <v>0.9928105476125912</v>
       </c>
       <c r="G25" t="n">
-        <v>0.006946525047718592</v>
+        <v>0.006946525047705957</v>
       </c>
     </row>
     <row r="26">
@@ -2415,13 +2415,13 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0002069530559144696</v>
+        <v>0.000206953055915693</v>
       </c>
       <c r="F26" t="n">
         <v>0.9907670660047121</v>
       </c>
       <c r="G26" t="n">
-        <v>0.009025980939367632</v>
+        <v>0.009025980939353266</v>
       </c>
     </row>
     <row r="27">
@@ -2438,13 +2438,13 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0005679546789582613</v>
+        <v>0.0005679546789608441</v>
       </c>
       <c r="F27" t="n">
         <v>0.9994206330535904</v>
       </c>
       <c r="G27" t="n">
-        <v>1.141226755972827e-05</v>
+        <v>1.14122675597101e-05</v>
       </c>
     </row>
     <row r="28">
@@ -2461,13 +2461,13 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0007356825648444112</v>
+        <v>0.0007356825648460839</v>
       </c>
       <c r="F28" t="n">
         <v>0.9990375339585039</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0002267834765824724</v>
+        <v>0.0002267834765820084</v>
       </c>
     </row>
     <row r="29">
@@ -2484,13 +2484,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0006203654303591393</v>
+        <v>0.0006203654303598445</v>
       </c>
       <c r="F29" t="n">
         <v>0.9966970421611322</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002682592408580394</v>
+        <v>0.002682592408574905</v>
       </c>
     </row>
     <row r="30">
@@ -2498,7 +2498,7 @@
         <v>37042</v>
       </c>
       <c r="B30" t="n">
-        <v>0.003486086443238612</v>
+        <v>0.003486086443238613</v>
       </c>
       <c r="C30" t="n">
         <v>-0.001127279284296733</v>
@@ -2507,13 +2507,13 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0001662068938531783</v>
+        <v>0.0001662068938540098</v>
       </c>
       <c r="F30" t="n">
         <v>0.9887183401811207</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01111545292500545</v>
+        <v>0.01111545292498776</v>
       </c>
     </row>
     <row r="31">
@@ -2530,13 +2530,13 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0001433310502059089</v>
+        <v>0.0001433310502068214</v>
       </c>
       <c r="F31" t="n">
         <v>0.9920117498550518</v>
       </c>
       <c r="G31" t="n">
-        <v>0.007844919094689347</v>
+        <v>0.007844919094678646</v>
       </c>
     </row>
     <row r="32">
@@ -2553,13 +2553,13 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0002030807673143626</v>
+        <v>0.0002030807673153785</v>
       </c>
       <c r="F32" t="n">
         <v>0.996334852025199</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003462067207516756</v>
+        <v>0.003462067207512033</v>
       </c>
     </row>
     <row r="33">
@@ -2570,19 +2570,19 @@
         <v>-0.06774638797380172</v>
       </c>
       <c r="C33" t="n">
-        <v>0.009266260116781109</v>
+        <v>0.009266260116781111</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000420467367296761</v>
+        <v>0.0004204673672980039</v>
       </c>
       <c r="F33" t="n">
         <v>0.9994305090413039</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0001490235914578153</v>
+        <v>0.000149023591457612</v>
       </c>
     </row>
     <row r="34">
@@ -2599,13 +2599,13 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0007959096809923748</v>
+        <v>0.0007959096809930987</v>
       </c>
       <c r="F34" t="n">
         <v>0.9991938468181716</v>
       </c>
       <c r="G34" t="n">
-        <v>1.02435008429788e-05</v>
+        <v>1.024350084296249e-05</v>
       </c>
     </row>
     <row r="35">
@@ -2622,13 +2622,13 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000724906549547163</v>
+        <v>0.0007249065495478223</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9908807180470592</v>
+        <v>0.9908807180472845</v>
       </c>
       <c r="G35" t="n">
-        <v>0.008394375403287919</v>
+        <v>0.008394375403276469</v>
       </c>
     </row>
     <row r="36">
@@ -2645,13 +2645,13 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001169424903658783</v>
+        <v>0.001169424903658517</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9908674145379285</v>
+        <v>0.9908674145381537</v>
       </c>
       <c r="G36" t="n">
-        <v>0.007963160558307678</v>
+        <v>0.007963160558295003</v>
       </c>
     </row>
     <row r="37">
@@ -2668,13 +2668,13 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0003864318786529968</v>
+        <v>0.0003864318786538755</v>
       </c>
       <c r="F37" t="n">
         <v>0.9719999899199364</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02761357820150987</v>
+        <v>0.02761357820146592</v>
       </c>
     </row>
     <row r="38">
@@ -2685,19 +2685,19 @@
         <v>-0.01610219756674967</v>
       </c>
       <c r="C38" t="n">
-        <v>0.004747939606516225</v>
+        <v>0.004747939606516224</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001901227167822536</v>
+        <v>0.0001901227167829885</v>
       </c>
       <c r="F38" t="n">
         <v>0.9753257338128171</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02448414347042927</v>
+        <v>0.02448414347038473</v>
       </c>
     </row>
     <row r="39">
@@ -2708,19 +2708,19 @@
         <v>-0.02076850133664727</v>
       </c>
       <c r="C39" t="n">
-        <v>0.009776868601837064</v>
+        <v>0.009776868601837062</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001676923132392347</v>
+        <v>0.0001676923132401498</v>
       </c>
       <c r="F39" t="n">
         <v>0.9820607035237493</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01777160416300663</v>
+        <v>0.01777160416297026</v>
       </c>
     </row>
     <row r="40">
@@ -2737,13 +2737,13 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002160032545386798</v>
+        <v>0.0002160032545405461</v>
       </c>
       <c r="F40" t="n">
         <v>0.9862237227976317</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01356027394783309</v>
+        <v>0.01356027394780843</v>
       </c>
     </row>
     <row r="41">
@@ -2760,13 +2760,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002242131731174277</v>
+        <v>0.0002242131731186003</v>
       </c>
       <c r="F41" t="n">
         <v>0.9995385541367663</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0002372326900971362</v>
+        <v>0.0002372326900967586</v>
       </c>
     </row>
     <row r="42">
@@ -2783,13 +2783,13 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0001181696894536702</v>
+        <v>0.0001181696894546913</v>
       </c>
       <c r="F42" t="n">
         <v>0.997206979157766</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00267485115279467</v>
+        <v>0.002674851152790413</v>
       </c>
     </row>
     <row r="43">
@@ -2806,13 +2806,13 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.000225695409946299</v>
+        <v>0.0002256954099476846</v>
       </c>
       <c r="F43" t="n">
         <v>0.9997453833587034</v>
       </c>
       <c r="G43" t="n">
-        <v>2.892123143017789e-05</v>
+        <v>2.892123143013185e-05</v>
       </c>
     </row>
     <row r="44">
@@ -2829,13 +2829,13 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0004007836928993396</v>
+        <v>0.0004007836929007066</v>
       </c>
       <c r="F44" t="n">
         <v>0.9995955381425373</v>
       </c>
       <c r="G44" t="n">
-        <v>3.67816448909442e-06</v>
+        <v>3.678164489087729e-06</v>
       </c>
     </row>
     <row r="45">
@@ -2852,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0005075021855656009</v>
+        <v>0.0005075021855669857</v>
       </c>
       <c r="F45" t="n">
         <v>0.9968949392540493</v>
       </c>
       <c r="G45" t="n">
-        <v>0.002597558560481441</v>
+        <v>0.002597558560477307</v>
       </c>
     </row>
     <row r="46">
@@ -2875,13 +2875,13 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001083075889444239</v>
+        <v>0.001083075889445471</v>
       </c>
       <c r="F46" t="n">
         <v>0.998916911550545</v>
       </c>
       <c r="G46" t="n">
-        <v>1.255991436726283e-08</v>
+        <v>1.255991436723998e-08</v>
       </c>
     </row>
     <row r="47">
@@ -2898,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.001595509783150559</v>
+        <v>0.001595509783149833</v>
       </c>
       <c r="F47" t="n">
         <v>0.997880247504392</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0005242427123944719</v>
+        <v>0.0005242427123935184</v>
       </c>
     </row>
     <row r="48">
@@ -2921,13 +2921,13 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.003017741773369032</v>
+        <v>0.003017741773366974</v>
       </c>
       <c r="F48" t="n">
         <v>0.9950110253267763</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001971232899922277</v>
+        <v>0.001971232899918691</v>
       </c>
     </row>
     <row r="49">
@@ -2944,13 +2944,13 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.006826110004241347</v>
+        <v>0.006826110004238242</v>
       </c>
       <c r="F49" t="n">
         <v>0.9922443878970157</v>
       </c>
       <c r="G49" t="n">
-        <v>0.000929502098791497</v>
+        <v>0.0009295020987910743</v>
       </c>
     </row>
     <row r="50">
@@ -2967,13 +2967,13 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.007850477436820181</v>
+        <v>0.007850477436818395</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8952287305636051</v>
+        <v>0.8952287305638087</v>
       </c>
       <c r="G50" t="n">
-        <v>0.09692079199947749</v>
+        <v>0.09692079199945546</v>
       </c>
     </row>
     <row r="51">
@@ -2993,7 +2993,7 @@
         <v>0.009379703439753879</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8136755580098508</v>
+        <v>0.8136755580100358</v>
       </c>
       <c r="G51" t="n">
         <v>0.1769447385503123</v>
@@ -3013,13 +3013,13 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01133135654800186</v>
+        <v>0.01133135654799671</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6311495940887666</v>
+        <v>0.6311495940889101</v>
       </c>
       <c r="G52" t="n">
-        <v>0.3575190493632643</v>
+        <v>0.3575190493631017</v>
       </c>
     </row>
     <row r="53">
@@ -3036,13 +3036,13 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02815157532975769</v>
+        <v>0.02815157532974489</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5362158530196282</v>
+        <v>0.5362158530198721</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4356325716506289</v>
+        <v>0.4356325716504308</v>
       </c>
     </row>
     <row r="54">
@@ -3059,13 +3059,13 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.05633345547527899</v>
+        <v>0.05633345547525338</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2838655465832618</v>
+        <v>0.2838655465833264</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6598009979415639</v>
+        <v>0.6598009979414138</v>
       </c>
     </row>
     <row r="55">
@@ -3082,13 +3082,13 @@
         <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0.05222996375842068</v>
+        <v>0.05222996375839693</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1900099107409634</v>
+        <v>0.1900099107410498</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7577601255006898</v>
+        <v>0.7577601255005175</v>
       </c>
     </row>
     <row r="56">
@@ -3105,10 +3105,10 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.08002269929062289</v>
+        <v>0.0800226992905865</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1269950125450969</v>
+        <v>0.1269950125452124</v>
       </c>
       <c r="G56" t="n">
         <v>0.7929822881642004</v>
@@ -3128,10 +3128,10 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.03848972361844997</v>
+        <v>0.03848972361844122</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1367795073915603</v>
+        <v>0.1367795073916847</v>
       </c>
       <c r="G57" t="n">
         <v>0.8247307689899669</v>
@@ -3154,7 +3154,7 @@
         <v>0.03420215763927174</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1669107757865086</v>
+        <v>0.1669107757866224</v>
       </c>
       <c r="G58" t="n">
         <v>0.798887066574156</v>
@@ -3174,13 +3174,13 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0163177053466984</v>
+        <v>0.01631770534669098</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1427697024768737</v>
+        <v>0.1427697024769386</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8409125921764847</v>
+        <v>0.8409125921762935</v>
       </c>
     </row>
     <row r="60">
@@ -3197,10 +3197,10 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003116370791479455</v>
+        <v>0.003116370791478038</v>
       </c>
       <c r="F60" t="n">
-        <v>0.09191269003814262</v>
+        <v>0.09191269003818442</v>
       </c>
       <c r="G60" t="n">
         <v>0.904970939170335</v>
@@ -3220,10 +3220,10 @@
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001154566421946223</v>
+        <v>0.001154566421945697</v>
       </c>
       <c r="F61" t="n">
-        <v>0.06600239375755189</v>
+        <v>0.06600239375758191</v>
       </c>
       <c r="G61" t="n">
         <v>0.9328430398205673</v>
@@ -3243,10 +3243,10 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0004634110981765776</v>
+        <v>0.0004634110981764723</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04785668680768669</v>
+        <v>0.04785668680770846</v>
       </c>
       <c r="G62" t="n">
         <v>0.951679902094124</v>
@@ -3266,10 +3266,10 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0004378122152622204</v>
+        <v>0.0004378122152621208</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03923728536502403</v>
+        <v>0.03923728536504187</v>
       </c>
       <c r="G63" t="n">
         <v>0.9603249024196072</v>
@@ -3289,10 +3289,10 @@
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>0.000849440255420292</v>
+        <v>0.0008494402554200988</v>
       </c>
       <c r="F64" t="n">
-        <v>0.03440388320382422</v>
+        <v>0.03440388320383204</v>
       </c>
       <c r="G64" t="n">
         <v>0.9647466765406718</v>
@@ -3312,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0.002270359050297261</v>
+        <v>0.002270359050295196</v>
       </c>
       <c r="F65" t="n">
         <v>0.01514910623887766</v>
@@ -3335,10 +3335,10 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000399953410149255</v>
+        <v>0.0003999534101489822</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0237061849013998</v>
+        <v>0.02370618490139441</v>
       </c>
       <c r="G66" t="n">
         <v>0.9758938616884832</v>
@@ -3358,10 +3358,10 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0001590070326827564</v>
+        <v>0.0001590070326826841</v>
       </c>
       <c r="F67" t="n">
-        <v>0.04358238344179919</v>
+        <v>0.04358238344178928</v>
       </c>
       <c r="G67" t="n">
         <v>0.9562586095255035</v>
@@ -3381,13 +3381,13 @@
         <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0003126936304015251</v>
+        <v>0.0003126936304013118</v>
       </c>
       <c r="F68" t="n">
-        <v>0.08027550358477892</v>
+        <v>0.08027550358474242</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9194118027847571</v>
+        <v>0.9194118027849661</v>
       </c>
     </row>
     <row r="69">
@@ -3404,10 +3404,10 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0005866301535283365</v>
+        <v>0.0005866301535276696</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06963444697292337</v>
+        <v>0.06963444697287588</v>
       </c>
       <c r="G69" t="n">
         <v>0.9297789228735759</v>
@@ -3427,10 +3427,10 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0002735152650395013</v>
+        <v>0.0002735152650391903</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05182059570297379</v>
+        <v>0.05182059570293845</v>
       </c>
       <c r="G70" t="n">
         <v>0.9479058890320518</v>
@@ -3450,10 +3450,10 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0001880067083518329</v>
+        <v>0.0001880067083516192</v>
       </c>
       <c r="F71" t="n">
-        <v>0.04492055561937627</v>
+        <v>0.04492055561935585</v>
       </c>
       <c r="G71" t="n">
         <v>0.9548914376722588</v>
@@ -3473,10 +3473,10 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0002285527171575529</v>
+        <v>0.0002285527171572931</v>
       </c>
       <c r="F72" t="n">
-        <v>0.04495060004457819</v>
+        <v>0.04495060004454753</v>
       </c>
       <c r="G72" t="n">
         <v>0.9548208472383591</v>
@@ -3496,10 +3496,10 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.000161521709865122</v>
+        <v>0.0001615217098649384</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04656155349527858</v>
+        <v>0.04656155349524682</v>
       </c>
       <c r="G73" t="n">
         <v>0.9532769247948882</v>
@@ -3519,10 +3519,10 @@
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0002434250776524402</v>
+        <v>0.0002434250776521081</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0572997538701957</v>
+        <v>0.05729975387015662</v>
       </c>
       <c r="G74" t="n">
         <v>0.9424568210522137</v>
@@ -3542,10 +3542,10 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0002280982390909816</v>
+        <v>0.0002280982390907222</v>
       </c>
       <c r="F75" t="n">
-        <v>0.05135453457975575</v>
+        <v>0.05135453457972072</v>
       </c>
       <c r="G75" t="n">
         <v>0.9484173671810797</v>
@@ -3565,13 +3565,13 @@
         <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0003112691598928663</v>
+        <v>0.0003112691598925125</v>
       </c>
       <c r="F76" t="n">
-        <v>0.059129268258857</v>
+        <v>0.05912926825880322</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9405594625811589</v>
+        <v>0.9405594625813728</v>
       </c>
     </row>
     <row r="77">
@@ -3588,10 +3588,10 @@
         <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0005327940183322704</v>
+        <v>0.000532794018331907</v>
       </c>
       <c r="F77" t="n">
-        <v>0.07202065304140452</v>
+        <v>0.07202065304133902</v>
       </c>
       <c r="G77" t="n">
         <v>0.9274465529403543</v>
@@ -3611,10 +3611,10 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0003734538863895329</v>
+        <v>0.0003734538863891083</v>
       </c>
       <c r="F78" t="n">
-        <v>0.04946530200369863</v>
+        <v>0.04946530200366489</v>
       </c>
       <c r="G78" t="n">
         <v>0.9501612441098342</v>
@@ -3634,10 +3634,10 @@
         <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0002684889465542745</v>
+        <v>0.0002684889465540302</v>
       </c>
       <c r="F79" t="n">
-        <v>0.039254615995027</v>
+        <v>0.03925461599500022</v>
       </c>
       <c r="G79" t="n">
         <v>0.9604768950585163</v>
@@ -3657,10 +3657,10 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0003470574367912832</v>
+        <v>0.0003470574367908097</v>
       </c>
       <c r="F80" t="n">
-        <v>0.03301709838231251</v>
+        <v>0.03301709838228248</v>
       </c>
       <c r="G80" t="n">
         <v>0.9666358441808554</v>
@@ -3680,13 +3680,13 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0003674544446837866</v>
+        <v>0.0003674544446835359</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0301637819038029</v>
+        <v>0.03016378190378233</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9694687636514074</v>
+        <v>0.9694687636516279</v>
       </c>
     </row>
     <row r="82">
@@ -3703,10 +3703,10 @@
         <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0003175060573310536</v>
+        <v>0.0003175060573306205</v>
       </c>
       <c r="F82" t="n">
-        <v>0.01463097604983156</v>
+        <v>0.01463097604981492</v>
       </c>
       <c r="G82" t="n">
         <v>0.9850515178929012</v>
@@ -3726,10 +3726,10 @@
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0002052570695719403</v>
+        <v>0.0002052570695717536</v>
       </c>
       <c r="F83" t="n">
-        <v>0.01078204156973577</v>
+        <v>0.01078204156973087</v>
       </c>
       <c r="G83" t="n">
         <v>0.989012701360676</v>
@@ -3743,19 +3743,19 @@
         <v>0.03402946422756281</v>
       </c>
       <c r="C84" t="n">
-        <v>0.002718764958117402</v>
+        <v>0.002718764958117403</v>
       </c>
       <c r="D84" t="n">
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.338343421535754e-05</v>
+        <v>7.33834342152908e-05</v>
       </c>
       <c r="F84" t="n">
-        <v>0.009942528195589094</v>
+        <v>0.009942528195582312</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9899840883700823</v>
+        <v>0.9899840883703075</v>
       </c>
     </row>
     <row r="85">
@@ -3763,7 +3763,7 @@
         <v>38717</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.002845288954795244</v>
+        <v>-0.002845288954795243</v>
       </c>
       <c r="C85" t="n">
         <v>0.008921207357914518</v>
@@ -3772,10 +3772,10 @@
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>6.054050768528933e-05</v>
+        <v>6.05405076852205e-05</v>
       </c>
       <c r="F85" t="n">
-        <v>0.01007011903372469</v>
+        <v>0.01007011903371553</v>
       </c>
       <c r="G85" t="n">
         <v>0.9898693404585539</v>
@@ -3795,10 +3795,10 @@
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>5.112121543196245e-05</v>
+        <v>5.112121543190434e-05</v>
       </c>
       <c r="F86" t="n">
-        <v>0.007451542137423973</v>
+        <v>0.007451542137417196</v>
       </c>
       <c r="G86" t="n">
         <v>0.9924973366470728</v>
@@ -3809,7 +3809,7 @@
         <v>38776</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.0006837315003157397</v>
+        <v>-0.0006837315003157393</v>
       </c>
       <c r="C87" t="n">
         <v>-0.004183623699470881</v>
@@ -3818,10 +3818,10 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.217567072921763e-05</v>
+        <v>4.217567072917927e-05</v>
       </c>
       <c r="F87" t="n">
-        <v>0.006511497980406748</v>
+        <v>0.006511497980400825</v>
       </c>
       <c r="G87" t="n">
         <v>0.9934463263489609</v>
@@ -3841,10 +3841,10 @@
         <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>4.200775022740476e-05</v>
+        <v>4.200775022736656e-05</v>
       </c>
       <c r="F88" t="n">
-        <v>0.006016317020633139</v>
+        <v>0.006016317020629035</v>
       </c>
       <c r="G88" t="n">
         <v>0.9939416752291599</v>
@@ -3864,10 +3864,10 @@
         <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>3.347517909708263e-05</v>
+        <v>3.347517909703697e-05</v>
       </c>
       <c r="F89" t="n">
-        <v>0.008682292704935148</v>
+        <v>0.008682292704927251</v>
       </c>
       <c r="G89" t="n">
         <v>0.9912842321159735</v>
@@ -3887,10 +3887,10 @@
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>8.147250234889547e-05</v>
+        <v>8.147250234880284e-05</v>
       </c>
       <c r="F90" t="n">
-        <v>0.01518046741608775</v>
+        <v>0.0151804674160774</v>
       </c>
       <c r="G90" t="n">
         <v>0.9847380600816205</v>
@@ -3910,10 +3910,10 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>6.944528871041661e-05</v>
+        <v>6.944528871030608e-05</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01414853305242749</v>
+        <v>0.01414853305242106</v>
       </c>
       <c r="G91" t="n">
         <v>0.9857820216589451</v>
@@ -3933,10 +3933,10 @@
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>6.873570725176719e-05</v>
+        <v>6.873570725167342e-05</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01444152728410838</v>
+        <v>0.01444152728410509</v>
       </c>
       <c r="G92" t="n">
         <v>0.9854897370087236</v>
@@ -3956,10 +3956,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>6.481273624296417e-05</v>
+        <v>6.481273624287575e-05</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0131137888135972</v>
+        <v>0.01311378881359422</v>
       </c>
       <c r="G93" t="n">
         <v>0.9868213984501445</v>
@@ -3979,10 +3979,10 @@
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>4.487622184388718e-05</v>
+        <v>4.487622184382595e-05</v>
       </c>
       <c r="F94" t="n">
-        <v>0.01324693798793671</v>
+        <v>0.01324693798793972</v>
       </c>
       <c r="G94" t="n">
         <v>0.98670818579021</v>
@@ -4002,10 +4002,10 @@
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>3.490086810882186e-05</v>
+        <v>3.490086810877424e-05</v>
       </c>
       <c r="F95" t="n">
-        <v>0.01586035083739551</v>
+        <v>0.01586035083739911</v>
       </c>
       <c r="G95" t="n">
         <v>0.9841047482943938</v>
@@ -4025,10 +4025,10 @@
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>3.336635722766436e-05</v>
+        <v>3.336635722761884e-05</v>
       </c>
       <c r="F96" t="n">
-        <v>0.02221022835625462</v>
+        <v>0.02221022835625967</v>
       </c>
       <c r="G96" t="n">
         <v>0.9777564052865667</v>
@@ -4048,10 +4048,10 @@
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>3.873397624176807e-05</v>
+        <v>3.873397624171522e-05</v>
       </c>
       <c r="F97" t="n">
-        <v>0.03334479755682131</v>
+        <v>0.03334479755683648</v>
       </c>
       <c r="G97" t="n">
         <v>0.9666164684668817</v>
@@ -4071,10 +4071,10 @@
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>3.320119512165016e-05</v>
+        <v>3.320119512161997e-05</v>
       </c>
       <c r="F98" t="n">
-        <v>0.06671169733389666</v>
+        <v>0.06671169733394217</v>
       </c>
       <c r="G98" t="n">
         <v>0.9332551014709517</v>
@@ -4094,10 +4094,10 @@
         <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>9.433121755098405e-05</v>
+        <v>9.433121755087681e-05</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1420345790488552</v>
+        <v>0.1420345790489521</v>
       </c>
       <c r="G99" t="n">
         <v>0.8578710897335572</v>
@@ -4117,10 +4117,10 @@
         <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>9.759249602272502e-05</v>
+        <v>9.759249602268064e-05</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1568679733296016</v>
+        <v>0.1568679733297086</v>
       </c>
       <c r="G100" t="n">
         <v>0.8430344341742932</v>
@@ -4140,13 +4140,13 @@
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>7.374526757548237e-05</v>
+        <v>7.374526757544882e-05</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2036206909347302</v>
+        <v>0.2036206909347765</v>
       </c>
       <c r="G101" t="n">
-        <v>0.7963055637977384</v>
+        <v>0.7963055637975573</v>
       </c>
     </row>
     <row r="102">
@@ -4163,13 +4163,13 @@
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>8.578995958738073e-05</v>
+        <v>8.578995958747827e-05</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2837960682262126</v>
+        <v>0.2837960682264062</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7161181418140963</v>
+        <v>0.7161181418139334</v>
       </c>
     </row>
     <row r="103">
@@ -4186,10 +4186,10 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0001163318465505681</v>
+        <v>0.0001163318465507532</v>
       </c>
       <c r="F103" t="n">
-        <v>0.4310030848267231</v>
+        <v>0.4310030848269191</v>
       </c>
       <c r="G103" t="n">
         <v>0.5688805833266366</v>
@@ -4209,13 +4209,13 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0002314674056028435</v>
+        <v>0.0002314674056027908</v>
       </c>
       <c r="F104" t="n">
-        <v>0.6538582021286306</v>
+        <v>0.6538582021287792</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3459103304658031</v>
+        <v>0.3459103304657245</v>
       </c>
     </row>
     <row r="105">
@@ -4232,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0001914969443318649</v>
+        <v>0.0001914969443320391</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6782276467881257</v>
+        <v>0.67822764678828</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3215808562674543</v>
+        <v>0.3215808562673812</v>
       </c>
     </row>
     <row r="106">
@@ -4249,19 +4249,19 @@
         <v>0.03352305135437444</v>
       </c>
       <c r="C106" t="n">
-        <v>0.000268536980876533</v>
+        <v>0.0002685369808765334</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>9.24106508762352e-05</v>
+        <v>9.241065087655036e-05</v>
       </c>
       <c r="F106" t="n">
         <v>0.7241205273204205</v>
       </c>
       <c r="G106" t="n">
-        <v>0.2757870620287147</v>
+        <v>0.2757870620285893</v>
       </c>
     </row>
     <row r="107">
@@ -4272,19 +4272,19 @@
         <v>0.01258704390080084</v>
       </c>
       <c r="C107" t="n">
-        <v>0.007736157572576452</v>
+        <v>0.007736157572576453</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>8.083393455703094e-05</v>
+        <v>8.083393455745367e-05</v>
       </c>
       <c r="F107" t="n">
         <v>0.8187939120643354</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1811252540011823</v>
+        <v>0.1811252540011411</v>
       </c>
     </row>
     <row r="108">
@@ -4301,13 +4301,13 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000238169405696395</v>
+        <v>0.0002381694056969906</v>
       </c>
       <c r="F108" t="n">
         <v>0.9899687943612464</v>
       </c>
       <c r="G108" t="n">
-        <v>0.009793036233119379</v>
+        <v>0.009793036233114926</v>
       </c>
     </row>
     <row r="109">
@@ -4324,13 +4324,13 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0003390540806023143</v>
+        <v>0.0003390540806027769</v>
       </c>
       <c r="F109" t="n">
         <v>0.9901086962884903</v>
       </c>
       <c r="G109" t="n">
-        <v>0.009552249630826336</v>
+        <v>0.009552249630817649</v>
       </c>
     </row>
     <row r="110">
@@ -4353,7 +4353,7 @@
         <v>0.9989634638242093</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0001238115859102774</v>
+        <v>0.0001238115859101085</v>
       </c>
     </row>
     <row r="111">
@@ -4370,13 +4370,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.001946721075703751</v>
+        <v>0.001946721075702423</v>
       </c>
       <c r="F111" t="n">
         <v>0.9949610293869986</v>
       </c>
       <c r="G111" t="n">
-        <v>0.003092249537394432</v>
+        <v>0.003092249537388808</v>
       </c>
     </row>
     <row r="112">
@@ -4384,7 +4384,7 @@
         <v>39538</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.006027409667488031</v>
+        <v>-0.006027409667488032</v>
       </c>
       <c r="C112" t="n">
         <v>0.01148223471221401</v>
@@ -4393,13 +4393,13 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.004914560130935905</v>
+        <v>0.004914560130931436</v>
       </c>
       <c r="F112" t="n">
         <v>0.9829763630399002</v>
       </c>
       <c r="G112" t="n">
-        <v>0.01210907682918074</v>
+        <v>0.01210907682915872</v>
       </c>
     </row>
     <row r="113">
@@ -4416,13 +4416,13 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0.01597283157933009</v>
+        <v>0.01597283157931556</v>
       </c>
       <c r="F113" t="n">
         <v>0.967742662219268</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01628450620145329</v>
+        <v>0.01628450620141996</v>
       </c>
     </row>
     <row r="114">
@@ -4439,13 +4439,13 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.03560421281644818</v>
+        <v>0.03560421281643199</v>
       </c>
       <c r="F114" t="n">
         <v>0.9465445275731845</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01785125961030812</v>
+        <v>0.01785125961027971</v>
       </c>
     </row>
     <row r="115">
@@ -4462,13 +4462,13 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.07234872626911502</v>
+        <v>0.07234872626908213</v>
       </c>
       <c r="F115" t="n">
         <v>0.9274960445444421</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0001552291864890288</v>
+        <v>0.0001552291864887112</v>
       </c>
     </row>
     <row r="116">
@@ -4491,7 +4491,7 @@
         <v>0.8817247608724171</v>
       </c>
       <c r="G116" t="n">
-        <v>0.003432051686411816</v>
+        <v>0.003432051686407915</v>
       </c>
     </row>
     <row r="117">
@@ -4508,13 +4508,13 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.2642861858189324</v>
+        <v>0.2642861858189925</v>
       </c>
       <c r="F117" t="n">
         <v>0.7335444547775177</v>
       </c>
       <c r="G117" t="n">
-        <v>0.002169359403483066</v>
+        <v>0.002169359403480107</v>
       </c>
     </row>
     <row r="118">
@@ -4534,10 +4534,10 @@
         <v>0.7387523984646643</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2612475583590057</v>
+        <v>0.2612475583590651</v>
       </c>
       <c r="G118" t="n">
-        <v>4.31762403827882e-08</v>
+        <v>4.317624038269985e-08</v>
       </c>
     </row>
     <row r="119">
@@ -4557,10 +4557,10 @@
         <v>0.9993694513225264</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0006305486774361289</v>
+        <v>0.0006305486774362723</v>
       </c>
       <c r="G119" t="n">
-        <v>1.985820390022753e-14</v>
+        <v>1.985820390017787e-14</v>
       </c>
     </row>
     <row r="120">
@@ -4580,10 +4580,10 @@
         <v>0.9999403000017146</v>
       </c>
       <c r="F120" t="n">
-        <v>5.969997153504796e-05</v>
+        <v>5.969997153515655e-05</v>
       </c>
       <c r="G120" t="n">
-        <v>2.667173862016113e-11</v>
+        <v>2.667173862011868e-11</v>
       </c>
     </row>
     <row r="121">
@@ -4603,10 +4603,10 @@
         <v>0.9999609998753437</v>
       </c>
       <c r="F121" t="n">
-        <v>3.545334226289516e-05</v>
+        <v>3.545334226323373e-05</v>
       </c>
       <c r="G121" t="n">
-        <v>3.546782455714678e-06</v>
+        <v>3.546782455717097e-06</v>
       </c>
     </row>
     <row r="122">
@@ -4626,7 +4626,7 @@
         <v>0.9999774584970017</v>
       </c>
       <c r="F122" t="n">
-        <v>1.163094793593814e-05</v>
+        <v>1.16309479360783e-05</v>
       </c>
       <c r="G122" t="n">
         <v>1.091055512998737e-05</v>
@@ -4649,10 +4649,10 @@
         <v>0.9990833684993177</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0009074276637083875</v>
+        <v>0.0009074276637222113</v>
       </c>
       <c r="G123" t="n">
-        <v>9.203837017271855e-06</v>
+        <v>9.203837017267671e-06</v>
       </c>
     </row>
     <row r="124">
@@ -4669,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9739857401599193</v>
+        <v>0.973985740159698</v>
       </c>
       <c r="F124" t="n">
-        <v>0.006103319443178156</v>
+        <v>0.00610331944327391</v>
       </c>
       <c r="G124" t="n">
-        <v>0.01991094039693238</v>
+        <v>0.01991094039692333</v>
       </c>
     </row>
     <row r="125">
@@ -4692,13 +4692,13 @@
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>0.919663084647654</v>
+        <v>0.9196630846470267</v>
       </c>
       <c r="F125" t="n">
-        <v>0.04611387445067102</v>
+        <v>0.04611387445119527</v>
       </c>
       <c r="G125" t="n">
-        <v>0.03422304090177875</v>
+        <v>0.03422304090173984</v>
       </c>
     </row>
     <row r="126">
@@ -4715,13 +4715,13 @@
         <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>0.4116300158922167</v>
+        <v>0.4116300158919359</v>
       </c>
       <c r="F126" t="n">
-        <v>0.05875442650209126</v>
+        <v>0.05875442650282601</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5296155576057058</v>
+        <v>0.5296155576052241</v>
       </c>
     </row>
     <row r="127">
@@ -4738,13 +4738,13 @@
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>0.09235225465844524</v>
+        <v>0.09235225465836124</v>
       </c>
       <c r="F127" t="n">
-        <v>0.07024944235467982</v>
+        <v>0.07024944235544651</v>
       </c>
       <c r="G127" t="n">
-        <v>0.837398302986895</v>
+        <v>0.8373983029861334</v>
       </c>
     </row>
     <row r="128">
@@ -4761,13 +4761,13 @@
         <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>0.04301740534554987</v>
+        <v>0.04301740534551075</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1032750194591522</v>
+        <v>0.1032750194599036</v>
       </c>
       <c r="G128" t="n">
-        <v>0.8537075751952319</v>
+        <v>0.8537075751946496</v>
       </c>
     </row>
     <row r="129">
@@ -4784,13 +4784,13 @@
         <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>0.007765109055730014</v>
+        <v>0.007765109055728248</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1169947810602295</v>
+        <v>0.1169947810609477</v>
       </c>
       <c r="G129" t="n">
-        <v>0.8752401098839508</v>
+        <v>0.8752401098833539</v>
       </c>
     </row>
     <row r="130">
@@ -4807,13 +4807,13 @@
         <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>0.001805822860954864</v>
+        <v>0.001805822860955685</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1512038408078418</v>
+        <v>0.1512038408085294</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8469903363311923</v>
+        <v>0.8469903363306145</v>
       </c>
     </row>
     <row r="131">
@@ -4830,13 +4830,13 @@
         <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0008392059112783273</v>
+        <v>0.0008392059112800446</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2187208260521316</v>
+        <v>0.2187208260528278</v>
       </c>
       <c r="G131" t="n">
-        <v>0.7804399680365219</v>
+        <v>0.7804399680359896</v>
       </c>
     </row>
     <row r="132">
@@ -4853,13 +4853,13 @@
         <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0007704626757630698</v>
+        <v>0.0007704626757656975</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2898120182909146</v>
+        <v>0.2898120182914418</v>
       </c>
       <c r="G132" t="n">
-        <v>0.7094175190333251</v>
+        <v>0.7094175190326799</v>
       </c>
     </row>
     <row r="133">
@@ -4876,13 +4876,13 @@
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0009356527624009996</v>
+        <v>0.0009356527624046163</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4093906889585759</v>
+        <v>0.4093906889590413</v>
       </c>
       <c r="G133" t="n">
-        <v>0.5896736582790313</v>
+        <v>0.589673658278495</v>
       </c>
     </row>
     <row r="134">
@@ -4899,13 +4899,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0006657545730707381</v>
+        <v>0.0006657545730722518</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7639679319206382</v>
+        <v>0.7639679319209856</v>
       </c>
       <c r="G134" t="n">
-        <v>0.235366313506263</v>
+        <v>0.2353663135060489</v>
       </c>
     </row>
     <row r="135">
@@ -4922,13 +4922,13 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0001763242327643477</v>
+        <v>0.0001763242327650293</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7957679276243933</v>
+        <v>0.7957679276247552</v>
       </c>
       <c r="G135" t="n">
-        <v>0.204055748142767</v>
+        <v>0.204055748142535</v>
       </c>
     </row>
     <row r="136">
@@ -4945,13 +4945,13 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0001431538352578251</v>
+        <v>0.0001431538352583785</v>
       </c>
       <c r="F136" t="n">
-        <v>0.871023046657066</v>
+        <v>0.871023046657264</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1288337995076743</v>
+        <v>0.1288337995074986</v>
       </c>
     </row>
     <row r="137">
@@ -4968,13 +4968,13 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0001201865720968959</v>
+        <v>0.0001201865720976337</v>
       </c>
       <c r="F137" t="n">
-        <v>0.9175160503548431</v>
+        <v>0.9175160503550517</v>
       </c>
       <c r="G137" t="n">
-        <v>0.08236376307304184</v>
+        <v>0.08236376307294821</v>
       </c>
     </row>
     <row r="138">
@@ -4991,13 +4991,13 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0002796555890137566</v>
+        <v>0.0002796555890146468</v>
       </c>
       <c r="F138" t="n">
         <v>0.9996598340855976</v>
       </c>
       <c r="G138" t="n">
-        <v>6.051032545954254e-05</v>
+        <v>6.051032545944624e-05</v>
       </c>
     </row>
     <row r="139">
@@ -5014,13 +5014,13 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0005613858572600458</v>
+        <v>0.0005613858572604287</v>
       </c>
       <c r="F139" t="n">
         <v>0.9993666958741541</v>
       </c>
       <c r="G139" t="n">
-        <v>7.191826848976679e-05</v>
+        <v>7.191826848965233e-05</v>
       </c>
     </row>
     <row r="140">
@@ -5037,13 +5037,13 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0.001022426105712764</v>
+        <v>0.001022426105712299</v>
       </c>
       <c r="F140" t="n">
         <v>0.9962937742367707</v>
       </c>
       <c r="G140" t="n">
-        <v>0.002683799657530443</v>
+        <v>0.002683799657525562</v>
       </c>
     </row>
     <row r="141">
@@ -5060,13 +5060,13 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.002006938224088488</v>
+        <v>0.002006938224086207</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9972257402206248</v>
+        <v>0.9972257402208516</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0007673215551736556</v>
+        <v>0.0007673215551724342</v>
       </c>
     </row>
     <row r="142">
@@ -5083,13 +5083,13 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0.003029294247149735</v>
+        <v>0.003029294247142847</v>
       </c>
       <c r="F142" t="n">
         <v>0.9818130040269581</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01515770172585835</v>
+        <v>0.01515770172582388</v>
       </c>
     </row>
     <row r="143">
@@ -5106,13 +5106,13 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>0.001499387810676986</v>
+        <v>0.00149938781067494</v>
       </c>
       <c r="F143" t="n">
-        <v>0.9239553136815251</v>
+        <v>0.9239553136817352</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0745452985076876</v>
+        <v>0.074545298507552</v>
       </c>
     </row>
     <row r="144">
@@ -5129,13 +5129,13 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0.001988843681754521</v>
+        <v>0.001988843681751356</v>
       </c>
       <c r="F144" t="n">
-        <v>0.8944339756176085</v>
+        <v>0.8944339756178118</v>
       </c>
       <c r="G144" t="n">
-        <v>0.1035771807005859</v>
+        <v>0.1035771807003739</v>
       </c>
     </row>
     <row r="145">
@@ -5152,13 +5152,13 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>0.004547053445650208</v>
+        <v>0.004547053445644006</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8927005956889474</v>
+        <v>0.8927005956891504</v>
       </c>
       <c r="G145" t="n">
-        <v>0.1027523508653704</v>
+        <v>0.1027523508651601</v>
       </c>
     </row>
     <row r="146">
@@ -5175,13 +5175,13 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>0.001102010176999661</v>
+        <v>0.001102010176998409</v>
       </c>
       <c r="F146" t="n">
-        <v>0.8294514528413776</v>
+        <v>0.8294514528415662</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1694465369817159</v>
+        <v>0.1694465369813306</v>
       </c>
     </row>
     <row r="147">
@@ -5198,13 +5198,13 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.000430503876006113</v>
+        <v>0.0004305038760060151</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8068044824412169</v>
+        <v>0.8068044824415839</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1927650136826749</v>
+        <v>0.1927650136823243</v>
       </c>
     </row>
     <row r="148">
@@ -5221,13 +5221,13 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0002175038566694499</v>
+        <v>0.0002175038566698456</v>
       </c>
       <c r="F148" t="n">
-        <v>0.8097014903412009</v>
+        <v>0.809701490341569</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1900810058020441</v>
+        <v>0.1900810058017847</v>
       </c>
     </row>
     <row r="149">
@@ -5244,13 +5244,13 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0001535464227660657</v>
+        <v>0.0001535464227666243</v>
       </c>
       <c r="F149" t="n">
-        <v>0.8387409712234841</v>
+        <v>0.8387409712236749</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1611054823538107</v>
+        <v>0.1611054823535176</v>
       </c>
     </row>
     <row r="150">
@@ -5267,13 +5267,13 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0002024859173456859</v>
+        <v>0.0002024859173464225</v>
       </c>
       <c r="F150" t="n">
-        <v>0.9085499811576755</v>
+        <v>0.9085499811578821</v>
       </c>
       <c r="G150" t="n">
-        <v>0.09124753292491165</v>
+        <v>0.09124753292476642</v>
       </c>
     </row>
     <row r="151">
@@ -5290,13 +5290,13 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0002343090248736612</v>
+        <v>0.0002343090248745669</v>
       </c>
       <c r="F151" t="n">
         <v>0.9393696871734279</v>
       </c>
       <c r="G151" t="n">
-        <v>0.06039600380174328</v>
+        <v>0.06039600380166088</v>
       </c>
     </row>
     <row r="152">
@@ -5313,13 +5313,13 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0005129843605441473</v>
+        <v>0.0005129843605451971</v>
       </c>
       <c r="F152" t="n">
         <v>0.9879771442530045</v>
       </c>
       <c r="G152" t="n">
-        <v>0.01150987138636985</v>
+        <v>0.01150987138634892</v>
       </c>
     </row>
     <row r="153">
@@ -5336,13 +5336,13 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0.001191321347593497</v>
+        <v>0.00119132134759458</v>
       </c>
       <c r="F153" t="n">
         <v>0.9987728404437504</v>
       </c>
       <c r="G153" t="n">
-        <v>3.583820863582299e-05</v>
+        <v>3.583820863576596e-05</v>
       </c>
     </row>
     <row r="154">
@@ -5359,13 +5359,13 @@
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.001755097500248252</v>
+        <v>0.001755097500246256</v>
       </c>
       <c r="F154" t="n">
         <v>0.9982229681268698</v>
       </c>
       <c r="G154" t="n">
-        <v>2.193437293946093e-05</v>
+        <v>2.193437293942103e-05</v>
       </c>
     </row>
     <row r="155">
@@ -5382,13 +5382,13 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>0.003000435583825286</v>
+        <v>0.003000435583819829</v>
       </c>
       <c r="F155" t="n">
         <v>0.9958518774941472</v>
       </c>
       <c r="G155" t="n">
-        <v>0.001147686922072784</v>
+        <v>0.001147686922070174</v>
       </c>
     </row>
     <row r="156">
@@ -5405,13 +5405,13 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0.001315012175158424</v>
+        <v>0.00131501217515663</v>
       </c>
       <c r="F156" t="n">
         <v>0.9472365053527024</v>
       </c>
       <c r="G156" t="n">
-        <v>0.05144848247210579</v>
+        <v>0.0514484824720356</v>
       </c>
     </row>
     <row r="157">
@@ -5428,13 +5428,13 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0008360367037989631</v>
+        <v>0.0008360367037982027</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9111772961831263</v>
+        <v>0.9111772961833334</v>
       </c>
       <c r="G157" t="n">
-        <v>0.08798666711300684</v>
+        <v>0.0879866671128868</v>
       </c>
     </row>
     <row r="158">
@@ -5451,13 +5451,13 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0006088360434983527</v>
+        <v>0.0006088360434980759</v>
       </c>
       <c r="F158" t="n">
-        <v>0.8917934652590339</v>
+        <v>0.8917934652592368</v>
       </c>
       <c r="G158" t="n">
-        <v>0.1075976986975536</v>
+        <v>0.1075976986973579</v>
       </c>
     </row>
     <row r="159">
@@ -5477,10 +5477,10 @@
         <v>0.0007476507841071669</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8921620695819866</v>
+        <v>0.8921620695821895</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1070902796339001</v>
+        <v>0.1070902796337296</v>
       </c>
     </row>
     <row r="160">
@@ -5497,13 +5497,13 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>0.001740415018773629</v>
+        <v>0.001740415018773234</v>
       </c>
       <c r="F160" t="n">
-        <v>0.9040647854789656</v>
+        <v>0.9040647854791711</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0941947995021635</v>
+        <v>0.09419479950201358</v>
       </c>
     </row>
     <row r="161">
@@ -5520,13 +5520,13 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0.00468459632024034</v>
+        <v>0.004684596320239274</v>
       </c>
       <c r="F161" t="n">
         <v>0.9376492868862113</v>
       </c>
       <c r="G161" t="n">
-        <v>0.05766611679352651</v>
+        <v>0.05766611679344784</v>
       </c>
     </row>
     <row r="162">
@@ -5543,13 +5543,13 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>0.01261493426120468</v>
+        <v>0.01261493426120181</v>
       </c>
       <c r="F162" t="n">
         <v>0.9521716077233423</v>
       </c>
       <c r="G162" t="n">
-        <v>0.03521345801544545</v>
+        <v>0.03521345801542143</v>
       </c>
     </row>
     <row r="163">
@@ -5566,13 +5566,13 @@
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>0.006160232972617484</v>
+        <v>0.006160232972614682</v>
       </c>
       <c r="F163" t="n">
-        <v>0.5920809347502833</v>
+        <v>0.5920809347504179</v>
       </c>
       <c r="G163" t="n">
-        <v>0.4017588322770499</v>
+        <v>0.4017588322768672</v>
       </c>
     </row>
     <row r="164">
@@ -5589,13 +5589,13 @@
         <v>2</v>
       </c>
       <c r="E164" t="n">
-        <v>0.003496336992836639</v>
+        <v>0.003496336992835844</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3530328428638749</v>
+        <v>0.3530328428640355</v>
       </c>
       <c r="G164" t="n">
-        <v>0.643470820143304</v>
+        <v>0.6434708201431577</v>
       </c>
     </row>
     <row r="165">
@@ -5615,10 +5615,10 @@
         <v>0.001617899591861278</v>
       </c>
       <c r="F165" t="n">
-        <v>0.2047235643527095</v>
+        <v>0.2047235643528026</v>
       </c>
       <c r="G165" t="n">
-        <v>0.793658536055495</v>
+        <v>0.7936585360553144</v>
       </c>
     </row>
     <row r="166">
@@ -5635,10 +5635,10 @@
         <v>2</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0009353061740932385</v>
+        <v>0.0009353061740930259</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1314633259621266</v>
+        <v>0.1314633259622163</v>
       </c>
       <c r="G166" t="n">
         <v>0.867601367863685</v>
@@ -5661,10 +5661,10 @@
         <v>0.0009279780414227788</v>
       </c>
       <c r="F167" t="n">
-        <v>0.09584557818697671</v>
+        <v>0.0958455781870203</v>
       </c>
       <c r="G167" t="n">
-        <v>0.9032264437716611</v>
+        <v>0.9032264437714557</v>
       </c>
     </row>
     <row r="168">
@@ -5681,10 +5681,10 @@
         <v>2</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0005258226758812134</v>
+        <v>0.000525822675881333</v>
       </c>
       <c r="F168" t="n">
-        <v>0.06566769794268255</v>
+        <v>0.06566769794274227</v>
       </c>
       <c r="G168" t="n">
         <v>0.9338064793813854</v>
@@ -5707,7 +5707,7 @@
         <v>0.0003407135119450661</v>
       </c>
       <c r="F169" t="n">
-        <v>0.04474433813796649</v>
+        <v>0.044744338137997</v>
       </c>
       <c r="G169" t="n">
         <v>0.9549149483500368</v>
@@ -5727,10 +5727,10 @@
         <v>2</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0003729065807863321</v>
+        <v>0.0003729065807865017</v>
       </c>
       <c r="F170" t="n">
-        <v>0.03895828209834509</v>
+        <v>0.03895828209838052</v>
       </c>
       <c r="G170" t="n">
         <v>0.960668811320758</v>
@@ -5750,10 +5750,10 @@
         <v>2</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0002223075651303404</v>
+        <v>0.0002223075651303909</v>
       </c>
       <c r="F171" t="n">
-        <v>0.02564445247044633</v>
+        <v>0.02564445247045799</v>
       </c>
       <c r="G171" t="n">
         <v>0.9741332399643355</v>
@@ -5776,7 +5776,7 @@
         <v>0.0001541763416011468</v>
       </c>
       <c r="F172" t="n">
-        <v>0.01726843352955729</v>
+        <v>0.01726843352956121</v>
       </c>
       <c r="G172" t="n">
         <v>0.9825773901287483</v>
@@ -5796,10 +5796,10 @@
         <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0001535379002435277</v>
+        <v>0.0001535379002434928</v>
       </c>
       <c r="F173" t="n">
-        <v>0.01219216186295781</v>
+        <v>0.01219216186296058</v>
       </c>
       <c r="G173" t="n">
         <v>0.9876543002367523</v>
@@ -5819,7 +5819,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0002712271621209573</v>
+        <v>0.0002712271621208339</v>
       </c>
       <c r="F174" t="n">
         <v>0.008547765271808366</v>
@@ -5842,7 +5842,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0001744629931404256</v>
+        <v>0.0001744629931403066</v>
       </c>
       <c r="F175" t="n">
         <v>0.008100897779760101</v>
@@ -5865,7 +5865,7 @@
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>8.388569987675772e-05</v>
+        <v>8.38856998767005e-05</v>
       </c>
       <c r="F176" t="n">
         <v>0.01509090583820965</v>
@@ -5888,7 +5888,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>0.000131354695083663</v>
+        <v>0.0001313546950835734</v>
       </c>
       <c r="F177" t="n">
         <v>0.01898557633769095</v>
@@ -5911,10 +5911,10 @@
         <v>2</v>
       </c>
       <c r="E178" t="n">
-        <v>7.65278516486681e-05</v>
+        <v>7.652785164858109e-05</v>
       </c>
       <c r="F178" t="n">
-        <v>0.02214998868323328</v>
+        <v>0.02214998868322824</v>
       </c>
       <c r="G178" t="n">
         <v>0.9777734834650127</v>
@@ -5934,7 +5934,7 @@
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>6.369961783981108e-05</v>
+        <v>6.369961783973865e-05</v>
       </c>
       <c r="F179" t="n">
         <v>0.03060646279649526</v>
@@ -5957,7 +5957,7 @@
         <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>7.638615700725307e-05</v>
+        <v>7.63861570071836e-05</v>
       </c>
       <c r="F180" t="n">
         <v>0.04421742472163448</v>
@@ -5980,10 +5980,10 @@
         <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0002170232446854555</v>
+        <v>0.0002170232446852087</v>
       </c>
       <c r="F181" t="n">
-        <v>0.07024756315382143</v>
+        <v>0.07024756315380545</v>
       </c>
       <c r="G181" t="n">
         <v>0.929535413601454</v>
@@ -6003,10 +6003,10 @@
         <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0007085915082151049</v>
+        <v>0.0007085915082147827</v>
       </c>
       <c r="F182" t="n">
-        <v>0.1255298394437134</v>
+        <v>0.1255298394436563</v>
       </c>
       <c r="G182" t="n">
         <v>0.8737615690480672</v>
@@ -6026,7 +6026,7 @@
         <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0006544724058379201</v>
+        <v>0.0006544724058373249</v>
       </c>
       <c r="F183" t="n">
         <v>0.08139463966411004</v>
@@ -6049,7 +6049,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0003566590781283898</v>
+        <v>0.0003566590781280654</v>
       </c>
       <c r="F184" t="n">
         <v>0.05260082050211338</v>
@@ -6072,10 +6072,10 @@
         <v>2</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0002214156842102573</v>
+        <v>0.0002214156842101062</v>
       </c>
       <c r="F185" t="n">
-        <v>0.04167771182269282</v>
+        <v>0.04167771182271177</v>
       </c>
       <c r="G185" t="n">
         <v>0.9581008724931013</v>
@@ -6095,10 +6095,10 @@
         <v>2</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0001830810720665433</v>
+        <v>0.0001830810720664184</v>
       </c>
       <c r="F186" t="n">
-        <v>0.03603949322720273</v>
+        <v>0.03603949322721912</v>
       </c>
       <c r="G186" t="n">
         <v>0.9637774257006935</v>
@@ -6118,10 +6118,10 @@
         <v>2</v>
       </c>
       <c r="E187" t="n">
-        <v>9.265514143358793e-05</v>
+        <v>9.26551414335458e-05</v>
       </c>
       <c r="F187" t="n">
-        <v>0.03636037895829393</v>
+        <v>0.03636037895831046</v>
       </c>
       <c r="G187" t="n">
         <v>0.9635469659001842</v>
@@ -6141,10 +6141,10 @@
         <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>9.587223397785758e-05</v>
+        <v>9.587223397779218e-05</v>
       </c>
       <c r="F188" t="n">
-        <v>0.04574535000906364</v>
+        <v>0.04574535000908444</v>
       </c>
       <c r="G188" t="n">
         <v>0.9541587777568487</v>
@@ -6164,10 +6164,10 @@
         <v>2</v>
       </c>
       <c r="E189" t="n">
-        <v>9.538599946034029e-05</v>
+        <v>9.538599946029691e-05</v>
       </c>
       <c r="F189" t="n">
-        <v>0.05849313882608849</v>
+        <v>0.05849313882611509</v>
       </c>
       <c r="G189" t="n">
         <v>0.9414114751743642</v>
@@ -6190,7 +6190,7 @@
         <v>7.412635689681706e-05</v>
       </c>
       <c r="F190" t="n">
-        <v>0.08702579800243299</v>
+        <v>0.08702579800247257</v>
       </c>
       <c r="G190" t="n">
         <v>0.9129000756406537</v>
@@ -6213,7 +6213,7 @@
         <v>4.92988464984087e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>0.1448222016480409</v>
+        <v>0.1448222016481068</v>
       </c>
       <c r="G191" t="n">
         <v>0.8551284995053942</v>
@@ -6236,7 +6236,7 @@
         <v>6.265391628775602e-05</v>
       </c>
       <c r="F192" t="n">
-        <v>0.2495430332003903</v>
+        <v>0.2495430332004471</v>
       </c>
       <c r="G192" t="n">
         <v>0.7503943128832634</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="E193" t="n">
-        <v>0.0002071331183152848</v>
+        <v>0.0002071331183151906</v>
       </c>
       <c r="F193" t="n">
-        <v>0.4450160344082109</v>
+        <v>0.4450160344083121</v>
       </c>
       <c r="G193" t="n">
         <v>0.5547768324733992</v>
@@ -6279,13 +6279,13 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.00117354930092331</v>
+        <v>0.00117354930092171</v>
       </c>
       <c r="F194" t="n">
-        <v>0.7466517093419073</v>
+        <v>0.746651709342077</v>
       </c>
       <c r="G194" t="n">
-        <v>0.2521747413571557</v>
+        <v>0.2521747413570984</v>
       </c>
     </row>
     <row r="195">
@@ -6302,13 +6302,13 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0.001879054586783528</v>
+        <v>0.001879054586780964</v>
       </c>
       <c r="F195" t="n">
-        <v>0.7399788198315054</v>
+        <v>0.7399788198316736</v>
       </c>
       <c r="G195" t="n">
-        <v>0.2581421255817569</v>
+        <v>0.2581421255816396</v>
       </c>
     </row>
     <row r="196">
@@ -6325,13 +6325,13 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.001368148423811775</v>
+        <v>0.001368148423810531</v>
       </c>
       <c r="F196" t="n">
-        <v>0.7058895123816656</v>
+        <v>0.7058895123819866</v>
       </c>
       <c r="G196" t="n">
-        <v>0.2927423391944819</v>
+        <v>0.2927423391942822</v>
       </c>
     </row>
     <row r="197">
@@ -6348,13 +6348,13 @@
         <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0006058535933483791</v>
+        <v>0.0006058535933478281</v>
       </c>
       <c r="F197" t="n">
-        <v>0.659814768313959</v>
+        <v>0.6598147683142591</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3395793780926573</v>
+        <v>0.3395793780923484</v>
       </c>
     </row>
     <row r="198">
@@ -6371,13 +6371,13 @@
         <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0002929700308733563</v>
+        <v>0.0002929700308735561</v>
       </c>
       <c r="F198" t="n">
-        <v>0.6561627268283865</v>
+        <v>0.6561627268286849</v>
       </c>
       <c r="G198" t="n">
-        <v>0.3435443031406832</v>
+        <v>0.3435443031403708</v>
       </c>
     </row>
     <row r="199">
@@ -6394,13 +6394,13 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0002861902140768444</v>
+        <v>0.0002861902140777554</v>
       </c>
       <c r="F199" t="n">
-        <v>0.68871016142601</v>
+        <v>0.6887101614263232</v>
       </c>
       <c r="G199" t="n">
-        <v>0.3110036483599001</v>
+        <v>0.3110036483596172</v>
       </c>
     </row>
     <row r="200">
@@ -6417,13 +6417,13 @@
         <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0001571578004153691</v>
+        <v>0.0001571578004160481</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7866924142198447</v>
+        <v>0.7866924142200236</v>
       </c>
       <c r="G200" t="n">
-        <v>0.2131504279798477</v>
+        <v>0.2131504279796053</v>
       </c>
     </row>
     <row r="201">
@@ -6440,13 +6440,13 @@
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0003396184066520945</v>
+        <v>0.0003396184066528667</v>
       </c>
       <c r="F201" t="n">
-        <v>0.9697971420083775</v>
+        <v>0.9697971420085981</v>
       </c>
       <c r="G201" t="n">
-        <v>0.02986323958487435</v>
+        <v>0.02986323958483361</v>
       </c>
     </row>
     <row r="202">
@@ -6463,13 +6463,13 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.0004600370039350481</v>
+        <v>0.0004600370039352573</v>
       </c>
       <c r="F202" t="n">
         <v>0.981104194188484</v>
       </c>
       <c r="G202" t="n">
-        <v>0.01843576880761499</v>
+        <v>0.01843576880758565</v>
       </c>
     </row>
     <row r="203">
@@ -6486,13 +6486,13 @@
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>0.00092840512813263</v>
+        <v>0.0009284051281324189</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9820762032624941</v>
+        <v>0.9820762032627174</v>
       </c>
       <c r="G203" t="n">
-        <v>0.01699539160926007</v>
+        <v>0.01699539160923302</v>
       </c>
     </row>
     <row r="204">
@@ -6512,10 +6512,10 @@
         <v>0.001092151618015416</v>
       </c>
       <c r="F204" t="n">
-        <v>0.9647160751935049</v>
+        <v>0.9647160751937242</v>
       </c>
       <c r="G204" t="n">
-        <v>0.03419177318839399</v>
+        <v>0.03419177318835512</v>
       </c>
     </row>
     <row r="205">
@@ -6532,13 +6532,13 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>0.00273742289027252</v>
+        <v>0.002737422890271897</v>
       </c>
       <c r="F205" t="n">
         <v>0.9641379412824563</v>
       </c>
       <c r="G205" t="n">
-        <v>0.03312463582726619</v>
+        <v>0.03312463582722101</v>
       </c>
     </row>
     <row r="206">
@@ -6555,13 +6555,13 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>0.007526358993221411</v>
+        <v>0.0075263589932197</v>
       </c>
       <c r="F206" t="n">
         <v>0.9703681741843131</v>
       </c>
       <c r="G206" t="n">
-        <v>0.02210546682241084</v>
+        <v>0.02210546682238068</v>
       </c>
     </row>
     <row r="207">
@@ -6578,13 +6578,13 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>0.005831596966819421</v>
+        <v>0.005831596966818096</v>
       </c>
       <c r="F207" t="n">
-        <v>0.7914943751241679</v>
+        <v>0.7914943751243477</v>
       </c>
       <c r="G207" t="n">
-        <v>0.2026740279089873</v>
+        <v>0.2026740279089412</v>
       </c>
     </row>
     <row r="208">
@@ -6601,13 +6601,13 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>0.006822611590323794</v>
+        <v>0.006822611590319141</v>
       </c>
       <c r="F208" t="n">
-        <v>0.6240647548779266</v>
+        <v>0.6240647548780685</v>
       </c>
       <c r="G208" t="n">
-        <v>0.3691126335317523</v>
+        <v>0.3691126335315844</v>
       </c>
     </row>
     <row r="209">
@@ -6624,13 +6624,13 @@
         <v>2</v>
       </c>
       <c r="E209" t="n">
-        <v>0.003242033249994833</v>
+        <v>0.003242033249993358</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3794723355407108</v>
+        <v>0.3794723355409697</v>
       </c>
       <c r="G209" t="n">
-        <v>0.6172856312093137</v>
+        <v>0.617285631209033</v>
       </c>
     </row>
     <row r="210">
@@ -6650,10 +6650,10 @@
         <v>0.002051659305341426</v>
       </c>
       <c r="F210" t="n">
-        <v>0.2487469774845694</v>
+        <v>0.248746977484739</v>
       </c>
       <c r="G210" t="n">
-        <v>0.7492013632100517</v>
+        <v>0.7492013632098813</v>
       </c>
     </row>
     <row r="211">
@@ -6670,13 +6670,13 @@
         <v>2</v>
       </c>
       <c r="E211" t="n">
-        <v>0.003100638332744529</v>
+        <v>0.003100638332745234</v>
       </c>
       <c r="F211" t="n">
-        <v>0.185214954624051</v>
+        <v>0.1852149546242194</v>
       </c>
       <c r="G211" t="n">
-        <v>0.8116844070432703</v>
+        <v>0.8116844070430858</v>
       </c>
     </row>
     <row r="212">
@@ -6696,10 +6696,10 @@
         <v>0.001279762279131238</v>
       </c>
       <c r="F212" t="n">
-        <v>0.103138617533132</v>
+        <v>0.1031386175332258</v>
       </c>
       <c r="G212" t="n">
-        <v>0.8955816201877812</v>
+        <v>0.8955816201875776</v>
       </c>
     </row>
     <row r="213">
@@ -6716,13 +6716,13 @@
         <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>0.000723605509733771</v>
+        <v>0.0007236055097339356</v>
       </c>
       <c r="F213" t="n">
-        <v>0.05582073703345516</v>
+        <v>0.05582073703350593</v>
       </c>
       <c r="G213" t="n">
-        <v>0.9434556574568917</v>
+        <v>0.9434556574566773</v>
       </c>
     </row>
     <row r="214">
@@ -6742,7 +6742,7 @@
         <v>0.0005236034987983881</v>
       </c>
       <c r="F214" t="n">
-        <v>0.0355682720499023</v>
+        <v>0.03556827204991847</v>
       </c>
       <c r="G214" t="n">
         <v>0.9639081244511943</v>
@@ -6762,10 +6762,10 @@
         <v>2</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0008871143034079776</v>
+        <v>0.0008871143034081794</v>
       </c>
       <c r="F215" t="n">
-        <v>0.02321319205561371</v>
+        <v>0.02321319205562427</v>
       </c>
       <c r="G215" t="n">
         <v>0.9758996936409808</v>
@@ -6788,7 +6788,7 @@
         <v>0.001332769982226236</v>
       </c>
       <c r="F216" t="n">
-        <v>0.01843475265027481</v>
+        <v>0.018434752650279</v>
       </c>
       <c r="G216" t="n">
         <v>0.980232477367453</v>
@@ -6808,10 +6808,10 @@
         <v>2</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0002472694389474593</v>
+        <v>0.0002472694389474031</v>
       </c>
       <c r="F217" t="n">
-        <v>0.01220846082528365</v>
+        <v>0.01220846082528087</v>
       </c>
       <c r="G217" t="n">
         <v>0.9875442697357066</v>
@@ -6831,7 +6831,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>7.707255530493678e-05</v>
+        <v>7.707255530491926e-05</v>
       </c>
       <c r="F218" t="n">
         <v>0.009588794102978684</v>
@@ -6854,10 +6854,10 @@
         <v>2</v>
       </c>
       <c r="E219" t="n">
-        <v>5.238670807437976e-05</v>
+        <v>5.238670807434403e-05</v>
       </c>
       <c r="F219" t="n">
-        <v>0.008898002494868121</v>
+        <v>0.008898002494864074</v>
       </c>
       <c r="G219" t="n">
         <v>0.9910496107970233</v>
@@ -6877,10 +6877,10 @@
         <v>2</v>
       </c>
       <c r="E220" t="n">
-        <v>4.203687509251928e-05</v>
+        <v>4.203687509249061e-05</v>
       </c>
       <c r="F220" t="n">
-        <v>0.00865656178261991</v>
+        <v>0.008656561782615974</v>
       </c>
       <c r="G220" t="n">
         <v>0.9913014013423659</v>
@@ -6900,10 +6900,10 @@
         <v>2</v>
       </c>
       <c r="E221" t="n">
-        <v>4.081513085891682e-05</v>
+        <v>4.08151308588797e-05</v>
       </c>
       <c r="F221" t="n">
-        <v>0.008728478899048603</v>
+        <v>0.008728478899044633</v>
       </c>
       <c r="G221" t="n">
         <v>0.9912307059701269</v>
@@ -6923,10 +6923,10 @@
         <v>2</v>
       </c>
       <c r="E222" t="n">
-        <v>3.787384358760065e-05</v>
+        <v>3.787384358756621e-05</v>
       </c>
       <c r="F222" t="n">
-        <v>0.008183216022271537</v>
+        <v>0.008183216022267816</v>
       </c>
       <c r="G222" t="n">
         <v>0.9917789101341293</v>
@@ -6946,10 +6946,10 @@
         <v>2</v>
       </c>
       <c r="E223" t="n">
-        <v>3.409836052335121e-05</v>
+        <v>3.40983605233202e-05</v>
       </c>
       <c r="F223" t="n">
-        <v>0.007832954779472068</v>
+        <v>0.007832954779470288</v>
       </c>
       <c r="G223" t="n">
         <v>0.9921329468601141</v>
@@ -6969,10 +6969,10 @@
         <v>2</v>
       </c>
       <c r="E224" t="n">
-        <v>2.734358829227651e-05</v>
+        <v>2.734358829223299e-05</v>
       </c>
       <c r="F224" t="n">
-        <v>0.009540869729980731</v>
+        <v>0.009540869729978561</v>
       </c>
       <c r="G224" t="n">
         <v>0.9904317866816856</v>
@@ -6992,10 +6992,10 @@
         <v>2</v>
       </c>
       <c r="E225" t="n">
-        <v>3.980953241744106e-05</v>
+        <v>3.980953241738675e-05</v>
       </c>
       <c r="F225" t="n">
-        <v>0.01308613590301522</v>
+        <v>0.01308613590300927</v>
       </c>
       <c r="G225" t="n">
         <v>0.9868740545645994</v>
@@ -7015,7 +7015,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="n">
-        <v>4.391844642749504e-05</v>
+        <v>4.391844642743513e-05</v>
       </c>
       <c r="F226" t="n">
         <v>0.01422077884690376</v>
@@ -7038,7 +7038,7 @@
         <v>2</v>
       </c>
       <c r="E227" t="n">
-        <v>2.750899967955016e-05</v>
+        <v>2.750899967951263e-05</v>
       </c>
       <c r="F227" t="n">
         <v>0.02089310205858009</v>
@@ -7061,10 +7061,10 @@
         <v>2</v>
       </c>
       <c r="E228" t="n">
-        <v>2.864999987172485e-05</v>
+        <v>2.864999987169228e-05</v>
       </c>
       <c r="F228" t="n">
-        <v>0.03510131217602287</v>
+        <v>0.03510131217603085</v>
       </c>
       <c r="G228" t="n">
         <v>0.9648700378239939</v>
@@ -7078,16 +7078,16 @@
         <v>0.01015736928597801</v>
       </c>
       <c r="C229" t="n">
-        <v>0.001216387825317767</v>
+        <v>0.001216387825317766</v>
       </c>
       <c r="D229" t="n">
         <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>5.503147900217211e-05</v>
+        <v>5.503147900209704e-05</v>
       </c>
       <c r="F229" t="n">
-        <v>0.06150821899874163</v>
+        <v>0.06150821899875562</v>
       </c>
       <c r="G229" t="n">
         <v>0.9384367495222158</v>
@@ -7107,10 +7107,10 @@
         <v>2</v>
       </c>
       <c r="E230" t="n">
-        <v>0.0002472523469965845</v>
+        <v>0.0002472523469963596</v>
       </c>
       <c r="F230" t="n">
-        <v>0.1113449189973794</v>
+        <v>0.11134491899743</v>
       </c>
       <c r="G230" t="n">
         <v>0.8884078286556102</v>
@@ -7130,13 +7130,13 @@
         <v>2</v>
       </c>
       <c r="E231" t="n">
-        <v>0.0006906280676823306</v>
+        <v>0.0006906280676817026</v>
       </c>
       <c r="F231" t="n">
-        <v>0.1313995924039206</v>
+        <v>0.1313995924039505</v>
       </c>
       <c r="G231" t="n">
-        <v>0.8679097795284533</v>
+        <v>0.8679097795282559</v>
       </c>
     </row>
     <row r="232">
@@ -7153,10 +7153,10 @@
         <v>2</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0007428296767442931</v>
+        <v>0.0007428296767436175</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1435437539700763</v>
+        <v>0.1435437539701089</v>
       </c>
       <c r="G232" t="n">
         <v>0.8557134163531566</v>
@@ -7176,10 +7176,10 @@
         <v>2</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0004170403687893286</v>
+        <v>0.0004170403687886648</v>
       </c>
       <c r="F233" t="n">
-        <v>0.1205816185633972</v>
+        <v>0.1205816185634246</v>
       </c>
       <c r="G233" t="n">
         <v>0.8790013410677965</v>
@@ -7199,10 +7199,10 @@
         <v>2</v>
       </c>
       <c r="E234" t="n">
-        <v>0.0001678377553411413</v>
+        <v>0.0001678377553409505</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1258571794659203</v>
+        <v>0.1258571794659775</v>
       </c>
       <c r="G234" t="n">
         <v>0.8739749827787882</v>
@@ -7213,16 +7213,16 @@
         <v>43281</v>
       </c>
       <c r="B235" t="n">
-        <v>0.004736567679959356</v>
+        <v>0.004736567679959355</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.0008148956246944808</v>
+        <v>-0.000814895624694481</v>
       </c>
       <c r="D235" t="n">
         <v>2</v>
       </c>
       <c r="E235" t="n">
-        <v>8.784025991750995e-05</v>
+        <v>8.784025991745003e-05</v>
       </c>
       <c r="F235" t="n">
         <v>0.1494965534412009</v>
@@ -7251,7 +7251,7 @@
         <v>0.2015642969050456</v>
       </c>
       <c r="G236" t="n">
-        <v>0.7983736460341265</v>
+        <v>0.798373646033945</v>
       </c>
     </row>
     <row r="237">
@@ -7268,7 +7268,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="n">
-        <v>5.7922964342458e-05</v>
+        <v>5.792296434257654e-05</v>
       </c>
       <c r="F237" t="n">
         <v>0.2908851375500926</v>
@@ -7291,10 +7291,10 @@
         <v>2</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0001246750084486823</v>
+        <v>0.0001246750084490508</v>
       </c>
       <c r="F238" t="n">
-        <v>0.4614889428645876</v>
+        <v>0.4614889428644827</v>
       </c>
       <c r="G238" t="n">
         <v>0.5383863821269854</v>
@@ -7314,13 +7314,13 @@
         <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>0.0004036783708659263</v>
+        <v>0.0004036783708668442</v>
       </c>
       <c r="F239" t="n">
         <v>0.909923799172596</v>
       </c>
       <c r="G239" t="n">
-        <v>0.08967252245658199</v>
+        <v>0.08967252245662276</v>
       </c>
     </row>
     <row r="240">
@@ -7337,13 +7337,13 @@
         <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>0.0004191668030957002</v>
+        <v>0.0004191668030960814</v>
       </c>
       <c r="F240" t="n">
         <v>0.9386393992066812</v>
       </c>
       <c r="G240" t="n">
-        <v>0.06094143399016868</v>
+        <v>0.06094143399018254</v>
       </c>
     </row>
     <row r="241">
@@ -7360,13 +7360,13 @@
         <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>0.001092697235822834</v>
+        <v>0.001092697235822337</v>
       </c>
       <c r="F241" t="n">
         <v>0.9988361161089919</v>
       </c>
       <c r="G241" t="n">
-        <v>7.118665517934905e-05</v>
+        <v>7.118665517928431e-05</v>
       </c>
     </row>
     <row r="242">
@@ -7383,13 +7383,13 @@
         <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0.001097606103501334</v>
+        <v>0.001097606103500835</v>
       </c>
       <c r="F242" t="n">
         <v>0.9856634504533214</v>
       </c>
       <c r="G242" t="n">
-        <v>0.01323894344324248</v>
+        <v>0.01323894344321839</v>
       </c>
     </row>
     <row r="243">
@@ -7406,13 +7406,13 @@
         <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>0.00041092357408027</v>
+        <v>0.0004109235740805503</v>
       </c>
       <c r="F243" t="n">
         <v>0.9659350538472473</v>
       </c>
       <c r="G243" t="n">
-        <v>0.03365402257864154</v>
+        <v>0.03365402257860328</v>
       </c>
     </row>
     <row r="244">
@@ -7429,13 +7429,13 @@
         <v>1</v>
       </c>
       <c r="E244" t="n">
-        <v>0.0004228276672192706</v>
+        <v>0.000422827667219559</v>
       </c>
       <c r="F244" t="n">
         <v>0.9633848894525074</v>
       </c>
       <c r="G244" t="n">
-        <v>0.03619228288022594</v>
+        <v>0.03619228288016834</v>
       </c>
     </row>
     <row r="245">
@@ -7452,13 +7452,13 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0006424184502399028</v>
+        <v>0.0006424184502394647</v>
       </c>
       <c r="F245" t="n">
         <v>0.9728044107819749</v>
       </c>
       <c r="G245" t="n">
-        <v>0.02655317076778654</v>
+        <v>0.02655317076773824</v>
       </c>
     </row>
     <row r="246">
@@ -7475,13 +7475,13 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.001871281048455205</v>
+        <v>0.001871281048453078</v>
       </c>
       <c r="F246" t="n">
         <v>0.9962271830800169</v>
       </c>
       <c r="G246" t="n">
-        <v>0.001901535871454088</v>
+        <v>0.001901535871450196</v>
       </c>
     </row>
     <row r="247">
@@ -7498,13 +7498,13 @@
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0.002164663909890382</v>
+        <v>0.002164663909887921</v>
       </c>
       <c r="F247" t="n">
         <v>0.9596142742259502</v>
       </c>
       <c r="G247" t="n">
-        <v>0.03822106186425724</v>
+        <v>0.0382210618641964</v>
       </c>
     </row>
     <row r="248">
@@ -7521,13 +7521,13 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>0.001783641927588562</v>
+        <v>0.001783641927586129</v>
       </c>
       <c r="F248" t="n">
         <v>0.9286425461787747</v>
       </c>
       <c r="G248" t="n">
-        <v>0.06957381189368364</v>
+        <v>0.06957381189355709</v>
       </c>
     </row>
     <row r="249">
@@ -7544,13 +7544,13 @@
         <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>0.004071230600815687</v>
+        <v>0.004071230600809207</v>
       </c>
       <c r="F249" t="n">
         <v>0.9217917209359945</v>
       </c>
       <c r="G249" t="n">
-        <v>0.07413704846329482</v>
+        <v>0.07413704846317683</v>
       </c>
     </row>
     <row r="250">
@@ -7567,13 +7567,13 @@
         <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>0.001229832896833751</v>
+        <v>0.001229832896832632</v>
       </c>
       <c r="F250" t="n">
-        <v>0.8509897161682818</v>
+        <v>0.8509897161684753</v>
       </c>
       <c r="G250" t="n">
-        <v>0.1477804509348598</v>
+        <v>0.1477804509346246</v>
       </c>
     </row>
     <row r="251">
@@ -7590,13 +7590,13 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>0.0004033064458458953</v>
+        <v>0.000403306445845987</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8305015631205604</v>
+        <v>0.8305015631207493</v>
       </c>
       <c r="G251" t="n">
-        <v>0.169095130433629</v>
+        <v>0.1690951304333599</v>
       </c>
     </row>
     <row r="252">
@@ -7607,19 +7607,19 @@
         <v>0.03445648173694641</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.007765814965729999</v>
+        <v>-0.00776581496573</v>
       </c>
       <c r="D252" t="n">
         <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0002864469476510304</v>
+        <v>0.0002864469476512258</v>
       </c>
       <c r="F252" t="n">
-        <v>0.838989649443575</v>
+        <v>0.8389896494437658</v>
       </c>
       <c r="G252" t="n">
-        <v>0.1607239036088817</v>
+        <v>0.1607239036086259</v>
       </c>
     </row>
     <row r="253">
@@ -7636,13 +7636,13 @@
         <v>1</v>
       </c>
       <c r="E253" t="n">
-        <v>0.0004756581943414858</v>
+        <v>0.0004756581943418102</v>
       </c>
       <c r="F253" t="n">
-        <v>0.871917121930429</v>
+        <v>0.8719171219306273</v>
       </c>
       <c r="G253" t="n">
-        <v>0.127607219875161</v>
+        <v>0.1276072198750159</v>
       </c>
     </row>
     <row r="254">
@@ -7659,13 +7659,13 @@
         <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0.001441674392312414</v>
+        <v>0.001441674392312742</v>
       </c>
       <c r="F254" t="n">
         <v>0.9475691629407781</v>
       </c>
       <c r="G254" t="n">
-        <v>0.05098916266697616</v>
+        <v>0.05098916266691819</v>
       </c>
     </row>
     <row r="255">
@@ -7682,13 +7682,13 @@
         <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>0.003439686924704616</v>
+        <v>0.003439686924703052</v>
       </c>
       <c r="F255" t="n">
         <v>0.9965422724360217</v>
       </c>
       <c r="G255" t="n">
-        <v>1.804063934780812e-05</v>
+        <v>1.804063934778762e-05</v>
       </c>
     </row>
     <row r="256">
@@ -7705,13 +7705,13 @@
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.007346977676317563</v>
+        <v>0.007346977676310881</v>
       </c>
       <c r="F256" t="n">
-        <v>0.9926530215744765</v>
+        <v>0.9926530215747023</v>
       </c>
       <c r="G256" t="n">
-        <v>7.49095437991012e-10</v>
+        <v>7.490954379893087e-10</v>
       </c>
     </row>
     <row r="257">
@@ -7728,13 +7728,13 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.01039386171220938</v>
+        <v>0.0103938617121952</v>
       </c>
       <c r="F257" t="n">
         <v>0.9884907396592765</v>
       </c>
       <c r="G257" t="n">
-        <v>0.001115398628584084</v>
+        <v>0.001115398628581548</v>
       </c>
     </row>
     <row r="258">
@@ -7751,13 +7751,13 @@
         <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0.002604813020335797</v>
+        <v>0.002604813020332835</v>
       </c>
       <c r="F258" t="n">
         <v>0.9501033953625054</v>
       </c>
       <c r="G258" t="n">
-        <v>0.04729179161714917</v>
+        <v>0.04729179161706315</v>
       </c>
     </row>
     <row r="259">
@@ -7774,13 +7774,13 @@
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0009099390955879679</v>
+        <v>0.0009099390955873472</v>
       </c>
       <c r="F259" t="n">
-        <v>0.9284003786156749</v>
+        <v>0.9284003786158861</v>
       </c>
       <c r="G259" t="n">
-        <v>0.07068968228873043</v>
+        <v>0.07068968228860185</v>
       </c>
     </row>
     <row r="260">
@@ -7797,13 +7797,13 @@
         <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0.001215211977256401</v>
+        <v>0.001215211977255849</v>
       </c>
       <c r="F260" t="n">
-        <v>0.9290414803669533</v>
+        <v>0.9290414803671645</v>
       </c>
       <c r="G260" t="n">
-        <v>0.06974330765573598</v>
+        <v>0.06974330765562498</v>
       </c>
     </row>
     <row r="261">
@@ -7820,13 +7820,13 @@
         <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>0.002493556201554665</v>
+        <v>0.002493556201551263</v>
       </c>
       <c r="F261" t="n">
-        <v>0.9398607858816236</v>
+        <v>0.9398607858818373</v>
       </c>
       <c r="G261" t="n">
-        <v>0.0576456579168243</v>
+        <v>0.05764565791671944</v>
       </c>
     </row>
     <row r="262">
@@ -7843,13 +7843,13 @@
         <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>0.006047136563028366</v>
+        <v>0.006047136563024241</v>
       </c>
       <c r="F262" t="n">
-        <v>0.9310399633090205</v>
+        <v>0.9310399633092322</v>
       </c>
       <c r="G262" t="n">
-        <v>0.06291290012792841</v>
+        <v>0.06291290012784259</v>
       </c>
     </row>
     <row r="263">
@@ -7866,13 +7866,13 @@
         <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>0.01328719848855481</v>
+        <v>0.01328719848854273</v>
       </c>
       <c r="F263" t="n">
-        <v>0.892718008346971</v>
+        <v>0.892718008347174</v>
       </c>
       <c r="G263" t="n">
-        <v>0.09399479316452022</v>
+        <v>0.09399479316437062</v>
       </c>
     </row>
     <row r="264">
@@ -7889,13 +7889,13 @@
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.02294388550430939</v>
+        <v>0.02294388550428853</v>
       </c>
       <c r="F264" t="n">
-        <v>0.8717400066770292</v>
+        <v>0.8717400066772275</v>
       </c>
       <c r="G264" t="n">
-        <v>0.1053161078185774</v>
+        <v>0.1053161078184338</v>
       </c>
     </row>
     <row r="265">
@@ -7912,13 +7912,13 @@
         <v>1</v>
       </c>
       <c r="E265" t="n">
-        <v>0.007034671760659535</v>
+        <v>0.007034671760653137</v>
       </c>
       <c r="F265" t="n">
-        <v>0.6104465205465441</v>
+        <v>0.6104465205469605</v>
       </c>
       <c r="G265" t="n">
-        <v>0.3825188076927514</v>
+        <v>0.3825188076924035</v>
       </c>
     </row>
     <row r="266">
@@ -7935,13 +7935,13 @@
         <v>1</v>
       </c>
       <c r="E266" t="n">
-        <v>0.004129526923191339</v>
+        <v>0.004129526923187583</v>
       </c>
       <c r="F266" t="n">
-        <v>0.4505556163488937</v>
+        <v>0.450555616349201</v>
       </c>
       <c r="G266" t="n">
-        <v>0.5453148567278774</v>
+        <v>0.5453148567276294</v>
       </c>
     </row>
     <row r="267">
@@ -7958,13 +7958,13 @@
         <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.003042648610529792</v>
+        <v>0.003042648610526333</v>
       </c>
       <c r="F267" t="n">
-        <v>0.3787928910228334</v>
+        <v>0.3787928910231779</v>
       </c>
       <c r="G267" t="n">
-        <v>0.6181644603666744</v>
+        <v>0.6181644603662527</v>
       </c>
     </row>
     <row r="268">
@@ -7981,13 +7981,13 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0.002379959010380437</v>
+        <v>0.002379959010378814</v>
       </c>
       <c r="F268" t="n">
-        <v>0.3511730579537627</v>
+        <v>0.351173057954162</v>
       </c>
       <c r="G268" t="n">
-        <v>0.6464469830357435</v>
+        <v>0.6464469830354496</v>
       </c>
     </row>
     <row r="269">
@@ -8004,13 +8004,13 @@
         <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0.001154966202305426</v>
+        <v>0.001154966202304901</v>
       </c>
       <c r="F269" t="n">
-        <v>0.3245352473925984</v>
+        <v>0.3245352473929674</v>
       </c>
       <c r="G269" t="n">
-        <v>0.6743097864050883</v>
+        <v>0.6743097864047817</v>
       </c>
     </row>
     <row r="270">
@@ -8027,13 +8027,13 @@
         <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>0.0004756925322992539</v>
+        <v>0.0004756925322993621</v>
       </c>
       <c r="F270" t="n">
-        <v>0.3146179072710996</v>
+        <v>0.3146179072714573</v>
       </c>
       <c r="G270" t="n">
-        <v>0.6849064001964974</v>
+        <v>0.6849064001961859</v>
       </c>
     </row>
     <row r="271">
@@ -8050,13 +8050,13 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0004010972341791999</v>
+        <v>0.0004010972341792911</v>
       </c>
       <c r="F271" t="n">
-        <v>0.3255151668208824</v>
+        <v>0.3255151668211784</v>
       </c>
       <c r="G271" t="n">
-        <v>0.6740837359448485</v>
+        <v>0.674083735944542</v>
       </c>
     </row>
     <row r="272">
@@ -8073,13 +8073,13 @@
         <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0008541785591023239</v>
+        <v>0.0008541785591027124</v>
       </c>
       <c r="F272" t="n">
-        <v>0.3674056211563482</v>
+        <v>0.3674056211566823</v>
       </c>
       <c r="G272" t="n">
-        <v>0.6317402002845154</v>
+        <v>0.6317402002842282</v>
       </c>
     </row>
     <row r="273">
@@ -8096,13 +8096,13 @@
         <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>0.00222705074019128</v>
+        <v>0.002227050740191786</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4498591625132057</v>
+        <v>0.4498591625136149</v>
       </c>
       <c r="G273" t="n">
-        <v>0.5479137867466494</v>
+        <v>0.5479137867462756</v>
       </c>
     </row>
     <row r="274">
@@ -8122,10 +8122,10 @@
         <v>0.008701928838461225</v>
       </c>
       <c r="F274" t="n">
-        <v>0.6036076671134316</v>
+        <v>0.6036076671135688</v>
       </c>
       <c r="G274" t="n">
-        <v>0.387690404048219</v>
+        <v>0.3876904040478664</v>
       </c>
     </row>
     <row r="275">
@@ -8145,10 +8145,10 @@
         <v>0.01460703595154151</v>
       </c>
       <c r="F275" t="n">
-        <v>0.7380009373050027</v>
+        <v>0.7380009373051706</v>
       </c>
       <c r="G275" t="n">
-        <v>0.2473920267435272</v>
+        <v>0.2473920267433022</v>
       </c>
     </row>
     <row r="276">
@@ -8165,13 +8165,13 @@
         <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>0.03675107255197354</v>
+        <v>0.03675107255196518</v>
       </c>
       <c r="F276" t="n">
-        <v>0.7840165358065436</v>
+        <v>0.7840165358067219</v>
       </c>
       <c r="G276" t="n">
-        <v>0.1792323916415497</v>
+        <v>0.1792323916413459</v>
       </c>
     </row>
     <row r="277">
@@ -8188,13 +8188,13 @@
         <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>0.1250711332647289</v>
+        <v>0.125071133264672</v>
       </c>
       <c r="F277" t="n">
         <v>0.7583892816390788</v>
       </c>
       <c r="G277" t="n">
-        <v>0.1165395850962761</v>
+        <v>0.1165395850961436</v>
       </c>
     </row>
     <row r="278">
@@ -8217,7 +8217,7 @@
         <v>0.4719725554612338</v>
       </c>
       <c r="G278" t="n">
-        <v>0.06625140430793254</v>
+        <v>0.0662514043078723</v>
       </c>
     </row>
     <row r="279">
@@ -8234,13 +8234,13 @@
         <v>0</v>
       </c>
       <c r="E279" t="n">
-        <v>0.5687384948116644</v>
+        <v>0.5687384948117937</v>
       </c>
       <c r="F279" t="n">
-        <v>0.416351413859709</v>
+        <v>0.4163514138596144</v>
       </c>
       <c r="G279" t="n">
-        <v>0.01491009132860877</v>
+        <v>0.01491009132860199</v>
       </c>
     </row>
     <row r="280">
@@ -8257,13 +8257,13 @@
         <v>0</v>
       </c>
       <c r="E280" t="n">
-        <v>0.8472161609631831</v>
+        <v>0.8472161609633757</v>
       </c>
       <c r="F280" t="n">
-        <v>0.1518249440785871</v>
+        <v>0.1518249440785525</v>
       </c>
       <c r="G280" t="n">
-        <v>0.0009588949581194764</v>
+        <v>0.0009588949581186044</v>
       </c>
     </row>
     <row r="281">
@@ -8283,10 +8283,10 @@
         <v>0.9954575976562137</v>
       </c>
       <c r="F281" t="n">
-        <v>0.003965587939661344</v>
+        <v>0.003965587939660443</v>
       </c>
       <c r="G281" t="n">
-        <v>0.0005768144040975274</v>
+        <v>0.0005768144040967405</v>
       </c>
     </row>
     <row r="282">
@@ -8306,10 +8306,10 @@
         <v>0.9954087896287294</v>
       </c>
       <c r="F282" t="n">
-        <v>0.004143136498226696</v>
+        <v>0.004143136498231405</v>
       </c>
       <c r="G282" t="n">
-        <v>0.000448073873045929</v>
+        <v>0.0004480738730452158</v>
       </c>
     </row>
     <row r="283">
@@ -8329,10 +8329,10 @@
         <v>0.9982336369896193</v>
       </c>
       <c r="F283" t="n">
-        <v>0.001761266293517014</v>
+        <v>0.001761266293517815</v>
       </c>
       <c r="G283" t="n">
-        <v>5.096716900567067e-06</v>
+        <v>5.096716900561273e-06</v>
       </c>
     </row>
     <row r="284">
@@ -8352,10 +8352,10 @@
         <v>0.9995648922684061</v>
       </c>
       <c r="F284" t="n">
-        <v>0.0004278051246934862</v>
+        <v>0.0004278051246940699</v>
       </c>
       <c r="G284" t="n">
-        <v>7.302606960059723e-06</v>
+        <v>7.302606960058063e-06</v>
       </c>
     </row>
     <row r="285">
@@ -8375,10 +8375,10 @@
         <v>0.9999543545677207</v>
       </c>
       <c r="F285" t="n">
-        <v>2.512862261048176e-05</v>
+        <v>2.512862261056175e-05</v>
       </c>
       <c r="G285" t="n">
-        <v>2.051680970062781e-05</v>
+        <v>2.051680970063248e-05</v>
       </c>
     </row>
     <row r="286">
@@ -8398,10 +8398,10 @@
         <v>0.9999279781775831</v>
       </c>
       <c r="F286" t="n">
-        <v>2.124983290138336e-06</v>
+        <v>2.12498329015573e-06</v>
       </c>
       <c r="G286" t="n">
-        <v>6.98968390921646e-05</v>
+        <v>6.989683909218049e-05</v>
       </c>
     </row>
     <row r="287">
@@ -8421,10 +8421,10 @@
         <v>0.9579961074166568</v>
       </c>
       <c r="F287" t="n">
-        <v>0.00157454593747374</v>
+        <v>0.001574545937496653</v>
       </c>
       <c r="G287" t="n">
-        <v>0.04042934664581402</v>
+        <v>0.04042934664580483</v>
       </c>
     </row>
     <row r="288">
@@ -8444,10 +8444,10 @@
         <v>0.8794665562436333</v>
       </c>
       <c r="F288" t="n">
-        <v>0.001698570422820326</v>
+        <v>0.001698570422840409</v>
       </c>
       <c r="G288" t="n">
-        <v>0.1188348733335853</v>
+        <v>0.1188348733336124</v>
       </c>
     </row>
     <row r="289">
@@ -8467,10 +8467,10 @@
         <v>0.8256807819556757</v>
       </c>
       <c r="F289" t="n">
-        <v>0.003205016271516216</v>
+        <v>0.00320501627153662</v>
       </c>
       <c r="G289" t="n">
-        <v>0.1711142017728526</v>
+        <v>0.1711142017728915</v>
       </c>
     </row>
     <row r="290">
@@ -8490,7 +8490,7 @@
         <v>0.5318788831177715</v>
       </c>
       <c r="F290" t="n">
-        <v>0.001975856413400836</v>
+        <v>0.001975856413413416</v>
       </c>
       <c r="G290" t="n">
         <v>0.466145260468784</v>
@@ -8513,7 +8513,7 @@
         <v>0.3498413493748427</v>
       </c>
       <c r="F291" t="n">
-        <v>0.00120118826074061</v>
+        <v>0.001201188260745799</v>
       </c>
       <c r="G291" t="n">
         <v>0.6489574623643102</v>
@@ -8536,7 +8536,7 @@
         <v>0.1397248803046435</v>
       </c>
       <c r="F292" t="n">
-        <v>0.003396155742275032</v>
+        <v>0.003396155742282754</v>
       </c>
       <c r="G292" t="n">
         <v>0.856878963953104</v>
@@ -8556,10 +8556,10 @@
         <v>2</v>
       </c>
       <c r="E293" t="n">
-        <v>0.02707801893488894</v>
+        <v>0.0270780189348951</v>
       </c>
       <c r="F293" t="n">
-        <v>0.006144187209569081</v>
+        <v>0.00614418720957467</v>
       </c>
       <c r="G293" t="n">
         <v>0.9667777938555213</v>
@@ -8585,7 +8585,7 @@
         <v>0.009266434133047207</v>
       </c>
       <c r="G294" t="n">
-        <v>0.9804649306886741</v>
+        <v>0.980464930688674</v>
       </c>
     </row>
     <row r="295">
@@ -8602,10 +8602,10 @@
         <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>0.006903686073517877</v>
+        <v>0.006903686073516307</v>
       </c>
       <c r="F295" t="n">
-        <v>0.01977439630206041</v>
+        <v>0.01977439630204692</v>
       </c>
       <c r="G295" t="n">
         <v>0.9733219176244187</v>
@@ -8625,10 +8625,10 @@
         <v>2</v>
       </c>
       <c r="E296" t="n">
-        <v>0.005054477876488879</v>
+        <v>0.005054477876485431</v>
       </c>
       <c r="F296" t="n">
-        <v>0.01552548237926302</v>
+        <v>0.01552548237925243</v>
       </c>
       <c r="G296" t="n">
         <v>0.9794200397443328</v>
@@ -8648,10 +8648,10 @@
         <v>2</v>
       </c>
       <c r="E297" t="n">
-        <v>0.006848023690152847</v>
+        <v>0.006848023690149732</v>
       </c>
       <c r="F297" t="n">
-        <v>0.01217310181892242</v>
+        <v>0.01217310181891135</v>
       </c>
       <c r="G297" t="n">
         <v>0.9809788744909909</v>
@@ -8671,10 +8671,10 @@
         <v>2</v>
       </c>
       <c r="E298" t="n">
-        <v>0.01216172687537701</v>
+        <v>0.01216172687536318</v>
       </c>
       <c r="F298" t="n">
-        <v>0.003959178216306221</v>
+        <v>0.00395917821630082</v>
       </c>
       <c r="G298" t="n">
         <v>0.9838790949082266</v>
@@ -8694,10 +8694,10 @@
         <v>2</v>
       </c>
       <c r="E299" t="n">
-        <v>0.01075408067574636</v>
+        <v>0.01075408067572924</v>
       </c>
       <c r="F299" t="n">
-        <v>0.003452303636842808</v>
+        <v>0.003452303636838099</v>
       </c>
       <c r="G299" t="n">
         <v>0.9857936156874455</v>
@@ -8717,13 +8717,13 @@
         <v>2</v>
       </c>
       <c r="E300" t="n">
-        <v>0.010253290570842</v>
+        <v>0.01025329057083034</v>
       </c>
       <c r="F300" t="n">
-        <v>0.003722734180198686</v>
+        <v>0.003722734180195301</v>
       </c>
       <c r="G300" t="n">
-        <v>0.9860239752488562</v>
+        <v>0.9860239752490805</v>
       </c>
     </row>
     <row r="301">
@@ -8740,10 +8740,10 @@
         <v>2</v>
       </c>
       <c r="E301" t="n">
-        <v>0.004929404182906932</v>
+        <v>0.004929404182900206</v>
       </c>
       <c r="F301" t="n">
-        <v>0.004698803674444531</v>
+        <v>0.004698803674439189</v>
       </c>
       <c r="G301" t="n">
         <v>0.990371792142645</v>
@@ -8757,16 +8757,16 @@
         <v>0.01197547558860675</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.006295415534405311</v>
+        <v>-0.00629541553440531</v>
       </c>
       <c r="D302" t="n">
         <v>2</v>
       </c>
       <c r="E302" t="n">
-        <v>0.001158576873250885</v>
+        <v>0.001158576873249041</v>
       </c>
       <c r="F302" t="n">
-        <v>0.006684974851249998</v>
+        <v>0.006684974851243918</v>
       </c>
       <c r="G302" t="n">
         <v>0.9921564482755154</v>
@@ -8786,10 +8786,10 @@
         <v>2</v>
       </c>
       <c r="E303" t="n">
-        <v>0.0007037271758824167</v>
+        <v>0.0007037271758814567</v>
       </c>
       <c r="F303" t="n">
-        <v>0.01048408747720742</v>
+        <v>0.01048408747719789</v>
       </c>
       <c r="G303" t="n">
         <v>0.9888121853468613</v>
@@ -8809,10 +8809,10 @@
         <v>2</v>
       </c>
       <c r="E304" t="n">
-        <v>0.0004686859163254778</v>
+        <v>0.0004686859163247318</v>
       </c>
       <c r="F304" t="n">
-        <v>0.007205538878785805</v>
+        <v>0.007205538878779252</v>
       </c>
       <c r="G304" t="n">
         <v>0.9923257752049046</v>
@@ -8832,10 +8832,10 @@
         <v>2</v>
       </c>
       <c r="E305" t="n">
-        <v>0.001101309435058083</v>
+        <v>0.00110130943505633</v>
       </c>
       <c r="F305" t="n">
-        <v>0.003849649113017144</v>
+        <v>0.003849649113012768</v>
       </c>
       <c r="G305" t="n">
         <v>0.995049041451919</v>
@@ -8855,10 +8855,10 @@
         <v>2</v>
       </c>
       <c r="E306" t="n">
-        <v>0.0002610436727026643</v>
+        <v>0.0002610436727022488</v>
       </c>
       <c r="F306" t="n">
-        <v>0.006079546018378435</v>
+        <v>0.006079546018371523</v>
       </c>
       <c r="G306" t="n">
         <v>0.9936594103088838</v>
@@ -8878,10 +8878,10 @@
         <v>2</v>
       </c>
       <c r="E307" t="n">
-        <v>7.284194946575563e-05</v>
+        <v>7.28419494656397e-05</v>
       </c>
       <c r="F307" t="n">
-        <v>0.008071030513639879</v>
+        <v>0.008071030513632539</v>
       </c>
       <c r="G307" t="n">
         <v>0.9918561275369651</v>
@@ -8901,10 +8901,10 @@
         <v>2</v>
       </c>
       <c r="E308" t="n">
-        <v>7.278627052385362e-05</v>
+        <v>7.278627052375432e-05</v>
       </c>
       <c r="F308" t="n">
-        <v>0.01100948012438792</v>
+        <v>0.0110094801243754</v>
       </c>
       <c r="G308" t="n">
         <v>0.9889177336050435</v>
@@ -8924,10 +8924,10 @@
         <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>5.430666658370652e-05</v>
+        <v>5.430666658363243e-05</v>
       </c>
       <c r="F309" t="n">
-        <v>0.01037711368200761</v>
+        <v>0.01037711368200053</v>
       </c>
       <c r="G309" t="n">
         <v>0.9895685796514629</v>
@@ -8947,10 +8947,10 @@
         <v>2</v>
       </c>
       <c r="E310" t="n">
-        <v>7.477268361517613e-05</v>
+        <v>7.477268361505712e-05</v>
       </c>
       <c r="F310" t="n">
-        <v>0.01098728827516935</v>
+        <v>0.01098728827515936</v>
       </c>
       <c r="G310" t="n">
         <v>0.9889379390412395</v>
@@ -8970,10 +8970,10 @@
         <v>2</v>
       </c>
       <c r="E311" t="n">
-        <v>0.0002394367728147178</v>
+        <v>0.0002394367728143367</v>
       </c>
       <c r="F311" t="n">
-        <v>0.01261409402828906</v>
+        <v>0.01261409402828332</v>
       </c>
       <c r="G311" t="n">
         <v>0.9871464691989918</v>
@@ -8993,10 +8993,10 @@
         <v>2</v>
       </c>
       <c r="E312" t="n">
-        <v>0.0001149424872570336</v>
+        <v>0.0001149424872569291</v>
       </c>
       <c r="F312" t="n">
-        <v>0.03995741546013133</v>
+        <v>0.03995741546014041</v>
       </c>
       <c r="G312" t="n">
         <v>0.9599276420525443</v>
@@ -9016,10 +9016,10 @@
         <v>2</v>
       </c>
       <c r="E313" t="n">
-        <v>0.0002062766802213256</v>
+        <v>0.0002062766802212787</v>
       </c>
       <c r="F313" t="n">
-        <v>0.07105736231883328</v>
+        <v>0.07105736231880097</v>
       </c>
       <c r="G313" t="n">
         <v>0.9287363610009178</v>
@@ -9039,13 +9039,13 @@
         <v>2</v>
       </c>
       <c r="E314" t="n">
-        <v>0.000168109001712286</v>
+        <v>0.0001681090017122095</v>
       </c>
       <c r="F314" t="n">
-        <v>0.1762869156808687</v>
+        <v>0.1762869156807886</v>
       </c>
       <c r="G314" t="n">
-        <v>0.8235449753173667</v>
+        <v>0.823544975317554</v>
       </c>
     </row>
     <row r="315">
@@ -9062,13 +9062,13 @@
         <v>2</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0006766602215451896</v>
+        <v>0.000676660221544728</v>
       </c>
       <c r="F315" t="n">
-        <v>0.3775551150455362</v>
+        <v>0.3775551150453645</v>
       </c>
       <c r="G315" t="n">
-        <v>0.6217682247328614</v>
+        <v>0.6217682247331442</v>
       </c>
     </row>
     <row r="316">
@@ -9079,19 +9079,19 @@
         <v>-0.06138811628823403</v>
       </c>
       <c r="C316" t="n">
-        <v>0.0003471971954322061</v>
+        <v>0.0003471971954322065</v>
       </c>
       <c r="D316" t="n">
         <v>2</v>
       </c>
       <c r="E316" t="n">
-        <v>0.003468598939420698</v>
+        <v>0.003468598939416755</v>
       </c>
       <c r="F316" t="n">
-        <v>0.4417070115273837</v>
+        <v>0.4417070115271828</v>
       </c>
       <c r="G316" t="n">
-        <v>0.5548243895331749</v>
+        <v>0.5548243895334273</v>
       </c>
     </row>
     <row r="317">
@@ -9108,13 +9108,13 @@
         <v>2</v>
       </c>
       <c r="E317" t="n">
-        <v>0.00271880650495592</v>
+        <v>0.002718806504952829</v>
       </c>
       <c r="F317" t="n">
-        <v>0.3683642086410064</v>
+        <v>0.3683642086408389</v>
       </c>
       <c r="G317" t="n">
-        <v>0.6289169848540002</v>
+        <v>0.6289169848541432</v>
       </c>
     </row>
     <row r="318">
@@ -9131,10 +9131,10 @@
         <v>2</v>
       </c>
       <c r="E318" t="n">
-        <v>0.003610326079634336</v>
+        <v>0.00361032607962941</v>
       </c>
       <c r="F318" t="n">
-        <v>0.2968942559045708</v>
+        <v>0.2968942559044358</v>
       </c>
       <c r="G318" t="n">
         <v>0.6994954180158782</v>
@@ -9154,10 +9154,10 @@
         <v>2</v>
       </c>
       <c r="E319" t="n">
-        <v>0.002355659647772252</v>
+        <v>0.002355659647770646</v>
       </c>
       <c r="F319" t="n">
-        <v>0.1732365529425052</v>
+        <v>0.1732365529424264</v>
       </c>
       <c r="G319" t="n">
         <v>0.8244077874097283</v>
@@ -9177,10 +9177,10 @@
         <v>2</v>
       </c>
       <c r="E320" t="n">
-        <v>0.0009754001448558163</v>
+        <v>0.000975400144855151</v>
       </c>
       <c r="F320" t="n">
-        <v>0.1001156589792943</v>
+        <v>0.1001156589792487</v>
       </c>
       <c r="G320" t="n">
         <v>0.8989089408759328</v>
@@ -9200,10 +9200,10 @@
         <v>2</v>
       </c>
       <c r="E321" t="n">
-        <v>0.000510508170855012</v>
+        <v>0.0005105081708546638</v>
       </c>
       <c r="F321" t="n">
-        <v>0.06836052008739656</v>
+        <v>0.06836052008738101</v>
       </c>
       <c r="G321" t="n">
         <v>0.9311289717417022</v>
@@ -9223,7 +9223,7 @@
         <v>2</v>
       </c>
       <c r="E322" t="n">
-        <v>0.0002630084110344767</v>
+        <v>0.0002630084110341777</v>
       </c>
       <c r="F322" t="n">
         <v>0.05054010674653931</v>
@@ -9246,10 +9246,10 @@
         <v>2</v>
       </c>
       <c r="E323" t="n">
-        <v>0.0001486191619279097</v>
+        <v>0.0001486191619278083</v>
       </c>
       <c r="F323" t="n">
-        <v>0.0433015424134592</v>
+        <v>0.04330154241346904</v>
       </c>
       <c r="G323" t="n">
         <v>0.9565498384246721</v>
@@ -9269,10 +9269,10 @@
         <v>2</v>
       </c>
       <c r="E324" t="n">
-        <v>0.0001342372619871105</v>
+        <v>0.000134237261987019</v>
       </c>
       <c r="F324" t="n">
-        <v>0.04502953564700917</v>
+        <v>0.04502953564701941</v>
       </c>
       <c r="G324" t="n">
         <v>0.9548362270910029</v>
@@ -9283,7 +9283,7 @@
         <v>46022</v>
       </c>
       <c r="B325" t="n">
-        <v>-0.002782332919957095</v>
+        <v>-0.002782332919957094</v>
       </c>
       <c r="C325" t="n">
         <v>-0.009222956945157942</v>
@@ -9292,7 +9292,7 @@
         <v>2</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0001773903056241351</v>
+        <v>0.0001773903056239738</v>
       </c>
       <c r="F325" t="n">
         <v>0.04878851821988994</v>
@@ -9315,7 +9315,7 @@
         <v>2</v>
       </c>
       <c r="E326" t="n">
-        <v>0.0003610358152162176</v>
+        <v>0.0003610358152158893</v>
       </c>
       <c r="F326" t="n">
         <v>0.0665193853485828</v>

--- a/hmm_regime_results_monthly.xlsx
+++ b/hmm_regime_results_monthly.xlsx
@@ -491,7 +491,7 @@
         <v>-2.915567756089579</v>
       </c>
       <c r="F2" t="n">
-        <v>7.94878388408506</v>
+        <v>7.948783884085062</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5231463948411231</v>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.94878388408506</v>
+        <v>7.948783884085062</v>
       </c>
       <c r="C10" t="n">
         <v>5.037871764325111</v>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8913880599458304</v>
+        <v>0.8913880599458675</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003881296849025836</v>
+        <v>0.003881296848967605</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1047306432051439</v>
+        <v>0.104730643205165</v>
       </c>
     </row>
     <row r="23">
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01661618766126477</v>
+        <v>0.0166161876612837</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9406735407165159</v>
+        <v>0.940673540716451</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04271027162221921</v>
+        <v>0.04271027162226536</v>
       </c>
     </row>
     <row r="24">
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.485350796600124e-08</v>
+        <v>4.485350796670785e-08</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04973435529074275</v>
+        <v>0.04973435529075192</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9502655998557493</v>
+        <v>0.9502655998557402</v>
       </c>
     </row>
     <row r="27">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8913880599458304</v>
+        <v>0.8913880599458675</v>
       </c>
       <c r="C28" t="n">
-        <v>9.207090854847591</v>
+        <v>9.207090854850735</v>
       </c>
     </row>
     <row r="29">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9406735407165159</v>
+        <v>0.940673540716451</v>
       </c>
       <c r="C29" t="n">
-        <v>16.85588541904421</v>
+        <v>16.85588541902579</v>
       </c>
     </row>
     <row r="30">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9502655998557493</v>
+        <v>0.9502655998557402</v>
       </c>
       <c r="C30" t="n">
-        <v>20.10680730238184</v>
+        <v>20.10680730237816</v>
       </c>
     </row>
     <row r="33">
@@ -1158,7 +1158,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>1445.788715168303</v>
+        <v>1445.788715168305</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -1184,7 +1184,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>1444.535471227111</v>
+        <v>1444.53547122711</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1210,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1444.534569317038</v>
+        <v>1444.534569317037</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1262,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>1442.925003415807</v>
+        <v>1442.925003415813</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -1288,7 +1288,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>1440.262283589453</v>
+        <v>1440.262283589452</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -1314,7 +1314,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>1440.224319393116</v>
+        <v>1440.224319393109</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -1366,7 +1366,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>1439.914657167448</v>
+        <v>1439.914657167446</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -1392,7 +1392,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>1439.068577161563</v>
+        <v>1439.068577161559</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
@@ -1418,7 +1418,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="n">
-        <v>1438.648160393587</v>
+        <v>1438.64816039359</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
@@ -1444,7 +1444,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>1438.481325457343</v>
+        <v>1438.481325457338</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -1470,7 +1470,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>1438.257985253284</v>
+        <v>1438.257985253289</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
@@ -1496,7 +1496,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>1438.257974771671</v>
+        <v>1438.257974771667</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1522,7 +1522,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>1437.950053028632</v>
+        <v>1437.950053028634</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="n">
-        <v>1437.549368362972</v>
+        <v>1437.549368362985</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
@@ -1574,7 +1574,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1437.517860523411</v>
+        <v>1437.51786052341</v>
       </c>
       <c r="C18" t="n">
         <v>3</v>
@@ -1626,7 +1626,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1432.264318100713</v>
+        <v>1432.264318100705</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -1652,7 +1652,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>1432.159907672292</v>
+        <v>1432.159907672288</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>1429.27111550752</v>
+        <v>1429.271115507528</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -1704,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="n">
-        <v>1429.227096908193</v>
+        <v>1429.227096908194</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -1730,7 +1730,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="n">
-        <v>1428.661687114704</v>
+        <v>1428.661687114702</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -1756,7 +1756,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="n">
-        <v>1422.695318049556</v>
+        <v>1422.695318049565</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
@@ -1782,7 +1782,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="n">
-        <v>1420.959985288537</v>
+        <v>1420.959985288543</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
@@ -1857,16 +1857,16 @@
         <v>0.03746962579352606</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008686003136073347</v>
+        <v>0.0008686003136073352</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1.822856416200579e-150</v>
+        <v>1.822856416171981e-150</v>
       </c>
       <c r="F2" t="n">
-        <v>8.797567933629813e-87</v>
+        <v>8.797567933541798e-87</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1886,10 +1886,10 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1.259713813952306e-08</v>
+        <v>1.259713813972069e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003160906853459077</v>
+        <v>0.00316090685345764</v>
       </c>
       <c r="G3" t="n">
         <v>0.9968390805494566</v>
@@ -1909,10 +1909,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3.537756398705721e-06</v>
+        <v>3.537756398709743e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01962311378488497</v>
+        <v>0.01962311378487605</v>
       </c>
       <c r="G4" t="n">
         <v>0.9803733484588154</v>
@@ -1932,10 +1932,10 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.959218544951844e-05</v>
+        <v>1.959218544953181e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04503615748766535</v>
+        <v>0.04503615748764486</v>
       </c>
       <c r="G5" t="n">
         <v>0.9549442503269683</v>
@@ -1955,10 +1955,10 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>7.847441962621107e-05</v>
+        <v>7.84744196262289e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08740437739247146</v>
+        <v>0.08740437739243172</v>
       </c>
       <c r="G6" t="n">
         <v>0.9125171481879744</v>
@@ -1978,13 +1978,13 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>6.161816837180178e-05</v>
+        <v>6.161816837181579e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1897170413200703</v>
+        <v>0.1897170413199841</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8102213405115429</v>
+        <v>0.8102213405117272</v>
       </c>
     </row>
     <row r="8">
@@ -2001,10 +2001,10 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000149834043979628</v>
+        <v>0.0001498340439795939</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2929818593958676</v>
+        <v>0.2929818593957344</v>
       </c>
       <c r="G8" t="n">
         <v>0.7068683065602283</v>
@@ -2027,10 +2027,10 @@
         <v>0.0001186262957228101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3739390329166346</v>
+        <v>0.3739390329165496</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6259423407876629</v>
+        <v>0.6259423407878051</v>
       </c>
     </row>
     <row r="10">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001919811178946188</v>
+        <v>0.0001919811178947498</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5209401592073154</v>
+        <v>0.5209401592071969</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4788678596746764</v>
+        <v>0.4788678596750031</v>
       </c>
     </row>
     <row r="11">
@@ -2070,13 +2070,13 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0002360692610640169</v>
+        <v>0.0002360692610641242</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5772896318436036</v>
+        <v>0.577289631843341</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4224742988953135</v>
+        <v>0.4224742988955056</v>
       </c>
     </row>
     <row r="12">
@@ -2093,13 +2093,13 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0002474442275575945</v>
+        <v>0.000247444227557482</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6221819812203651</v>
+        <v>0.6221819812200822</v>
       </c>
       <c r="G12" t="n">
-        <v>0.377570574552085</v>
+        <v>0.3775705745522567</v>
       </c>
     </row>
     <row r="13">
@@ -2119,10 +2119,10 @@
         <v>0.0006394049830491329</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7364270562112317</v>
+        <v>0.7364270562108969</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2629335388057588</v>
+        <v>0.262933538805998</v>
       </c>
     </row>
     <row r="14">
@@ -2139,13 +2139,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001942487279818264</v>
+        <v>0.001942487279819148</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8222438154347671</v>
+        <v>0.8222438154345801</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1758136972855157</v>
+        <v>0.1758136972856756</v>
       </c>
     </row>
     <row r="15">
@@ -2162,13 +2162,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002295234634897322</v>
+        <v>0.002295234634897844</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8466025836448442</v>
+        <v>0.8466025836446517</v>
       </c>
       <c r="G15" t="n">
-        <v>0.151102181720314</v>
+        <v>0.1511021817204858</v>
       </c>
     </row>
     <row r="16">
@@ -2185,13 +2185,13 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.004557637629760871</v>
+        <v>0.004557637629761906</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8539614955690308</v>
+        <v>0.8539614955688367</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1414808668011264</v>
+        <v>0.1414808668013194</v>
       </c>
     </row>
     <row r="17">
@@ -2208,13 +2208,13 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002725585641748611</v>
+        <v>0.002725585641747992</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8572385664425676</v>
+        <v>0.8572385664423727</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1400358479157309</v>
+        <v>0.1400358479158901</v>
       </c>
     </row>
     <row r="18">
@@ -2231,13 +2231,13 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001130359933035374</v>
+        <v>0.00113035993303486</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8659207492962679</v>
+        <v>0.865920749296071</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1329488907706763</v>
+        <v>0.1329488907707972</v>
       </c>
     </row>
     <row r="19">
@@ -2254,13 +2254,13 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0003496028528428674</v>
+        <v>0.000349602852841993</v>
       </c>
       <c r="F19" t="n">
         <v>0.8741493193380432</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1255010778090021</v>
+        <v>0.1255010778091448</v>
       </c>
     </row>
     <row r="20">
@@ -2271,19 +2271,19 @@
         <v>-0.02054671670874412</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002590752718941236</v>
+        <v>0.002590752718941235</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0002069109463851315</v>
+        <v>0.0002069109463842847</v>
       </c>
       <c r="F20" t="n">
         <v>0.9063597636783753</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09343332537513192</v>
+        <v>0.09343332537525939</v>
       </c>
     </row>
     <row r="21">
@@ -2300,13 +2300,13 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0001880533632518729</v>
+        <v>0.0001880533632507184</v>
       </c>
       <c r="F21" t="n">
         <v>0.9365742602204776</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06323768641627725</v>
+        <v>0.06323768641634914</v>
       </c>
     </row>
     <row r="22">
@@ -2323,13 +2323,13 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0003117600593365154</v>
+        <v>0.0003117600593350977</v>
       </c>
       <c r="F22" t="n">
-        <v>0.985775203219411</v>
+        <v>0.9857752032191869</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01391303672136173</v>
+        <v>0.01391303672137754</v>
       </c>
     </row>
     <row r="23">
@@ -2337,22 +2337,22 @@
         <v>36830</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.00981737301929868</v>
+        <v>-0.009817373019298678</v>
       </c>
       <c r="C23" t="n">
-        <v>0.003564715507369099</v>
+        <v>0.0035647155073691</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0002075823107732683</v>
+        <v>0.0002075823107723243</v>
       </c>
       <c r="F23" t="n">
         <v>0.9892334094044088</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01055900828491158</v>
+        <v>0.01055900828492359</v>
       </c>
     </row>
     <row r="24">
@@ -2369,13 +2369,13 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0004453946856033056</v>
+        <v>0.0004453946856024954</v>
       </c>
       <c r="F24" t="n">
         <v>0.9995014964064887</v>
       </c>
       <c r="G24" t="n">
-        <v>5.310890788480719e-05</v>
+        <v>5.310890788491587e-05</v>
       </c>
     </row>
     <row r="25">
@@ -2392,13 +2392,13 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0002429273396511591</v>
+        <v>0.0002429273396503306</v>
       </c>
       <c r="F25" t="n">
         <v>0.9928105476125912</v>
       </c>
       <c r="G25" t="n">
-        <v>0.006946525047705957</v>
+        <v>0.006946525047718592</v>
       </c>
     </row>
     <row r="26">
@@ -2415,13 +2415,13 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.000206953055915693</v>
+        <v>0.0002069530559144696</v>
       </c>
       <c r="F26" t="n">
         <v>0.9907670660047121</v>
       </c>
       <c r="G26" t="n">
-        <v>0.009025980939353266</v>
+        <v>0.009025980939367632</v>
       </c>
     </row>
     <row r="27">
@@ -2438,13 +2438,13 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0005679546789608441</v>
+        <v>0.0005679546789582613</v>
       </c>
       <c r="F27" t="n">
         <v>0.9994206330535904</v>
       </c>
       <c r="G27" t="n">
-        <v>1.14122675597101e-05</v>
+        <v>1.141226755972827e-05</v>
       </c>
     </row>
     <row r="28">
@@ -2461,13 +2461,13 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0007356825648460839</v>
+        <v>0.0007356825648444112</v>
       </c>
       <c r="F28" t="n">
         <v>0.9990375339585039</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0002267834765820084</v>
+        <v>0.0002267834765824724</v>
       </c>
     </row>
     <row r="29">
@@ -2484,13 +2484,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0006203654303598445</v>
+        <v>0.0006203654303591393</v>
       </c>
       <c r="F29" t="n">
         <v>0.9966970421611322</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002682592408574905</v>
+        <v>0.002682592408580394</v>
       </c>
     </row>
     <row r="30">
@@ -2498,7 +2498,7 @@
         <v>37042</v>
       </c>
       <c r="B30" t="n">
-        <v>0.003486086443238613</v>
+        <v>0.003486086443238612</v>
       </c>
       <c r="C30" t="n">
         <v>-0.001127279284296733</v>
@@ -2507,13 +2507,13 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0001662068938540098</v>
+        <v>0.0001662068938531783</v>
       </c>
       <c r="F30" t="n">
         <v>0.9887183401811207</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01111545292498776</v>
+        <v>0.01111545292500545</v>
       </c>
     </row>
     <row r="31">
@@ -2530,13 +2530,13 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0001433310502068214</v>
+        <v>0.0001433310502059089</v>
       </c>
       <c r="F31" t="n">
         <v>0.9920117498550518</v>
       </c>
       <c r="G31" t="n">
-        <v>0.007844919094678646</v>
+        <v>0.007844919094689347</v>
       </c>
     </row>
     <row r="32">
@@ -2553,13 +2553,13 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0002030807673153785</v>
+        <v>0.0002030807673143626</v>
       </c>
       <c r="F32" t="n">
         <v>0.996334852025199</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003462067207512033</v>
+        <v>0.003462067207516756</v>
       </c>
     </row>
     <row r="33">
@@ -2570,19 +2570,19 @@
         <v>-0.06774638797380172</v>
       </c>
       <c r="C33" t="n">
-        <v>0.009266260116781111</v>
+        <v>0.009266260116781109</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0004204673672980039</v>
+        <v>0.000420467367296761</v>
       </c>
       <c r="F33" t="n">
         <v>0.9994305090413039</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000149023591457612</v>
+        <v>0.0001490235914578153</v>
       </c>
     </row>
     <row r="34">
@@ -2599,13 +2599,13 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0007959096809930987</v>
+        <v>0.0007959096809923748</v>
       </c>
       <c r="F34" t="n">
         <v>0.9991938468181716</v>
       </c>
       <c r="G34" t="n">
-        <v>1.024350084296249e-05</v>
+        <v>1.02435008429788e-05</v>
       </c>
     </row>
     <row r="35">
@@ -2622,13 +2622,13 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0007249065495478223</v>
+        <v>0.000724906549547163</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9908807180472845</v>
+        <v>0.9908807180470592</v>
       </c>
       <c r="G35" t="n">
-        <v>0.008394375403276469</v>
+        <v>0.008394375403287919</v>
       </c>
     </row>
     <row r="36">
@@ -2645,13 +2645,13 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001169424903658517</v>
+        <v>0.001169424903658783</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9908674145381537</v>
+        <v>0.9908674145379285</v>
       </c>
       <c r="G36" t="n">
-        <v>0.007963160558295003</v>
+        <v>0.007963160558307678</v>
       </c>
     </row>
     <row r="37">
@@ -2668,13 +2668,13 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0003864318786538755</v>
+        <v>0.0003864318786529968</v>
       </c>
       <c r="F37" t="n">
         <v>0.9719999899199364</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02761357820146592</v>
+        <v>0.02761357820150987</v>
       </c>
     </row>
     <row r="38">
@@ -2685,19 +2685,19 @@
         <v>-0.01610219756674967</v>
       </c>
       <c r="C38" t="n">
-        <v>0.004747939606516224</v>
+        <v>0.004747939606516225</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001901227167829885</v>
+        <v>0.0001901227167822536</v>
       </c>
       <c r="F38" t="n">
         <v>0.9753257338128171</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02448414347038473</v>
+        <v>0.02448414347042927</v>
       </c>
     </row>
     <row r="39">
@@ -2708,19 +2708,19 @@
         <v>-0.02076850133664727</v>
       </c>
       <c r="C39" t="n">
-        <v>0.009776868601837062</v>
+        <v>0.009776868601837064</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001676923132401498</v>
+        <v>0.0001676923132392347</v>
       </c>
       <c r="F39" t="n">
         <v>0.9820607035237493</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01777160416297026</v>
+        <v>0.01777160416300663</v>
       </c>
     </row>
     <row r="40">
@@ -2737,13 +2737,13 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002160032545405461</v>
+        <v>0.0002160032545386798</v>
       </c>
       <c r="F40" t="n">
         <v>0.9862237227976317</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01356027394780843</v>
+        <v>0.01356027394783309</v>
       </c>
     </row>
     <row r="41">
@@ -2760,13 +2760,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002242131731186003</v>
+        <v>0.0002242131731174277</v>
       </c>
       <c r="F41" t="n">
         <v>0.9995385541367663</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0002372326900967586</v>
+        <v>0.0002372326900971362</v>
       </c>
     </row>
     <row r="42">
@@ -2783,13 +2783,13 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0001181696894546913</v>
+        <v>0.0001181696894536702</v>
       </c>
       <c r="F42" t="n">
         <v>0.997206979157766</v>
       </c>
       <c r="G42" t="n">
-        <v>0.002674851152790413</v>
+        <v>0.00267485115279467</v>
       </c>
     </row>
     <row r="43">
@@ -2806,13 +2806,13 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0002256954099476846</v>
+        <v>0.000225695409946299</v>
       </c>
       <c r="F43" t="n">
         <v>0.9997453833587034</v>
       </c>
       <c r="G43" t="n">
-        <v>2.892123143013185e-05</v>
+        <v>2.892123143017789e-05</v>
       </c>
     </row>
     <row r="44">
@@ -2829,13 +2829,13 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0004007836929007066</v>
+        <v>0.0004007836928993396</v>
       </c>
       <c r="F44" t="n">
         <v>0.9995955381425373</v>
       </c>
       <c r="G44" t="n">
-        <v>3.678164489087729e-06</v>
+        <v>3.67816448909442e-06</v>
       </c>
     </row>
     <row r="45">
@@ -2852,13 +2852,13 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0005075021855669857</v>
+        <v>0.0005075021855656009</v>
       </c>
       <c r="F45" t="n">
         <v>0.9968949392540493</v>
       </c>
       <c r="G45" t="n">
-        <v>0.002597558560477307</v>
+        <v>0.002597558560481441</v>
       </c>
     </row>
     <row r="46">
@@ -2875,13 +2875,13 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001083075889445471</v>
+        <v>0.001083075889444239</v>
       </c>
       <c r="F46" t="n">
         <v>0.998916911550545</v>
       </c>
       <c r="G46" t="n">
-        <v>1.255991436723998e-08</v>
+        <v>1.255991436726283e-08</v>
       </c>
     </row>
     <row r="47">
@@ -2898,13 +2898,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.001595509783149833</v>
+        <v>0.001595509783150559</v>
       </c>
       <c r="F47" t="n">
         <v>0.997880247504392</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0005242427123935184</v>
+        <v>0.0005242427123944719</v>
       </c>
     </row>
     <row r="48">
@@ -2921,13 +2921,13 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.003017741773366974</v>
+        <v>0.003017741773369032</v>
       </c>
       <c r="F48" t="n">
         <v>0.9950110253267763</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001971232899918691</v>
+        <v>0.001971232899922277</v>
       </c>
     </row>
     <row r="49">
@@ -2944,13 +2944,13 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.006826110004238242</v>
+        <v>0.006826110004241347</v>
       </c>
       <c r="F49" t="n">
         <v>0.9922443878970157</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0009295020987910743</v>
+        <v>0.000929502098791497</v>
       </c>
     </row>
     <row r="50">
@@ -2967,13 +2967,13 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.007850477436818395</v>
+        <v>0.007850477436820181</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8952287305638087</v>
+        <v>0.8952287305636051</v>
       </c>
       <c r="G50" t="n">
-        <v>0.09692079199945546</v>
+        <v>0.09692079199947749</v>
       </c>
     </row>
     <row r="51">
@@ -2993,7 +2993,7 @@
         <v>0.009379703439753879</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8136755580100358</v>
+        <v>0.8136755580098508</v>
       </c>
       <c r="G51" t="n">
         <v>0.1769447385503123</v>
@@ -3013,13 +3013,13 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01133135654799671</v>
+        <v>0.01133135654800186</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6311495940889101</v>
+        <v>0.6311495940887666</v>
       </c>
       <c r="G52" t="n">
-        <v>0.3575190493631017</v>
+        <v>0.3575190493632643</v>
       </c>
     </row>
     <row r="53">
@@ -3036,13 +3036,13 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02815157532974489</v>
+        <v>0.02815157532975769</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5362158530198721</v>
+        <v>0.5362158530196282</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4356325716504308</v>
+        <v>0.4356325716506289</v>
       </c>
     </row>
     <row r="54">
@@ -3059,13 +3059,13 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.05633345547525338</v>
+        <v>0.05633345547527899</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2838655465833264</v>
+        <v>0.2838655465832618</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6598009979414138</v>
+        <v>0.6598009979415639</v>
       </c>
     </row>
     <row r="55">
@@ -3082,13 +3082,13 @@
         <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0.05222996375839693</v>
+        <v>0.05222996375842068</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1900099107410498</v>
+        <v>0.1900099107409634</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7577601255005175</v>
+        <v>0.7577601255006898</v>
       </c>
     </row>
     <row r="56">
@@ -3105,10 +3105,10 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0800226992905865</v>
+        <v>0.08002269929062289</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1269950125452124</v>
+        <v>0.1269950125450969</v>
       </c>
       <c r="G56" t="n">
         <v>0.7929822881642004</v>
@@ -3128,10 +3128,10 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.03848972361844122</v>
+        <v>0.03848972361844997</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1367795073916847</v>
+        <v>0.1367795073915603</v>
       </c>
       <c r="G57" t="n">
         <v>0.8247307689899669</v>
@@ -3154,7 +3154,7 @@
         <v>0.03420215763927174</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1669107757866224</v>
+        <v>0.1669107757865086</v>
       </c>
       <c r="G58" t="n">
         <v>0.798887066574156</v>
@@ -3174,13 +3174,13 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>0.01631770534669098</v>
+        <v>0.0163177053466984</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1427697024769386</v>
+        <v>0.1427697024768737</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8409125921762935</v>
+        <v>0.8409125921764847</v>
       </c>
     </row>
     <row r="60">
@@ -3197,10 +3197,10 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003116370791478038</v>
+        <v>0.003116370791479455</v>
       </c>
       <c r="F60" t="n">
-        <v>0.09191269003818442</v>
+        <v>0.09191269003814262</v>
       </c>
       <c r="G60" t="n">
         <v>0.904970939170335</v>
@@ -3220,10 +3220,10 @@
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001154566421945697</v>
+        <v>0.001154566421946223</v>
       </c>
       <c r="F61" t="n">
-        <v>0.06600239375758191</v>
+        <v>0.06600239375755189</v>
       </c>
       <c r="G61" t="n">
         <v>0.9328430398205673</v>
@@ -3243,10 +3243,10 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0004634110981764723</v>
+        <v>0.0004634110981765776</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04785668680770846</v>
+        <v>0.04785668680768669</v>
       </c>
       <c r="G62" t="n">
         <v>0.951679902094124</v>
@@ -3266,10 +3266,10 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0004378122152621208</v>
+        <v>0.0004378122152622204</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03923728536504187</v>
+        <v>0.03923728536502403</v>
       </c>
       <c r="G63" t="n">
         <v>0.9603249024196072</v>
@@ -3289,10 +3289,10 @@
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0008494402554200988</v>
+        <v>0.000849440255420292</v>
       </c>
       <c r="F64" t="n">
-        <v>0.03440388320383204</v>
+        <v>0.03440388320382422</v>
       </c>
       <c r="G64" t="n">
         <v>0.9647466765406718</v>
@@ -3312,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0.002270359050295196</v>
+        <v>0.002270359050297261</v>
       </c>
       <c r="F65" t="n">
         <v>0.01514910623887766</v>
@@ -3335,10 +3335,10 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0.0003999534101489822</v>
+        <v>0.000399953410149255</v>
       </c>
       <c r="F66" t="n">
-        <v>0.02370618490139441</v>
+        <v>0.0237061849013998</v>
       </c>
       <c r="G66" t="n">
         <v>0.9758938616884832</v>
@@ -3358,10 +3358,10 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0001590070326826841</v>
+        <v>0.0001590070326827564</v>
       </c>
       <c r="F67" t="n">
-        <v>0.04358238344178928</v>
+        <v>0.04358238344179919</v>
       </c>
       <c r="G67" t="n">
         <v>0.9562586095255035</v>
@@ -3381,13 +3381,13 @@
         <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0003126936304013118</v>
+        <v>0.0003126936304015251</v>
       </c>
       <c r="F68" t="n">
-        <v>0.08027550358474242</v>
+        <v>0.08027550358477892</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9194118027849661</v>
+        <v>0.9194118027847571</v>
       </c>
     </row>
     <row r="69">
@@ -3404,10 +3404,10 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0005866301535276696</v>
+        <v>0.0005866301535283365</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06963444697287588</v>
+        <v>0.06963444697292337</v>
       </c>
       <c r="G69" t="n">
         <v>0.9297789228735759</v>
@@ -3427,10 +3427,10 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0002735152650391903</v>
+        <v>0.0002735152650395013</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05182059570293845</v>
+        <v>0.05182059570297379</v>
       </c>
       <c r="G70" t="n">
         <v>0.9479058890320518</v>
@@ -3450,10 +3450,10 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0001880067083516192</v>
+        <v>0.0001880067083518329</v>
       </c>
       <c r="F71" t="n">
-        <v>0.04492055561935585</v>
+        <v>0.04492055561937627</v>
       </c>
       <c r="G71" t="n">
         <v>0.9548914376722588</v>
@@ -3473,10 +3473,10 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0002285527171572931</v>
+        <v>0.0002285527171575529</v>
       </c>
       <c r="F72" t="n">
-        <v>0.04495060004454753</v>
+        <v>0.04495060004457819</v>
       </c>
       <c r="G72" t="n">
         <v>0.9548208472383591</v>
@@ -3496,10 +3496,10 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0001615217098649384</v>
+        <v>0.000161521709865122</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04656155349524682</v>
+        <v>0.04656155349527858</v>
       </c>
       <c r="G73" t="n">
         <v>0.9532769247948882</v>
@@ -3519,10 +3519,10 @@
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0002434250776521081</v>
+        <v>0.0002434250776524402</v>
       </c>
       <c r="F74" t="n">
-        <v>0.05729975387015662</v>
+        <v>0.0572997538701957</v>
       </c>
       <c r="G74" t="n">
         <v>0.9424568210522137</v>
@@ -3542,10 +3542,10 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0002280982390907222</v>
+        <v>0.0002280982390909816</v>
       </c>
       <c r="F75" t="n">
-        <v>0.05135453457972072</v>
+        <v>0.05135453457975575</v>
       </c>
       <c r="G75" t="n">
         <v>0.9484173671810797</v>
@@ -3565,13 +3565,13 @@
         <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0003112691598925125</v>
+        <v>0.0003112691598928663</v>
       </c>
       <c r="F76" t="n">
-        <v>0.05912926825880322</v>
+        <v>0.059129268258857</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9405594625813728</v>
+        <v>0.9405594625811589</v>
       </c>
     </row>
     <row r="77">
@@ -3588,10 +3588,10 @@
         <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>0.000532794018331907</v>
+        <v>0.0005327940183322704</v>
       </c>
       <c r="F77" t="n">
-        <v>0.07202065304133902</v>
+        <v>0.07202065304140452</v>
       </c>
       <c r="G77" t="n">
         <v>0.9274465529403543</v>
@@ -3611,10 +3611,10 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0003734538863891083</v>
+        <v>0.0003734538863895329</v>
       </c>
       <c r="F78" t="n">
-        <v>0.04946530200366489</v>
+        <v>0.04946530200369863</v>
       </c>
       <c r="G78" t="n">
         <v>0.9501612441098342</v>
@@ -3634,10 +3634,10 @@
         <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0002684889465540302</v>
+        <v>0.0002684889465542745</v>
       </c>
       <c r="F79" t="n">
-        <v>0.03925461599500022</v>
+        <v>0.039254615995027</v>
       </c>
       <c r="G79" t="n">
         <v>0.9604768950585163</v>
@@ -3657,10 +3657,10 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0003470574367908097</v>
+        <v>0.0003470574367912832</v>
       </c>
       <c r="F80" t="n">
-        <v>0.03301709838228248</v>
+        <v>0.03301709838231251</v>
       </c>
       <c r="G80" t="n">
         <v>0.9666358441808554</v>
@@ -3680,13 +3680,13 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0003674544446835359</v>
+        <v>0.0003674544446837866</v>
       </c>
       <c r="F81" t="n">
-        <v>0.03016378190378233</v>
+        <v>0.0301637819038029</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9694687636516279</v>
+        <v>0.9694687636514074</v>
       </c>
     </row>
     <row r="82">
@@ -3703,10 +3703,10 @@
         <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0003175060573306205</v>
+        <v>0.0003175060573310536</v>
       </c>
       <c r="F82" t="n">
-        <v>0.01463097604981492</v>
+        <v>0.01463097604983156</v>
       </c>
       <c r="G82" t="n">
         <v>0.9850515178929012</v>
@@ -3726,10 +3726,10 @@
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0002052570695717536</v>
+        <v>0.0002052570695719403</v>
       </c>
       <c r="F83" t="n">
-        <v>0.01078204156973087</v>
+        <v>0.01078204156973577</v>
       </c>
       <c r="G83" t="n">
         <v>0.989012701360676</v>
@@ -3743,19 +3743,19 @@
         <v>0.03402946422756281</v>
       </c>
       <c r="C84" t="n">
-        <v>0.002718764958117403</v>
+        <v>0.002718764958117402</v>
       </c>
       <c r="D84" t="n">
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.33834342152908e-05</v>
+        <v>7.338343421535754e-05</v>
       </c>
       <c r="F84" t="n">
-        <v>0.009942528195582312</v>
+        <v>0.009942528195589094</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9899840883703075</v>
+        <v>0.9899840883700823</v>
       </c>
     </row>
     <row r="85">
@@ -3763,7 +3763,7 @@
         <v>38717</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.002845288954795243</v>
+        <v>-0.002845288954795244</v>
       </c>
       <c r="C85" t="n">
         <v>0.008921207357914518</v>
@@ -3772,10 +3772,10 @@
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>6.05405076852205e-05</v>
+        <v>6.054050768528933e-05</v>
       </c>
       <c r="F85" t="n">
-        <v>0.01007011903371553</v>
+        <v>0.01007011903372469</v>
       </c>
       <c r="G85" t="n">
         <v>0.9898693404585539</v>
@@ -3795,10 +3795,10 @@
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>5.112121543190434e-05</v>
+        <v>5.112121543196245e-05</v>
       </c>
       <c r="F86" t="n">
-        <v>0.007451542137417196</v>
+        <v>0.007451542137423973</v>
       </c>
       <c r="G86" t="n">
         <v>0.9924973366470728</v>
@@ -3809,7 +3809,7 @@
         <v>38776</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.0006837315003157393</v>
+        <v>-0.0006837315003157397</v>
       </c>
       <c r="C87" t="n">
         <v>-0.004183623699470881</v>
@@ -3818,10 +3818,10 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.217567072917927e-05</v>
+        <v>4.217567072921763e-05</v>
       </c>
       <c r="F87" t="n">
-        <v>0.006511497980400825</v>
+        <v>0.006511497980406748</v>
       </c>
       <c r="G87" t="n">
         <v>0.9934463263489609</v>
@@ -3841,10 +3841,10 @@
         <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>4.200775022736656e-05</v>
+        <v>4.200775022740476e-05</v>
       </c>
       <c r="F88" t="n">
-        <v>0.006016317020629035</v>
+        <v>0.006016317020633139</v>
       </c>
       <c r="G88" t="n">
         <v>0.9939416752291599</v>
@@ -3864,10 +3864,10 @@
         <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>3.347517909703697e-05</v>
+        <v>3.347517909708263e-05</v>
       </c>
       <c r="F89" t="n">
-        <v>0.008682292704927251</v>
+        <v>0.008682292704935148</v>
       </c>
       <c r="G89" t="n">
         <v>0.9912842321159735</v>
@@ -3887,10 +3887,10 @@
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>8.147250234880284e-05</v>
+        <v>8.147250234889547e-05</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0151804674160774</v>
+        <v>0.01518046741608775</v>
       </c>
       <c r="G90" t="n">
         <v>0.9847380600816205</v>
@@ -3910,10 +3910,10 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>6.944528871030608e-05</v>
+        <v>6.944528871041661e-05</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01414853305242106</v>
+        <v>0.01414853305242749</v>
       </c>
       <c r="G91" t="n">
         <v>0.9857820216589451</v>
@@ -3933,10 +3933,10 @@
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>6.873570725167342e-05</v>
+        <v>6.873570725176719e-05</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01444152728410509</v>
+        <v>0.01444152728410838</v>
       </c>
       <c r="G92" t="n">
         <v>0.9854897370087236</v>
@@ -3956,10 +3956,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>6.481273624287575e-05</v>
+        <v>6.481273624296417e-05</v>
       </c>
       <c r="F93" t="n">
-        <v>0.01311378881359422</v>
+        <v>0.0131137888135972</v>
       </c>
       <c r="G93" t="n">
         <v>0.9868213984501445</v>
@@ -3979,10 +3979,10 @@
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>4.487622184382595e-05</v>
+        <v>4.487622184388718e-05</v>
       </c>
       <c r="F94" t="n">
-        <v>0.01324693798793972</v>
+        <v>0.01324693798793671</v>
       </c>
       <c r="G94" t="n">
         <v>0.98670818579021</v>
@@ -4002,10 +4002,10 @@
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>3.490086810877424e-05</v>
+        <v>3.490086810882186e-05</v>
       </c>
       <c r="F95" t="n">
-        <v>0.01586035083739911</v>
+        <v>0.01586035083739551</v>
       </c>
       <c r="G95" t="n">
         <v>0.9841047482943938</v>
@@ -4025,10 +4025,10 @@
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>3.336635722761884e-05</v>
+        <v>3.336635722766436e-05</v>
       </c>
       <c r="F96" t="n">
-        <v>0.02221022835625967</v>
+        <v>0.02221022835625462</v>
       </c>
       <c r="G96" t="n">
         <v>0.9777564052865667</v>
@@ -4048,10 +4048,10 @@
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>3.873397624171522e-05</v>
+        <v>3.873397624176807e-05</v>
       </c>
       <c r="F97" t="n">
-        <v>0.03334479755683648</v>
+        <v>0.03334479755682131</v>
       </c>
       <c r="G97" t="n">
         <v>0.9666164684668817</v>
@@ -4071,10 +4071,10 @@
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>3.320119512161997e-05</v>
+        <v>3.320119512165016e-05</v>
       </c>
       <c r="F98" t="n">
-        <v>0.06671169733394217</v>
+        <v>0.06671169733389666</v>
       </c>
       <c r="G98" t="n">
         <v>0.9332551014709517</v>
@@ -4094,10 +4094,10 @@
         <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>9.433121755087681e-05</v>
+        <v>9.433121755098405e-05</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1420345790489521</v>
+        <v>0.1420345790488552</v>
       </c>
       <c r="G99" t="n">
         <v>0.8578710897335572</v>
@@ -4117,10 +4117,10 @@
         <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>9.759249602268064e-05</v>
+        <v>9.759249602272502e-05</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1568679733297086</v>
+        <v>0.1568679733296016</v>
       </c>
       <c r="G100" t="n">
         <v>0.8430344341742932</v>
@@ -4140,13 +4140,13 @@
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>7.374526757544882e-05</v>
+        <v>7.374526757548237e-05</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2036206909347765</v>
+        <v>0.2036206909347302</v>
       </c>
       <c r="G101" t="n">
-        <v>0.7963055637975573</v>
+        <v>0.7963055637977384</v>
       </c>
     </row>
     <row r="102">
@@ -4163,13 +4163,13 @@
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>8.578995958747827e-05</v>
+        <v>8.578995958738073e-05</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2837960682264062</v>
+        <v>0.2837960682262126</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7161181418139334</v>
+        <v>0.7161181418140963</v>
       </c>
     </row>
     <row r="103">
@@ -4186,10 +4186,10 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0001163318465507532</v>
+        <v>0.0001163318465505681</v>
       </c>
       <c r="F103" t="n">
-        <v>0.4310030848269191</v>
+        <v>0.4310030848267231</v>
       </c>
       <c r="G103" t="n">
         <v>0.5688805833266366</v>
@@ -4209,13 +4209,13 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0002314674056027908</v>
+        <v>0.0002314674056028435</v>
       </c>
       <c r="F104" t="n">
-        <v>0.6538582021287792</v>
+        <v>0.6538582021286306</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3459103304657245</v>
+        <v>0.3459103304658031</v>
       </c>
     </row>
     <row r="105">
@@ -4232,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0001914969443320391</v>
+        <v>0.0001914969443318649</v>
       </c>
       <c r="F105" t="n">
-        <v>0.67822764678828</v>
+        <v>0.6782276467881257</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3215808562673812</v>
+        <v>0.3215808562674543</v>
       </c>
     </row>
     <row r="106">
@@ -4249,19 +4249,19 @@
         <v>0.03352305135437444</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0002685369808765334</v>
+        <v>0.000268536980876533</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>9.241065087655036e-05</v>
+        <v>9.24106508762352e-05</v>
       </c>
       <c r="F106" t="n">
         <v>0.7241205273204205</v>
       </c>
       <c r="G106" t="n">
-        <v>0.2757870620285893</v>
+        <v>0.2757870620287147</v>
       </c>
     </row>
     <row r="107">
@@ -4272,19 +4272,19 @@
         <v>0.01258704390080084</v>
       </c>
       <c r="C107" t="n">
-        <v>0.007736157572576453</v>
+        <v>0.007736157572576452</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>8.083393455745367e-05</v>
+        <v>8.083393455703094e-05</v>
       </c>
       <c r="F107" t="n">
         <v>0.8187939120643354</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1811252540011411</v>
+        <v>0.1811252540011823</v>
       </c>
     </row>
     <row r="108">
@@ -4301,13 +4301,13 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0.0002381694056969906</v>
+        <v>0.000238169405696395</v>
       </c>
       <c r="F108" t="n">
         <v>0.9899687943612464</v>
       </c>
       <c r="G108" t="n">
-        <v>0.009793036233114926</v>
+        <v>0.009793036233119379</v>
       </c>
     </row>
     <row r="109">
@@ -4324,13 +4324,13 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0003390540806027769</v>
+        <v>0.0003390540806023143</v>
       </c>
       <c r="F109" t="n">
         <v>0.9901086962884903</v>
       </c>
       <c r="G109" t="n">
-        <v>0.009552249630817649</v>
+        <v>0.009552249630826336</v>
       </c>
     </row>
     <row r="110">
@@ -4353,7 +4353,7 @@
         <v>0.9989634638242093</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0001238115859101085</v>
+        <v>0.0001238115859102774</v>
       </c>
     </row>
     <row r="111">
@@ -4370,13 +4370,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.001946721075702423</v>
+        <v>0.001946721075703751</v>
       </c>
       <c r="F111" t="n">
         <v>0.9949610293869986</v>
       </c>
       <c r="G111" t="n">
-        <v>0.003092249537388808</v>
+        <v>0.003092249537394432</v>
       </c>
     </row>
     <row r="112">
@@ -4384,7 +4384,7 @@
         <v>39538</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.006027409667488032</v>
+        <v>-0.006027409667488031</v>
       </c>
       <c r="C112" t="n">
         <v>0.01148223471221401</v>
@@ -4393,13 +4393,13 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.004914560130931436</v>
+        <v>0.004914560130935905</v>
       </c>
       <c r="F112" t="n">
         <v>0.9829763630399002</v>
       </c>
       <c r="G112" t="n">
-        <v>0.01210907682915872</v>
+        <v>0.01210907682918074</v>
       </c>
     </row>
     <row r="113">
@@ -4416,13 +4416,13 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0.01597283157931556</v>
+        <v>0.01597283157933009</v>
       </c>
       <c r="F113" t="n">
         <v>0.967742662219268</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01628450620141996</v>
+        <v>0.01628450620145329</v>
       </c>
     </row>
     <row r="114">
@@ -4439,13 +4439,13 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.03560421281643199</v>
+        <v>0.03560421281644818</v>
       </c>
       <c r="F114" t="n">
         <v>0.9465445275731845</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01785125961027971</v>
+        <v>0.01785125961030812</v>
       </c>
     </row>
     <row r="115">
@@ -4462,13 +4462,13 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.07234872626908213</v>
+        <v>0.07234872626911502</v>
       </c>
       <c r="F115" t="n">
         <v>0.9274960445444421</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0001552291864887112</v>
+        <v>0.0001552291864890288</v>
       </c>
     </row>
     <row r="116">
@@ -4491,7 +4491,7 @@
         <v>0.8817247608724171</v>
       </c>
       <c r="G116" t="n">
-        <v>0.003432051686407915</v>
+        <v>0.003432051686411816</v>
       </c>
     </row>
     <row r="117">
@@ -4508,13 +4508,13 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.2642861858189925</v>
+        <v>0.2642861858189324</v>
       </c>
       <c r="F117" t="n">
         <v>0.7335444547775177</v>
       </c>
       <c r="G117" t="n">
-        <v>0.002169359403480107</v>
+        <v>0.002169359403483066</v>
       </c>
     </row>
     <row r="118">
@@ -4534,10 +4534,10 @@
         <v>0.7387523984646643</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2612475583590651</v>
+        <v>0.2612475583590057</v>
       </c>
       <c r="G118" t="n">
-        <v>4.317624038269985e-08</v>
+        <v>4.31762403827882e-08</v>
       </c>
     </row>
     <row r="119">
@@ -4557,10 +4557,10 @@
         <v>0.9993694513225264</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0006305486774362723</v>
+        <v>0.0006305486774361289</v>
       </c>
       <c r="G119" t="n">
-        <v>1.985820390017787e-14</v>
+        <v>1.985820390022753e-14</v>
       </c>
     </row>
     <row r="120">
@@ -4580,10 +4580,10 @@
         <v>0.9999403000017146</v>
       </c>
       <c r="F120" t="n">
-        <v>5.969997153515655e-05</v>
+        <v>5.969997153504796e-05</v>
       </c>
       <c r="G120" t="n">
-        <v>2.667173862011868e-11</v>
+        <v>2.667173862016113e-11</v>
       </c>
     </row>
     <row r="121">
@@ -4603,10 +4603,10 @@
         <v>0.9999609998753437</v>
       </c>
       <c r="F121" t="n">
-        <v>3.545334226323373e-05</v>
+        <v>3.545334226289516e-05</v>
       </c>
       <c r="G121" t="n">
-        <v>3.546782455717097e-06</v>
+        <v>3.546782455714678e-06</v>
       </c>
     </row>
     <row r="122">
@@ -4626,7 +4626,7 @@
         <v>0.9999774584970017</v>
       </c>
       <c r="F122" t="n">
-        <v>1.16309479360783e-05</v>
+        <v>1.163094793593814e-05</v>
       </c>
       <c r="G122" t="n">
         <v>1.091055512998737e-05</v>
@@ -4649,10 +4649,10 @@
         <v>0.9990833684993177</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0009074276637222113</v>
+        <v>0.0009074276637083875</v>
       </c>
       <c r="G123" t="n">
-        <v>9.203837017267671e-06</v>
+        <v>9.203837017271855e-06</v>
       </c>
     </row>
     <row r="124">
@@ -4669,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>0.973985740159698</v>
+        <v>0.9739857401599193</v>
       </c>
       <c r="F124" t="n">
-        <v>0.00610331944327391</v>
+        <v>0.006103319443178156</v>
       </c>
       <c r="G124" t="n">
-        <v>0.01991094039692333</v>
+        <v>0.01991094039693238</v>
       </c>
     </row>
     <row r="125">
@@ -4692,13 +4692,13 @@
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>0.9196630846470267</v>
+        <v>0.919663084647654</v>
       </c>
       <c r="F125" t="n">
-        <v>0.04611387445119527</v>
+        <v>0.04611387445067102</v>
       </c>
       <c r="G125" t="n">
-        <v>0.03422304090173984</v>
+        <v>0.03422304090177875</v>
       </c>
     </row>
     <row r="126">
@@ -4715,13 +4715,13 @@
         <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>0.4116300158919359</v>
+        <v>0.4116300158922167</v>
       </c>
       <c r="F126" t="n">
-        <v>0.05875442650282601</v>
+        <v>0.05875442650209126</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5296155576052241</v>
+        <v>0.5296155576057058</v>
       </c>
     </row>
     <row r="127">
@@ -4738,13 +4738,13 @@
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>0.09235225465836124</v>
+        <v>0.09235225465844524</v>
       </c>
       <c r="F127" t="n">
-        <v>0.07024944235544651</v>
+        <v>0.07024944235467982</v>
       </c>
       <c r="G127" t="n">
-        <v>0.8373983029861334</v>
+        <v>0.837398302986895</v>
       </c>
     </row>
     <row r="128">
@@ -4761,13 +4761,13 @@
         <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>0.04301740534551075</v>
+        <v>0.04301740534554987</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1032750194599036</v>
+        <v>0.1032750194591522</v>
       </c>
       <c r="G128" t="n">
-        <v>0.8537075751946496</v>
+        <v>0.8537075751952319</v>
       </c>
     </row>
     <row r="129">
@@ -4784,13 +4784,13 @@
         <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>0.007765109055728248</v>
+        <v>0.007765109055730014</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1169947810609477</v>
+        <v>0.1169947810602295</v>
       </c>
       <c r="G129" t="n">
-        <v>0.8752401098833539</v>
+        <v>0.8752401098839508</v>
       </c>
     </row>
     <row r="130">
@@ -4807,13 +4807,13 @@
         <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>0.001805822860955685</v>
+        <v>0.001805822860954864</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1512038408085294</v>
+        <v>0.1512038408078418</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8469903363306145</v>
+        <v>0.8469903363311923</v>
       </c>
     </row>
     <row r="131">
@@ -4830,13 +4830,13 @@
         <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0008392059112800446</v>
+        <v>0.0008392059112783273</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2187208260528278</v>
+        <v>0.2187208260521316</v>
       </c>
       <c r="G131" t="n">
-        <v>0.7804399680359896</v>
+        <v>0.7804399680365219</v>
       </c>
     </row>
     <row r="132">
@@ -4853,13 +4853,13 @@
         <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0007704626757656975</v>
+        <v>0.0007704626757630698</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2898120182914418</v>
+        <v>0.2898120182909146</v>
       </c>
       <c r="G132" t="n">
-        <v>0.7094175190326799</v>
+        <v>0.7094175190333251</v>
       </c>
     </row>
     <row r="133">
@@ -4876,13 +4876,13 @@
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0009356527624046163</v>
+        <v>0.0009356527624009996</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4093906889590413</v>
+        <v>0.4093906889585759</v>
       </c>
       <c r="G133" t="n">
-        <v>0.589673658278495</v>
+        <v>0.5896736582790313</v>
       </c>
     </row>
     <row r="134">
@@ -4899,13 +4899,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0006657545730722518</v>
+        <v>0.0006657545730707381</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7639679319209856</v>
+        <v>0.7639679319206382</v>
       </c>
       <c r="G134" t="n">
-        <v>0.2353663135060489</v>
+        <v>0.235366313506263</v>
       </c>
     </row>
     <row r="135">
@@ -4922,13 +4922,13 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0001763242327650293</v>
+        <v>0.0001763242327643477</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7957679276247552</v>
+        <v>0.7957679276243933</v>
       </c>
       <c r="G135" t="n">
-        <v>0.204055748142535</v>
+        <v>0.204055748142767</v>
       </c>
     </row>
     <row r="136">
@@ -4945,13 +4945,13 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0001431538352583785</v>
+        <v>0.0001431538352578251</v>
       </c>
       <c r="F136" t="n">
-        <v>0.871023046657264</v>
+        <v>0.871023046657066</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1288337995074986</v>
+        <v>0.1288337995076743</v>
       </c>
     </row>
     <row r="137">
@@ -4968,13 +4968,13 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0001201865720976337</v>
+        <v>0.0001201865720968959</v>
       </c>
       <c r="F137" t="n">
-        <v>0.9175160503550517</v>
+        <v>0.9175160503548431</v>
       </c>
       <c r="G137" t="n">
-        <v>0.08236376307294821</v>
+        <v>0.08236376307304184</v>
       </c>
     </row>
     <row r="138">
@@ -4991,13 +4991,13 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0002796555890146468</v>
+        <v>0.0002796555890137566</v>
       </c>
       <c r="F138" t="n">
         <v>0.9996598340855976</v>
       </c>
       <c r="G138" t="n">
-        <v>6.051032545944624e-05</v>
+        <v>6.051032545954254e-05</v>
       </c>
     </row>
     <row r="139">
@@ -5014,13 +5014,13 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0005613858572604287</v>
+        <v>0.0005613858572600458</v>
       </c>
       <c r="F139" t="n">
         <v>0.9993666958741541</v>
       </c>
       <c r="G139" t="n">
-        <v>7.191826848965233e-05</v>
+        <v>7.191826848976679e-05</v>
       </c>
     </row>
     <row r="140">
@@ -5037,13 +5037,13 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0.001022426105712299</v>
+        <v>0.001022426105712764</v>
       </c>
       <c r="F140" t="n">
         <v>0.9962937742367707</v>
       </c>
       <c r="G140" t="n">
-        <v>0.002683799657525562</v>
+        <v>0.002683799657530443</v>
       </c>
     </row>
     <row r="141">
@@ -5060,13 +5060,13 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.002006938224086207</v>
+        <v>0.002006938224088488</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9972257402208516</v>
+        <v>0.9972257402206248</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0007673215551724342</v>
+        <v>0.0007673215551736556</v>
       </c>
     </row>
     <row r="142">
@@ -5083,13 +5083,13 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0.003029294247142847</v>
+        <v>0.003029294247149735</v>
       </c>
       <c r="F142" t="n">
         <v>0.9818130040269581</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01515770172582388</v>
+        <v>0.01515770172585835</v>
       </c>
     </row>
     <row r="143">
@@ -5106,13 +5106,13 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>0.00149938781067494</v>
+        <v>0.001499387810676986</v>
       </c>
       <c r="F143" t="n">
-        <v>0.9239553136817352</v>
+        <v>0.9239553136815251</v>
       </c>
       <c r="G143" t="n">
-        <v>0.074545298507552</v>
+        <v>0.0745452985076876</v>
       </c>
     </row>
     <row r="144">
@@ -5129,13 +5129,13 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0.001988843681751356</v>
+        <v>0.001988843681754521</v>
       </c>
       <c r="F144" t="n">
-        <v>0.8944339756178118</v>
+        <v>0.8944339756176085</v>
       </c>
       <c r="G144" t="n">
-        <v>0.1035771807003739</v>
+        <v>0.1035771807005859</v>
       </c>
     </row>
     <row r="145">
@@ -5152,13 +5152,13 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>0.004547053445644006</v>
+        <v>0.004547053445650208</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8927005956891504</v>
+        <v>0.8927005956889474</v>
       </c>
       <c r="G145" t="n">
-        <v>0.1027523508651601</v>
+        <v>0.1027523508653704</v>
       </c>
     </row>
     <row r="146">
@@ -5175,13 +5175,13 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>0.001102010176998409</v>
+        <v>0.001102010176999661</v>
       </c>
       <c r="F146" t="n">
-        <v>0.8294514528415662</v>
+        <v>0.8294514528413776</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1694465369813306</v>
+        <v>0.1694465369817159</v>
       </c>
     </row>
     <row r="147">
@@ -5198,13 +5198,13 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.0004305038760060151</v>
+        <v>0.000430503876006113</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8068044824415839</v>
+        <v>0.8068044824412169</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1927650136823243</v>
+        <v>0.1927650136826749</v>
       </c>
     </row>
     <row r="148">
@@ -5221,13 +5221,13 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0002175038566698456</v>
+        <v>0.0002175038566694499</v>
       </c>
       <c r="F148" t="n">
-        <v>0.809701490341569</v>
+        <v>0.8097014903412009</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1900810058017847</v>
+        <v>0.1900810058020441</v>
       </c>
     </row>
     <row r="149">
@@ -5244,13 +5244,13 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0001535464227666243</v>
+        <v>0.0001535464227660657</v>
       </c>
       <c r="F149" t="n">
-        <v>0.8387409712236749</v>
+        <v>0.8387409712234841</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1611054823535176</v>
+        <v>0.1611054823538107</v>
       </c>
     </row>
     <row r="150">
@@ -5267,13 +5267,13 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0002024859173464225</v>
+        <v>0.0002024859173456859</v>
       </c>
       <c r="F150" t="n">
-        <v>0.9085499811578821</v>
+        <v>0.9085499811576755</v>
       </c>
       <c r="G150" t="n">
-        <v>0.09124753292476642</v>
+        <v>0.09124753292491165</v>
       </c>
     </row>
     <row r="151">
@@ -5290,13 +5290,13 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0002343090248745669</v>
+        <v>0.0002343090248736612</v>
       </c>
       <c r="F151" t="n">
         <v>0.9393696871734279</v>
       </c>
       <c r="G151" t="n">
-        <v>0.06039600380166088</v>
+        <v>0.06039600380174328</v>
       </c>
     </row>
     <row r="152">
@@ -5313,13 +5313,13 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0005129843605451971</v>
+        <v>0.0005129843605441473</v>
       </c>
       <c r="F152" t="n">
         <v>0.9879771442530045</v>
       </c>
       <c r="G152" t="n">
-        <v>0.01150987138634892</v>
+        <v>0.01150987138636985</v>
       </c>
     </row>
     <row r="153">
@@ -5336,13 +5336,13 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0.00119132134759458</v>
+        <v>0.001191321347593497</v>
       </c>
       <c r="F153" t="n">
         <v>0.9987728404437504</v>
       </c>
       <c r="G153" t="n">
-        <v>3.583820863576596e-05</v>
+        <v>3.583820863582299e-05</v>
       </c>
     </row>
     <row r="154">
@@ -5359,13 +5359,13 @@
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.001755097500246256</v>
+        <v>0.001755097500248252</v>
       </c>
       <c r="F154" t="n">
         <v>0.9982229681268698</v>
       </c>
       <c r="G154" t="n">
-        <v>2.193437293942103e-05</v>
+        <v>2.193437293946093e-05</v>
       </c>
     </row>
     <row r="155">
@@ -5382,13 +5382,13 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>0.003000435583819829</v>
+        <v>0.003000435583825286</v>
       </c>
       <c r="F155" t="n">
         <v>0.9958518774941472</v>
       </c>
       <c r="G155" t="n">
-        <v>0.001147686922070174</v>
+        <v>0.001147686922072784</v>
       </c>
     </row>
     <row r="156">
@@ -5405,13 +5405,13 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0.00131501217515663</v>
+        <v>0.001315012175158424</v>
       </c>
       <c r="F156" t="n">
         <v>0.9472365053527024</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0514484824720356</v>
+        <v>0.05144848247210579</v>
       </c>
     </row>
     <row r="157">
@@ -5428,13 +5428,13 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0008360367037982027</v>
+        <v>0.0008360367037989631</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9111772961833334</v>
+        <v>0.9111772961831263</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0879866671128868</v>
+        <v>0.08798666711300684</v>
       </c>
     </row>
     <row r="158">
@@ -5451,13 +5451,13 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0006088360434980759</v>
+        <v>0.0006088360434983527</v>
       </c>
       <c r="F158" t="n">
-        <v>0.8917934652592368</v>
+        <v>0.8917934652590339</v>
       </c>
       <c r="G158" t="n">
-        <v>0.1075976986973579</v>
+        <v>0.1075976986975536</v>
       </c>
     </row>
     <row r="159">
@@ -5477,10 +5477,10 @@
         <v>0.0007476507841071669</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8921620695821895</v>
+        <v>0.8921620695819866</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1070902796337296</v>
+        <v>0.1070902796339001</v>
       </c>
     </row>
     <row r="160">
@@ -5497,13 +5497,13 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>0.001740415018773234</v>
+        <v>0.001740415018773629</v>
       </c>
       <c r="F160" t="n">
-        <v>0.9040647854791711</v>
+        <v>0.9040647854789656</v>
       </c>
       <c r="G160" t="n">
-        <v>0.09419479950201358</v>
+        <v>0.0941947995021635</v>
       </c>
     </row>
     <row r="161">
@@ -5520,13 +5520,13 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0.004684596320239274</v>
+        <v>0.00468459632024034</v>
       </c>
       <c r="F161" t="n">
         <v>0.9376492868862113</v>
       </c>
       <c r="G161" t="n">
-        <v>0.05766611679344784</v>
+        <v>0.05766611679352651</v>
       </c>
     </row>
     <row r="162">
@@ -5543,13 +5543,13 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>0.01261493426120181</v>
+        <v>0.01261493426120468</v>
       </c>
       <c r="F162" t="n">
         <v>0.9521716077233423</v>
       </c>
       <c r="G162" t="n">
-        <v>0.03521345801542143</v>
+        <v>0.03521345801544545</v>
       </c>
     </row>
     <row r="163">
@@ -5566,13 +5566,13 @@
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>0.006160232972614682</v>
+        <v>0.006160232972617484</v>
       </c>
       <c r="F163" t="n">
-        <v>0.5920809347504179</v>
+        <v>0.5920809347502833</v>
       </c>
       <c r="G163" t="n">
-        <v>0.4017588322768672</v>
+        <v>0.4017588322770499</v>
       </c>
     </row>
     <row r="164">
@@ -5589,13 +5589,13 @@
         <v>2</v>
       </c>
       <c r="E164" t="n">
-        <v>0.003496336992835844</v>
+        <v>0.003496336992836639</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3530328428640355</v>
+        <v>0.3530328428638749</v>
       </c>
       <c r="G164" t="n">
-        <v>0.6434708201431577</v>
+        <v>0.643470820143304</v>
       </c>
     </row>
     <row r="165">
@@ -5615,10 +5615,10 @@
         <v>0.001617899591861278</v>
       </c>
       <c r="F165" t="n">
-        <v>0.2047235643528026</v>
+        <v>0.2047235643527095</v>
       </c>
       <c r="G165" t="n">
-        <v>0.7936585360553144</v>
+        <v>0.793658536055495</v>
       </c>
     </row>
     <row r="166">
@@ -5635,10 +5635,10 @@
         <v>2</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0009353061740930259</v>
+        <v>0.0009353061740932385</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1314633259622163</v>
+        <v>0.1314633259621266</v>
       </c>
       <c r="G166" t="n">
         <v>0.867601367863685</v>
@@ -5661,10 +5661,10 @@
         <v>0.0009279780414227788</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0958455781870203</v>
+        <v>0.09584557818697671</v>
       </c>
       <c r="G167" t="n">
-        <v>0.9032264437714557</v>
+        <v>0.9032264437716611</v>
       </c>
     </row>
     <row r="168">
@@ -5681,10 +5681,10 @@
         <v>2</v>
       </c>
       <c r="E168" t="n">
-        <v>0.000525822675881333</v>
+        <v>0.0005258226758812134</v>
       </c>
       <c r="F168" t="n">
-        <v>0.06566769794274227</v>
+        <v>0.06566769794268255</v>
       </c>
       <c r="G168" t="n">
         <v>0.9338064793813854</v>
@@ -5707,7 +5707,7 @@
         <v>0.0003407135119450661</v>
       </c>
       <c r="F169" t="n">
-        <v>0.044744338137997</v>
+        <v>0.04474433813796649</v>
       </c>
       <c r="G169" t="n">
         <v>0.9549149483500368</v>
@@ -5727,10 +5727,10 @@
         <v>2</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0003729065807865017</v>
+        <v>0.0003729065807863321</v>
       </c>
       <c r="F170" t="n">
-        <v>0.03895828209838052</v>
+        <v>0.03895828209834509</v>
       </c>
       <c r="G170" t="n">
         <v>0.960668811320758</v>
@@ -5750,10 +5750,10 @@
         <v>2</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0002223075651303909</v>
+        <v>0.0002223075651303404</v>
       </c>
       <c r="F171" t="n">
-        <v>0.02564445247045799</v>
+        <v>0.02564445247044633</v>
       </c>
       <c r="G171" t="n">
         <v>0.9741332399643355</v>
@@ -5776,7 +5776,7 @@
         <v>0.0001541763416011468</v>
       </c>
       <c r="F172" t="n">
-        <v>0.01726843352956121</v>
+        <v>0.01726843352955729</v>
       </c>
       <c r="G172" t="n">
         <v>0.9825773901287483</v>
@@ -5796,10 +5796,10 @@
         <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0001535379002434928</v>
+        <v>0.0001535379002435277</v>
       </c>
       <c r="F173" t="n">
-        <v>0.01219216186296058</v>
+        <v>0.01219216186295781</v>
       </c>
       <c r="G173" t="n">
         <v>0.9876543002367523</v>
@@ -5819,7 +5819,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0002712271621208339</v>
+        <v>0.0002712271621209573</v>
       </c>
       <c r="F174" t="n">
         <v>0.008547765271808366</v>
@@ -5842,7 +5842,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0001744629931403066</v>
+        <v>0.0001744629931404256</v>
       </c>
       <c r="F175" t="n">
         <v>0.008100897779760101</v>
@@ -5865,7 +5865,7 @@
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>8.38856998767005e-05</v>
+        <v>8.388569987675772e-05</v>
       </c>
       <c r="F176" t="n">
         <v>0.01509090583820965</v>
@@ -5888,7 +5888,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>0.0001313546950835734</v>
+        <v>0.000131354695083663</v>
       </c>
       <c r="F177" t="n">
         <v>0.01898557633769095</v>
@@ -5911,10 +5911,10 @@
         <v>2</v>
       </c>
       <c r="E178" t="n">
-        <v>7.652785164858109e-05</v>
+        <v>7.65278516486681e-05</v>
       </c>
       <c r="F178" t="n">
-        <v>0.02214998868322824</v>
+        <v>0.02214998868323328</v>
       </c>
       <c r="G178" t="n">
         <v>0.9777734834650127</v>
@@ -5934,7 +5934,7 @@
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>6.369961783973865e-05</v>
+        <v>6.369961783981108e-05</v>
       </c>
       <c r="F179" t="n">
         <v>0.03060646279649526</v>
@@ -5957,7 +5957,7 @@
         <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>7.63861570071836e-05</v>
+        <v>7.638615700725307e-05</v>
       </c>
       <c r="F180" t="n">
         <v>0.04421742472163448</v>
@@ -5980,10 +5980,10 @@
         <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0002170232446852087</v>
+        <v>0.0002170232446854555</v>
       </c>
       <c r="F181" t="n">
-        <v>0.07024756315380545</v>
+        <v>0.07024756315382143</v>
       </c>
       <c r="G181" t="n">
         <v>0.929535413601454</v>
@@ -6003,10 +6003,10 @@
         <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0007085915082147827</v>
+        <v>0.0007085915082151049</v>
       </c>
       <c r="F182" t="n">
-        <v>0.1255298394436563</v>
+        <v>0.1255298394437134</v>
       </c>
       <c r="G182" t="n">
         <v>0.8737615690480672</v>
@@ -6026,7 +6026,7 @@
         <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0006544724058373249</v>
+        <v>0.0006544724058379201</v>
       </c>
       <c r="F183" t="n">
         <v>0.08139463966411004</v>
@@ -6049,7 +6049,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0003566590781280654</v>
+        <v>0.0003566590781283898</v>
       </c>
       <c r="F184" t="n">
         <v>0.05260082050211338</v>
@@ -6072,10 +6072,10 @@
         <v>2</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0002214156842101062</v>
+        <v>0.0002214156842102573</v>
       </c>
       <c r="F185" t="n">
-        <v>0.04167771182271177</v>
+        <v>0.04167771182269282</v>
       </c>
       <c r="G185" t="n">
         <v>0.9581008724931013</v>
@@ -6095,10 +6095,10 @@
         <v>2</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0001830810720664184</v>
+        <v>0.0001830810720665433</v>
       </c>
       <c r="F186" t="n">
-        <v>0.03603949322721912</v>
+        <v>0.03603949322720273</v>
       </c>
       <c r="G186" t="n">
         <v>0.9637774257006935</v>
@@ -6118,10 +6118,10 @@
         <v>2</v>
       </c>
       <c r="E187" t="n">
-        <v>9.26551414335458e-05</v>
+        <v>9.265514143358793e-05</v>
       </c>
       <c r="F187" t="n">
-        <v>0.03636037895831046</v>
+        <v>0.03636037895829393</v>
       </c>
       <c r="G187" t="n">
         <v>0.9635469659001842</v>
@@ -6141,10 +6141,10 @@
         <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>9.587223397779218e-05</v>
+        <v>9.587223397785758e-05</v>
       </c>
       <c r="F188" t="n">
-        <v>0.04574535000908444</v>
+        <v>0.04574535000906364</v>
       </c>
       <c r="G188" t="n">
         <v>0.9541587777568487</v>
@@ -6164,10 +6164,10 @@
         <v>2</v>
       </c>
       <c r="E189" t="n">
-        <v>9.538599946029691e-05</v>
+        <v>9.538599946034029e-05</v>
       </c>
       <c r="F189" t="n">
-        <v>0.05849313882611509</v>
+        <v>0.05849313882608849</v>
       </c>
       <c r="G189" t="n">
         <v>0.9414114751743642</v>
@@ -6190,7 +6190,7 @@
         <v>7.412635689681706e-05</v>
       </c>
       <c r="F190" t="n">
-        <v>0.08702579800247257</v>
+        <v>0.08702579800243299</v>
       </c>
       <c r="G190" t="n">
         <v>0.9129000756406537</v>
@@ -6213,7 +6213,7 @@
         <v>4.92988464984087e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>0.1448222016481068</v>
+        <v>0.1448222016480409</v>
       </c>
       <c r="G191" t="n">
         <v>0.8551284995053942</v>
@@ -6236,7 +6236,7 @@
         <v>6.265391628775602e-05</v>
       </c>
       <c r="F192" t="n">
-        <v>0.2495430332004471</v>
+        <v>0.2495430332003903</v>
       </c>
       <c r="G192" t="n">
         <v>0.7503943128832634</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="E193" t="n">
-        <v>0.0002071331183151906</v>
+        <v>0.0002071331183152848</v>
       </c>
       <c r="F193" t="n">
-        <v>0.4450160344083121</v>
+        <v>0.4450160344082109</v>
       </c>
       <c r="G193" t="n">
         <v>0.5547768324733992</v>
@@ -6279,13 +6279,13 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.00117354930092171</v>
+        <v>0.00117354930092331</v>
       </c>
       <c r="F194" t="n">
-        <v>0.746651709342077</v>
+        <v>0.7466517093419073</v>
       </c>
       <c r="G194" t="n">
-        <v>0.2521747413570984</v>
+        <v>0.2521747413571557</v>
       </c>
     </row>
     <row r="195">
@@ -6302,13 +6302,13 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0.001879054586780964</v>
+        <v>0.001879054586783528</v>
       </c>
       <c r="F195" t="n">
-        <v>0.7399788198316736</v>
+        <v>0.7399788198315054</v>
       </c>
       <c r="G195" t="n">
-        <v>0.2581421255816396</v>
+        <v>0.2581421255817569</v>
       </c>
     </row>
     <row r="196">
@@ -6325,13 +6325,13 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.001368148423810531</v>
+        <v>0.001368148423811775</v>
       </c>
       <c r="F196" t="n">
-        <v>0.7058895123819866</v>
+        <v>0.7058895123816656</v>
       </c>
       <c r="G196" t="n">
-        <v>0.2927423391942822</v>
+        <v>0.2927423391944819</v>
       </c>
     </row>
     <row r="197">
@@ -6348,13 +6348,13 @@
         <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0006058535933478281</v>
+        <v>0.0006058535933483791</v>
       </c>
       <c r="F197" t="n">
-        <v>0.6598147683142591</v>
+        <v>0.659814768313959</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3395793780923484</v>
+        <v>0.3395793780926573</v>
       </c>
     </row>
     <row r="198">
@@ -6371,13 +6371,13 @@
         <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0002929700308735561</v>
+        <v>0.0002929700308733563</v>
       </c>
       <c r="F198" t="n">
-        <v>0.6561627268286849</v>
+        <v>0.6561627268283865</v>
       </c>
       <c r="G198" t="n">
-        <v>0.3435443031403708</v>
+        <v>0.3435443031406832</v>
       </c>
     </row>
     <row r="199">
@@ -6394,13 +6394,13 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0002861902140777554</v>
+        <v>0.0002861902140768444</v>
       </c>
       <c r="F199" t="n">
-        <v>0.6887101614263232</v>
+        <v>0.68871016142601</v>
       </c>
       <c r="G199" t="n">
-        <v>0.3110036483596172</v>
+        <v>0.3110036483599001</v>
       </c>
     </row>
     <row r="200">
@@ -6417,13 +6417,13 @@
         <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0001571578004160481</v>
+        <v>0.0001571578004153691</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7866924142200236</v>
+        <v>0.7866924142198447</v>
       </c>
       <c r="G200" t="n">
-        <v>0.2131504279796053</v>
+        <v>0.2131504279798477</v>
       </c>
     </row>
     <row r="201">
@@ -6440,13 +6440,13 @@
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0003396184066528667</v>
+        <v>0.0003396184066520945</v>
       </c>
       <c r="F201" t="n">
-        <v>0.9697971420085981</v>
+        <v>0.9697971420083775</v>
       </c>
       <c r="G201" t="n">
-        <v>0.02986323958483361</v>
+        <v>0.02986323958487435</v>
       </c>
     </row>
     <row r="202">
@@ -6463,13 +6463,13 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.0004600370039352573</v>
+        <v>0.0004600370039350481</v>
       </c>
       <c r="F202" t="n">
         <v>0.981104194188484</v>
       </c>
       <c r="G202" t="n">
-        <v>0.01843576880758565</v>
+        <v>0.01843576880761499</v>
       </c>
     </row>
     <row r="203">
@@ -6486,13 +6486,13 @@
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0009284051281324189</v>
+        <v>0.00092840512813263</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9820762032627174</v>
+        <v>0.9820762032624941</v>
       </c>
       <c r="G203" t="n">
-        <v>0.01699539160923302</v>
+        <v>0.01699539160926007</v>
       </c>
     </row>
     <row r="204">
@@ -6512,10 +6512,10 @@
         <v>0.001092151618015416</v>
       </c>
       <c r="F204" t="n">
-        <v>0.9647160751937242</v>
+        <v>0.9647160751935049</v>
       </c>
       <c r="G204" t="n">
-        <v>0.03419177318835512</v>
+        <v>0.03419177318839399</v>
       </c>
     </row>
     <row r="205">
@@ -6532,13 +6532,13 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>0.002737422890271897</v>
+        <v>0.00273742289027252</v>
       </c>
       <c r="F205" t="n">
         <v>0.9641379412824563</v>
       </c>
       <c r="G205" t="n">
-        <v>0.03312463582722101</v>
+        <v>0.03312463582726619</v>
       </c>
     </row>
     <row r="206">
@@ -6555,13 +6555,13 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>0.0075263589932197</v>
+        <v>0.007526358993221411</v>
       </c>
       <c r="F206" t="n">
         <v>0.9703681741843131</v>
       </c>
       <c r="G206" t="n">
-        <v>0.02210546682238068</v>
+        <v>0.02210546682241084</v>
       </c>
     </row>
     <row r="207">
@@ -6578,13 +6578,13 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>0.005831596966818096</v>
+        <v>0.005831596966819421</v>
       </c>
       <c r="F207" t="n">
-        <v>0.7914943751243477</v>
+        <v>0.7914943751241679</v>
       </c>
       <c r="G207" t="n">
-        <v>0.2026740279089412</v>
+        <v>0.2026740279089873</v>
       </c>
     </row>
     <row r="208">
@@ -6601,13 +6601,13 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>0.006822611590319141</v>
+        <v>0.006822611590323794</v>
       </c>
       <c r="F208" t="n">
-        <v>0.6240647548780685</v>
+        <v>0.6240647548779266</v>
       </c>
       <c r="G208" t="n">
-        <v>0.3691126335315844</v>
+        <v>0.3691126335317523</v>
       </c>
     </row>
     <row r="209">
@@ -6624,13 +6624,13 @@
         <v>2</v>
       </c>
       <c r="E209" t="n">
-        <v>0.003242033249993358</v>
+        <v>0.003242033249994833</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3794723355409697</v>
+        <v>0.3794723355407108</v>
       </c>
       <c r="G209" t="n">
-        <v>0.617285631209033</v>
+        <v>0.6172856312093137</v>
       </c>
     </row>
     <row r="210">
@@ -6650,10 +6650,10 @@
         <v>0.002051659305341426</v>
       </c>
       <c r="F210" t="n">
-        <v>0.248746977484739</v>
+        <v>0.2487469774845694</v>
       </c>
       <c r="G210" t="n">
-        <v>0.7492013632098813</v>
+        <v>0.7492013632100517</v>
       </c>
     </row>
     <row r="211">
@@ -6670,13 +6670,13 @@
         <v>2</v>
       </c>
       <c r="E211" t="n">
-        <v>0.003100638332745234</v>
+        <v>0.003100638332744529</v>
       </c>
       <c r="F211" t="n">
-        <v>0.1852149546242194</v>
+        <v>0.185214954624051</v>
       </c>
       <c r="G211" t="n">
-        <v>0.8116844070430858</v>
+        <v>0.8116844070432703</v>
       </c>
     </row>
     <row r="212">
@@ -6696,10 +6696,10 @@
         <v>0.001279762279131238</v>
       </c>
       <c r="F212" t="n">
-        <v>0.1031386175332258</v>
+        <v>0.103138617533132</v>
       </c>
       <c r="G212" t="n">
-        <v>0.8955816201875776</v>
+        <v>0.8955816201877812</v>
       </c>
     </row>
     <row r="213">
@@ -6716,13 +6716,13 @@
         <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>0.0007236055097339356</v>
+        <v>0.000723605509733771</v>
       </c>
       <c r="F213" t="n">
-        <v>0.05582073703350593</v>
+        <v>0.05582073703345516</v>
       </c>
       <c r="G213" t="n">
-        <v>0.9434556574566773</v>
+        <v>0.9434556574568917</v>
       </c>
     </row>
     <row r="214">
@@ -6742,7 +6742,7 @@
         <v>0.0005236034987983881</v>
       </c>
       <c r="F214" t="n">
-        <v>0.03556827204991847</v>
+        <v>0.0355682720499023</v>
       </c>
       <c r="G214" t="n">
         <v>0.9639081244511943</v>
@@ -6762,10 +6762,10 @@
         <v>2</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0008871143034081794</v>
+        <v>0.0008871143034079776</v>
       </c>
       <c r="F215" t="n">
-        <v>0.02321319205562427</v>
+        <v>0.02321319205561371</v>
       </c>
       <c r="G215" t="n">
         <v>0.9758996936409808</v>
@@ -6788,7 +6788,7 @@
         <v>0.001332769982226236</v>
       </c>
       <c r="F216" t="n">
-        <v>0.018434752650279</v>
+        <v>0.01843475265027481</v>
       </c>
       <c r="G216" t="n">
         <v>0.980232477367453</v>
@@ -6808,10 +6808,10 @@
         <v>2</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0002472694389474031</v>
+        <v>0.0002472694389474593</v>
       </c>
       <c r="F217" t="n">
-        <v>0.01220846082528087</v>
+        <v>0.01220846082528365</v>
       </c>
       <c r="G217" t="n">
         <v>0.9875442697357066</v>
@@ -6831,7 +6831,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>7.707255530491926e-05</v>
+        <v>7.707255530493678e-05</v>
       </c>
       <c r="F218" t="n">
         <v>0.009588794102978684</v>
@@ -6854,10 +6854,10 @@
         <v>2</v>
       </c>
       <c r="E219" t="n">
-        <v>5.238670807434403e-05</v>
+        <v>5.238670807437976e-05</v>
       </c>
       <c r="F219" t="n">
-        <v>0.008898002494864074</v>
+        <v>0.008898002494868121</v>
       </c>
       <c r="G219" t="n">
         <v>0.9910496107970233</v>
@@ -6877,10 +6877,10 @@
         <v>2</v>
       </c>
       <c r="E220" t="n">
-        <v>4.203687509249061e-05</v>
+        <v>4.203687509251928e-05</v>
       </c>
       <c r="F220" t="n">
-        <v>0.008656561782615974</v>
+        <v>0.00865656178261991</v>
       </c>
       <c r="G220" t="n">
         <v>0.9913014013423659</v>
@@ -6900,10 +6900,10 @@
         <v>2</v>
       </c>
       <c r="E221" t="n">
-        <v>4.08151308588797e-05</v>
+        <v>4.081513085891682e-05</v>
       </c>
       <c r="F221" t="n">
-        <v>0.008728478899044633</v>
+        <v>0.008728478899048603</v>
       </c>
       <c r="G221" t="n">
         <v>0.9912307059701269</v>
@@ -6923,10 +6923,10 @@
         <v>2</v>
       </c>
       <c r="E222" t="n">
-        <v>3.787384358756621e-05</v>
+        <v>3.787384358760065e-05</v>
       </c>
       <c r="F222" t="n">
-        <v>0.008183216022267816</v>
+        <v>0.008183216022271537</v>
       </c>
       <c r="G222" t="n">
         <v>0.9917789101341293</v>
@@ -6946,10 +6946,10 @@
         <v>2</v>
       </c>
       <c r="E223" t="n">
-        <v>3.40983605233202e-05</v>
+        <v>3.409836052335121e-05</v>
       </c>
       <c r="F223" t="n">
-        <v>0.007832954779470288</v>
+        <v>0.007832954779472068</v>
       </c>
       <c r="G223" t="n">
         <v>0.9921329468601141</v>
@@ -6969,10 +6969,10 @@
         <v>2</v>
       </c>
       <c r="E224" t="n">
-        <v>2.734358829223299e-05</v>
+        <v>2.734358829227651e-05</v>
       </c>
       <c r="F224" t="n">
-        <v>0.009540869729978561</v>
+        <v>0.009540869729980731</v>
       </c>
       <c r="G224" t="n">
         <v>0.9904317866816856</v>
@@ -6992,10 +6992,10 @@
         <v>2</v>
       </c>
       <c r="E225" t="n">
-        <v>3.980953241738675e-05</v>
+        <v>3.980953241744106e-05</v>
       </c>
       <c r="F225" t="n">
-        <v>0.01308613590300927</v>
+        <v>0.01308613590301522</v>
       </c>
       <c r="G225" t="n">
         <v>0.9868740545645994</v>
@@ -7015,7 +7015,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="n">
-        <v>4.391844642743513e-05</v>
+        <v>4.391844642749504e-05</v>
       </c>
       <c r="F226" t="n">
         <v>0.01422077884690376</v>
@@ -7038,7 +7038,7 @@
         <v>2</v>
       </c>
       <c r="E227" t="n">
-        <v>2.750899967951263e-05</v>
+        <v>2.750899967955016e-05</v>
       </c>
       <c r="F227" t="n">
         <v>0.02089310205858009</v>
@@ -7061,10 +7061,10 @@
         <v>2</v>
       </c>
       <c r="E228" t="n">
-        <v>2.864999987169228e-05</v>
+        <v>2.864999987172485e-05</v>
       </c>
       <c r="F228" t="n">
-        <v>0.03510131217603085</v>
+        <v>0.03510131217602287</v>
       </c>
       <c r="G228" t="n">
         <v>0.9648700378239939</v>
@@ -7078,16 +7078,16 @@
         <v>0.01015736928597801</v>
       </c>
       <c r="C229" t="n">
-        <v>0.001216387825317766</v>
+        <v>0.001216387825317767</v>
       </c>
       <c r="D229" t="n">
         <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>5.503147900209704e-05</v>
+        <v>5.503147900217211e-05</v>
       </c>
       <c r="F229" t="n">
-        <v>0.06150821899875562</v>
+        <v>0.06150821899874163</v>
       </c>
       <c r="G229" t="n">
         <v>0.9384367495222158</v>
@@ -7107,10 +7107,10 @@
         <v>2</v>
       </c>
       <c r="E230" t="n">
-        <v>0.0002472523469963596</v>
+        <v>0.0002472523469965845</v>
       </c>
       <c r="F230" t="n">
-        <v>0.11134491899743</v>
+        <v>0.1113449189973794</v>
       </c>
       <c r="G230" t="n">
         <v>0.8884078286556102</v>
@@ -7130,13 +7130,13 @@
         <v>2</v>
       </c>
       <c r="E231" t="n">
-        <v>0.0006906280676817026</v>
+        <v>0.0006906280676823306</v>
       </c>
       <c r="F231" t="n">
-        <v>0.1313995924039505</v>
+        <v>0.1313995924039206</v>
       </c>
       <c r="G231" t="n">
-        <v>0.8679097795282559</v>
+        <v>0.8679097795284533</v>
       </c>
     </row>
     <row r="232">
@@ -7153,10 +7153,10 @@
         <v>2</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0007428296767436175</v>
+        <v>0.0007428296767442931</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1435437539701089</v>
+        <v>0.1435437539700763</v>
       </c>
       <c r="G232" t="n">
         <v>0.8557134163531566</v>
@@ -7176,10 +7176,10 @@
         <v>2</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0004170403687886648</v>
+        <v>0.0004170403687893286</v>
       </c>
       <c r="F233" t="n">
-        <v>0.1205816185634246</v>
+        <v>0.1205816185633972</v>
       </c>
       <c r="G233" t="n">
         <v>0.8790013410677965</v>
@@ -7199,10 +7199,10 @@
         <v>2</v>
       </c>
       <c r="E234" t="n">
-        <v>0.0001678377553409505</v>
+        <v>0.0001678377553411413</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1258571794659775</v>
+        <v>0.1258571794659203</v>
       </c>
       <c r="G234" t="n">
         <v>0.8739749827787882</v>
@@ -7213,16 +7213,16 @@
         <v>43281</v>
       </c>
       <c r="B235" t="n">
-        <v>0.004736567679959355</v>
+        <v>0.004736567679959356</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.000814895624694481</v>
+        <v>-0.0008148956246944808</v>
       </c>
       <c r="D235" t="n">
         <v>2</v>
       </c>
       <c r="E235" t="n">
-        <v>8.784025991745003e-05</v>
+        <v>8.784025991750995e-05</v>
       </c>
       <c r="F235" t="n">
         <v>0.1494965534412009</v>
@@ -7251,7 +7251,7 @@
         <v>0.2015642969050456</v>
       </c>
       <c r="G236" t="n">
-        <v>0.798373646033945</v>
+        <v>0.7983736460341265</v>
       </c>
     </row>
     <row r="237">
@@ -7268,7 +7268,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="n">
-        <v>5.792296434257654e-05</v>
+        <v>5.7922964342458e-05</v>
       </c>
       <c r="F237" t="n">
         <v>0.2908851375500926</v>
@@ -7291,10 +7291,10 @@
         <v>2</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0001246750084490508</v>
+        <v>0.0001246750084486823</v>
       </c>
       <c r="F238" t="n">
-        <v>0.4614889428644827</v>
+        <v>0.4614889428645876</v>
       </c>
       <c r="G238" t="n">
         <v>0.5383863821269854</v>
@@ -7314,13 +7314,13 @@
         <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>0.0004036783708668442</v>
+        <v>0.0004036783708659263</v>
       </c>
       <c r="F239" t="n">
         <v>0.909923799172596</v>
       </c>
       <c r="G239" t="n">
-        <v>0.08967252245662276</v>
+        <v>0.08967252245658199</v>
       </c>
     </row>
     <row r="240">
@@ -7337,13 +7337,13 @@
         <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>0.0004191668030960814</v>
+        <v>0.0004191668030957002</v>
       </c>
       <c r="F240" t="n">
         <v>0.9386393992066812</v>
       </c>
       <c r="G240" t="n">
-        <v>0.06094143399018254</v>
+        <v>0.06094143399016868</v>
       </c>
     </row>
     <row r="241">
@@ -7360,13 +7360,13 @@
         <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>0.001092697235822337</v>
+        <v>0.001092697235822834</v>
       </c>
       <c r="F241" t="n">
         <v>0.9988361161089919</v>
       </c>
       <c r="G241" t="n">
-        <v>7.118665517928431e-05</v>
+        <v>7.118665517934905e-05</v>
       </c>
     </row>
     <row r="242">
@@ -7383,13 +7383,13 @@
         <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0.001097606103500835</v>
+        <v>0.001097606103501334</v>
       </c>
       <c r="F242" t="n">
         <v>0.9856634504533214</v>
       </c>
       <c r="G242" t="n">
-        <v>0.01323894344321839</v>
+        <v>0.01323894344324248</v>
       </c>
     </row>
     <row r="243">
@@ -7406,13 +7406,13 @@
         <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>0.0004109235740805503</v>
+        <v>0.00041092357408027</v>
       </c>
       <c r="F243" t="n">
         <v>0.9659350538472473</v>
       </c>
       <c r="G243" t="n">
-        <v>0.03365402257860328</v>
+        <v>0.03365402257864154</v>
       </c>
     </row>
     <row r="244">
@@ -7429,13 +7429,13 @@
         <v>1</v>
       </c>
       <c r="E244" t="n">
-        <v>0.000422827667219559</v>
+        <v>0.0004228276672192706</v>
       </c>
       <c r="F244" t="n">
         <v>0.9633848894525074</v>
       </c>
       <c r="G244" t="n">
-        <v>0.03619228288016834</v>
+        <v>0.03619228288022594</v>
       </c>
     </row>
     <row r="245">
@@ -7452,13 +7452,13 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0006424184502394647</v>
+        <v>0.0006424184502399028</v>
       </c>
       <c r="F245" t="n">
         <v>0.9728044107819749</v>
       </c>
       <c r="G245" t="n">
-        <v>0.02655317076773824</v>
+        <v>0.02655317076778654</v>
       </c>
     </row>
     <row r="246">
@@ -7475,13 +7475,13 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.001871281048453078</v>
+        <v>0.001871281048455205</v>
       </c>
       <c r="F246" t="n">
         <v>0.9962271830800169</v>
       </c>
       <c r="G246" t="n">
-        <v>0.001901535871450196</v>
+        <v>0.001901535871454088</v>
       </c>
     </row>
     <row r="247">
@@ -7498,13 +7498,13 @@
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0.002164663909887921</v>
+        <v>0.002164663909890382</v>
       </c>
       <c r="F247" t="n">
         <v>0.9596142742259502</v>
       </c>
       <c r="G247" t="n">
-        <v>0.0382210618641964</v>
+        <v>0.03822106186425724</v>
       </c>
     </row>
     <row r="248">
@@ -7521,13 +7521,13 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>0.001783641927586129</v>
+        <v>0.001783641927588562</v>
       </c>
       <c r="F248" t="n">
         <v>0.9286425461787747</v>
       </c>
       <c r="G248" t="n">
-        <v>0.06957381189355709</v>
+        <v>0.06957381189368364</v>
       </c>
     </row>
     <row r="249">
@@ -7544,13 +7544,13 @@
         <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>0.004071230600809207</v>
+        <v>0.004071230600815687</v>
       </c>
       <c r="F249" t="n">
         <v>0.9217917209359945</v>
       </c>
       <c r="G249" t="n">
-        <v>0.07413704846317683</v>
+        <v>0.07413704846329482</v>
       </c>
     </row>
     <row r="250">
@@ -7567,13 +7567,13 @@
         <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>0.001229832896832632</v>
+        <v>0.001229832896833751</v>
       </c>
       <c r="F250" t="n">
-        <v>0.8509897161684753</v>
+        <v>0.8509897161682818</v>
       </c>
       <c r="G250" t="n">
-        <v>0.1477804509346246</v>
+        <v>0.1477804509348598</v>
       </c>
     </row>
     <row r="251">
@@ -7590,13 +7590,13 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>0.000403306445845987</v>
+        <v>0.0004033064458458953</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8305015631207493</v>
+        <v>0.8305015631205604</v>
       </c>
       <c r="G251" t="n">
-        <v>0.1690951304333599</v>
+        <v>0.169095130433629</v>
       </c>
     </row>
     <row r="252">
@@ -7607,19 +7607,19 @@
         <v>0.03445648173694641</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.00776581496573</v>
+        <v>-0.007765814965729999</v>
       </c>
       <c r="D252" t="n">
         <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0002864469476512258</v>
+        <v>0.0002864469476510304</v>
       </c>
       <c r="F252" t="n">
-        <v>0.8389896494437658</v>
+        <v>0.838989649443575</v>
       </c>
       <c r="G252" t="n">
-        <v>0.1607239036086259</v>
+        <v>0.1607239036088817</v>
       </c>
     </row>
     <row r="253">
@@ -7636,13 +7636,13 @@
         <v>1</v>
       </c>
       <c r="E253" t="n">
-        <v>0.0004756581943418102</v>
+        <v>0.0004756581943414858</v>
       </c>
       <c r="F253" t="n">
-        <v>0.8719171219306273</v>
+        <v>0.871917121930429</v>
       </c>
       <c r="G253" t="n">
-        <v>0.1276072198750159</v>
+        <v>0.127607219875161</v>
       </c>
     </row>
     <row r="254">
@@ -7659,13 +7659,13 @@
         <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0.001441674392312742</v>
+        <v>0.001441674392312414</v>
       </c>
       <c r="F254" t="n">
         <v>0.9475691629407781</v>
       </c>
       <c r="G254" t="n">
-        <v>0.05098916266691819</v>
+        <v>0.05098916266697616</v>
       </c>
     </row>
     <row r="255">
@@ -7682,13 +7682,13 @@
         <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>0.003439686924703052</v>
+        <v>0.003439686924704616</v>
       </c>
       <c r="F255" t="n">
         <v>0.9965422724360217</v>
       </c>
       <c r="G255" t="n">
-        <v>1.804063934778762e-05</v>
+        <v>1.804063934780812e-05</v>
       </c>
     </row>
     <row r="256">
@@ -7705,13 +7705,13 @@
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.007346977676310881</v>
+        <v>0.007346977676317563</v>
       </c>
       <c r="F256" t="n">
-        <v>0.9926530215747023</v>
+        <v>0.9926530215744765</v>
       </c>
       <c r="G256" t="n">
-        <v>7.490954379893087e-10</v>
+        <v>7.49095437991012e-10</v>
       </c>
     </row>
     <row r="257">
@@ -7728,13 +7728,13 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.0103938617121952</v>
+        <v>0.01039386171220938</v>
       </c>
       <c r="F257" t="n">
         <v>0.9884907396592765</v>
       </c>
       <c r="G257" t="n">
-        <v>0.001115398628581548</v>
+        <v>0.001115398628584084</v>
       </c>
     </row>
     <row r="258">
@@ -7751,13 +7751,13 @@
         <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0.002604813020332835</v>
+        <v>0.002604813020335797</v>
       </c>
       <c r="F258" t="n">
         <v>0.9501033953625054</v>
       </c>
       <c r="G258" t="n">
-        <v>0.04729179161706315</v>
+        <v>0.04729179161714917</v>
       </c>
     </row>
     <row r="259">
@@ -7774,13 +7774,13 @@
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0009099390955873472</v>
+        <v>0.0009099390955879679</v>
       </c>
       <c r="F259" t="n">
-        <v>0.9284003786158861</v>
+        <v>0.9284003786156749</v>
       </c>
       <c r="G259" t="n">
-        <v>0.07068968228860185</v>
+        <v>0.07068968228873043</v>
       </c>
     </row>
     <row r="260">
@@ -7797,13 +7797,13 @@
         <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0.001215211977255849</v>
+        <v>0.001215211977256401</v>
       </c>
       <c r="F260" t="n">
-        <v>0.9290414803671645</v>
+        <v>0.9290414803669533</v>
       </c>
       <c r="G260" t="n">
-        <v>0.06974330765562498</v>
+        <v>0.06974330765573598</v>
       </c>
     </row>
     <row r="261">
@@ -7820,13 +7820,13 @@
         <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>0.002493556201551263</v>
+        <v>0.002493556201554665</v>
       </c>
       <c r="F261" t="n">
-        <v>0.9398607858818373</v>
+        <v>0.9398607858816236</v>
       </c>
       <c r="G261" t="n">
-        <v>0.05764565791671944</v>
+        <v>0.0576456579168243</v>
       </c>
     </row>
     <row r="262">
@@ -7843,13 +7843,13 @@
         <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>0.006047136563024241</v>
+        <v>0.006047136563028366</v>
       </c>
       <c r="F262" t="n">
-        <v>0.9310399633092322</v>
+        <v>0.9310399633090205</v>
       </c>
       <c r="G262" t="n">
-        <v>0.06291290012784259</v>
+        <v>0.06291290012792841</v>
       </c>
     </row>
     <row r="263">
@@ -7866,13 +7866,13 @@
         <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>0.01328719848854273</v>
+        <v>0.01328719848855481</v>
       </c>
       <c r="F263" t="n">
-        <v>0.892718008347174</v>
+        <v>0.892718008346971</v>
       </c>
       <c r="G263" t="n">
-        <v>0.09399479316437062</v>
+        <v>0.09399479316452022</v>
       </c>
     </row>
     <row r="264">
@@ -7889,13 +7889,13 @@
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.02294388550428853</v>
+        <v>0.02294388550430939</v>
       </c>
       <c r="F264" t="n">
-        <v>0.8717400066772275</v>
+        <v>0.8717400066770292</v>
       </c>
       <c r="G264" t="n">
-        <v>0.1053161078184338</v>
+        <v>0.1053161078185774</v>
       </c>
     </row>
     <row r="265">
@@ -7912,13 +7912,13 @@
         <v>1</v>
       </c>
       <c r="E265" t="n">
-        <v>0.007034671760653137</v>
+        <v>0.007034671760659535</v>
       </c>
       <c r="F265" t="n">
-        <v>0.6104465205469605</v>
+        <v>0.6104465205465441</v>
       </c>
       <c r="G265" t="n">
-        <v>0.3825188076924035</v>
+        <v>0.3825188076927514</v>
       </c>
     </row>
     <row r="266">
@@ -7935,13 +7935,13 @@
         <v>1</v>
       </c>
       <c r="E266" t="n">
-        <v>0.004129526923187583</v>
+        <v>0.004129526923191339</v>
       </c>
       <c r="F266" t="n">
-        <v>0.450555616349201</v>
+        <v>0.4505556163488937</v>
       </c>
       <c r="G266" t="n">
-        <v>0.5453148567276294</v>
+        <v>0.5453148567278774</v>
       </c>
     </row>
     <row r="267">
@@ -7958,13 +7958,13 @@
         <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.003042648610526333</v>
+        <v>0.003042648610529792</v>
       </c>
       <c r="F267" t="n">
-        <v>0.3787928910231779</v>
+        <v>0.3787928910228334</v>
       </c>
       <c r="G267" t="n">
-        <v>0.6181644603662527</v>
+        <v>0.6181644603666744</v>
       </c>
     </row>
     <row r="268">
@@ -7981,13 +7981,13 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0.002379959010378814</v>
+        <v>0.002379959010380437</v>
       </c>
       <c r="F268" t="n">
-        <v>0.351173057954162</v>
+        <v>0.3511730579537627</v>
       </c>
       <c r="G268" t="n">
-        <v>0.6464469830354496</v>
+        <v>0.6464469830357435</v>
       </c>
     </row>
     <row r="269">
@@ -8004,13 +8004,13 @@
         <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0.001154966202304901</v>
+        <v>0.001154966202305426</v>
       </c>
       <c r="F269" t="n">
-        <v>0.3245352473929674</v>
+        <v>0.3245352473925984</v>
       </c>
       <c r="G269" t="n">
-        <v>0.6743097864047817</v>
+        <v>0.6743097864050883</v>
       </c>
     </row>
     <row r="270">
@@ -8027,13 +8027,13 @@
         <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>0.0004756925322993621</v>
+        <v>0.0004756925322992539</v>
       </c>
       <c r="F270" t="n">
-        <v>0.3146179072714573</v>
+        <v>0.3146179072710996</v>
       </c>
       <c r="G270" t="n">
-        <v>0.6849064001961859</v>
+        <v>0.6849064001964974</v>
       </c>
     </row>
     <row r="271">
@@ -8050,13 +8050,13 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0004010972341792911</v>
+        <v>0.0004010972341791999</v>
       </c>
       <c r="F271" t="n">
-        <v>0.3255151668211784</v>
+        <v>0.3255151668208824</v>
       </c>
       <c r="G271" t="n">
-        <v>0.674083735944542</v>
+        <v>0.6740837359448485</v>
       </c>
     </row>
     <row r="272">
@@ -8073,13 +8073,13 @@
         <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0008541785591027124</v>
+        <v>0.0008541785591023239</v>
       </c>
       <c r="F272" t="n">
-        <v>0.3674056211566823</v>
+        <v>0.3674056211563482</v>
       </c>
       <c r="G272" t="n">
-        <v>0.6317402002842282</v>
+        <v>0.6317402002845154</v>
       </c>
     </row>
     <row r="273">
@@ -8096,13 +8096,13 @@
         <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>0.002227050740191786</v>
+        <v>0.00222705074019128</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4498591625136149</v>
+        <v>0.4498591625132057</v>
       </c>
       <c r="G273" t="n">
-        <v>0.5479137867462756</v>
+        <v>0.5479137867466494</v>
       </c>
     </row>
     <row r="274">
@@ -8122,10 +8122,10 @@
         <v>0.008701928838461225</v>
       </c>
       <c r="F274" t="n">
-        <v>0.6036076671135688</v>
+        <v>0.6036076671134316</v>
       </c>
       <c r="G274" t="n">
-        <v>0.3876904040478664</v>
+        <v>0.387690404048219</v>
       </c>
     </row>
     <row r="275">
@@ -8145,10 +8145,10 @@
         <v>0.01460703595154151</v>
       </c>
       <c r="F275" t="n">
-        <v>0.7380009373051706</v>
+        <v>0.7380009373050027</v>
       </c>
       <c r="G275" t="n">
-        <v>0.2473920267433022</v>
+        <v>0.2473920267435272</v>
       </c>
     </row>
     <row r="276">
@@ -8165,13 +8165,13 @@
         <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>0.03675107255196518</v>
+        <v>0.03675107255197354</v>
       </c>
       <c r="F276" t="n">
-        <v>0.7840165358067219</v>
+        <v>0.7840165358065436</v>
       </c>
       <c r="G276" t="n">
-        <v>0.1792323916413459</v>
+        <v>0.1792323916415497</v>
       </c>
     </row>
     <row r="277">
@@ -8188,13 +8188,13 @@
         <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>0.125071133264672</v>
+        <v>0.1250711332647289</v>
       </c>
       <c r="F277" t="n">
         <v>0.7583892816390788</v>
       </c>
       <c r="G277" t="n">
-        <v>0.1165395850961436</v>
+        <v>0.1165395850962761</v>
       </c>
     </row>
     <row r="278">
@@ -8217,7 +8217,7 @@
         <v>0.4719725554612338</v>
       </c>
       <c r="G278" t="n">
-        <v>0.0662514043078723</v>
+        <v>0.06625140430793254</v>
       </c>
     </row>
     <row r="279">
@@ -8234,13 +8234,13 @@
         <v>0</v>
       </c>
       <c r="E279" t="n">
-        <v>0.5687384948117937</v>
+        <v>0.5687384948116644</v>
       </c>
       <c r="F279" t="n">
-        <v>0.4163514138596144</v>
+        <v>0.416351413859709</v>
       </c>
       <c r="G279" t="n">
-        <v>0.01491009132860199</v>
+        <v>0.01491009132860877</v>
       </c>
     </row>
     <row r="280">
@@ -8257,13 +8257,13 @@
         <v>0</v>
       </c>
       <c r="E280" t="n">
-        <v>0.8472161609633757</v>
+        <v>0.8472161609631831</v>
       </c>
       <c r="F280" t="n">
-        <v>0.1518249440785525</v>
+        <v>0.1518249440785871</v>
       </c>
       <c r="G280" t="n">
-        <v>0.0009588949581186044</v>
+        <v>0.0009588949581194764</v>
       </c>
     </row>
     <row r="281">
@@ -8283,10 +8283,10 @@
         <v>0.9954575976562137</v>
       </c>
       <c r="F281" t="n">
-        <v>0.003965587939660443</v>
+        <v>0.003965587939661344</v>
       </c>
       <c r="G281" t="n">
-        <v>0.0005768144040967405</v>
+        <v>0.0005768144040975274</v>
       </c>
     </row>
     <row r="282">
@@ -8306,10 +8306,10 @@
         <v>0.9954087896287294</v>
       </c>
       <c r="F282" t="n">
-        <v>0.004143136498231405</v>
+        <v>0.004143136498226696</v>
       </c>
       <c r="G282" t="n">
-        <v>0.0004480738730452158</v>
+        <v>0.000448073873045929</v>
       </c>
     </row>
     <row r="283">
@@ -8329,10 +8329,10 @@
         <v>0.9982336369896193</v>
       </c>
       <c r="F283" t="n">
-        <v>0.001761266293517815</v>
+        <v>0.001761266293517014</v>
       </c>
       <c r="G283" t="n">
-        <v>5.096716900561273e-06</v>
+        <v>5.096716900567067e-06</v>
       </c>
     </row>
     <row r="284">
@@ -8352,10 +8352,10 @@
         <v>0.9995648922684061</v>
       </c>
       <c r="F284" t="n">
-        <v>0.0004278051246940699</v>
+        <v>0.0004278051246934862</v>
       </c>
       <c r="G284" t="n">
-        <v>7.302606960058063e-06</v>
+        <v>7.302606960059723e-06</v>
       </c>
     </row>
     <row r="285">
@@ -8375,10 +8375,10 @@
         <v>0.9999543545677207</v>
       </c>
       <c r="F285" t="n">
-        <v>2.512862261056175e-05</v>
+        <v>2.512862261048176e-05</v>
       </c>
       <c r="G285" t="n">
-        <v>2.051680970063248e-05</v>
+        <v>2.051680970062781e-05</v>
       </c>
     </row>
     <row r="286">
@@ -8398,10 +8398,10 @@
         <v>0.9999279781775831</v>
       </c>
       <c r="F286" t="n">
-        <v>2.12498329015573e-06</v>
+        <v>2.124983290138336e-06</v>
       </c>
       <c r="G286" t="n">
-        <v>6.989683909218049e-05</v>
+        <v>6.98968390921646e-05</v>
       </c>
     </row>
     <row r="287">
@@ -8421,10 +8421,10 @@
         <v>0.9579961074166568</v>
       </c>
       <c r="F287" t="n">
-        <v>0.001574545937496653</v>
+        <v>0.00157454593747374</v>
       </c>
       <c r="G287" t="n">
-        <v>0.04042934664580483</v>
+        <v>0.04042934664581402</v>
       </c>
     </row>
     <row r="288">
@@ -8444,10 +8444,10 @@
         <v>0.8794665562436333</v>
       </c>
       <c r="F288" t="n">
-        <v>0.001698570422840409</v>
+        <v>0.001698570422820326</v>
       </c>
       <c r="G288" t="n">
-        <v>0.1188348733336124</v>
+        <v>0.1188348733335853</v>
       </c>
     </row>
     <row r="289">
@@ -8467,10 +8467,10 @@
         <v>0.8256807819556757</v>
       </c>
       <c r="F289" t="n">
-        <v>0.00320501627153662</v>
+        <v>0.003205016271516216</v>
       </c>
       <c r="G289" t="n">
-        <v>0.1711142017728915</v>
+        <v>0.1711142017728526</v>
       </c>
     </row>
     <row r="290">
@@ -8490,7 +8490,7 @@
         <v>0.5318788831177715</v>
       </c>
       <c r="F290" t="n">
-        <v>0.001975856413413416</v>
+        <v>0.001975856413400836</v>
       </c>
       <c r="G290" t="n">
         <v>0.466145260468784</v>
@@ -8513,7 +8513,7 @@
         <v>0.3498413493748427</v>
       </c>
       <c r="F291" t="n">
-        <v>0.001201188260745799</v>
+        <v>0.00120118826074061</v>
       </c>
       <c r="G291" t="n">
         <v>0.6489574623643102</v>
@@ -8536,7 +8536,7 @@
         <v>0.1397248803046435</v>
       </c>
       <c r="F292" t="n">
-        <v>0.003396155742282754</v>
+        <v>0.003396155742275032</v>
       </c>
       <c r="G292" t="n">
         <v>0.856878963953104</v>
@@ -8556,10 +8556,10 @@
         <v>2</v>
       </c>
       <c r="E293" t="n">
-        <v>0.0270780189348951</v>
+        <v>0.02707801893488894</v>
       </c>
       <c r="F293" t="n">
-        <v>0.00614418720957467</v>
+        <v>0.006144187209569081</v>
       </c>
       <c r="G293" t="n">
         <v>0.9667777938555213</v>
@@ -8585,7 +8585,7 @@
         <v>0.009266434133047207</v>
       </c>
       <c r="G294" t="n">
-        <v>0.980464930688674</v>
+        <v>0.9804649306886741</v>
       </c>
     </row>
     <row r="295">
@@ -8602,10 +8602,10 @@
         <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>0.006903686073516307</v>
+        <v>0.006903686073517877</v>
       </c>
       <c r="F295" t="n">
-        <v>0.01977439630204692</v>
+        <v>0.01977439630206041</v>
       </c>
       <c r="G295" t="n">
         <v>0.9733219176244187</v>
@@ -8625,10 +8625,10 @@
         <v>2</v>
       </c>
       <c r="E296" t="n">
-        <v>0.005054477876485431</v>
+        <v>0.005054477876488879</v>
       </c>
       <c r="F296" t="n">
-        <v>0.01552548237925243</v>
+        <v>0.01552548237926302</v>
       </c>
       <c r="G296" t="n">
         <v>0.9794200397443328</v>
@@ -8648,10 +8648,10 @@
         <v>2</v>
       </c>
       <c r="E297" t="n">
-        <v>0.006848023690149732</v>
+        <v>0.006848023690152847</v>
       </c>
       <c r="F297" t="n">
-        <v>0.01217310181891135</v>
+        <v>0.01217310181892242</v>
       </c>
       <c r="G297" t="n">
         <v>0.9809788744909909</v>
@@ -8671,10 +8671,10 @@
         <v>2</v>
       </c>
       <c r="E298" t="n">
-        <v>0.01216172687536318</v>
+        <v>0.01216172687537701</v>
       </c>
       <c r="F298" t="n">
-        <v>0.00395917821630082</v>
+        <v>0.003959178216306221</v>
       </c>
       <c r="G298" t="n">
         <v>0.9838790949082266</v>
@@ -8694,10 +8694,10 @@
         <v>2</v>
       </c>
       <c r="E299" t="n">
-        <v>0.01075408067572924</v>
+        <v>0.01075408067574636</v>
       </c>
       <c r="F299" t="n">
-        <v>0.003452303636838099</v>
+        <v>0.003452303636842808</v>
       </c>
       <c r="G299" t="n">
         <v>0.9857936156874455</v>
@@ -8717,13 +8717,13 @@
         <v>2</v>
       </c>
       <c r="E300" t="n">
-        <v>0.01025329057083034</v>
+        <v>0.010253290570842</v>
       </c>
       <c r="F300" t="n">
-        <v>0.003722734180195301</v>
+        <v>0.003722734180198686</v>
       </c>
       <c r="G300" t="n">
-        <v>0.9860239752490805</v>
+        <v>0.9860239752488562</v>
       </c>
     </row>
     <row r="301">
@@ -8740,10 +8740,10 @@
         <v>2</v>
       </c>
       <c r="E301" t="n">
-        <v>0.004929404182900206</v>
+        <v>0.004929404182906932</v>
       </c>
       <c r="F301" t="n">
-        <v>0.004698803674439189</v>
+        <v>0.004698803674444531</v>
       </c>
       <c r="G301" t="n">
         <v>0.990371792142645</v>
@@ -8757,16 +8757,16 @@
         <v>0.01197547558860675</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.00629541553440531</v>
+        <v>-0.006295415534405311</v>
       </c>
       <c r="D302" t="n">
         <v>2</v>
       </c>
       <c r="E302" t="n">
-        <v>0.001158576873249041</v>
+        <v>0.001158576873250885</v>
       </c>
       <c r="F302" t="n">
-        <v>0.006684974851243918</v>
+        <v>0.006684974851249998</v>
       </c>
       <c r="G302" t="n">
         <v>0.9921564482755154</v>
@@ -8786,10 +8786,10 @@
         <v>2</v>
       </c>
       <c r="E303" t="n">
-        <v>0.0007037271758814567</v>
+        <v>0.0007037271758824167</v>
       </c>
       <c r="F303" t="n">
-        <v>0.01048408747719789</v>
+        <v>0.01048408747720742</v>
       </c>
       <c r="G303" t="n">
         <v>0.9888121853468613</v>
@@ -8809,10 +8809,10 @@
         <v>2</v>
       </c>
       <c r="E304" t="n">
-        <v>0.0004686859163247318</v>
+        <v>0.0004686859163254778</v>
       </c>
       <c r="F304" t="n">
-        <v>0.007205538878779252</v>
+        <v>0.007205538878785805</v>
       </c>
       <c r="G304" t="n">
         <v>0.9923257752049046</v>
@@ -8832,10 +8832,10 @@
         <v>2</v>
       </c>
       <c r="E305" t="n">
-        <v>0.00110130943505633</v>
+        <v>0.001101309435058083</v>
       </c>
       <c r="F305" t="n">
-        <v>0.003849649113012768</v>
+        <v>0.003849649113017144</v>
       </c>
       <c r="G305" t="n">
         <v>0.995049041451919</v>
@@ -8855,10 +8855,10 @@
         <v>2</v>
       </c>
       <c r="E306" t="n">
-        <v>0.0002610436727022488</v>
+        <v>0.0002610436727026643</v>
       </c>
       <c r="F306" t="n">
-        <v>0.006079546018371523</v>
+        <v>0.006079546018378435</v>
       </c>
       <c r="G306" t="n">
         <v>0.9936594103088838</v>
@@ -8878,10 +8878,10 @@
         <v>2</v>
       </c>
       <c r="E307" t="n">
-        <v>7.28419494656397e-05</v>
+        <v>7.284194946575563e-05</v>
       </c>
       <c r="F307" t="n">
-        <v>0.008071030513632539</v>
+        <v>0.008071030513639879</v>
       </c>
       <c r="G307" t="n">
         <v>0.9918561275369651</v>
@@ -8901,10 +8901,10 @@
         <v>2</v>
       </c>
       <c r="E308" t="n">
-        <v>7.278627052375432e-05</v>
+        <v>7.278627052385362e-05</v>
       </c>
       <c r="F308" t="n">
-        <v>0.0110094801243754</v>
+        <v>0.01100948012438792</v>
       </c>
       <c r="G308" t="n">
         <v>0.9889177336050435</v>
@@ -8924,10 +8924,10 @@
         <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>5.430666658363243e-05</v>
+        <v>5.430666658370652e-05</v>
       </c>
       <c r="F309" t="n">
-        <v>0.01037711368200053</v>
+        <v>0.01037711368200761</v>
       </c>
       <c r="G309" t="n">
         <v>0.9895685796514629</v>
@@ -8947,10 +8947,10 @@
         <v>2</v>
       </c>
       <c r="E310" t="n">
-        <v>7.477268361505712e-05</v>
+        <v>7.477268361517613e-05</v>
       </c>
       <c r="F310" t="n">
-        <v>0.01098728827515936</v>
+        <v>0.01098728827516935</v>
       </c>
       <c r="G310" t="n">
         <v>0.9889379390412395</v>
@@ -8970,10 +8970,10 @@
         <v>2</v>
       </c>
       <c r="E311" t="n">
-        <v>0.0002394367728143367</v>
+        <v>0.0002394367728147178</v>
       </c>
       <c r="F311" t="n">
-        <v>0.01261409402828332</v>
+        <v>0.01261409402828906</v>
       </c>
       <c r="G311" t="n">
         <v>0.9871464691989918</v>
@@ -8993,10 +8993,10 @@
         <v>2</v>
       </c>
       <c r="E312" t="n">
-        <v>0.0001149424872569291</v>
+        <v>0.0001149424872570336</v>
       </c>
       <c r="F312" t="n">
-        <v>0.03995741546014041</v>
+        <v>0.03995741546013133</v>
       </c>
       <c r="G312" t="n">
         <v>0.9599276420525443</v>
@@ -9016,10 +9016,10 @@
         <v>2</v>
       </c>
       <c r="E313" t="n">
-        <v>0.0002062766802212787</v>
+        <v>0.0002062766802213256</v>
       </c>
       <c r="F313" t="n">
-        <v>0.07105736231880097</v>
+        <v>0.07105736231883328</v>
       </c>
       <c r="G313" t="n">
         <v>0.9287363610009178</v>
@@ -9039,13 +9039,13 @@
         <v>2</v>
       </c>
       <c r="E314" t="n">
-        <v>0.0001681090017122095</v>
+        <v>0.000168109001712286</v>
       </c>
       <c r="F314" t="n">
-        <v>0.1762869156807886</v>
+        <v>0.1762869156808687</v>
       </c>
       <c r="G314" t="n">
-        <v>0.823544975317554</v>
+        <v>0.8235449753173667</v>
       </c>
     </row>
     <row r="315">
@@ -9062,13 +9062,13 @@
         <v>2</v>
       </c>
       <c r="E315" t="n">
-        <v>0.000676660221544728</v>
+        <v>0.0006766602215451896</v>
       </c>
       <c r="F315" t="n">
-        <v>0.3775551150453645</v>
+        <v>0.3775551150455362</v>
       </c>
       <c r="G315" t="n">
-        <v>0.6217682247331442</v>
+        <v>0.6217682247328614</v>
       </c>
     </row>
     <row r="316">
@@ -9079,19 +9079,19 @@
         <v>-0.06138811628823403</v>
       </c>
       <c r="C316" t="n">
-        <v>0.0003471971954322065</v>
+        <v>0.0003471971954322061</v>
       </c>
       <c r="D316" t="n">
         <v>2</v>
       </c>
       <c r="E316" t="n">
-        <v>0.003468598939416755</v>
+        <v>0.003468598939420698</v>
       </c>
       <c r="F316" t="n">
-        <v>0.4417070115271828</v>
+        <v>0.4417070115273837</v>
       </c>
       <c r="G316" t="n">
-        <v>0.5548243895334273</v>
+        <v>0.5548243895331749</v>
       </c>
     </row>
     <row r="317">
@@ -9108,13 +9108,13 @@
         <v>2</v>
       </c>
       <c r="E317" t="n">
-        <v>0.002718806504952829</v>
+        <v>0.00271880650495592</v>
       </c>
       <c r="F317" t="n">
-        <v>0.3683642086408389</v>
+        <v>0.3683642086410064</v>
       </c>
       <c r="G317" t="n">
-        <v>0.6289169848541432</v>
+        <v>0.6289169848540002</v>
       </c>
     </row>
     <row r="318">
@@ -9131,10 +9131,10 @@
         <v>2</v>
       </c>
       <c r="E318" t="n">
-        <v>0.00361032607962941</v>
+        <v>0.003610326079634336</v>
       </c>
       <c r="F318" t="n">
-        <v>0.2968942559044358</v>
+        <v>0.2968942559045708</v>
       </c>
       <c r="G318" t="n">
         <v>0.6994954180158782</v>
@@ -9154,10 +9154,10 @@
         <v>2</v>
       </c>
       <c r="E319" t="n">
-        <v>0.002355659647770646</v>
+        <v>0.002355659647772252</v>
       </c>
       <c r="F319" t="n">
-        <v>0.1732365529424264</v>
+        <v>0.1732365529425052</v>
       </c>
       <c r="G319" t="n">
         <v>0.8244077874097283</v>
@@ -9177,10 +9177,10 @@
         <v>2</v>
       </c>
       <c r="E320" t="n">
-        <v>0.000975400144855151</v>
+        <v>0.0009754001448558163</v>
       </c>
       <c r="F320" t="n">
-        <v>0.1001156589792487</v>
+        <v>0.1001156589792943</v>
       </c>
       <c r="G320" t="n">
         <v>0.8989089408759328</v>
@@ -9200,10 +9200,10 @@
         <v>2</v>
       </c>
       <c r="E321" t="n">
-        <v>0.0005105081708546638</v>
+        <v>0.000510508170855012</v>
       </c>
       <c r="F321" t="n">
-        <v>0.06836052008738101</v>
+        <v>0.06836052008739656</v>
       </c>
       <c r="G321" t="n">
         <v>0.9311289717417022</v>
@@ -9223,7 +9223,7 @@
         <v>2</v>
       </c>
       <c r="E322" t="n">
-        <v>0.0002630084110341777</v>
+        <v>0.0002630084110344767</v>
       </c>
       <c r="F322" t="n">
         <v>0.05054010674653931</v>
@@ -9246,10 +9246,10 @@
         <v>2</v>
       </c>
       <c r="E323" t="n">
-        <v>0.0001486191619278083</v>
+        <v>0.0001486191619279097</v>
       </c>
       <c r="F323" t="n">
-        <v>0.04330154241346904</v>
+        <v>0.0433015424134592</v>
       </c>
       <c r="G323" t="n">
         <v>0.9565498384246721</v>
@@ -9269,10 +9269,10 @@
         <v>2</v>
       </c>
       <c r="E324" t="n">
-        <v>0.000134237261987019</v>
+        <v>0.0001342372619871105</v>
       </c>
       <c r="F324" t="n">
-        <v>0.04502953564701941</v>
+        <v>0.04502953564700917</v>
       </c>
       <c r="G324" t="n">
         <v>0.9548362270910029</v>
@@ -9283,7 +9283,7 @@
         <v>46022</v>
       </c>
       <c r="B325" t="n">
-        <v>-0.002782332919957094</v>
+        <v>-0.002782332919957095</v>
       </c>
       <c r="C325" t="n">
         <v>-0.009222956945157942</v>
@@ -9292,7 +9292,7 @@
         <v>2</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0001773903056239738</v>
+        <v>0.0001773903056241351</v>
       </c>
       <c r="F325" t="n">
         <v>0.04878851821988994</v>
@@ -9315,7 +9315,7 @@
         <v>2</v>
       </c>
       <c r="E326" t="n">
-        <v>0.0003610358152158893</v>
+        <v>0.0003610358152162176</v>
       </c>
       <c r="F326" t="n">
         <v>0.0665193853485828</v>

--- a/hmm_regime_results_monthly.xlsx
+++ b/hmm_regime_results_monthly.xlsx
@@ -494,7 +494,7 @@
         <v>-2.915567756089579</v>
       </c>
       <c r="F2" t="n">
-        <v>7.948783884085062</v>
+        <v>7.94878388408506</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5231463948411231</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.948783884085062</v>
+        <v>7.94878388408506</v>
       </c>
       <c r="C10" t="n">
         <v>5.037871764325111</v>
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8913880599458675</v>
+        <v>0.8913880599458304</v>
       </c>
       <c r="C22" t="n">
-        <v>0.003881296848967605</v>
+        <v>0.003881296849025836</v>
       </c>
       <c r="D22" t="n">
-        <v>0.104730643205165</v>
+        <v>0.1047306432051439</v>
       </c>
     </row>
     <row r="23">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0166161876612837</v>
+        <v>0.01661618766126477</v>
       </c>
       <c r="C23" t="n">
-        <v>0.940673540716451</v>
+        <v>0.9406735407165159</v>
       </c>
       <c r="D23" t="n">
-        <v>0.04271027162226536</v>
+        <v>0.04271027162221921</v>
       </c>
     </row>
     <row r="24">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.485350796670785e-08</v>
+        <v>4.485350796600124e-08</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04973435529075192</v>
+        <v>0.04973435529074275</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9502655998557402</v>
+        <v>0.9502655998557493</v>
       </c>
     </row>
     <row r="27">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8913880599458675</v>
+        <v>0.8913880599458304</v>
       </c>
       <c r="C28" t="n">
-        <v>9.207090854850735</v>
+        <v>9.207090854847591</v>
       </c>
     </row>
     <row r="29">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.940673540716451</v>
+        <v>0.9406735407165159</v>
       </c>
       <c r="C29" t="n">
-        <v>16.85588541902579</v>
+        <v>16.85588541904421</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9502655998557402</v>
+        <v>0.9502655998557493</v>
       </c>
       <c r="C30" t="n">
-        <v>20.10680730237816</v>
+        <v>20.10680730238184</v>
       </c>
     </row>
     <row r="33">
@@ -1161,7 +1161,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>1445.788715168305</v>
+        <v>1445.788715168303</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -1187,7 +1187,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>1444.53547122711</v>
+        <v>1444.535471227111</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -1213,7 +1213,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1444.534569317037</v>
+        <v>1444.534569317038</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1265,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>1442.925003415813</v>
+        <v>1442.925003415807</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -1291,7 +1291,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>1440.262283589452</v>
+        <v>1440.262283589453</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -1317,7 +1317,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>1440.224319393109</v>
+        <v>1440.224319393116</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -1369,7 +1369,7 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>1439.914657167446</v>
+        <v>1439.914657167448</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -1395,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="n">
-        <v>1439.068577161559</v>
+        <v>1439.068577161563</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
@@ -1421,7 +1421,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="n">
-        <v>1438.64816039359</v>
+        <v>1438.648160393587</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
@@ -1447,7 +1447,7 @@
         <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>1438.481325457338</v>
+        <v>1438.481325457343</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -1473,7 +1473,7 @@
         <v>6</v>
       </c>
       <c r="B14" t="n">
-        <v>1438.257985253289</v>
+        <v>1438.257985253284</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
@@ -1499,7 +1499,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>1438.257974771667</v>
+        <v>1438.257974771671</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1525,7 +1525,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>1437.950053028634</v>
+        <v>1437.950053028632</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -1551,7 +1551,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="n">
-        <v>1437.549368362985</v>
+        <v>1437.549368362972</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
@@ -1577,7 +1577,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1437.51786052341</v>
+        <v>1437.517860523411</v>
       </c>
       <c r="C18" t="n">
         <v>3</v>
@@ -1629,7 +1629,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1432.264318100705</v>
+        <v>1432.264318100713</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -1655,7 +1655,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>1432.159907672288</v>
+        <v>1432.159907672292</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -1681,7 +1681,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="n">
-        <v>1429.271115507528</v>
+        <v>1429.27111550752</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -1707,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="B23" t="n">
-        <v>1429.227096908194</v>
+        <v>1429.227096908193</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -1733,7 +1733,7 @@
         <v>13</v>
       </c>
       <c r="B24" t="n">
-        <v>1428.661687114702</v>
+        <v>1428.661687114704</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -1759,7 +1759,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="n">
-        <v>1422.695318049565</v>
+        <v>1422.695318049556</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
@@ -1785,7 +1785,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="n">
-        <v>1420.959985288543</v>
+        <v>1420.959985288537</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
@@ -1860,16 +1860,16 @@
         <v>0.03746962579352606</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008686003136073352</v>
+        <v>0.0008686003136073347</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>1.822856416171981e-150</v>
+        <v>1.822856416200579e-150</v>
       </c>
       <c r="F2" t="n">
-        <v>8.797567933541798e-87</v>
+        <v>8.797567933629813e-87</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1889,10 +1889,10 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1.259713813972069e-08</v>
+        <v>1.259713813952306e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00316090685345764</v>
+        <v>0.003160906853459077</v>
       </c>
       <c r="G3" t="n">
         <v>0.9968390805494566</v>
@@ -1912,10 +1912,10 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3.537756398709743e-06</v>
+        <v>3.537756398705721e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01962311378487605</v>
+        <v>0.01962311378488497</v>
       </c>
       <c r="G4" t="n">
         <v>0.9803733484588154</v>
@@ -1935,10 +1935,10 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.959218544953181e-05</v>
+        <v>1.959218544951844e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04503615748764486</v>
+        <v>0.04503615748766535</v>
       </c>
       <c r="G5" t="n">
         <v>0.9549442503269683</v>
@@ -1958,10 +1958,10 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>7.84744196262289e-05</v>
+        <v>7.847441962621107e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08740437739243172</v>
+        <v>0.08740437739247146</v>
       </c>
       <c r="G6" t="n">
         <v>0.9125171481879744</v>
@@ -1981,13 +1981,13 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>6.161816837181579e-05</v>
+        <v>6.161816837180178e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1897170413199841</v>
+        <v>0.1897170413200703</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8102213405117272</v>
+        <v>0.8102213405115429</v>
       </c>
     </row>
     <row r="8">
@@ -2004,10 +2004,10 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001498340439795939</v>
+        <v>0.000149834043979628</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2929818593957344</v>
+        <v>0.2929818593958676</v>
       </c>
       <c r="G8" t="n">
         <v>0.7068683065602283</v>
@@ -2030,10 +2030,10 @@
         <v>0.0001186262957228101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3739390329165496</v>
+        <v>0.3739390329166346</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6259423407878051</v>
+        <v>0.6259423407876629</v>
       </c>
     </row>
     <row r="10">
@@ -2050,13 +2050,13 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0001919811178947498</v>
+        <v>0.0001919811178946188</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5209401592071969</v>
+        <v>0.5209401592073154</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4788678596750031</v>
+        <v>0.4788678596746764</v>
       </c>
     </row>
     <row r="11">
@@ -2073,13 +2073,13 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0002360692610641242</v>
+        <v>0.0002360692610640169</v>
       </c>
       <c r="F11" t="n">
-        <v>0.577289631843341</v>
+        <v>0.5772896318436036</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4224742988955056</v>
+        <v>0.4224742988953135</v>
       </c>
     </row>
     <row r="12">
@@ -2096,13 +2096,13 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000247444227557482</v>
+        <v>0.0002474442275575945</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6221819812200822</v>
+        <v>0.6221819812203651</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3775705745522567</v>
+        <v>0.377570574552085</v>
       </c>
     </row>
     <row r="13">
@@ -2122,10 +2122,10 @@
         <v>0.0006394049830491329</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7364270562108969</v>
+        <v>0.7364270562112317</v>
       </c>
       <c r="G13" t="n">
-        <v>0.262933538805998</v>
+        <v>0.2629335388057588</v>
       </c>
     </row>
     <row r="14">
@@ -2142,13 +2142,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001942487279819148</v>
+        <v>0.001942487279818264</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8222438154345801</v>
+        <v>0.8222438154347671</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1758136972856756</v>
+        <v>0.1758136972855157</v>
       </c>
     </row>
     <row r="15">
@@ -2165,13 +2165,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002295234634897844</v>
+        <v>0.002295234634897322</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8466025836446517</v>
+        <v>0.8466025836448442</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1511021817204858</v>
+        <v>0.151102181720314</v>
       </c>
     </row>
     <row r="16">
@@ -2188,13 +2188,13 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0.004557637629761906</v>
+        <v>0.004557637629760871</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8539614955688367</v>
+        <v>0.8539614955690308</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1414808668013194</v>
+        <v>0.1414808668011264</v>
       </c>
     </row>
     <row r="17">
@@ -2211,13 +2211,13 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002725585641747992</v>
+        <v>0.002725585641748611</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8572385664423727</v>
+        <v>0.8572385664425676</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1400358479158901</v>
+        <v>0.1400358479157309</v>
       </c>
     </row>
     <row r="18">
@@ -2234,13 +2234,13 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00113035993303486</v>
+        <v>0.001130359933035374</v>
       </c>
       <c r="F18" t="n">
-        <v>0.865920749296071</v>
+        <v>0.8659207492962679</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1329488907707972</v>
+        <v>0.1329488907706763</v>
       </c>
     </row>
     <row r="19">
@@ -2257,13 +2257,13 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000349602852841993</v>
+        <v>0.0003496028528428674</v>
       </c>
       <c r="F19" t="n">
         <v>0.8741493193380432</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1255010778091448</v>
+        <v>0.1255010778090021</v>
       </c>
     </row>
     <row r="20">
@@ -2274,19 +2274,19 @@
         <v>-0.02054671670874412</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002590752718941235</v>
+        <v>0.002590752718941236</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0002069109463842847</v>
+        <v>0.0002069109463851315</v>
       </c>
       <c r="F20" t="n">
         <v>0.9063597636783753</v>
       </c>
       <c r="G20" t="n">
-        <v>0.09343332537525939</v>
+        <v>0.09343332537513192</v>
       </c>
     </row>
     <row r="21">
@@ -2303,13 +2303,13 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0001880533632507184</v>
+        <v>0.0001880533632518729</v>
       </c>
       <c r="F21" t="n">
         <v>0.9365742602204776</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06323768641634914</v>
+        <v>0.06323768641627725</v>
       </c>
     </row>
     <row r="22">
@@ -2326,13 +2326,13 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0003117600593350977</v>
+        <v>0.0003117600593365154</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9857752032191869</v>
+        <v>0.985775203219411</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01391303672137754</v>
+        <v>0.01391303672136173</v>
       </c>
     </row>
     <row r="23">
@@ -2340,22 +2340,22 @@
         <v>36830</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.009817373019298678</v>
+        <v>-0.00981737301929868</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0035647155073691</v>
+        <v>0.003564715507369099</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0002075823107723243</v>
+        <v>0.0002075823107732683</v>
       </c>
       <c r="F23" t="n">
         <v>0.9892334094044088</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01055900828492359</v>
+        <v>0.01055900828491158</v>
       </c>
     </row>
     <row r="24">
@@ -2372,13 +2372,13 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0004453946856024954</v>
+        <v>0.0004453946856033056</v>
       </c>
       <c r="F24" t="n">
         <v>0.9995014964064887</v>
       </c>
       <c r="G24" t="n">
-        <v>5.310890788491587e-05</v>
+        <v>5.310890788480719e-05</v>
       </c>
     </row>
     <row r="25">
@@ -2395,13 +2395,13 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0002429273396503306</v>
+        <v>0.0002429273396511591</v>
       </c>
       <c r="F25" t="n">
         <v>0.9928105476125912</v>
       </c>
       <c r="G25" t="n">
-        <v>0.006946525047718592</v>
+        <v>0.006946525047705957</v>
       </c>
     </row>
     <row r="26">
@@ -2418,13 +2418,13 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0002069530559144696</v>
+        <v>0.000206953055915693</v>
       </c>
       <c r="F26" t="n">
         <v>0.9907670660047121</v>
       </c>
       <c r="G26" t="n">
-        <v>0.009025980939367632</v>
+        <v>0.009025980939353266</v>
       </c>
     </row>
     <row r="27">
@@ -2441,13 +2441,13 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0005679546789582613</v>
+        <v>0.0005679546789608441</v>
       </c>
       <c r="F27" t="n">
         <v>0.9994206330535904</v>
       </c>
       <c r="G27" t="n">
-        <v>1.141226755972827e-05</v>
+        <v>1.14122675597101e-05</v>
       </c>
     </row>
     <row r="28">
@@ -2464,13 +2464,13 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0007356825648444112</v>
+        <v>0.0007356825648460839</v>
       </c>
       <c r="F28" t="n">
         <v>0.9990375339585039</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0002267834765824724</v>
+        <v>0.0002267834765820084</v>
       </c>
     </row>
     <row r="29">
@@ -2487,13 +2487,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0006203654303591393</v>
+        <v>0.0006203654303598445</v>
       </c>
       <c r="F29" t="n">
         <v>0.9966970421611322</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002682592408580394</v>
+        <v>0.002682592408574905</v>
       </c>
     </row>
     <row r="30">
@@ -2501,7 +2501,7 @@
         <v>37042</v>
       </c>
       <c r="B30" t="n">
-        <v>0.003486086443238612</v>
+        <v>0.003486086443238613</v>
       </c>
       <c r="C30" t="n">
         <v>-0.001127279284296733</v>
@@ -2510,13 +2510,13 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0001662068938531783</v>
+        <v>0.0001662068938540098</v>
       </c>
       <c r="F30" t="n">
         <v>0.9887183401811207</v>
       </c>
       <c r="G30" t="n">
-        <v>0.01111545292500545</v>
+        <v>0.01111545292498776</v>
       </c>
     </row>
     <row r="31">
@@ -2533,13 +2533,13 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0001433310502059089</v>
+        <v>0.0001433310502068214</v>
       </c>
       <c r="F31" t="n">
         <v>0.9920117498550518</v>
       </c>
       <c r="G31" t="n">
-        <v>0.007844919094689347</v>
+        <v>0.007844919094678646</v>
       </c>
     </row>
     <row r="32">
@@ -2556,13 +2556,13 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0002030807673143626</v>
+        <v>0.0002030807673153785</v>
       </c>
       <c r="F32" t="n">
         <v>0.996334852025199</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003462067207516756</v>
+        <v>0.003462067207512033</v>
       </c>
     </row>
     <row r="33">
@@ -2573,19 +2573,19 @@
         <v>-0.06774638797380172</v>
       </c>
       <c r="C33" t="n">
-        <v>0.009266260116781109</v>
+        <v>0.009266260116781111</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000420467367296761</v>
+        <v>0.0004204673672980039</v>
       </c>
       <c r="F33" t="n">
         <v>0.9994305090413039</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0001490235914578153</v>
+        <v>0.000149023591457612</v>
       </c>
     </row>
     <row r="34">
@@ -2602,13 +2602,13 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0007959096809923748</v>
+        <v>0.0007959096809930987</v>
       </c>
       <c r="F34" t="n">
         <v>0.9991938468181716</v>
       </c>
       <c r="G34" t="n">
-        <v>1.02435008429788e-05</v>
+        <v>1.024350084296249e-05</v>
       </c>
     </row>
     <row r="35">
@@ -2625,13 +2625,13 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000724906549547163</v>
+        <v>0.0007249065495478223</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9908807180470592</v>
+        <v>0.9908807180472845</v>
       </c>
       <c r="G35" t="n">
-        <v>0.008394375403287919</v>
+        <v>0.008394375403276469</v>
       </c>
     </row>
     <row r="36">
@@ -2648,13 +2648,13 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001169424903658783</v>
+        <v>0.001169424903658517</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9908674145379285</v>
+        <v>0.9908674145381537</v>
       </c>
       <c r="G36" t="n">
-        <v>0.007963160558307678</v>
+        <v>0.007963160558295003</v>
       </c>
     </row>
     <row r="37">
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0003864318786529968</v>
+        <v>0.0003864318786538755</v>
       </c>
       <c r="F37" t="n">
         <v>0.9719999899199364</v>
       </c>
       <c r="G37" t="n">
-        <v>0.02761357820150987</v>
+        <v>0.02761357820146592</v>
       </c>
     </row>
     <row r="38">
@@ -2688,19 +2688,19 @@
         <v>-0.01610219756674967</v>
       </c>
       <c r="C38" t="n">
-        <v>0.004747939606516225</v>
+        <v>0.004747939606516224</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0001901227167822536</v>
+        <v>0.0001901227167829885</v>
       </c>
       <c r="F38" t="n">
         <v>0.9753257338128171</v>
       </c>
       <c r="G38" t="n">
-        <v>0.02448414347042927</v>
+        <v>0.02448414347038473</v>
       </c>
     </row>
     <row r="39">
@@ -2711,19 +2711,19 @@
         <v>-0.02076850133664727</v>
       </c>
       <c r="C39" t="n">
-        <v>0.009776868601837064</v>
+        <v>0.009776868601837062</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0001676923132392347</v>
+        <v>0.0001676923132401498</v>
       </c>
       <c r="F39" t="n">
         <v>0.9820607035237493</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01777160416300663</v>
+        <v>0.01777160416297026</v>
       </c>
     </row>
     <row r="40">
@@ -2740,13 +2740,13 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0002160032545386798</v>
+        <v>0.0002160032545405461</v>
       </c>
       <c r="F40" t="n">
         <v>0.9862237227976317</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01356027394783309</v>
+        <v>0.01356027394780843</v>
       </c>
     </row>
     <row r="41">
@@ -2763,13 +2763,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0002242131731174277</v>
+        <v>0.0002242131731186003</v>
       </c>
       <c r="F41" t="n">
         <v>0.9995385541367663</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0002372326900971362</v>
+        <v>0.0002372326900967586</v>
       </c>
     </row>
     <row r="42">
@@ -2786,13 +2786,13 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0001181696894536702</v>
+        <v>0.0001181696894546913</v>
       </c>
       <c r="F42" t="n">
         <v>0.997206979157766</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00267485115279467</v>
+        <v>0.002674851152790413</v>
       </c>
     </row>
     <row r="43">
@@ -2809,13 +2809,13 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.000225695409946299</v>
+        <v>0.0002256954099476846</v>
       </c>
       <c r="F43" t="n">
         <v>0.9997453833587034</v>
       </c>
       <c r="G43" t="n">
-        <v>2.892123143017789e-05</v>
+        <v>2.892123143013185e-05</v>
       </c>
     </row>
     <row r="44">
@@ -2832,13 +2832,13 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0004007836928993396</v>
+        <v>0.0004007836929007066</v>
       </c>
       <c r="F44" t="n">
         <v>0.9995955381425373</v>
       </c>
       <c r="G44" t="n">
-        <v>3.67816448909442e-06</v>
+        <v>3.678164489087729e-06</v>
       </c>
     </row>
     <row r="45">
@@ -2855,13 +2855,13 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0005075021855656009</v>
+        <v>0.0005075021855669857</v>
       </c>
       <c r="F45" t="n">
         <v>0.9968949392540493</v>
       </c>
       <c r="G45" t="n">
-        <v>0.002597558560481441</v>
+        <v>0.002597558560477307</v>
       </c>
     </row>
     <row r="46">
@@ -2878,13 +2878,13 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001083075889444239</v>
+        <v>0.001083075889445471</v>
       </c>
       <c r="F46" t="n">
         <v>0.998916911550545</v>
       </c>
       <c r="G46" t="n">
-        <v>1.255991436726283e-08</v>
+        <v>1.255991436723998e-08</v>
       </c>
     </row>
     <row r="47">
@@ -2901,13 +2901,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.001595509783150559</v>
+        <v>0.001595509783149833</v>
       </c>
       <c r="F47" t="n">
         <v>0.997880247504392</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0005242427123944719</v>
+        <v>0.0005242427123935184</v>
       </c>
     </row>
     <row r="48">
@@ -2924,13 +2924,13 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.003017741773369032</v>
+        <v>0.003017741773366974</v>
       </c>
       <c r="F48" t="n">
         <v>0.9950110253267763</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001971232899922277</v>
+        <v>0.001971232899918691</v>
       </c>
     </row>
     <row r="49">
@@ -2947,13 +2947,13 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.006826110004241347</v>
+        <v>0.006826110004238242</v>
       </c>
       <c r="F49" t="n">
         <v>0.9922443878970157</v>
       </c>
       <c r="G49" t="n">
-        <v>0.000929502098791497</v>
+        <v>0.0009295020987910743</v>
       </c>
     </row>
     <row r="50">
@@ -2970,13 +2970,13 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.007850477436820181</v>
+        <v>0.007850477436818395</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8952287305636051</v>
+        <v>0.8952287305638087</v>
       </c>
       <c r="G50" t="n">
-        <v>0.09692079199947749</v>
+        <v>0.09692079199945546</v>
       </c>
     </row>
     <row r="51">
@@ -2996,7 +2996,7 @@
         <v>0.009379703439753879</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8136755580098508</v>
+        <v>0.8136755580100358</v>
       </c>
       <c r="G51" t="n">
         <v>0.1769447385503123</v>
@@ -3016,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01133135654800186</v>
+        <v>0.01133135654799671</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6311495940887666</v>
+        <v>0.6311495940889101</v>
       </c>
       <c r="G52" t="n">
-        <v>0.3575190493632643</v>
+        <v>0.3575190493631017</v>
       </c>
     </row>
     <row r="53">
@@ -3039,13 +3039,13 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02815157532975769</v>
+        <v>0.02815157532974489</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5362158530196282</v>
+        <v>0.5362158530198721</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4356325716506289</v>
+        <v>0.4356325716504308</v>
       </c>
     </row>
     <row r="54">
@@ -3062,13 +3062,13 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.05633345547527899</v>
+        <v>0.05633345547525338</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2838655465832618</v>
+        <v>0.2838655465833264</v>
       </c>
       <c r="G54" t="n">
-        <v>0.6598009979415639</v>
+        <v>0.6598009979414138</v>
       </c>
     </row>
     <row r="55">
@@ -3085,13 +3085,13 @@
         <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>0.05222996375842068</v>
+        <v>0.05222996375839693</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1900099107409634</v>
+        <v>0.1900099107410498</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7577601255006898</v>
+        <v>0.7577601255005175</v>
       </c>
     </row>
     <row r="56">
@@ -3108,10 +3108,10 @@
         <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.08002269929062289</v>
+        <v>0.0800226992905865</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1269950125450969</v>
+        <v>0.1269950125452124</v>
       </c>
       <c r="G56" t="n">
         <v>0.7929822881642004</v>
@@ -3131,10 +3131,10 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.03848972361844997</v>
+        <v>0.03848972361844122</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1367795073915603</v>
+        <v>0.1367795073916847</v>
       </c>
       <c r="G57" t="n">
         <v>0.8247307689899669</v>
@@ -3157,7 +3157,7 @@
         <v>0.03420215763927174</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1669107757865086</v>
+        <v>0.1669107757866224</v>
       </c>
       <c r="G58" t="n">
         <v>0.798887066574156</v>
@@ -3177,13 +3177,13 @@
         <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0163177053466984</v>
+        <v>0.01631770534669098</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1427697024768737</v>
+        <v>0.1427697024769386</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8409125921764847</v>
+        <v>0.8409125921762935</v>
       </c>
     </row>
     <row r="60">
@@ -3200,10 +3200,10 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.003116370791479455</v>
+        <v>0.003116370791478038</v>
       </c>
       <c r="F60" t="n">
-        <v>0.09191269003814262</v>
+        <v>0.09191269003818442</v>
       </c>
       <c r="G60" t="n">
         <v>0.904970939170335</v>
@@ -3223,10 +3223,10 @@
         <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>0.001154566421946223</v>
+        <v>0.001154566421945697</v>
       </c>
       <c r="F61" t="n">
-        <v>0.06600239375755189</v>
+        <v>0.06600239375758191</v>
       </c>
       <c r="G61" t="n">
         <v>0.9328430398205673</v>
@@ -3246,10 +3246,10 @@
         <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0004634110981765776</v>
+        <v>0.0004634110981764723</v>
       </c>
       <c r="F62" t="n">
-        <v>0.04785668680768669</v>
+        <v>0.04785668680770846</v>
       </c>
       <c r="G62" t="n">
         <v>0.951679902094124</v>
@@ -3269,10 +3269,10 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0004378122152622204</v>
+        <v>0.0004378122152621208</v>
       </c>
       <c r="F63" t="n">
-        <v>0.03923728536502403</v>
+        <v>0.03923728536504187</v>
       </c>
       <c r="G63" t="n">
         <v>0.9603249024196072</v>
@@ -3292,10 +3292,10 @@
         <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>0.000849440255420292</v>
+        <v>0.0008494402554200988</v>
       </c>
       <c r="F64" t="n">
-        <v>0.03440388320382422</v>
+        <v>0.03440388320383204</v>
       </c>
       <c r="G64" t="n">
         <v>0.9647466765406718</v>
@@ -3315,7 +3315,7 @@
         <v>2</v>
       </c>
       <c r="E65" t="n">
-        <v>0.002270359050297261</v>
+        <v>0.002270359050295196</v>
       </c>
       <c r="F65" t="n">
         <v>0.01514910623887766</v>
@@ -3338,10 +3338,10 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>0.000399953410149255</v>
+        <v>0.0003999534101489822</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0237061849013998</v>
+        <v>0.02370618490139441</v>
       </c>
       <c r="G66" t="n">
         <v>0.9758938616884832</v>
@@ -3361,10 +3361,10 @@
         <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>0.0001590070326827564</v>
+        <v>0.0001590070326826841</v>
       </c>
       <c r="F67" t="n">
-        <v>0.04358238344179919</v>
+        <v>0.04358238344178928</v>
       </c>
       <c r="G67" t="n">
         <v>0.9562586095255035</v>
@@ -3384,13 +3384,13 @@
         <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0003126936304015251</v>
+        <v>0.0003126936304013118</v>
       </c>
       <c r="F68" t="n">
-        <v>0.08027550358477892</v>
+        <v>0.08027550358474242</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9194118027847571</v>
+        <v>0.9194118027849661</v>
       </c>
     </row>
     <row r="69">
@@ -3407,10 +3407,10 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>0.0005866301535283365</v>
+        <v>0.0005866301535276696</v>
       </c>
       <c r="F69" t="n">
-        <v>0.06963444697292337</v>
+        <v>0.06963444697287588</v>
       </c>
       <c r="G69" t="n">
         <v>0.9297789228735759</v>
@@ -3430,10 +3430,10 @@
         <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>0.0002735152650395013</v>
+        <v>0.0002735152650391903</v>
       </c>
       <c r="F70" t="n">
-        <v>0.05182059570297379</v>
+        <v>0.05182059570293845</v>
       </c>
       <c r="G70" t="n">
         <v>0.9479058890320518</v>
@@ -3453,10 +3453,10 @@
         <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>0.0001880067083518329</v>
+        <v>0.0001880067083516192</v>
       </c>
       <c r="F71" t="n">
-        <v>0.04492055561937627</v>
+        <v>0.04492055561935585</v>
       </c>
       <c r="G71" t="n">
         <v>0.9548914376722588</v>
@@ -3476,10 +3476,10 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>0.0002285527171575529</v>
+        <v>0.0002285527171572931</v>
       </c>
       <c r="F72" t="n">
-        <v>0.04495060004457819</v>
+        <v>0.04495060004454753</v>
       </c>
       <c r="G72" t="n">
         <v>0.9548208472383591</v>
@@ -3499,10 +3499,10 @@
         <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.000161521709865122</v>
+        <v>0.0001615217098649384</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04656155349527858</v>
+        <v>0.04656155349524682</v>
       </c>
       <c r="G73" t="n">
         <v>0.9532769247948882</v>
@@ -3522,10 +3522,10 @@
         <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0002434250776524402</v>
+        <v>0.0002434250776521081</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0572997538701957</v>
+        <v>0.05729975387015662</v>
       </c>
       <c r="G74" t="n">
         <v>0.9424568210522137</v>
@@ -3545,10 +3545,10 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0002280982390909816</v>
+        <v>0.0002280982390907222</v>
       </c>
       <c r="F75" t="n">
-        <v>0.05135453457975575</v>
+        <v>0.05135453457972072</v>
       </c>
       <c r="G75" t="n">
         <v>0.9484173671810797</v>
@@ -3568,13 +3568,13 @@
         <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0003112691598928663</v>
+        <v>0.0003112691598925125</v>
       </c>
       <c r="F76" t="n">
-        <v>0.059129268258857</v>
+        <v>0.05912926825880322</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9405594625811589</v>
+        <v>0.9405594625813728</v>
       </c>
     </row>
     <row r="77">
@@ -3591,10 +3591,10 @@
         <v>2</v>
       </c>
       <c r="E77" t="n">
-        <v>0.0005327940183322704</v>
+        <v>0.000532794018331907</v>
       </c>
       <c r="F77" t="n">
-        <v>0.07202065304140452</v>
+        <v>0.07202065304133902</v>
       </c>
       <c r="G77" t="n">
         <v>0.9274465529403543</v>
@@ -3614,10 +3614,10 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>0.0003734538863895329</v>
+        <v>0.0003734538863891083</v>
       </c>
       <c r="F78" t="n">
-        <v>0.04946530200369863</v>
+        <v>0.04946530200366489</v>
       </c>
       <c r="G78" t="n">
         <v>0.9501612441098342</v>
@@ -3637,10 +3637,10 @@
         <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>0.0002684889465542745</v>
+        <v>0.0002684889465540302</v>
       </c>
       <c r="F79" t="n">
-        <v>0.039254615995027</v>
+        <v>0.03925461599500022</v>
       </c>
       <c r="G79" t="n">
         <v>0.9604768950585163</v>
@@ -3660,10 +3660,10 @@
         <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>0.0003470574367912832</v>
+        <v>0.0003470574367908097</v>
       </c>
       <c r="F80" t="n">
-        <v>0.03301709838231251</v>
+        <v>0.03301709838228248</v>
       </c>
       <c r="G80" t="n">
         <v>0.9666358441808554</v>
@@ -3683,13 +3683,13 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>0.0003674544446837866</v>
+        <v>0.0003674544446835359</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0301637819038029</v>
+        <v>0.03016378190378233</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9694687636514074</v>
+        <v>0.9694687636516279</v>
       </c>
     </row>
     <row r="82">
@@ -3706,10 +3706,10 @@
         <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0003175060573310536</v>
+        <v>0.0003175060573306205</v>
       </c>
       <c r="F82" t="n">
-        <v>0.01463097604983156</v>
+        <v>0.01463097604981492</v>
       </c>
       <c r="G82" t="n">
         <v>0.9850515178929012</v>
@@ -3729,10 +3729,10 @@
         <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0002052570695719403</v>
+        <v>0.0002052570695717536</v>
       </c>
       <c r="F83" t="n">
-        <v>0.01078204156973577</v>
+        <v>0.01078204156973087</v>
       </c>
       <c r="G83" t="n">
         <v>0.989012701360676</v>
@@ -3746,19 +3746,19 @@
         <v>0.03402946422756281</v>
       </c>
       <c r="C84" t="n">
-        <v>0.002718764958117402</v>
+        <v>0.002718764958117403</v>
       </c>
       <c r="D84" t="n">
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.338343421535754e-05</v>
+        <v>7.33834342152908e-05</v>
       </c>
       <c r="F84" t="n">
-        <v>0.009942528195589094</v>
+        <v>0.009942528195582312</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9899840883700823</v>
+        <v>0.9899840883703075</v>
       </c>
     </row>
     <row r="85">
@@ -3766,7 +3766,7 @@
         <v>38717</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.002845288954795244</v>
+        <v>-0.002845288954795243</v>
       </c>
       <c r="C85" t="n">
         <v>0.008921207357914518</v>
@@ -3775,10 +3775,10 @@
         <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>6.054050768528933e-05</v>
+        <v>6.05405076852205e-05</v>
       </c>
       <c r="F85" t="n">
-        <v>0.01007011903372469</v>
+        <v>0.01007011903371553</v>
       </c>
       <c r="G85" t="n">
         <v>0.9898693404585539</v>
@@ -3798,10 +3798,10 @@
         <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>5.112121543196245e-05</v>
+        <v>5.112121543190434e-05</v>
       </c>
       <c r="F86" t="n">
-        <v>0.007451542137423973</v>
+        <v>0.007451542137417196</v>
       </c>
       <c r="G86" t="n">
         <v>0.9924973366470728</v>
@@ -3812,7 +3812,7 @@
         <v>38776</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.0006837315003157397</v>
+        <v>-0.0006837315003157393</v>
       </c>
       <c r="C87" t="n">
         <v>-0.004183623699470881</v>
@@ -3821,10 +3821,10 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.217567072921763e-05</v>
+        <v>4.217567072917927e-05</v>
       </c>
       <c r="F87" t="n">
-        <v>0.006511497980406748</v>
+        <v>0.006511497980400825</v>
       </c>
       <c r="G87" t="n">
         <v>0.9934463263489609</v>
@@ -3844,10 +3844,10 @@
         <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>4.200775022740476e-05</v>
+        <v>4.200775022736656e-05</v>
       </c>
       <c r="F88" t="n">
-        <v>0.006016317020633139</v>
+        <v>0.006016317020629035</v>
       </c>
       <c r="G88" t="n">
         <v>0.9939416752291599</v>
@@ -3867,10 +3867,10 @@
         <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>3.347517909708263e-05</v>
+        <v>3.347517909703697e-05</v>
       </c>
       <c r="F89" t="n">
-        <v>0.008682292704935148</v>
+        <v>0.008682292704927251</v>
       </c>
       <c r="G89" t="n">
         <v>0.9912842321159735</v>
@@ -3890,10 +3890,10 @@
         <v>2</v>
       </c>
       <c r="E90" t="n">
-        <v>8.147250234889547e-05</v>
+        <v>8.147250234880284e-05</v>
       </c>
       <c r="F90" t="n">
-        <v>0.01518046741608775</v>
+        <v>0.0151804674160774</v>
       </c>
       <c r="G90" t="n">
         <v>0.9847380600816205</v>
@@ -3913,10 +3913,10 @@
         <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>6.944528871041661e-05</v>
+        <v>6.944528871030608e-05</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01414853305242749</v>
+        <v>0.01414853305242106</v>
       </c>
       <c r="G91" t="n">
         <v>0.9857820216589451</v>
@@ -3936,10 +3936,10 @@
         <v>2</v>
       </c>
       <c r="E92" t="n">
-        <v>6.873570725176719e-05</v>
+        <v>6.873570725167342e-05</v>
       </c>
       <c r="F92" t="n">
-        <v>0.01444152728410838</v>
+        <v>0.01444152728410509</v>
       </c>
       <c r="G92" t="n">
         <v>0.9854897370087236</v>
@@ -3959,10 +3959,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="n">
-        <v>6.481273624296417e-05</v>
+        <v>6.481273624287575e-05</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0131137888135972</v>
+        <v>0.01311378881359422</v>
       </c>
       <c r="G93" t="n">
         <v>0.9868213984501445</v>
@@ -3982,10 +3982,10 @@
         <v>2</v>
       </c>
       <c r="E94" t="n">
-        <v>4.487622184388718e-05</v>
+        <v>4.487622184382595e-05</v>
       </c>
       <c r="F94" t="n">
-        <v>0.01324693798793671</v>
+        <v>0.01324693798793972</v>
       </c>
       <c r="G94" t="n">
         <v>0.98670818579021</v>
@@ -4005,10 +4005,10 @@
         <v>2</v>
       </c>
       <c r="E95" t="n">
-        <v>3.490086810882186e-05</v>
+        <v>3.490086810877424e-05</v>
       </c>
       <c r="F95" t="n">
-        <v>0.01586035083739551</v>
+        <v>0.01586035083739911</v>
       </c>
       <c r="G95" t="n">
         <v>0.9841047482943938</v>
@@ -4028,10 +4028,10 @@
         <v>2</v>
       </c>
       <c r="E96" t="n">
-        <v>3.336635722766436e-05</v>
+        <v>3.336635722761884e-05</v>
       </c>
       <c r="F96" t="n">
-        <v>0.02221022835625462</v>
+        <v>0.02221022835625967</v>
       </c>
       <c r="G96" t="n">
         <v>0.9777564052865667</v>
@@ -4051,10 +4051,10 @@
         <v>2</v>
       </c>
       <c r="E97" t="n">
-        <v>3.873397624176807e-05</v>
+        <v>3.873397624171522e-05</v>
       </c>
       <c r="F97" t="n">
-        <v>0.03334479755682131</v>
+        <v>0.03334479755683648</v>
       </c>
       <c r="G97" t="n">
         <v>0.9666164684668817</v>
@@ -4074,10 +4074,10 @@
         <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>3.320119512165016e-05</v>
+        <v>3.320119512161997e-05</v>
       </c>
       <c r="F98" t="n">
-        <v>0.06671169733389666</v>
+        <v>0.06671169733394217</v>
       </c>
       <c r="G98" t="n">
         <v>0.9332551014709517</v>
@@ -4097,10 +4097,10 @@
         <v>2</v>
       </c>
       <c r="E99" t="n">
-        <v>9.433121755098405e-05</v>
+        <v>9.433121755087681e-05</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1420345790488552</v>
+        <v>0.1420345790489521</v>
       </c>
       <c r="G99" t="n">
         <v>0.8578710897335572</v>
@@ -4120,10 +4120,10 @@
         <v>2</v>
       </c>
       <c r="E100" t="n">
-        <v>9.759249602272502e-05</v>
+        <v>9.759249602268064e-05</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1568679733296016</v>
+        <v>0.1568679733297086</v>
       </c>
       <c r="G100" t="n">
         <v>0.8430344341742932</v>
@@ -4143,13 +4143,13 @@
         <v>2</v>
       </c>
       <c r="E101" t="n">
-        <v>7.374526757548237e-05</v>
+        <v>7.374526757544882e-05</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2036206909347302</v>
+        <v>0.2036206909347765</v>
       </c>
       <c r="G101" t="n">
-        <v>0.7963055637977384</v>
+        <v>0.7963055637975573</v>
       </c>
     </row>
     <row r="102">
@@ -4166,13 +4166,13 @@
         <v>2</v>
       </c>
       <c r="E102" t="n">
-        <v>8.578995958738073e-05</v>
+        <v>8.578995958747827e-05</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2837960682262126</v>
+        <v>0.2837960682264062</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7161181418140963</v>
+        <v>0.7161181418139334</v>
       </c>
     </row>
     <row r="103">
@@ -4189,10 +4189,10 @@
         <v>2</v>
       </c>
       <c r="E103" t="n">
-        <v>0.0001163318465505681</v>
+        <v>0.0001163318465507532</v>
       </c>
       <c r="F103" t="n">
-        <v>0.4310030848267231</v>
+        <v>0.4310030848269191</v>
       </c>
       <c r="G103" t="n">
         <v>0.5688805833266366</v>
@@ -4212,13 +4212,13 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>0.0002314674056028435</v>
+        <v>0.0002314674056027908</v>
       </c>
       <c r="F104" t="n">
-        <v>0.6538582021286306</v>
+        <v>0.6538582021287792</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3459103304658031</v>
+        <v>0.3459103304657245</v>
       </c>
     </row>
     <row r="105">
@@ -4235,13 +4235,13 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>0.0001914969443318649</v>
+        <v>0.0001914969443320391</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6782276467881257</v>
+        <v>0.67822764678828</v>
       </c>
       <c r="G105" t="n">
-        <v>0.3215808562674543</v>
+        <v>0.3215808562673812</v>
       </c>
     </row>
     <row r="106">
@@ -4252,19 +4252,19 @@
         <v>0.03352305135437444</v>
       </c>
       <c r="C106" t="n">
-        <v>0.000268536980876533</v>
+        <v>0.0002685369808765334</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>9.24106508762352e-05</v>
+        <v>9.241065087655036e-05</v>
       </c>
       <c r="F106" t="n">
         <v>0.7241205273204205</v>
       </c>
       <c r="G106" t="n">
-        <v>0.2757870620287147</v>
+        <v>0.2757870620285893</v>
       </c>
     </row>
     <row r="107">
@@ -4275,19 +4275,19 @@
         <v>0.01258704390080084</v>
       </c>
       <c r="C107" t="n">
-        <v>0.007736157572576452</v>
+        <v>0.007736157572576453</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>8.083393455703094e-05</v>
+        <v>8.083393455745367e-05</v>
       </c>
       <c r="F107" t="n">
         <v>0.8187939120643354</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1811252540011823</v>
+        <v>0.1811252540011411</v>
       </c>
     </row>
     <row r="108">
@@ -4304,13 +4304,13 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0.000238169405696395</v>
+        <v>0.0002381694056969906</v>
       </c>
       <c r="F108" t="n">
         <v>0.9899687943612464</v>
       </c>
       <c r="G108" t="n">
-        <v>0.009793036233119379</v>
+        <v>0.009793036233114926</v>
       </c>
     </row>
     <row r="109">
@@ -4327,13 +4327,13 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0.0003390540806023143</v>
+        <v>0.0003390540806027769</v>
       </c>
       <c r="F109" t="n">
         <v>0.9901086962884903</v>
       </c>
       <c r="G109" t="n">
-        <v>0.009552249630826336</v>
+        <v>0.009552249630817649</v>
       </c>
     </row>
     <row r="110">
@@ -4356,7 +4356,7 @@
         <v>0.9989634638242093</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0001238115859102774</v>
+        <v>0.0001238115859101085</v>
       </c>
     </row>
     <row r="111">
@@ -4373,13 +4373,13 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.001946721075703751</v>
+        <v>0.001946721075702423</v>
       </c>
       <c r="F111" t="n">
         <v>0.9949610293869986</v>
       </c>
       <c r="G111" t="n">
-        <v>0.003092249537394432</v>
+        <v>0.003092249537388808</v>
       </c>
     </row>
     <row r="112">
@@ -4387,7 +4387,7 @@
         <v>39538</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.006027409667488031</v>
+        <v>-0.006027409667488032</v>
       </c>
       <c r="C112" t="n">
         <v>0.01148223471221401</v>
@@ -4396,13 +4396,13 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.004914560130935905</v>
+        <v>0.004914560130931436</v>
       </c>
       <c r="F112" t="n">
         <v>0.9829763630399002</v>
       </c>
       <c r="G112" t="n">
-        <v>0.01210907682918074</v>
+        <v>0.01210907682915872</v>
       </c>
     </row>
     <row r="113">
@@ -4419,13 +4419,13 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0.01597283157933009</v>
+        <v>0.01597283157931556</v>
       </c>
       <c r="F113" t="n">
         <v>0.967742662219268</v>
       </c>
       <c r="G113" t="n">
-        <v>0.01628450620145329</v>
+        <v>0.01628450620141996</v>
       </c>
     </row>
     <row r="114">
@@ -4442,13 +4442,13 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.03560421281644818</v>
+        <v>0.03560421281643199</v>
       </c>
       <c r="F114" t="n">
         <v>0.9465445275731845</v>
       </c>
       <c r="G114" t="n">
-        <v>0.01785125961030812</v>
+        <v>0.01785125961027971</v>
       </c>
     </row>
     <row r="115">
@@ -4465,13 +4465,13 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.07234872626911502</v>
+        <v>0.07234872626908213</v>
       </c>
       <c r="F115" t="n">
         <v>0.9274960445444421</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0001552291864890288</v>
+        <v>0.0001552291864887112</v>
       </c>
     </row>
     <row r="116">
@@ -4494,7 +4494,7 @@
         <v>0.8817247608724171</v>
       </c>
       <c r="G116" t="n">
-        <v>0.003432051686411816</v>
+        <v>0.003432051686407915</v>
       </c>
     </row>
     <row r="117">
@@ -4511,13 +4511,13 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.2642861858189324</v>
+        <v>0.2642861858189925</v>
       </c>
       <c r="F117" t="n">
         <v>0.7335444547775177</v>
       </c>
       <c r="G117" t="n">
-        <v>0.002169359403483066</v>
+        <v>0.002169359403480107</v>
       </c>
     </row>
     <row r="118">
@@ -4537,10 +4537,10 @@
         <v>0.7387523984646643</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2612475583590057</v>
+        <v>0.2612475583590651</v>
       </c>
       <c r="G118" t="n">
-        <v>4.31762403827882e-08</v>
+        <v>4.317624038269985e-08</v>
       </c>
     </row>
     <row r="119">
@@ -4560,10 +4560,10 @@
         <v>0.9993694513225264</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0006305486774361289</v>
+        <v>0.0006305486774362723</v>
       </c>
       <c r="G119" t="n">
-        <v>1.985820390022753e-14</v>
+        <v>1.985820390017787e-14</v>
       </c>
     </row>
     <row r="120">
@@ -4583,10 +4583,10 @@
         <v>0.9999403000017146</v>
       </c>
       <c r="F120" t="n">
-        <v>5.969997153504796e-05</v>
+        <v>5.969997153515655e-05</v>
       </c>
       <c r="G120" t="n">
-        <v>2.667173862016113e-11</v>
+        <v>2.667173862011868e-11</v>
       </c>
     </row>
     <row r="121">
@@ -4606,10 +4606,10 @@
         <v>0.9999609998753437</v>
       </c>
       <c r="F121" t="n">
-        <v>3.545334226289516e-05</v>
+        <v>3.545334226323373e-05</v>
       </c>
       <c r="G121" t="n">
-        <v>3.546782455714678e-06</v>
+        <v>3.546782455717097e-06</v>
       </c>
     </row>
     <row r="122">
@@ -4629,7 +4629,7 @@
         <v>0.9999774584970017</v>
       </c>
       <c r="F122" t="n">
-        <v>1.163094793593814e-05</v>
+        <v>1.16309479360783e-05</v>
       </c>
       <c r="G122" t="n">
         <v>1.091055512998737e-05</v>
@@ -4652,10 +4652,10 @@
         <v>0.9990833684993177</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0009074276637083875</v>
+        <v>0.0009074276637222113</v>
       </c>
       <c r="G123" t="n">
-        <v>9.203837017271855e-06</v>
+        <v>9.203837017267671e-06</v>
       </c>
     </row>
     <row r="124">
@@ -4672,13 +4672,13 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>0.9739857401599193</v>
+        <v>0.973985740159698</v>
       </c>
       <c r="F124" t="n">
-        <v>0.006103319443178156</v>
+        <v>0.00610331944327391</v>
       </c>
       <c r="G124" t="n">
-        <v>0.01991094039693238</v>
+        <v>0.01991094039692333</v>
       </c>
     </row>
     <row r="125">
@@ -4695,13 +4695,13 @@
         <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>0.919663084647654</v>
+        <v>0.9196630846470267</v>
       </c>
       <c r="F125" t="n">
-        <v>0.04611387445067102</v>
+        <v>0.04611387445119527</v>
       </c>
       <c r="G125" t="n">
-        <v>0.03422304090177875</v>
+        <v>0.03422304090173984</v>
       </c>
     </row>
     <row r="126">
@@ -4718,13 +4718,13 @@
         <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>0.4116300158922167</v>
+        <v>0.4116300158919359</v>
       </c>
       <c r="F126" t="n">
-        <v>0.05875442650209126</v>
+        <v>0.05875442650282601</v>
       </c>
       <c r="G126" t="n">
-        <v>0.5296155576057058</v>
+        <v>0.5296155576052241</v>
       </c>
     </row>
     <row r="127">
@@ -4741,13 +4741,13 @@
         <v>2</v>
       </c>
       <c r="E127" t="n">
-        <v>0.09235225465844524</v>
+        <v>0.09235225465836124</v>
       </c>
       <c r="F127" t="n">
-        <v>0.07024944235467982</v>
+        <v>0.07024944235544651</v>
       </c>
       <c r="G127" t="n">
-        <v>0.837398302986895</v>
+        <v>0.8373983029861334</v>
       </c>
     </row>
     <row r="128">
@@ -4764,13 +4764,13 @@
         <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>0.04301740534554987</v>
+        <v>0.04301740534551075</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1032750194591522</v>
+        <v>0.1032750194599036</v>
       </c>
       <c r="G128" t="n">
-        <v>0.8537075751952319</v>
+        <v>0.8537075751946496</v>
       </c>
     </row>
     <row r="129">
@@ -4787,13 +4787,13 @@
         <v>2</v>
       </c>
       <c r="E129" t="n">
-        <v>0.007765109055730014</v>
+        <v>0.007765109055728248</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1169947810602295</v>
+        <v>0.1169947810609477</v>
       </c>
       <c r="G129" t="n">
-        <v>0.8752401098839508</v>
+        <v>0.8752401098833539</v>
       </c>
     </row>
     <row r="130">
@@ -4810,13 +4810,13 @@
         <v>2</v>
       </c>
       <c r="E130" t="n">
-        <v>0.001805822860954864</v>
+        <v>0.001805822860955685</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1512038408078418</v>
+        <v>0.1512038408085294</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8469903363311923</v>
+        <v>0.8469903363306145</v>
       </c>
     </row>
     <row r="131">
@@ -4833,13 +4833,13 @@
         <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0008392059112783273</v>
+        <v>0.0008392059112800446</v>
       </c>
       <c r="F131" t="n">
-        <v>0.2187208260521316</v>
+        <v>0.2187208260528278</v>
       </c>
       <c r="G131" t="n">
-        <v>0.7804399680365219</v>
+        <v>0.7804399680359896</v>
       </c>
     </row>
     <row r="132">
@@ -4856,13 +4856,13 @@
         <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0007704626757630698</v>
+        <v>0.0007704626757656975</v>
       </c>
       <c r="F132" t="n">
-        <v>0.2898120182909146</v>
+        <v>0.2898120182914418</v>
       </c>
       <c r="G132" t="n">
-        <v>0.7094175190333251</v>
+        <v>0.7094175190326799</v>
       </c>
     </row>
     <row r="133">
@@ -4879,13 +4879,13 @@
         <v>2</v>
       </c>
       <c r="E133" t="n">
-        <v>0.0009356527624009996</v>
+        <v>0.0009356527624046163</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4093906889585759</v>
+        <v>0.4093906889590413</v>
       </c>
       <c r="G133" t="n">
-        <v>0.5896736582790313</v>
+        <v>0.589673658278495</v>
       </c>
     </row>
     <row r="134">
@@ -4902,13 +4902,13 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0006657545730707381</v>
+        <v>0.0006657545730722518</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7639679319206382</v>
+        <v>0.7639679319209856</v>
       </c>
       <c r="G134" t="n">
-        <v>0.235366313506263</v>
+        <v>0.2353663135060489</v>
       </c>
     </row>
     <row r="135">
@@ -4925,13 +4925,13 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>0.0001763242327643477</v>
+        <v>0.0001763242327650293</v>
       </c>
       <c r="F135" t="n">
-        <v>0.7957679276243933</v>
+        <v>0.7957679276247552</v>
       </c>
       <c r="G135" t="n">
-        <v>0.204055748142767</v>
+        <v>0.204055748142535</v>
       </c>
     </row>
     <row r="136">
@@ -4948,13 +4948,13 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>0.0001431538352578251</v>
+        <v>0.0001431538352583785</v>
       </c>
       <c r="F136" t="n">
-        <v>0.871023046657066</v>
+        <v>0.871023046657264</v>
       </c>
       <c r="G136" t="n">
-        <v>0.1288337995076743</v>
+        <v>0.1288337995074986</v>
       </c>
     </row>
     <row r="137">
@@ -4971,13 +4971,13 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>0.0001201865720968959</v>
+        <v>0.0001201865720976337</v>
       </c>
       <c r="F137" t="n">
-        <v>0.9175160503548431</v>
+        <v>0.9175160503550517</v>
       </c>
       <c r="G137" t="n">
-        <v>0.08236376307304184</v>
+        <v>0.08236376307294821</v>
       </c>
     </row>
     <row r="138">
@@ -4994,13 +4994,13 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.0002796555890137566</v>
+        <v>0.0002796555890146468</v>
       </c>
       <c r="F138" t="n">
         <v>0.9996598340855976</v>
       </c>
       <c r="G138" t="n">
-        <v>6.051032545954254e-05</v>
+        <v>6.051032545944624e-05</v>
       </c>
     </row>
     <row r="139">
@@ -5017,13 +5017,13 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>0.0005613858572600458</v>
+        <v>0.0005613858572604287</v>
       </c>
       <c r="F139" t="n">
         <v>0.9993666958741541</v>
       </c>
       <c r="G139" t="n">
-        <v>7.191826848976679e-05</v>
+        <v>7.191826848965233e-05</v>
       </c>
     </row>
     <row r="140">
@@ -5040,13 +5040,13 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0.001022426105712764</v>
+        <v>0.001022426105712299</v>
       </c>
       <c r="F140" t="n">
         <v>0.9962937742367707</v>
       </c>
       <c r="G140" t="n">
-        <v>0.002683799657530443</v>
+        <v>0.002683799657525562</v>
       </c>
     </row>
     <row r="141">
@@ -5063,13 +5063,13 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.002006938224088488</v>
+        <v>0.002006938224086207</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9972257402206248</v>
+        <v>0.9972257402208516</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0007673215551736556</v>
+        <v>0.0007673215551724342</v>
       </c>
     </row>
     <row r="142">
@@ -5086,13 +5086,13 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0.003029294247149735</v>
+        <v>0.003029294247142847</v>
       </c>
       <c r="F142" t="n">
         <v>0.9818130040269581</v>
       </c>
       <c r="G142" t="n">
-        <v>0.01515770172585835</v>
+        <v>0.01515770172582388</v>
       </c>
     </row>
     <row r="143">
@@ -5109,13 +5109,13 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>0.001499387810676986</v>
+        <v>0.00149938781067494</v>
       </c>
       <c r="F143" t="n">
-        <v>0.9239553136815251</v>
+        <v>0.9239553136817352</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0745452985076876</v>
+        <v>0.074545298507552</v>
       </c>
     </row>
     <row r="144">
@@ -5132,13 +5132,13 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>0.001988843681754521</v>
+        <v>0.001988843681751356</v>
       </c>
       <c r="F144" t="n">
-        <v>0.8944339756176085</v>
+        <v>0.8944339756178118</v>
       </c>
       <c r="G144" t="n">
-        <v>0.1035771807005859</v>
+        <v>0.1035771807003739</v>
       </c>
     </row>
     <row r="145">
@@ -5155,13 +5155,13 @@
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>0.004547053445650208</v>
+        <v>0.004547053445644006</v>
       </c>
       <c r="F145" t="n">
-        <v>0.8927005956889474</v>
+        <v>0.8927005956891504</v>
       </c>
       <c r="G145" t="n">
-        <v>0.1027523508653704</v>
+        <v>0.1027523508651601</v>
       </c>
     </row>
     <row r="146">
@@ -5178,13 +5178,13 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>0.001102010176999661</v>
+        <v>0.001102010176998409</v>
       </c>
       <c r="F146" t="n">
-        <v>0.8294514528413776</v>
+        <v>0.8294514528415662</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1694465369817159</v>
+        <v>0.1694465369813306</v>
       </c>
     </row>
     <row r="147">
@@ -5201,13 +5201,13 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.000430503876006113</v>
+        <v>0.0004305038760060151</v>
       </c>
       <c r="F147" t="n">
-        <v>0.8068044824412169</v>
+        <v>0.8068044824415839</v>
       </c>
       <c r="G147" t="n">
-        <v>0.1927650136826749</v>
+        <v>0.1927650136823243</v>
       </c>
     </row>
     <row r="148">
@@ -5224,13 +5224,13 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>0.0002175038566694499</v>
+        <v>0.0002175038566698456</v>
       </c>
       <c r="F148" t="n">
-        <v>0.8097014903412009</v>
+        <v>0.809701490341569</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1900810058020441</v>
+        <v>0.1900810058017847</v>
       </c>
     </row>
     <row r="149">
@@ -5247,13 +5247,13 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0001535464227660657</v>
+        <v>0.0001535464227666243</v>
       </c>
       <c r="F149" t="n">
-        <v>0.8387409712234841</v>
+        <v>0.8387409712236749</v>
       </c>
       <c r="G149" t="n">
-        <v>0.1611054823538107</v>
+        <v>0.1611054823535176</v>
       </c>
     </row>
     <row r="150">
@@ -5270,13 +5270,13 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>0.0002024859173456859</v>
+        <v>0.0002024859173464225</v>
       </c>
       <c r="F150" t="n">
-        <v>0.9085499811576755</v>
+        <v>0.9085499811578821</v>
       </c>
       <c r="G150" t="n">
-        <v>0.09124753292491165</v>
+        <v>0.09124753292476642</v>
       </c>
     </row>
     <row r="151">
@@ -5293,13 +5293,13 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0002343090248736612</v>
+        <v>0.0002343090248745669</v>
       </c>
       <c r="F151" t="n">
         <v>0.9393696871734279</v>
       </c>
       <c r="G151" t="n">
-        <v>0.06039600380174328</v>
+        <v>0.06039600380166088</v>
       </c>
     </row>
     <row r="152">
@@ -5316,13 +5316,13 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>0.0005129843605441473</v>
+        <v>0.0005129843605451971</v>
       </c>
       <c r="F152" t="n">
         <v>0.9879771442530045</v>
       </c>
       <c r="G152" t="n">
-        <v>0.01150987138636985</v>
+        <v>0.01150987138634892</v>
       </c>
     </row>
     <row r="153">
@@ -5339,13 +5339,13 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0.001191321347593497</v>
+        <v>0.00119132134759458</v>
       </c>
       <c r="F153" t="n">
         <v>0.9987728404437504</v>
       </c>
       <c r="G153" t="n">
-        <v>3.583820863582299e-05</v>
+        <v>3.583820863576596e-05</v>
       </c>
     </row>
     <row r="154">
@@ -5362,13 +5362,13 @@
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.001755097500248252</v>
+        <v>0.001755097500246256</v>
       </c>
       <c r="F154" t="n">
         <v>0.9982229681268698</v>
       </c>
       <c r="G154" t="n">
-        <v>2.193437293946093e-05</v>
+        <v>2.193437293942103e-05</v>
       </c>
     </row>
     <row r="155">
@@ -5385,13 +5385,13 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>0.003000435583825286</v>
+        <v>0.003000435583819829</v>
       </c>
       <c r="F155" t="n">
         <v>0.9958518774941472</v>
       </c>
       <c r="G155" t="n">
-        <v>0.001147686922072784</v>
+        <v>0.001147686922070174</v>
       </c>
     </row>
     <row r="156">
@@ -5408,13 +5408,13 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>0.001315012175158424</v>
+        <v>0.00131501217515663</v>
       </c>
       <c r="F156" t="n">
         <v>0.9472365053527024</v>
       </c>
       <c r="G156" t="n">
-        <v>0.05144848247210579</v>
+        <v>0.0514484824720356</v>
       </c>
     </row>
     <row r="157">
@@ -5431,13 +5431,13 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>0.0008360367037989631</v>
+        <v>0.0008360367037982027</v>
       </c>
       <c r="F157" t="n">
-        <v>0.9111772961831263</v>
+        <v>0.9111772961833334</v>
       </c>
       <c r="G157" t="n">
-        <v>0.08798666711300684</v>
+        <v>0.0879866671128868</v>
       </c>
     </row>
     <row r="158">
@@ -5454,13 +5454,13 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>0.0006088360434983527</v>
+        <v>0.0006088360434980759</v>
       </c>
       <c r="F158" t="n">
-        <v>0.8917934652590339</v>
+        <v>0.8917934652592368</v>
       </c>
       <c r="G158" t="n">
-        <v>0.1075976986975536</v>
+        <v>0.1075976986973579</v>
       </c>
     </row>
     <row r="159">
@@ -5480,10 +5480,10 @@
         <v>0.0007476507841071669</v>
       </c>
       <c r="F159" t="n">
-        <v>0.8921620695819866</v>
+        <v>0.8921620695821895</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1070902796339001</v>
+        <v>0.1070902796337296</v>
       </c>
     </row>
     <row r="160">
@@ -5500,13 +5500,13 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>0.001740415018773629</v>
+        <v>0.001740415018773234</v>
       </c>
       <c r="F160" t="n">
-        <v>0.9040647854789656</v>
+        <v>0.9040647854791711</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0941947995021635</v>
+        <v>0.09419479950201358</v>
       </c>
     </row>
     <row r="161">
@@ -5523,13 +5523,13 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0.00468459632024034</v>
+        <v>0.004684596320239274</v>
       </c>
       <c r="F161" t="n">
         <v>0.9376492868862113</v>
       </c>
       <c r="G161" t="n">
-        <v>0.05766611679352651</v>
+        <v>0.05766611679344784</v>
       </c>
     </row>
     <row r="162">
@@ -5546,13 +5546,13 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>0.01261493426120468</v>
+        <v>0.01261493426120181</v>
       </c>
       <c r="F162" t="n">
         <v>0.9521716077233423</v>
       </c>
       <c r="G162" t="n">
-        <v>0.03521345801544545</v>
+        <v>0.03521345801542143</v>
       </c>
     </row>
     <row r="163">
@@ -5569,13 +5569,13 @@
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>0.006160232972617484</v>
+        <v>0.006160232972614682</v>
       </c>
       <c r="F163" t="n">
-        <v>0.5920809347502833</v>
+        <v>0.5920809347504179</v>
       </c>
       <c r="G163" t="n">
-        <v>0.4017588322770499</v>
+        <v>0.4017588322768672</v>
       </c>
     </row>
     <row r="164">
@@ -5592,13 +5592,13 @@
         <v>2</v>
       </c>
       <c r="E164" t="n">
-        <v>0.003496336992836639</v>
+        <v>0.003496336992835844</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3530328428638749</v>
+        <v>0.3530328428640355</v>
       </c>
       <c r="G164" t="n">
-        <v>0.643470820143304</v>
+        <v>0.6434708201431577</v>
       </c>
     </row>
     <row r="165">
@@ -5618,10 +5618,10 @@
         <v>0.001617899591861278</v>
       </c>
       <c r="F165" t="n">
-        <v>0.2047235643527095</v>
+        <v>0.2047235643528026</v>
       </c>
       <c r="G165" t="n">
-        <v>0.793658536055495</v>
+        <v>0.7936585360553144</v>
       </c>
     </row>
     <row r="166">
@@ -5638,10 +5638,10 @@
         <v>2</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0009353061740932385</v>
+        <v>0.0009353061740930259</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1314633259621266</v>
+        <v>0.1314633259622163</v>
       </c>
       <c r="G166" t="n">
         <v>0.867601367863685</v>
@@ -5664,10 +5664,10 @@
         <v>0.0009279780414227788</v>
       </c>
       <c r="F167" t="n">
-        <v>0.09584557818697671</v>
+        <v>0.0958455781870203</v>
       </c>
       <c r="G167" t="n">
-        <v>0.9032264437716611</v>
+        <v>0.9032264437714557</v>
       </c>
     </row>
     <row r="168">
@@ -5684,10 +5684,10 @@
         <v>2</v>
       </c>
       <c r="E168" t="n">
-        <v>0.0005258226758812134</v>
+        <v>0.000525822675881333</v>
       </c>
       <c r="F168" t="n">
-        <v>0.06566769794268255</v>
+        <v>0.06566769794274227</v>
       </c>
       <c r="G168" t="n">
         <v>0.9338064793813854</v>
@@ -5710,7 +5710,7 @@
         <v>0.0003407135119450661</v>
       </c>
       <c r="F169" t="n">
-        <v>0.04474433813796649</v>
+        <v>0.044744338137997</v>
       </c>
       <c r="G169" t="n">
         <v>0.9549149483500368</v>
@@ -5730,10 +5730,10 @@
         <v>2</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0003729065807863321</v>
+        <v>0.0003729065807865017</v>
       </c>
       <c r="F170" t="n">
-        <v>0.03895828209834509</v>
+        <v>0.03895828209838052</v>
       </c>
       <c r="G170" t="n">
         <v>0.960668811320758</v>
@@ -5753,10 +5753,10 @@
         <v>2</v>
       </c>
       <c r="E171" t="n">
-        <v>0.0002223075651303404</v>
+        <v>0.0002223075651303909</v>
       </c>
       <c r="F171" t="n">
-        <v>0.02564445247044633</v>
+        <v>0.02564445247045799</v>
       </c>
       <c r="G171" t="n">
         <v>0.9741332399643355</v>
@@ -5779,7 +5779,7 @@
         <v>0.0001541763416011468</v>
       </c>
       <c r="F172" t="n">
-        <v>0.01726843352955729</v>
+        <v>0.01726843352956121</v>
       </c>
       <c r="G172" t="n">
         <v>0.9825773901287483</v>
@@ -5799,10 +5799,10 @@
         <v>2</v>
       </c>
       <c r="E173" t="n">
-        <v>0.0001535379002435277</v>
+        <v>0.0001535379002434928</v>
       </c>
       <c r="F173" t="n">
-        <v>0.01219216186295781</v>
+        <v>0.01219216186296058</v>
       </c>
       <c r="G173" t="n">
         <v>0.9876543002367523</v>
@@ -5822,7 +5822,7 @@
         <v>2</v>
       </c>
       <c r="E174" t="n">
-        <v>0.0002712271621209573</v>
+        <v>0.0002712271621208339</v>
       </c>
       <c r="F174" t="n">
         <v>0.008547765271808366</v>
@@ -5845,7 +5845,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0001744629931404256</v>
+        <v>0.0001744629931403066</v>
       </c>
       <c r="F175" t="n">
         <v>0.008100897779760101</v>
@@ -5868,7 +5868,7 @@
         <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>8.388569987675772e-05</v>
+        <v>8.38856998767005e-05</v>
       </c>
       <c r="F176" t="n">
         <v>0.01509090583820965</v>
@@ -5891,7 +5891,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>0.000131354695083663</v>
+        <v>0.0001313546950835734</v>
       </c>
       <c r="F177" t="n">
         <v>0.01898557633769095</v>
@@ -5914,10 +5914,10 @@
         <v>2</v>
       </c>
       <c r="E178" t="n">
-        <v>7.65278516486681e-05</v>
+        <v>7.652785164858109e-05</v>
       </c>
       <c r="F178" t="n">
-        <v>0.02214998868323328</v>
+        <v>0.02214998868322824</v>
       </c>
       <c r="G178" t="n">
         <v>0.9777734834650127</v>
@@ -5937,7 +5937,7 @@
         <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>6.369961783981108e-05</v>
+        <v>6.369961783973865e-05</v>
       </c>
       <c r="F179" t="n">
         <v>0.03060646279649526</v>
@@ -5960,7 +5960,7 @@
         <v>2</v>
       </c>
       <c r="E180" t="n">
-        <v>7.638615700725307e-05</v>
+        <v>7.63861570071836e-05</v>
       </c>
       <c r="F180" t="n">
         <v>0.04421742472163448</v>
@@ -5983,10 +5983,10 @@
         <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>0.0002170232446854555</v>
+        <v>0.0002170232446852087</v>
       </c>
       <c r="F181" t="n">
-        <v>0.07024756315382143</v>
+        <v>0.07024756315380545</v>
       </c>
       <c r="G181" t="n">
         <v>0.929535413601454</v>
@@ -6006,10 +6006,10 @@
         <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>0.0007085915082151049</v>
+        <v>0.0007085915082147827</v>
       </c>
       <c r="F182" t="n">
-        <v>0.1255298394437134</v>
+        <v>0.1255298394436563</v>
       </c>
       <c r="G182" t="n">
         <v>0.8737615690480672</v>
@@ -6029,7 +6029,7 @@
         <v>2</v>
       </c>
       <c r="E183" t="n">
-        <v>0.0006544724058379201</v>
+        <v>0.0006544724058373249</v>
       </c>
       <c r="F183" t="n">
         <v>0.08139463966411004</v>
@@ -6052,7 +6052,7 @@
         <v>2</v>
       </c>
       <c r="E184" t="n">
-        <v>0.0003566590781283898</v>
+        <v>0.0003566590781280654</v>
       </c>
       <c r="F184" t="n">
         <v>0.05260082050211338</v>
@@ -6075,10 +6075,10 @@
         <v>2</v>
       </c>
       <c r="E185" t="n">
-        <v>0.0002214156842102573</v>
+        <v>0.0002214156842101062</v>
       </c>
       <c r="F185" t="n">
-        <v>0.04167771182269282</v>
+        <v>0.04167771182271177</v>
       </c>
       <c r="G185" t="n">
         <v>0.9581008724931013</v>
@@ -6098,10 +6098,10 @@
         <v>2</v>
       </c>
       <c r="E186" t="n">
-        <v>0.0001830810720665433</v>
+        <v>0.0001830810720664184</v>
       </c>
       <c r="F186" t="n">
-        <v>0.03603949322720273</v>
+        <v>0.03603949322721912</v>
       </c>
       <c r="G186" t="n">
         <v>0.9637774257006935</v>
@@ -6121,10 +6121,10 @@
         <v>2</v>
       </c>
       <c r="E187" t="n">
-        <v>9.265514143358793e-05</v>
+        <v>9.26551414335458e-05</v>
       </c>
       <c r="F187" t="n">
-        <v>0.03636037895829393</v>
+        <v>0.03636037895831046</v>
       </c>
       <c r="G187" t="n">
         <v>0.9635469659001842</v>
@@ -6144,10 +6144,10 @@
         <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>9.587223397785758e-05</v>
+        <v>9.587223397779218e-05</v>
       </c>
       <c r="F188" t="n">
-        <v>0.04574535000906364</v>
+        <v>0.04574535000908444</v>
       </c>
       <c r="G188" t="n">
         <v>0.9541587777568487</v>
@@ -6167,10 +6167,10 @@
         <v>2</v>
       </c>
       <c r="E189" t="n">
-        <v>9.538599946034029e-05</v>
+        <v>9.538599946029691e-05</v>
       </c>
       <c r="F189" t="n">
-        <v>0.05849313882608849</v>
+        <v>0.05849313882611509</v>
       </c>
       <c r="G189" t="n">
         <v>0.9414114751743642</v>
@@ -6193,7 +6193,7 @@
         <v>7.412635689681706e-05</v>
       </c>
       <c r="F190" t="n">
-        <v>0.08702579800243299</v>
+        <v>0.08702579800247257</v>
       </c>
       <c r="G190" t="n">
         <v>0.9129000756406537</v>
@@ -6216,7 +6216,7 @@
         <v>4.92988464984087e-05</v>
       </c>
       <c r="F191" t="n">
-        <v>0.1448222016480409</v>
+        <v>0.1448222016481068</v>
       </c>
       <c r="G191" t="n">
         <v>0.8551284995053942</v>
@@ -6239,7 +6239,7 @@
         <v>6.265391628775602e-05</v>
       </c>
       <c r="F192" t="n">
-        <v>0.2495430332003903</v>
+        <v>0.2495430332004471</v>
       </c>
       <c r="G192" t="n">
         <v>0.7503943128832634</v>
@@ -6259,10 +6259,10 @@
         <v>2</v>
       </c>
       <c r="E193" t="n">
-        <v>0.0002071331183152848</v>
+        <v>0.0002071331183151906</v>
       </c>
       <c r="F193" t="n">
-        <v>0.4450160344082109</v>
+        <v>0.4450160344083121</v>
       </c>
       <c r="G193" t="n">
         <v>0.5547768324733992</v>
@@ -6282,13 +6282,13 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>0.00117354930092331</v>
+        <v>0.00117354930092171</v>
       </c>
       <c r="F194" t="n">
-        <v>0.7466517093419073</v>
+        <v>0.746651709342077</v>
       </c>
       <c r="G194" t="n">
-        <v>0.2521747413571557</v>
+        <v>0.2521747413570984</v>
       </c>
     </row>
     <row r="195">
@@ -6305,13 +6305,13 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0.001879054586783528</v>
+        <v>0.001879054586780964</v>
       </c>
       <c r="F195" t="n">
-        <v>0.7399788198315054</v>
+        <v>0.7399788198316736</v>
       </c>
       <c r="G195" t="n">
-        <v>0.2581421255817569</v>
+        <v>0.2581421255816396</v>
       </c>
     </row>
     <row r="196">
@@ -6328,13 +6328,13 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>0.001368148423811775</v>
+        <v>0.001368148423810531</v>
       </c>
       <c r="F196" t="n">
-        <v>0.7058895123816656</v>
+        <v>0.7058895123819866</v>
       </c>
       <c r="G196" t="n">
-        <v>0.2927423391944819</v>
+        <v>0.2927423391942822</v>
       </c>
     </row>
     <row r="197">
@@ -6351,13 +6351,13 @@
         <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>0.0006058535933483791</v>
+        <v>0.0006058535933478281</v>
       </c>
       <c r="F197" t="n">
-        <v>0.659814768313959</v>
+        <v>0.6598147683142591</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3395793780926573</v>
+        <v>0.3395793780923484</v>
       </c>
     </row>
     <row r="198">
@@ -6374,13 +6374,13 @@
         <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>0.0002929700308733563</v>
+        <v>0.0002929700308735561</v>
       </c>
       <c r="F198" t="n">
-        <v>0.6561627268283865</v>
+        <v>0.6561627268286849</v>
       </c>
       <c r="G198" t="n">
-        <v>0.3435443031406832</v>
+        <v>0.3435443031403708</v>
       </c>
     </row>
     <row r="199">
@@ -6397,13 +6397,13 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>0.0002861902140768444</v>
+        <v>0.0002861902140777554</v>
       </c>
       <c r="F199" t="n">
-        <v>0.68871016142601</v>
+        <v>0.6887101614263232</v>
       </c>
       <c r="G199" t="n">
-        <v>0.3110036483599001</v>
+        <v>0.3110036483596172</v>
       </c>
     </row>
     <row r="200">
@@ -6420,13 +6420,13 @@
         <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0001571578004153691</v>
+        <v>0.0001571578004160481</v>
       </c>
       <c r="F200" t="n">
-        <v>0.7866924142198447</v>
+        <v>0.7866924142200236</v>
       </c>
       <c r="G200" t="n">
-        <v>0.2131504279798477</v>
+        <v>0.2131504279796053</v>
       </c>
     </row>
     <row r="201">
@@ -6443,13 +6443,13 @@
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0003396184066520945</v>
+        <v>0.0003396184066528667</v>
       </c>
       <c r="F201" t="n">
-        <v>0.9697971420083775</v>
+        <v>0.9697971420085981</v>
       </c>
       <c r="G201" t="n">
-        <v>0.02986323958487435</v>
+        <v>0.02986323958483361</v>
       </c>
     </row>
     <row r="202">
@@ -6466,13 +6466,13 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>0.0004600370039350481</v>
+        <v>0.0004600370039352573</v>
       </c>
       <c r="F202" t="n">
         <v>0.981104194188484</v>
       </c>
       <c r="G202" t="n">
-        <v>0.01843576880761499</v>
+        <v>0.01843576880758565</v>
       </c>
     </row>
     <row r="203">
@@ -6489,13 +6489,13 @@
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>0.00092840512813263</v>
+        <v>0.0009284051281324189</v>
       </c>
       <c r="F203" t="n">
-        <v>0.9820762032624941</v>
+        <v>0.9820762032627174</v>
       </c>
       <c r="G203" t="n">
-        <v>0.01699539160926007</v>
+        <v>0.01699539160923302</v>
       </c>
     </row>
     <row r="204">
@@ -6515,10 +6515,10 @@
         <v>0.001092151618015416</v>
       </c>
       <c r="F204" t="n">
-        <v>0.9647160751935049</v>
+        <v>0.9647160751937242</v>
       </c>
       <c r="G204" t="n">
-        <v>0.03419177318839399</v>
+        <v>0.03419177318835512</v>
       </c>
     </row>
     <row r="205">
@@ -6535,13 +6535,13 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>0.00273742289027252</v>
+        <v>0.002737422890271897</v>
       </c>
       <c r="F205" t="n">
         <v>0.9641379412824563</v>
       </c>
       <c r="G205" t="n">
-        <v>0.03312463582726619</v>
+        <v>0.03312463582722101</v>
       </c>
     </row>
     <row r="206">
@@ -6558,13 +6558,13 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>0.007526358993221411</v>
+        <v>0.0075263589932197</v>
       </c>
       <c r="F206" t="n">
         <v>0.9703681741843131</v>
       </c>
       <c r="G206" t="n">
-        <v>0.02210546682241084</v>
+        <v>0.02210546682238068</v>
       </c>
     </row>
     <row r="207">
@@ -6581,13 +6581,13 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>0.005831596966819421</v>
+        <v>0.005831596966818096</v>
       </c>
       <c r="F207" t="n">
-        <v>0.7914943751241679</v>
+        <v>0.7914943751243477</v>
       </c>
       <c r="G207" t="n">
-        <v>0.2026740279089873</v>
+        <v>0.2026740279089412</v>
       </c>
     </row>
     <row r="208">
@@ -6604,13 +6604,13 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>0.006822611590323794</v>
+        <v>0.006822611590319141</v>
       </c>
       <c r="F208" t="n">
-        <v>0.6240647548779266</v>
+        <v>0.6240647548780685</v>
       </c>
       <c r="G208" t="n">
-        <v>0.3691126335317523</v>
+        <v>0.3691126335315844</v>
       </c>
     </row>
     <row r="209">
@@ -6627,13 +6627,13 @@
         <v>2</v>
       </c>
       <c r="E209" t="n">
-        <v>0.003242033249994833</v>
+        <v>0.003242033249993358</v>
       </c>
       <c r="F209" t="n">
-        <v>0.3794723355407108</v>
+        <v>0.3794723355409697</v>
       </c>
       <c r="G209" t="n">
-        <v>0.6172856312093137</v>
+        <v>0.617285631209033</v>
       </c>
     </row>
     <row r="210">
@@ -6653,10 +6653,10 @@
         <v>0.002051659305341426</v>
       </c>
       <c r="F210" t="n">
-        <v>0.2487469774845694</v>
+        <v>0.248746977484739</v>
       </c>
       <c r="G210" t="n">
-        <v>0.7492013632100517</v>
+        <v>0.7492013632098813</v>
       </c>
     </row>
     <row r="211">
@@ -6673,13 +6673,13 @@
         <v>2</v>
       </c>
       <c r="E211" t="n">
-        <v>0.003100638332744529</v>
+        <v>0.003100638332745234</v>
       </c>
       <c r="F211" t="n">
-        <v>0.185214954624051</v>
+        <v>0.1852149546242194</v>
       </c>
       <c r="G211" t="n">
-        <v>0.8116844070432703</v>
+        <v>0.8116844070430858</v>
       </c>
     </row>
     <row r="212">
@@ -6699,10 +6699,10 @@
         <v>0.001279762279131238</v>
       </c>
       <c r="F212" t="n">
-        <v>0.103138617533132</v>
+        <v>0.1031386175332258</v>
       </c>
       <c r="G212" t="n">
-        <v>0.8955816201877812</v>
+        <v>0.8955816201875776</v>
       </c>
     </row>
     <row r="213">
@@ -6719,13 +6719,13 @@
         <v>2</v>
       </c>
       <c r="E213" t="n">
-        <v>0.000723605509733771</v>
+        <v>0.0007236055097339356</v>
       </c>
       <c r="F213" t="n">
-        <v>0.05582073703345516</v>
+        <v>0.05582073703350593</v>
       </c>
       <c r="G213" t="n">
-        <v>0.9434556574568917</v>
+        <v>0.9434556574566773</v>
       </c>
     </row>
     <row r="214">
@@ -6745,7 +6745,7 @@
         <v>0.0005236034987983881</v>
       </c>
       <c r="F214" t="n">
-        <v>0.0355682720499023</v>
+        <v>0.03556827204991847</v>
       </c>
       <c r="G214" t="n">
         <v>0.9639081244511943</v>
@@ -6765,10 +6765,10 @@
         <v>2</v>
       </c>
       <c r="E215" t="n">
-        <v>0.0008871143034079776</v>
+        <v>0.0008871143034081794</v>
       </c>
       <c r="F215" t="n">
-        <v>0.02321319205561371</v>
+        <v>0.02321319205562427</v>
       </c>
       <c r="G215" t="n">
         <v>0.9758996936409808</v>
@@ -6791,7 +6791,7 @@
         <v>0.001332769982226236</v>
       </c>
       <c r="F216" t="n">
-        <v>0.01843475265027481</v>
+        <v>0.018434752650279</v>
       </c>
       <c r="G216" t="n">
         <v>0.980232477367453</v>
@@ -6811,10 +6811,10 @@
         <v>2</v>
       </c>
       <c r="E217" t="n">
-        <v>0.0002472694389474593</v>
+        <v>0.0002472694389474031</v>
       </c>
       <c r="F217" t="n">
-        <v>0.01220846082528365</v>
+        <v>0.01220846082528087</v>
       </c>
       <c r="G217" t="n">
         <v>0.9875442697357066</v>
@@ -6834,7 +6834,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="n">
-        <v>7.707255530493678e-05</v>
+        <v>7.707255530491926e-05</v>
       </c>
       <c r="F218" t="n">
         <v>0.009588794102978684</v>
@@ -6857,10 +6857,10 @@
         <v>2</v>
       </c>
       <c r="E219" t="n">
-        <v>5.238670807437976e-05</v>
+        <v>5.238670807434403e-05</v>
       </c>
       <c r="F219" t="n">
-        <v>0.008898002494868121</v>
+        <v>0.008898002494864074</v>
       </c>
       <c r="G219" t="n">
         <v>0.9910496107970233</v>
@@ -6880,10 +6880,10 @@
         <v>2</v>
       </c>
       <c r="E220" t="n">
-        <v>4.203687509251928e-05</v>
+        <v>4.203687509249061e-05</v>
       </c>
       <c r="F220" t="n">
-        <v>0.00865656178261991</v>
+        <v>0.008656561782615974</v>
       </c>
       <c r="G220" t="n">
         <v>0.9913014013423659</v>
@@ -6903,10 +6903,10 @@
         <v>2</v>
       </c>
       <c r="E221" t="n">
-        <v>4.081513085891682e-05</v>
+        <v>4.08151308588797e-05</v>
       </c>
       <c r="F221" t="n">
-        <v>0.008728478899048603</v>
+        <v>0.008728478899044633</v>
       </c>
       <c r="G221" t="n">
         <v>0.9912307059701269</v>
@@ -6926,10 +6926,10 @@
         <v>2</v>
       </c>
       <c r="E222" t="n">
-        <v>3.787384358760065e-05</v>
+        <v>3.787384358756621e-05</v>
       </c>
       <c r="F222" t="n">
-        <v>0.008183216022271537</v>
+        <v>0.008183216022267816</v>
       </c>
       <c r="G222" t="n">
         <v>0.9917789101341293</v>
@@ -6949,10 +6949,10 @@
         <v>2</v>
       </c>
       <c r="E223" t="n">
-        <v>3.409836052335121e-05</v>
+        <v>3.40983605233202e-05</v>
       </c>
       <c r="F223" t="n">
-        <v>0.007832954779472068</v>
+        <v>0.007832954779470288</v>
       </c>
       <c r="G223" t="n">
         <v>0.9921329468601141</v>
@@ -6972,10 +6972,10 @@
         <v>2</v>
       </c>
       <c r="E224" t="n">
-        <v>2.734358829227651e-05</v>
+        <v>2.734358829223299e-05</v>
       </c>
       <c r="F224" t="n">
-        <v>0.009540869729980731</v>
+        <v>0.009540869729978561</v>
       </c>
       <c r="G224" t="n">
         <v>0.9904317866816856</v>
@@ -6995,10 +6995,10 @@
         <v>2</v>
       </c>
       <c r="E225" t="n">
-        <v>3.980953241744106e-05</v>
+        <v>3.980953241738675e-05</v>
       </c>
       <c r="F225" t="n">
-        <v>0.01308613590301522</v>
+        <v>0.01308613590300927</v>
       </c>
       <c r="G225" t="n">
         <v>0.9868740545645994</v>
@@ -7018,7 +7018,7 @@
         <v>2</v>
       </c>
       <c r="E226" t="n">
-        <v>4.391844642749504e-05</v>
+        <v>4.391844642743513e-05</v>
       </c>
       <c r="F226" t="n">
         <v>0.01422077884690376</v>
@@ -7041,7 +7041,7 @@
         <v>2</v>
       </c>
       <c r="E227" t="n">
-        <v>2.750899967955016e-05</v>
+        <v>2.750899967951263e-05</v>
       </c>
       <c r="F227" t="n">
         <v>0.02089310205858009</v>
@@ -7064,10 +7064,10 @@
         <v>2</v>
       </c>
       <c r="E228" t="n">
-        <v>2.864999987172485e-05</v>
+        <v>2.864999987169228e-05</v>
       </c>
       <c r="F228" t="n">
-        <v>0.03510131217602287</v>
+        <v>0.03510131217603085</v>
       </c>
       <c r="G228" t="n">
         <v>0.9648700378239939</v>
@@ -7081,16 +7081,16 @@
         <v>0.01015736928597801</v>
       </c>
       <c r="C229" t="n">
-        <v>0.001216387825317767</v>
+        <v>0.001216387825317766</v>
       </c>
       <c r="D229" t="n">
         <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>5.503147900217211e-05</v>
+        <v>5.503147900209704e-05</v>
       </c>
       <c r="F229" t="n">
-        <v>0.06150821899874163</v>
+        <v>0.06150821899875562</v>
       </c>
       <c r="G229" t="n">
         <v>0.9384367495222158</v>
@@ -7110,10 +7110,10 @@
         <v>2</v>
       </c>
       <c r="E230" t="n">
-        <v>0.0002472523469965845</v>
+        <v>0.0002472523469963596</v>
       </c>
       <c r="F230" t="n">
-        <v>0.1113449189973794</v>
+        <v>0.11134491899743</v>
       </c>
       <c r="G230" t="n">
         <v>0.8884078286556102</v>
@@ -7133,13 +7133,13 @@
         <v>2</v>
       </c>
       <c r="E231" t="n">
-        <v>0.0006906280676823306</v>
+        <v>0.0006906280676817026</v>
       </c>
       <c r="F231" t="n">
-        <v>0.1313995924039206</v>
+        <v>0.1313995924039505</v>
       </c>
       <c r="G231" t="n">
-        <v>0.8679097795284533</v>
+        <v>0.8679097795282559</v>
       </c>
     </row>
     <row r="232">
@@ -7156,10 +7156,10 @@
         <v>2</v>
       </c>
       <c r="E232" t="n">
-        <v>0.0007428296767442931</v>
+        <v>0.0007428296767436175</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1435437539700763</v>
+        <v>0.1435437539701089</v>
       </c>
       <c r="G232" t="n">
         <v>0.8557134163531566</v>
@@ -7179,10 +7179,10 @@
         <v>2</v>
       </c>
       <c r="E233" t="n">
-        <v>0.0004170403687893286</v>
+        <v>0.0004170403687886648</v>
       </c>
       <c r="F233" t="n">
-        <v>0.1205816185633972</v>
+        <v>0.1205816185634246</v>
       </c>
       <c r="G233" t="n">
         <v>0.8790013410677965</v>
@@ -7202,10 +7202,10 @@
         <v>2</v>
       </c>
       <c r="E234" t="n">
-        <v>0.0001678377553411413</v>
+        <v>0.0001678377553409505</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1258571794659203</v>
+        <v>0.1258571794659775</v>
       </c>
       <c r="G234" t="n">
         <v>0.8739749827787882</v>
@@ -7216,16 +7216,16 @@
         <v>43281</v>
       </c>
       <c r="B235" t="n">
-        <v>0.004736567679959356</v>
+        <v>0.004736567679959355</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.0008148956246944808</v>
+        <v>-0.000814895624694481</v>
       </c>
       <c r="D235" t="n">
         <v>2</v>
       </c>
       <c r="E235" t="n">
-        <v>8.784025991750995e-05</v>
+        <v>8.784025991745003e-05</v>
       </c>
       <c r="F235" t="n">
         <v>0.1494965534412009</v>
@@ -7254,7 +7254,7 @@
         <v>0.2015642969050456</v>
       </c>
       <c r="G236" t="n">
-        <v>0.7983736460341265</v>
+        <v>0.798373646033945</v>
       </c>
     </row>
     <row r="237">
@@ -7271,7 +7271,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="n">
-        <v>5.7922964342458e-05</v>
+        <v>5.792296434257654e-05</v>
       </c>
       <c r="F237" t="n">
         <v>0.2908851375500926</v>
@@ -7294,10 +7294,10 @@
         <v>2</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0001246750084486823</v>
+        <v>0.0001246750084490508</v>
       </c>
       <c r="F238" t="n">
-        <v>0.4614889428645876</v>
+        <v>0.4614889428644827</v>
       </c>
       <c r="G238" t="n">
         <v>0.5383863821269854</v>
@@ -7317,13 +7317,13 @@
         <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>0.0004036783708659263</v>
+        <v>0.0004036783708668442</v>
       </c>
       <c r="F239" t="n">
         <v>0.909923799172596</v>
       </c>
       <c r="G239" t="n">
-        <v>0.08967252245658199</v>
+        <v>0.08967252245662276</v>
       </c>
     </row>
     <row r="240">
@@ -7340,13 +7340,13 @@
         <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>0.0004191668030957002</v>
+        <v>0.0004191668030960814</v>
       </c>
       <c r="F240" t="n">
         <v>0.9386393992066812</v>
       </c>
       <c r="G240" t="n">
-        <v>0.06094143399016868</v>
+        <v>0.06094143399018254</v>
       </c>
     </row>
     <row r="241">
@@ -7363,13 +7363,13 @@
         <v>1</v>
       </c>
       <c r="E241" t="n">
-        <v>0.001092697235822834</v>
+        <v>0.001092697235822337</v>
       </c>
       <c r="F241" t="n">
         <v>0.9988361161089919</v>
       </c>
       <c r="G241" t="n">
-        <v>7.118665517934905e-05</v>
+        <v>7.118665517928431e-05</v>
       </c>
     </row>
     <row r="242">
@@ -7386,13 +7386,13 @@
         <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>0.001097606103501334</v>
+        <v>0.001097606103500835</v>
       </c>
       <c r="F242" t="n">
         <v>0.9856634504533214</v>
       </c>
       <c r="G242" t="n">
-        <v>0.01323894344324248</v>
+        <v>0.01323894344321839</v>
       </c>
     </row>
     <row r="243">
@@ -7409,13 +7409,13 @@
         <v>1</v>
       </c>
       <c r="E243" t="n">
-        <v>0.00041092357408027</v>
+        <v>0.0004109235740805503</v>
       </c>
       <c r="F243" t="n">
         <v>0.9659350538472473</v>
       </c>
       <c r="G243" t="n">
-        <v>0.03365402257864154</v>
+        <v>0.03365402257860328</v>
       </c>
     </row>
     <row r="244">
@@ -7432,13 +7432,13 @@
         <v>1</v>
       </c>
       <c r="E244" t="n">
-        <v>0.0004228276672192706</v>
+        <v>0.000422827667219559</v>
       </c>
       <c r="F244" t="n">
         <v>0.9633848894525074</v>
       </c>
       <c r="G244" t="n">
-        <v>0.03619228288022594</v>
+        <v>0.03619228288016834</v>
       </c>
     </row>
     <row r="245">
@@ -7455,13 +7455,13 @@
         <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>0.0006424184502399028</v>
+        <v>0.0006424184502394647</v>
       </c>
       <c r="F245" t="n">
         <v>0.9728044107819749</v>
       </c>
       <c r="G245" t="n">
-        <v>0.02655317076778654</v>
+        <v>0.02655317076773824</v>
       </c>
     </row>
     <row r="246">
@@ -7478,13 +7478,13 @@
         <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>0.001871281048455205</v>
+        <v>0.001871281048453078</v>
       </c>
       <c r="F246" t="n">
         <v>0.9962271830800169</v>
       </c>
       <c r="G246" t="n">
-        <v>0.001901535871454088</v>
+        <v>0.001901535871450196</v>
       </c>
     </row>
     <row r="247">
@@ -7501,13 +7501,13 @@
         <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>0.002164663909890382</v>
+        <v>0.002164663909887921</v>
       </c>
       <c r="F247" t="n">
         <v>0.9596142742259502</v>
       </c>
       <c r="G247" t="n">
-        <v>0.03822106186425724</v>
+        <v>0.0382210618641964</v>
       </c>
     </row>
     <row r="248">
@@ -7524,13 +7524,13 @@
         <v>1</v>
       </c>
       <c r="E248" t="n">
-        <v>0.001783641927588562</v>
+        <v>0.001783641927586129</v>
       </c>
       <c r="F248" t="n">
         <v>0.9286425461787747</v>
       </c>
       <c r="G248" t="n">
-        <v>0.06957381189368364</v>
+        <v>0.06957381189355709</v>
       </c>
     </row>
     <row r="249">
@@ -7547,13 +7547,13 @@
         <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>0.004071230600815687</v>
+        <v>0.004071230600809207</v>
       </c>
       <c r="F249" t="n">
         <v>0.9217917209359945</v>
       </c>
       <c r="G249" t="n">
-        <v>0.07413704846329482</v>
+        <v>0.07413704846317683</v>
       </c>
     </row>
     <row r="250">
@@ -7570,13 +7570,13 @@
         <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>0.001229832896833751</v>
+        <v>0.001229832896832632</v>
       </c>
       <c r="F250" t="n">
-        <v>0.8509897161682818</v>
+        <v>0.8509897161684753</v>
       </c>
       <c r="G250" t="n">
-        <v>0.1477804509348598</v>
+        <v>0.1477804509346246</v>
       </c>
     </row>
     <row r="251">
@@ -7593,13 +7593,13 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>0.0004033064458458953</v>
+        <v>0.000403306445845987</v>
       </c>
       <c r="F251" t="n">
-        <v>0.8305015631205604</v>
+        <v>0.8305015631207493</v>
       </c>
       <c r="G251" t="n">
-        <v>0.169095130433629</v>
+        <v>0.1690951304333599</v>
       </c>
     </row>
     <row r="252">
@@ -7610,19 +7610,19 @@
         <v>0.03445648173694641</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.007765814965729999</v>
+        <v>-0.00776581496573</v>
       </c>
       <c r="D252" t="n">
         <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>0.0002864469476510304</v>
+        <v>0.0002864469476512258</v>
       </c>
       <c r="F252" t="n">
-        <v>0.838989649443575</v>
+        <v>0.8389896494437658</v>
       </c>
       <c r="G252" t="n">
-        <v>0.1607239036088817</v>
+        <v>0.1607239036086259</v>
       </c>
     </row>
     <row r="253">
@@ -7639,13 +7639,13 @@
         <v>1</v>
       </c>
       <c r="E253" t="n">
-        <v>0.0004756581943414858</v>
+        <v>0.0004756581943418102</v>
       </c>
       <c r="F253" t="n">
-        <v>0.871917121930429</v>
+        <v>0.8719171219306273</v>
       </c>
       <c r="G253" t="n">
-        <v>0.127607219875161</v>
+        <v>0.1276072198750159</v>
       </c>
     </row>
     <row r="254">
@@ -7662,13 +7662,13 @@
         <v>1</v>
       </c>
       <c r="E254" t="n">
-        <v>0.001441674392312414</v>
+        <v>0.001441674392312742</v>
       </c>
       <c r="F254" t="n">
         <v>0.9475691629407781</v>
       </c>
       <c r="G254" t="n">
-        <v>0.05098916266697616</v>
+        <v>0.05098916266691819</v>
       </c>
     </row>
     <row r="255">
@@ -7685,13 +7685,13 @@
         <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>0.003439686924704616</v>
+        <v>0.003439686924703052</v>
       </c>
       <c r="F255" t="n">
         <v>0.9965422724360217</v>
       </c>
       <c r="G255" t="n">
-        <v>1.804063934780812e-05</v>
+        <v>1.804063934778762e-05</v>
       </c>
     </row>
     <row r="256">
@@ -7708,13 +7708,13 @@
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>0.007346977676317563</v>
+        <v>0.007346977676310881</v>
       </c>
       <c r="F256" t="n">
-        <v>0.9926530215744765</v>
+        <v>0.9926530215747023</v>
       </c>
       <c r="G256" t="n">
-        <v>7.49095437991012e-10</v>
+        <v>7.490954379893087e-10</v>
       </c>
     </row>
     <row r="257">
@@ -7731,13 +7731,13 @@
         <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>0.01039386171220938</v>
+        <v>0.0103938617121952</v>
       </c>
       <c r="F257" t="n">
         <v>0.9884907396592765</v>
       </c>
       <c r="G257" t="n">
-        <v>0.001115398628584084</v>
+        <v>0.001115398628581548</v>
       </c>
     </row>
     <row r="258">
@@ -7754,13 +7754,13 @@
         <v>1</v>
       </c>
       <c r="E258" t="n">
-        <v>0.002604813020335797</v>
+        <v>0.002604813020332835</v>
       </c>
       <c r="F258" t="n">
         <v>0.9501033953625054</v>
       </c>
       <c r="G258" t="n">
-        <v>0.04729179161714917</v>
+        <v>0.04729179161706315</v>
       </c>
     </row>
     <row r="259">
@@ -7777,13 +7777,13 @@
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>0.0009099390955879679</v>
+        <v>0.0009099390955873472</v>
       </c>
       <c r="F259" t="n">
-        <v>0.9284003786156749</v>
+        <v>0.9284003786158861</v>
       </c>
       <c r="G259" t="n">
-        <v>0.07068968228873043</v>
+        <v>0.07068968228860185</v>
       </c>
     </row>
     <row r="260">
@@ -7800,13 +7800,13 @@
         <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>0.001215211977256401</v>
+        <v>0.001215211977255849</v>
       </c>
       <c r="F260" t="n">
-        <v>0.9290414803669533</v>
+        <v>0.9290414803671645</v>
       </c>
       <c r="G260" t="n">
-        <v>0.06974330765573598</v>
+        <v>0.06974330765562498</v>
       </c>
     </row>
     <row r="261">
@@ -7823,13 +7823,13 @@
         <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>0.002493556201554665</v>
+        <v>0.002493556201551263</v>
       </c>
       <c r="F261" t="n">
-        <v>0.9398607858816236</v>
+        <v>0.9398607858818373</v>
       </c>
       <c r="G261" t="n">
-        <v>0.0576456579168243</v>
+        <v>0.05764565791671944</v>
       </c>
     </row>
     <row r="262">
@@ -7846,13 +7846,13 @@
         <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>0.006047136563028366</v>
+        <v>0.006047136563024241</v>
       </c>
       <c r="F262" t="n">
-        <v>0.9310399633090205</v>
+        <v>0.9310399633092322</v>
       </c>
       <c r="G262" t="n">
-        <v>0.06291290012792841</v>
+        <v>0.06291290012784259</v>
       </c>
     </row>
     <row r="263">
@@ -7869,13 +7869,13 @@
         <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>0.01328719848855481</v>
+        <v>0.01328719848854273</v>
       </c>
       <c r="F263" t="n">
-        <v>0.892718008346971</v>
+        <v>0.892718008347174</v>
       </c>
       <c r="G263" t="n">
-        <v>0.09399479316452022</v>
+        <v>0.09399479316437062</v>
       </c>
     </row>
     <row r="264">
@@ -7892,13 +7892,13 @@
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0.02294388550430939</v>
+        <v>0.02294388550428853</v>
       </c>
       <c r="F264" t="n">
-        <v>0.8717400066770292</v>
+        <v>0.8717400066772275</v>
       </c>
       <c r="G264" t="n">
-        <v>0.1053161078185774</v>
+        <v>0.1053161078184338</v>
       </c>
     </row>
     <row r="265">
@@ -7915,13 +7915,13 @@
         <v>1</v>
       </c>
       <c r="E265" t="n">
-        <v>0.007034671760659535</v>
+        <v>0.007034671760653137</v>
       </c>
       <c r="F265" t="n">
-        <v>0.6104465205465441</v>
+        <v>0.6104465205469605</v>
       </c>
       <c r="G265" t="n">
-        <v>0.3825188076927514</v>
+        <v>0.3825188076924035</v>
       </c>
     </row>
     <row r="266">
@@ -7938,13 +7938,13 @@
         <v>1</v>
       </c>
       <c r="E266" t="n">
-        <v>0.004129526923191339</v>
+        <v>0.004129526923187583</v>
       </c>
       <c r="F266" t="n">
-        <v>0.4505556163488937</v>
+        <v>0.450555616349201</v>
       </c>
       <c r="G266" t="n">
-        <v>0.5453148567278774</v>
+        <v>0.5453148567276294</v>
       </c>
     </row>
     <row r="267">
@@ -7961,13 +7961,13 @@
         <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>0.003042648610529792</v>
+        <v>0.003042648610526333</v>
       </c>
       <c r="F267" t="n">
-        <v>0.3787928910228334</v>
+        <v>0.3787928910231779</v>
       </c>
       <c r="G267" t="n">
-        <v>0.6181644603666744</v>
+        <v>0.6181644603662527</v>
       </c>
     </row>
     <row r="268">
@@ -7984,13 +7984,13 @@
         <v>1</v>
       </c>
       <c r="E268" t="n">
-        <v>0.002379959010380437</v>
+        <v>0.002379959010378814</v>
       </c>
       <c r="F268" t="n">
-        <v>0.3511730579537627</v>
+        <v>0.351173057954162</v>
       </c>
       <c r="G268" t="n">
-        <v>0.6464469830357435</v>
+        <v>0.6464469830354496</v>
       </c>
     </row>
     <row r="269">
@@ -8007,13 +8007,13 @@
         <v>1</v>
       </c>
       <c r="E269" t="n">
-        <v>0.001154966202305426</v>
+        <v>0.001154966202304901</v>
       </c>
       <c r="F269" t="n">
-        <v>0.3245352473925984</v>
+        <v>0.3245352473929674</v>
       </c>
       <c r="G269" t="n">
-        <v>0.6743097864050883</v>
+        <v>0.6743097864047817</v>
       </c>
     </row>
     <row r="270">
@@ -8030,13 +8030,13 @@
         <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>0.0004756925322992539</v>
+        <v>0.0004756925322993621</v>
       </c>
       <c r="F270" t="n">
-        <v>0.3146179072710996</v>
+        <v>0.3146179072714573</v>
       </c>
       <c r="G270" t="n">
-        <v>0.6849064001964974</v>
+        <v>0.6849064001961859</v>
       </c>
     </row>
     <row r="271">
@@ -8053,13 +8053,13 @@
         <v>1</v>
       </c>
       <c r="E271" t="n">
-        <v>0.0004010972341791999</v>
+        <v>0.0004010972341792911</v>
       </c>
       <c r="F271" t="n">
-        <v>0.3255151668208824</v>
+        <v>0.3255151668211784</v>
       </c>
       <c r="G271" t="n">
-        <v>0.6740837359448485</v>
+        <v>0.674083735944542</v>
       </c>
     </row>
     <row r="272">
@@ -8076,13 +8076,13 @@
         <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>0.0008541785591023239</v>
+        <v>0.0008541785591027124</v>
       </c>
       <c r="F272" t="n">
-        <v>0.3674056211563482</v>
+        <v>0.3674056211566823</v>
       </c>
       <c r="G272" t="n">
-        <v>0.6317402002845154</v>
+        <v>0.6317402002842282</v>
       </c>
     </row>
     <row r="273">
@@ -8099,13 +8099,13 @@
         <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>0.00222705074019128</v>
+        <v>0.002227050740191786</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4498591625132057</v>
+        <v>0.4498591625136149</v>
       </c>
       <c r="G273" t="n">
-        <v>0.5479137867466494</v>
+        <v>0.5479137867462756</v>
       </c>
     </row>
     <row r="274">
@@ -8125,10 +8125,10 @@
         <v>0.008701928838461225</v>
       </c>
       <c r="F274" t="n">
-        <v>0.6036076671134316</v>
+        <v>0.6036076671135688</v>
       </c>
       <c r="G274" t="n">
-        <v>0.387690404048219</v>
+        <v>0.3876904040478664</v>
       </c>
     </row>
     <row r="275">
@@ -8148,10 +8148,10 @@
         <v>0.01460703595154151</v>
       </c>
       <c r="F275" t="n">
-        <v>0.7380009373050027</v>
+        <v>0.7380009373051706</v>
       </c>
       <c r="G275" t="n">
-        <v>0.2473920267435272</v>
+        <v>0.2473920267433022</v>
       </c>
     </row>
     <row r="276">
@@ -8168,13 +8168,13 @@
         <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>0.03675107255197354</v>
+        <v>0.03675107255196518</v>
       </c>
       <c r="F276" t="n">
-        <v>0.7840165358065436</v>
+        <v>0.7840165358067219</v>
       </c>
       <c r="G276" t="n">
-        <v>0.1792323916415497</v>
+        <v>0.1792323916413459</v>
       </c>
     </row>
     <row r="277">
@@ -8191,13 +8191,13 @@
         <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>0.1250711332647289</v>
+        <v>0.125071133264672</v>
       </c>
       <c r="F277" t="n">
         <v>0.7583892816390788</v>
       </c>
       <c r="G277" t="n">
-        <v>0.1165395850962761</v>
+        <v>0.1165395850961436</v>
       </c>
     </row>
     <row r="278">
@@ -8220,7 +8220,7 @@
         <v>0.4719725554612338</v>
       </c>
       <c r="G278" t="n">
-        <v>0.06625140430793254</v>
+        <v>0.0662514043078723</v>
       </c>
     </row>
     <row r="279">
@@ -8237,13 +8237,13 @@
         <v>0</v>
       </c>
       <c r="E279" t="n">
-        <v>0.5687384948116644</v>
+        <v>0.5687384948117937</v>
       </c>
       <c r="F279" t="n">
-        <v>0.416351413859709</v>
+        <v>0.4163514138596144</v>
       </c>
       <c r="G279" t="n">
-        <v>0.01491009132860877</v>
+        <v>0.01491009132860199</v>
       </c>
     </row>
     <row r="280">
@@ -8260,13 +8260,13 @@
         <v>0</v>
       </c>
       <c r="E280" t="n">
-        <v>0.8472161609631831</v>
+        <v>0.8472161609633757</v>
       </c>
       <c r="F280" t="n">
-        <v>0.1518249440785871</v>
+        <v>0.1518249440785525</v>
       </c>
       <c r="G280" t="n">
-        <v>0.0009588949581194764</v>
+        <v>0.0009588949581186044</v>
       </c>
     </row>
     <row r="281">
@@ -8286,10 +8286,10 @@
         <v>0.9954575976562137</v>
       </c>
       <c r="F281" t="n">
-        <v>0.003965587939661344</v>
+        <v>0.003965587939660443</v>
       </c>
       <c r="G281" t="n">
-        <v>0.0005768144040975274</v>
+        <v>0.0005768144040967405</v>
       </c>
     </row>
     <row r="282">
@@ -8309,10 +8309,10 @@
         <v>0.9954087896287294</v>
       </c>
       <c r="F282" t="n">
-        <v>0.004143136498226696</v>
+        <v>0.004143136498231405</v>
       </c>
       <c r="G282" t="n">
-        <v>0.000448073873045929</v>
+        <v>0.0004480738730452158</v>
       </c>
     </row>
     <row r="283">
@@ -8332,10 +8332,10 @@
         <v>0.9982336369896193</v>
       </c>
       <c r="F283" t="n">
-        <v>0.001761266293517014</v>
+        <v>0.001761266293517815</v>
       </c>
       <c r="G283" t="n">
-        <v>5.096716900567067e-06</v>
+        <v>5.096716900561273e-06</v>
       </c>
     </row>
     <row r="284">
@@ -8355,10 +8355,10 @@
         <v>0.9995648922684061</v>
       </c>
       <c r="F284" t="n">
-        <v>0.0004278051246934862</v>
+        <v>0.0004278051246940699</v>
       </c>
       <c r="G284" t="n">
-        <v>7.302606960059723e-06</v>
+        <v>7.302606960058063e-06</v>
       </c>
     </row>
     <row r="285">
@@ -8378,10 +8378,10 @@
         <v>0.9999543545677207</v>
       </c>
       <c r="F285" t="n">
-        <v>2.512862261048176e-05</v>
+        <v>2.512862261056175e-05</v>
       </c>
       <c r="G285" t="n">
-        <v>2.051680970062781e-05</v>
+        <v>2.051680970063248e-05</v>
       </c>
     </row>
     <row r="286">
@@ -8401,10 +8401,10 @@
         <v>0.9999279781775831</v>
       </c>
       <c r="F286" t="n">
-        <v>2.124983290138336e-06</v>
+        <v>2.12498329015573e-06</v>
       </c>
       <c r="G286" t="n">
-        <v>6.98968390921646e-05</v>
+        <v>6.989683909218049e-05</v>
       </c>
     </row>
     <row r="287">
@@ -8424,10 +8424,10 @@
         <v>0.9579961074166568</v>
       </c>
       <c r="F287" t="n">
-        <v>0.00157454593747374</v>
+        <v>0.001574545937496653</v>
       </c>
       <c r="G287" t="n">
-        <v>0.04042934664581402</v>
+        <v>0.04042934664580483</v>
       </c>
     </row>
     <row r="288">
@@ -8447,10 +8447,10 @@
         <v>0.8794665562436333</v>
       </c>
       <c r="F288" t="n">
-        <v>0.001698570422820326</v>
+        <v>0.001698570422840409</v>
       </c>
       <c r="G288" t="n">
-        <v>0.1188348733335853</v>
+        <v>0.1188348733336124</v>
       </c>
     </row>
     <row r="289">
@@ -8470,10 +8470,10 @@
         <v>0.8256807819556757</v>
       </c>
       <c r="F289" t="n">
-        <v>0.003205016271516216</v>
+        <v>0.00320501627153662</v>
       </c>
       <c r="G289" t="n">
-        <v>0.1711142017728526</v>
+        <v>0.1711142017728915</v>
       </c>
     </row>
     <row r="290">
@@ -8493,7 +8493,7 @@
         <v>0.5318788831177715</v>
       </c>
       <c r="F290" t="n">
-        <v>0.001975856413400836</v>
+        <v>0.001975856413413416</v>
       </c>
       <c r="G290" t="n">
         <v>0.466145260468784</v>
@@ -8516,7 +8516,7 @@
         <v>0.3498413493748427</v>
       </c>
       <c r="F291" t="n">
-        <v>0.00120118826074061</v>
+        <v>0.001201188260745799</v>
       </c>
       <c r="G291" t="n">
         <v>0.6489574623643102</v>
@@ -8539,7 +8539,7 @@
         <v>0.1397248803046435</v>
       </c>
       <c r="F292" t="n">
-        <v>0.003396155742275032</v>
+        <v>0.003396155742282754</v>
       </c>
       <c r="G292" t="n">
         <v>0.856878963953104</v>
@@ -8559,10 +8559,10 @@
         <v>2</v>
       </c>
       <c r="E293" t="n">
-        <v>0.02707801893488894</v>
+        <v>0.0270780189348951</v>
       </c>
       <c r="F293" t="n">
-        <v>0.006144187209569081</v>
+        <v>0.00614418720957467</v>
       </c>
       <c r="G293" t="n">
         <v>0.9667777938555213</v>
@@ -8588,7 +8588,7 @@
         <v>0.009266434133047207</v>
       </c>
       <c r="G294" t="n">
-        <v>0.9804649306886741</v>
+        <v>0.980464930688674</v>
       </c>
     </row>
     <row r="295">
@@ -8605,10 +8605,10 @@
         <v>2</v>
       </c>
       <c r="E295" t="n">
-        <v>0.006903686073517877</v>
+        <v>0.006903686073516307</v>
       </c>
       <c r="F295" t="n">
-        <v>0.01977439630206041</v>
+        <v>0.01977439630204692</v>
       </c>
       <c r="G295" t="n">
         <v>0.9733219176244187</v>
@@ -8628,10 +8628,10 @@
         <v>2</v>
       </c>
       <c r="E296" t="n">
-        <v>0.005054477876488879</v>
+        <v>0.005054477876485431</v>
       </c>
       <c r="F296" t="n">
-        <v>0.01552548237926302</v>
+        <v>0.01552548237925243</v>
       </c>
       <c r="G296" t="n">
         <v>0.9794200397443328</v>
@@ -8651,10 +8651,10 @@
         <v>2</v>
       </c>
       <c r="E297" t="n">
-        <v>0.006848023690152847</v>
+        <v>0.006848023690149732</v>
       </c>
       <c r="F297" t="n">
-        <v>0.01217310181892242</v>
+        <v>0.01217310181891135</v>
       </c>
       <c r="G297" t="n">
         <v>0.9809788744909909</v>
@@ -8674,10 +8674,10 @@
         <v>2</v>
       </c>
       <c r="E298" t="n">
-        <v>0.01216172687537701</v>
+        <v>0.01216172687536318</v>
       </c>
       <c r="F298" t="n">
-        <v>0.003959178216306221</v>
+        <v>0.00395917821630082</v>
       </c>
       <c r="G298" t="n">
         <v>0.9838790949082266</v>
@@ -8697,10 +8697,10 @@
         <v>2</v>
       </c>
       <c r="E299" t="n">
-        <v>0.01075408067574636</v>
+        <v>0.01075408067572924</v>
       </c>
       <c r="F299" t="n">
-        <v>0.003452303636842808</v>
+        <v>0.003452303636838099</v>
       </c>
       <c r="G299" t="n">
         <v>0.9857936156874455</v>
@@ -8720,13 +8720,13 @@
         <v>2</v>
       </c>
       <c r="E300" t="n">
-        <v>0.010253290570842</v>
+        <v>0.01025329057083034</v>
       </c>
       <c r="F300" t="n">
-        <v>0.003722734180198686</v>
+        <v>0.003722734180195301</v>
       </c>
       <c r="G300" t="n">
-        <v>0.9860239752488562</v>
+        <v>0.9860239752490805</v>
       </c>
     </row>
     <row r="301">
@@ -8743,10 +8743,10 @@
         <v>2</v>
       </c>
       <c r="E301" t="n">
-        <v>0.004929404182906932</v>
+        <v>0.004929404182900206</v>
       </c>
       <c r="F301" t="n">
-        <v>0.004698803674444531</v>
+        <v>0.004698803674439189</v>
       </c>
       <c r="G301" t="n">
         <v>0.990371792142645</v>
@@ -8760,16 +8760,16 @@
         <v>0.01197547558860675</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.006295415534405311</v>
+        <v>-0.00629541553440531</v>
       </c>
       <c r="D302" t="n">
         <v>2</v>
       </c>
       <c r="E302" t="n">
-        <v>0.001158576873250885</v>
+        <v>0.001158576873249041</v>
       </c>
       <c r="F302" t="n">
-        <v>0.006684974851249998</v>
+        <v>0.006684974851243918</v>
       </c>
       <c r="G302" t="n">
         <v>0.9921564482755154</v>
@@ -8789,10 +8789,10 @@
         <v>2</v>
       </c>
       <c r="E303" t="n">
-        <v>0.0007037271758824167</v>
+        <v>0.0007037271758814567</v>
       </c>
       <c r="F303" t="n">
-        <v>0.01048408747720742</v>
+        <v>0.01048408747719789</v>
       </c>
       <c r="G303" t="n">
         <v>0.9888121853468613</v>
@@ -8812,10 +8812,10 @@
         <v>2</v>
       </c>
       <c r="E304" t="n">
-        <v>0.0004686859163254778</v>
+        <v>0.0004686859163247318</v>
       </c>
       <c r="F304" t="n">
-        <v>0.007205538878785805</v>
+        <v>0.007205538878779252</v>
       </c>
       <c r="G304" t="n">
         <v>0.9923257752049046</v>
@@ -8835,10 +8835,10 @@
         <v>2</v>
       </c>
       <c r="E305" t="n">
-        <v>0.001101309435058083</v>
+        <v>0.00110130943505633</v>
       </c>
       <c r="F305" t="n">
-        <v>0.003849649113017144</v>
+        <v>0.003849649113012768</v>
       </c>
       <c r="G305" t="n">
         <v>0.995049041451919</v>
@@ -8858,10 +8858,10 @@
         <v>2</v>
       </c>
       <c r="E306" t="n">
-        <v>0.0002610436727026643</v>
+        <v>0.0002610436727022488</v>
       </c>
       <c r="F306" t="n">
-        <v>0.006079546018378435</v>
+        <v>0.006079546018371523</v>
       </c>
       <c r="G306" t="n">
         <v>0.9936594103088838</v>
@@ -8881,10 +8881,10 @@
         <v>2</v>
       </c>
       <c r="E307" t="n">
-        <v>7.284194946575563e-05</v>
+        <v>7.28419494656397e-05</v>
       </c>
       <c r="F307" t="n">
-        <v>0.008071030513639879</v>
+        <v>0.008071030513632539</v>
       </c>
       <c r="G307" t="n">
         <v>0.9918561275369651</v>
@@ -8904,10 +8904,10 @@
         <v>2</v>
       </c>
       <c r="E308" t="n">
-        <v>7.278627052385362e-05</v>
+        <v>7.278627052375432e-05</v>
       </c>
       <c r="F308" t="n">
-        <v>0.01100948012438792</v>
+        <v>0.0110094801243754</v>
       </c>
       <c r="G308" t="n">
         <v>0.9889177336050435</v>
@@ -8927,10 +8927,10 @@
         <v>2</v>
       </c>
       <c r="E309" t="n">
-        <v>5.430666658370652e-05</v>
+        <v>5.430666658363243e-05</v>
       </c>
       <c r="F309" t="n">
-        <v>0.01037711368200761</v>
+        <v>0.01037711368200053</v>
       </c>
       <c r="G309" t="n">
         <v>0.9895685796514629</v>
@@ -8950,10 +8950,10 @@
         <v>2</v>
       </c>
       <c r="E310" t="n">
-        <v>7.477268361517613e-05</v>
+        <v>7.477268361505712e-05</v>
       </c>
       <c r="F310" t="n">
-        <v>0.01098728827516935</v>
+        <v>0.01098728827515936</v>
       </c>
       <c r="G310" t="n">
         <v>0.9889379390412395</v>
@@ -8973,10 +8973,10 @@
         <v>2</v>
       </c>
       <c r="E311" t="n">
-        <v>0.0002394367728147178</v>
+        <v>0.0002394367728143367</v>
       </c>
       <c r="F311" t="n">
-        <v>0.01261409402828906</v>
+        <v>0.01261409402828332</v>
       </c>
       <c r="G311" t="n">
         <v>0.9871464691989918</v>
@@ -8996,10 +8996,10 @@
         <v>2</v>
       </c>
       <c r="E312" t="n">
-        <v>0.0001149424872570336</v>
+        <v>0.0001149424872569291</v>
       </c>
       <c r="F312" t="n">
-        <v>0.03995741546013133</v>
+        <v>0.03995741546014041</v>
       </c>
       <c r="G312" t="n">
         <v>0.9599276420525443</v>
@@ -9019,10 +9019,10 @@
         <v>2</v>
       </c>
       <c r="E313" t="n">
-        <v>0.0002062766802213256</v>
+        <v>0.0002062766802212787</v>
       </c>
       <c r="F313" t="n">
-        <v>0.07105736231883328</v>
+        <v>0.07105736231880097</v>
       </c>
       <c r="G313" t="n">
         <v>0.9287363610009178</v>
@@ -9042,13 +9042,13 @@
         <v>2</v>
       </c>
       <c r="E314" t="n">
-        <v>0.000168109001712286</v>
+        <v>0.0001681090017122095</v>
       </c>
       <c r="F314" t="n">
-        <v>0.1762869156808687</v>
+        <v>0.1762869156807886</v>
       </c>
       <c r="G314" t="n">
-        <v>0.8235449753173667</v>
+        <v>0.823544975317554</v>
       </c>
     </row>
     <row r="315">
@@ -9065,13 +9065,13 @@
         <v>2</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0006766602215451896</v>
+        <v>0.000676660221544728</v>
       </c>
       <c r="F315" t="n">
-        <v>0.3775551150455362</v>
+        <v>0.3775551150453645</v>
       </c>
       <c r="G315" t="n">
-        <v>0.6217682247328614</v>
+        <v>0.6217682247331442</v>
       </c>
     </row>
     <row r="316">
@@ -9082,19 +9082,19 @@
         <v>-0.06138811628823403</v>
       </c>
       <c r="C316" t="n">
-        <v>0.0003471971954322061</v>
+        <v>0.0003471971954322065</v>
       </c>
       <c r="D316" t="n">
         <v>2</v>
       </c>
       <c r="E316" t="n">
-        <v>0.003468598939420698</v>
+        <v>0.003468598939416755</v>
       </c>
       <c r="F316" t="n">
-        <v>0.4417070115273837</v>
+        <v>0.4417070115271828</v>
       </c>
       <c r="G316" t="n">
-        <v>0.5548243895331749</v>
+        <v>0.5548243895334273</v>
       </c>
     </row>
     <row r="317">
@@ -9111,13 +9111,13 @@
         <v>2</v>
       </c>
       <c r="E317" t="n">
-        <v>0.00271880650495592</v>
+        <v>0.002718806504952829</v>
       </c>
       <c r="F317" t="n">
-        <v>0.3683642086410064</v>
+        <v>0.3683642086408389</v>
       </c>
       <c r="G317" t="n">
-        <v>0.6289169848540002</v>
+        <v>0.6289169848541432</v>
       </c>
     </row>
     <row r="318">
@@ -9134,10 +9134,10 @@
         <v>2</v>
       </c>
       <c r="E318" t="n">
-        <v>0.003610326079634336</v>
+        <v>0.00361032607962941</v>
       </c>
       <c r="F318" t="n">
-        <v>0.2968942559045708</v>
+        <v>0.2968942559044358</v>
       </c>
       <c r="G318" t="n">
         <v>0.6994954180158782</v>
@@ -9157,10 +9157,10 @@
         <v>2</v>
       </c>
       <c r="E319" t="n">
-        <v>0.002355659647772252</v>
+        <v>0.002355659647770646</v>
       </c>
       <c r="F319" t="n">
-        <v>0.1732365529425052</v>
+        <v>0.1732365529424264</v>
       </c>
       <c r="G319" t="n">
         <v>0.8244077874097283</v>
@@ -9180,10 +9180,10 @@
         <v>2</v>
       </c>
       <c r="E320" t="n">
-        <v>0.0009754001448558163</v>
+        <v>0.000975400144855151</v>
       </c>
       <c r="F320" t="n">
-        <v>0.1001156589792943</v>
+        <v>0.1001156589792487</v>
       </c>
       <c r="G320" t="n">
         <v>0.8989089408759328</v>
@@ -9203,10 +9203,10 @@
         <v>2</v>
       </c>
       <c r="E321" t="n">
-        <v>0.000510508170855012</v>
+        <v>0.0005105081708546638</v>
       </c>
       <c r="F321" t="n">
-        <v>0.06836052008739656</v>
+        <v>0.06836052008738101</v>
       </c>
       <c r="G321" t="n">
         <v>0.9311289717417022</v>
@@ -9226,7 +9226,7 @@
         <v>2</v>
       </c>
       <c r="E322" t="n">
-        <v>0.0002630084110344767</v>
+        <v>0.0002630084110341777</v>
       </c>
       <c r="F322" t="n">
         <v>0.05054010674653931</v>
@@ -9249,10 +9249,10 @@
         <v>2</v>
       </c>
       <c r="E323" t="n">
-        <v>0.0001486191619279097</v>
+        <v>0.0001486191619278083</v>
       </c>
       <c r="F323" t="n">
-        <v>0.0433015424134592</v>
+        <v>0.04330154241346904</v>
       </c>
       <c r="G323" t="n">
         <v>0.9565498384246721</v>
@@ -9272,10 +9272,10 @@
         <v>2</v>
       </c>
       <c r="E324" t="n">
-        <v>0.0001342372619871105</v>
+        <v>0.000134237261987019</v>
       </c>
       <c r="F324" t="n">
-        <v>0.04502953564700917</v>
+        <v>0.04502953564701941</v>
       </c>
       <c r="G324" t="n">
         <v>0.9548362270910029</v>
@@ -9286,7 +9286,7 @@
         <v>46022</v>
       </c>
       <c r="B325" t="n">
-        <v>-0.002782332919957095</v>
+        <v>-0.002782332919957094</v>
       </c>
       <c r="C325" t="n">
         <v>-0.009222956945157942</v>
@@ -9295,7 +9295,7 @@
         <v>2</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0001773903056241351</v>
+        <v>0.0001773903056239738</v>
       </c>
       <c r="F325" t="n">
         <v>0.04878851821988994</v>
@@ -9318,7 +9318,7 @@
         <v>2</v>
       </c>
       <c r="E326" t="n">
-        <v>0.0003610358152162176</v>
+        <v>0.0003610358152158893</v>
       </c>
       <c r="F326" t="n">
         <v>0.0665193853485828</v>
@@ -9451,7 +9451,7 @@
         <v>2.553821088304183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6705033279323741</v>
+        <v>0.6705033279323739</v>
       </c>
     </row>
     <row r="4">
@@ -9475,7 +9475,7 @@
         <v>1.309077358501373</v>
       </c>
       <c r="F4" t="n">
-        <v>3.085385141958819</v>
+        <v>3.085385141958818</v>
       </c>
       <c r="G4" t="n">
         <v>0.05561822845801535</v>
@@ -9484,7 +9484,7 @@
         <v>1.510196445421101</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1912287557505327</v>
+        <v>-0.1912287557505328</v>
       </c>
     </row>
     <row r="7">
@@ -9562,7 +9562,7 @@
         <v>6.970909093622122</v>
       </c>
       <c r="C11" t="n">
-        <v>3.085385141958819</v>
+        <v>3.085385141958818</v>
       </c>
       <c r="D11" t="n">
         <v>4.912287762024016</v>
@@ -9591,13 +9591,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.967802276779141</v>
+        <v>5.96780227677914</v>
       </c>
       <c r="C13" t="n">
         <v>4.555142635983143</v>
       </c>
       <c r="D13" t="n">
-        <v>3.676318499049032</v>
+        <v>3.676318499049033</v>
       </c>
     </row>
     <row r="14">
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7469677246327467</v>
+        <v>0.7469677246327342</v>
       </c>
       <c r="C27" t="n">
-        <v>0.000102181058251092</v>
+        <v>0.0001021810582511423</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2529300943090022</v>
+        <v>0.2529300943090146</v>
       </c>
     </row>
     <row r="28">
@@ -9800,13 +9800,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6.064632446586386e-05</v>
+        <v>6.064632446605379e-05</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9462266770272545</v>
+        <v>0.9462266770272358</v>
       </c>
       <c r="D28" t="n">
-        <v>0.05371267664827954</v>
+        <v>0.05371267664829821</v>
       </c>
     </row>
     <row r="29">
@@ -9816,13 +9816,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0712213585235837</v>
+        <v>0.07122135852358837</v>
       </c>
       <c r="C29" t="n">
-        <v>0.005216606261056959</v>
+        <v>0.005216606261051958</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9235620352153594</v>
+        <v>0.9235620352153596</v>
       </c>
     </row>
     <row r="32">
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7469677246327467</v>
+        <v>0.7469677246327342</v>
       </c>
       <c r="C33" t="n">
-        <v>3.952065002571673</v>
+        <v>3.952065002571477</v>
       </c>
     </row>
     <row r="34">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9462266770272545</v>
+        <v>0.9462266770272358</v>
       </c>
       <c r="C34" t="n">
-        <v>18.59658181263673</v>
+        <v>18.59658181263028</v>
       </c>
     </row>
     <row r="35">
@@ -9870,10 +9870,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9235620352153594</v>
+        <v>0.9235620352153596</v>
       </c>
       <c r="C35" t="n">
-        <v>13.08250426103626</v>
+        <v>13.08250426103629</v>
       </c>
     </row>
     <row r="38">
@@ -10034,7 +10034,7 @@
         <v>0.04917591483714769</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3582757703625186</v>
+        <v>0.3582757703625183</v>
       </c>
       <c r="F45" t="n">
         <v>1</v>
@@ -10079,7 +10079,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.6705033279323739</v>
+        <v>0.670503327932374</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -10106,7 +10106,7 @@
         <v>0.2233825173843047</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4386748552506711</v>
+        <v>0.4386748552506712</v>
       </c>
       <c r="F48" t="n">
         <v>1</v>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-0.1912287557505328</v>
+        <v>-0.1912287557505329</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.07728531742035202</v>
+        <v>0.07728531742035201</v>
       </c>
       <c r="E51" t="n">
         <v>0.2434153204194337</v>
@@ -10242,10 +10242,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>2012.999629148209</v>
+        <v>2014.630666022684</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -10257,13 +10257,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1846153846153846</v>
+        <v>0.916923076923077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8092307692307692</v>
+        <v>0.006153846153846154</v>
       </c>
       <c r="H2" t="n">
-        <v>0.006153846153846154</v>
+        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="3">
@@ -10271,7 +10271,7 @@
         <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>1999.703052661506</v>
+        <v>1999.703052661512</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -10297,7 +10297,7 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1999.699693420132</v>
+        <v>1999.699693420137</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -10323,7 +10323,7 @@
         <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>1999.698780150217</v>
+        <v>1999.698780150218</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -10349,7 +10349,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>1999.403302694786</v>
+        <v>1999.403302694787</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -10375,7 +10375,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>1999.005227767386</v>
+        <v>1999.005227767387</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -10401,7 +10401,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1998.797564959682</v>
+        <v>1998.797564959689</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
@@ -10427,7 +10427,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1996.614096705174</v>
+        <v>1996.614096705179</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -10453,7 +10453,7 @@
         <v>25</v>
       </c>
       <c r="B10" t="n">
-        <v>1996.301687728533</v>
+        <v>1996.301687728531</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -10479,7 +10479,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>1993.990258594793</v>
+        <v>1993.990258594798</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
@@ -10505,7 +10505,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="n">
-        <v>1993.787739472414</v>
+        <v>1993.787739472419</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
@@ -10531,7 +10531,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>1992.55119009208</v>
+        <v>1992.551190092084</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -10557,7 +10557,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>1991.954575495566</v>
+        <v>1991.954575495565</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
@@ -10583,7 +10583,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>1991.721150824205</v>
+        <v>1991.721150824201</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -10609,7 +10609,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="n">
-        <v>1991.716283104939</v>
+        <v>1991.716283104922</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
@@ -10635,7 +10635,7 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>1991.71432160941</v>
+        <v>1991.714321609421</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
@@ -10661,7 +10661,7 @@
         <v>4</v>
       </c>
       <c r="B18" t="n">
-        <v>1991.19878380388</v>
+        <v>1991.198783803881</v>
       </c>
       <c r="C18" t="n">
         <v>3</v>
@@ -10687,7 +10687,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1990.422829805384</v>
+        <v>1990.422829805381</v>
       </c>
       <c r="C19" t="n">
         <v>3</v>
@@ -10713,7 +10713,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>1988.906540204375</v>
+        <v>1988.90654020438</v>
       </c>
       <c r="C20" t="n">
         <v>3</v>
@@ -10736,10 +10736,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>1985.843478050544</v>
+        <v>1987.184967501878</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -10751,13 +10751,13 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0.916923076923077</v>
+        <v>0.1846153846153846</v>
       </c>
       <c r="G21" t="n">
+        <v>0.8092307692307692</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.006153846153846154</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.07692307692307693</v>
       </c>
     </row>
     <row r="22">
@@ -10791,7 +10791,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="n">
-        <v>1984.170504016129</v>
+        <v>1984.170504016137</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -10817,7 +10817,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>1982.244328365119</v>
+        <v>1982.244328365108</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -10843,7 +10843,7 @@
         <v>17</v>
       </c>
       <c r="B25" t="n">
-        <v>1981.650921320115</v>
+        <v>1981.650921320117</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
@@ -10869,7 +10869,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="n">
-        <v>1962.101072567986</v>
+        <v>1962.10107256799</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
@@ -10949,7 +10949,7 @@
         <v>0.03746962579352606</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008686003136073352</v>
+        <v>0.0008686003136073347</v>
       </c>
       <c r="D2" t="n">
         <v>-0.01080589954831271</v>
@@ -10958,13 +10958,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>8.056670957917813e-16</v>
+        <v>8.056670957923309e-16</v>
       </c>
       <c r="G2" t="n">
         <v>0.9999998616156158</v>
       </c>
       <c r="H2" t="n">
-        <v>1.383842710927139e-07</v>
+        <v>1.383842710928712e-07</v>
       </c>
     </row>
     <row r="3">
@@ -10978,19 +10978,19 @@
         <v>-0.0389385984265305</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0003536214957211813</v>
+        <v>-0.0003536214957211817</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.212899977194691e-05</v>
+        <v>1.212899977198276e-05</v>
       </c>
       <c r="G3" t="n">
         <v>0.9893451966820005</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01064267431822167</v>
+        <v>0.01064267431822409</v>
       </c>
     </row>
     <row r="4">
@@ -11010,13 +11010,13 @@
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001041915994909438</v>
+        <v>0.0001041915994910148</v>
       </c>
       <c r="G4" t="n">
         <v>0.6094440534467574</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3904517549536816</v>
+        <v>0.3904517549537704</v>
       </c>
     </row>
     <row r="5">
@@ -11143,7 +11143,7 @@
         <v>0.0646914650738018</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05541293280418563</v>
+        <v>0.05541293280417302</v>
       </c>
       <c r="H9" t="n">
         <v>0.8798956021220271</v>
@@ -11192,10 +11192,10 @@
         <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0639315348767608</v>
+        <v>0.06393153487677533</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02050971459953585</v>
+        <v>0.02050971459954051</v>
       </c>
       <c r="H11" t="n">
         <v>0.9155587505237355</v>
@@ -11218,7 +11218,7 @@
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02988900397326883</v>
+        <v>0.02988900397327562</v>
       </c>
       <c r="G12" t="n">
         <v>0.02008845586591707</v>
@@ -11244,7 +11244,7 @@
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0637288741436482</v>
+        <v>0.06372887414366268</v>
       </c>
       <c r="G13" t="n">
         <v>0.02335311501860043</v>
@@ -11273,7 +11273,7 @@
         <v>0.2446252699693398</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03020725543405388</v>
+        <v>0.03020725543404014</v>
       </c>
       <c r="H14" t="n">
         <v>0.7251674745966794</v>
@@ -11296,10 +11296,10 @@
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.283148865266299</v>
+        <v>0.2831488652662346</v>
       </c>
       <c r="G15" t="n">
-        <v>0.03129616376496868</v>
+        <v>0.03129616376495445</v>
       </c>
       <c r="H15" t="n">
         <v>0.6855549709688049</v>
@@ -11322,10 +11322,10 @@
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4465879763475035</v>
+        <v>0.446587976347605</v>
       </c>
       <c r="G16" t="n">
-        <v>0.03520233454702096</v>
+        <v>0.03520233454701295</v>
       </c>
       <c r="H16" t="n">
         <v>0.5182096891053908</v>
@@ -11351,7 +11351,7 @@
         <v>0.2383628038243836</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02640691128666642</v>
+        <v>0.02640691128666042</v>
       </c>
       <c r="H17" t="n">
         <v>0.7352302848889948</v>
@@ -11377,7 +11377,7 @@
         <v>0.1128058186806452</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01490458468163614</v>
+        <v>0.01490458468163275</v>
       </c>
       <c r="H18" t="n">
         <v>0.8722895966377759</v>
@@ -11403,7 +11403,7 @@
         <v>0.07253121465571638</v>
       </c>
       <c r="G19" t="n">
-        <v>0.007185691343394574</v>
+        <v>0.00718569134339294</v>
       </c>
       <c r="H19" t="n">
         <v>0.9202830940008951</v>
@@ -11417,7 +11417,7 @@
         <v>-0.02054671670874412</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002590752718941235</v>
+        <v>0.002590752718941236</v>
       </c>
       <c r="D20" t="n">
         <v>-0.04812780908847517</v>
@@ -11426,10 +11426,10 @@
         <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09646623131561077</v>
+        <v>0.09646623131558885</v>
       </c>
       <c r="G20" t="n">
-        <v>0.002350711377360707</v>
+        <v>0.002350711377360173</v>
       </c>
       <c r="H20" t="n">
         <v>0.9011830573070175</v>
@@ -11455,7 +11455,7 @@
         <v>0.1778024541067369</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001840212924827975</v>
+        <v>0.001840212924827557</v>
       </c>
       <c r="H21" t="n">
         <v>0.8203573329684882</v>
@@ -11481,10 +11481,10 @@
         <v>0.437886860487631</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0009391079034194951</v>
+        <v>0.0009391079034190681</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5611740316089296</v>
+        <v>0.5611740316090572</v>
       </c>
     </row>
     <row r="23">
@@ -11492,10 +11492,10 @@
         <v>36830</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.009817373019298678</v>
+        <v>-0.00981737301929868</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0035647155073691</v>
+        <v>0.003564715507369099</v>
       </c>
       <c r="D23" t="n">
         <v>-0.03932877386610094</v>
@@ -11507,7 +11507,7 @@
         <v>0.4940698733793991</v>
       </c>
       <c r="G23" t="n">
-        <v>8.999417177088147e-05</v>
+        <v>8.999417177084055e-05</v>
       </c>
       <c r="H23" t="n">
         <v>0.5058401324488022</v>
@@ -11533,7 +11533,7 @@
         <v>0.877389561819975</v>
       </c>
       <c r="G24" t="n">
-        <v>4.76010888812218e-05</v>
+        <v>4.760108888120016e-05</v>
       </c>
       <c r="H24" t="n">
         <v>0.1225628370911319</v>
@@ -11559,7 +11559,7 @@
         <v>0.6216584694307107</v>
       </c>
       <c r="G25" t="n">
-        <v>2.910857450026071e-05</v>
+        <v>2.910857450024085e-05</v>
       </c>
       <c r="H25" t="n">
         <v>0.3783124219948795</v>
@@ -11611,7 +11611,7 @@
         <v>0.9793251046267744</v>
       </c>
       <c r="G27" t="n">
-        <v>1.498926490216638e-05</v>
+        <v>1.498926490215616e-05</v>
       </c>
       <c r="H27" t="n">
         <v>0.02065990610834249</v>
@@ -11637,10 +11637,10 @@
         <v>0.8929408801694136</v>
       </c>
       <c r="G28" t="n">
-        <v>1.093411664825701e-05</v>
+        <v>1.093411664825203e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1070481857139369</v>
+        <v>0.1070481857139613</v>
       </c>
     </row>
     <row r="29">
@@ -11674,22 +11674,22 @@
         <v>37042</v>
       </c>
       <c r="B30" t="n">
-        <v>0.003486086443238612</v>
+        <v>0.003486086443238613</v>
       </c>
       <c r="C30" t="n">
         <v>-0.001127279284296733</v>
       </c>
       <c r="D30" t="n">
-        <v>0.003598869900885482</v>
+        <v>0.003598869900885483</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2465132599764704</v>
+        <v>0.2465132599764144</v>
       </c>
       <c r="G30" t="n">
-        <v>0.000157365095281138</v>
+        <v>0.0001573650952810664</v>
       </c>
       <c r="H30" t="n">
         <v>0.7533293749283203</v>
@@ -11715,7 +11715,7 @@
         <v>0.3362374089764807</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0001546007126297877</v>
+        <v>0.0001546007126297174</v>
       </c>
       <c r="H31" t="n">
         <v>0.6636079903108322</v>
@@ -11741,10 +11741,10 @@
         <v>0.5874826655297963</v>
       </c>
       <c r="G32" t="n">
-        <v>1.31744090734169e-05</v>
+        <v>1.317440907341091e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4125041600610415</v>
+        <v>0.4125041600611353</v>
       </c>
     </row>
     <row r="33">
@@ -11755,7 +11755,7 @@
         <v>-0.06774638797380172</v>
       </c>
       <c r="C33" t="n">
-        <v>0.009266260116781109</v>
+        <v>0.009266260116781111</v>
       </c>
       <c r="D33" t="n">
         <v>0.02555475389781614</v>
@@ -11767,10 +11767,10 @@
         <v>0.9252546110209743</v>
       </c>
       <c r="G33" t="n">
-        <v>1.403849126686317e-05</v>
+        <v>1.403849126685678e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07473135048779779</v>
+        <v>0.0747313504877808</v>
       </c>
     </row>
     <row r="34">
@@ -11793,10 +11793,10 @@
         <v>0.9778201425993034</v>
       </c>
       <c r="G34" t="n">
-        <v>1.241013242077458e-05</v>
+        <v>1.241013242076894e-05</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0221674472682653</v>
+        <v>0.02216744726826025</v>
       </c>
     </row>
     <row r="35">
@@ -11819,10 +11819,10 @@
         <v>0.5242277502286627</v>
       </c>
       <c r="G35" t="n">
-        <v>1.137579780577295e-05</v>
+        <v>1.137579780577037e-05</v>
       </c>
       <c r="H35" t="n">
-        <v>0.475760873973563</v>
+        <v>0.4757608739734548</v>
       </c>
     </row>
     <row r="36">
@@ -11845,10 +11845,10 @@
         <v>0.2426513770270717</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002044755864518963</v>
+        <v>0.0002044755864518498</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7571441473864055</v>
+        <v>0.7571441473865776</v>
       </c>
     </row>
     <row r="37">
@@ -11868,10 +11868,10 @@
         <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07917930664673986</v>
+        <v>0.07917930664672185</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0005546102654108448</v>
+        <v>0.0005546102654104665</v>
       </c>
       <c r="H37" t="n">
         <v>0.9202660830879087</v>
@@ -11885,7 +11885,7 @@
         <v>-0.01610219756674967</v>
       </c>
       <c r="C38" t="n">
-        <v>0.004747939606516225</v>
+        <v>0.004747939606516224</v>
       </c>
       <c r="D38" t="n">
         <v>0.01142395087060779</v>
@@ -11894,10 +11894,10 @@
         <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>0.07559539605971741</v>
+        <v>0.07559539605970021</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0005042341094030752</v>
+        <v>0.0005042341094028459</v>
       </c>
       <c r="H38" t="n">
         <v>0.9239003698309577</v>
@@ -11911,7 +11911,7 @@
         <v>-0.02076850133664727</v>
       </c>
       <c r="C39" t="n">
-        <v>0.009776868601837064</v>
+        <v>0.009776868601837062</v>
       </c>
       <c r="D39" t="n">
         <v>0.04706115647726332</v>
@@ -11923,10 +11923,10 @@
         <v>0.1409535399317332</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0003548463216892674</v>
+        <v>0.0003548463216891868</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8586916137464934</v>
+        <v>0.8586916137466887</v>
       </c>
     </row>
     <row r="40">
@@ -11946,10 +11946,10 @@
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2729019169171155</v>
+        <v>0.2729019169170534</v>
       </c>
       <c r="G40" t="n">
-        <v>0.000123496339436084</v>
+        <v>0.0001234963394360278</v>
       </c>
       <c r="H40" t="n">
         <v>0.7269745867434466</v>
@@ -11972,10 +11972,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7764818980625</v>
+        <v>0.7764818980623235</v>
       </c>
       <c r="G41" t="n">
-        <v>2.90140339654506e-05</v>
+        <v>2.901403396542421e-05</v>
       </c>
       <c r="H41" t="n">
         <v>0.2234890879036332</v>
@@ -12001,10 +12001,10 @@
         <v>0.77424830371974</v>
       </c>
       <c r="G42" t="n">
-        <v>4.003269263108961e-06</v>
+        <v>4.003269263108051e-06</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2257476930110978</v>
+        <v>0.2257476930110464</v>
       </c>
     </row>
     <row r="43">
@@ -12027,10 +12027,10 @@
         <v>0.9813089705584973</v>
       </c>
       <c r="G43" t="n">
-        <v>5.334127047636219e-08</v>
+        <v>5.334127047635006e-08</v>
       </c>
       <c r="H43" t="n">
-        <v>0.01869097610020466</v>
+        <v>0.01869097610020891</v>
       </c>
     </row>
     <row r="44">
@@ -12053,7 +12053,7 @@
         <v>0.9969416039061811</v>
       </c>
       <c r="G44" t="n">
-        <v>8.104239841984587e-09</v>
+        <v>8.104239841980901e-09</v>
       </c>
       <c r="H44" t="n">
         <v>0.003058387989467875</v>
@@ -12079,10 +12079,10 @@
         <v>0.9375507140462114</v>
       </c>
       <c r="G45" t="n">
-        <v>2.42022166772992e-08</v>
+        <v>2.420221667735423e-08</v>
       </c>
       <c r="H45" t="n">
-        <v>0.06244926175148436</v>
+        <v>0.06244926175149856</v>
       </c>
     </row>
     <row r="46">
@@ -12105,10 +12105,10 @@
         <v>0.9996752742254645</v>
       </c>
       <c r="G46" t="n">
-        <v>1.883573288905255e-08</v>
+        <v>1.883573288903541e-08</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0003247069388192591</v>
+        <v>0.0003247069388191853</v>
       </c>
     </row>
     <row r="47">
@@ -12128,13 +12128,13 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.795124985543636</v>
+        <v>0.7951249855438168</v>
       </c>
       <c r="G47" t="n">
-        <v>4.319963066407006e-06</v>
+        <v>4.319963066409953e-06</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2048706944932339</v>
+        <v>0.2048706944931874</v>
       </c>
     </row>
     <row r="48">
@@ -12148,7 +12148,7 @@
         <v>-0.01979083550891</v>
       </c>
       <c r="D48" t="n">
-        <v>5.877903375543043e-05</v>
+        <v>5.877903375543021e-05</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -12157,10 +12157,10 @@
         <v>0.6981648619087379</v>
       </c>
       <c r="G48" t="n">
-        <v>2.96990982818997e-05</v>
+        <v>2.969909828187944e-05</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3018054389929479</v>
+        <v>0.3018054389928793</v>
       </c>
     </row>
     <row r="49">
@@ -12183,7 +12183,7 @@
         <v>0.855914651935592</v>
       </c>
       <c r="G49" t="n">
-        <v>5.998798170844725e-05</v>
+        <v>5.998798170840633e-05</v>
       </c>
       <c r="H49" t="n">
         <v>0.1440253600825999</v>
@@ -12209,7 +12209,7 @@
         <v>0.5271215673020813</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0001630988149086463</v>
+        <v>0.0001630988149085721</v>
       </c>
       <c r="H50" t="n">
         <v>0.4727153338830348</v>
@@ -12232,10 +12232,10 @@
         <v>2</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3191795642371115</v>
+        <v>0.3191795642370389</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0001917687330685739</v>
+        <v>0.0001917687330684867</v>
       </c>
       <c r="H51" t="n">
         <v>0.6806286670299119</v>
@@ -12261,7 +12261,7 @@
         <v>0.1246298973555564</v>
       </c>
       <c r="G52" t="n">
-        <v>0.00260964643542504</v>
+        <v>0.002609646435423854</v>
       </c>
       <c r="H52" t="n">
         <v>0.8727604562091235</v>
@@ -12287,7 +12287,7 @@
         <v>0.139638085558695</v>
       </c>
       <c r="G53" t="n">
-        <v>0.009776491271235338</v>
+        <v>0.00977649127122867</v>
       </c>
       <c r="H53" t="n">
         <v>0.850585423170142</v>
@@ -12310,10 +12310,10 @@
         <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1854653374298174</v>
+        <v>0.1854653374298596</v>
       </c>
       <c r="G54" t="n">
-        <v>0.01471445646071626</v>
+        <v>0.01471445646070622</v>
       </c>
       <c r="H54" t="n">
         <v>0.7998202061095456</v>
@@ -12336,13 +12336,13 @@
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1293721860498165</v>
+        <v>0.129372186049846</v>
       </c>
       <c r="G55" t="n">
-        <v>0.01278363644458315</v>
+        <v>0.01278363644457443</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8578441775054949</v>
+        <v>0.85784417750569</v>
       </c>
     </row>
     <row r="56">
@@ -12362,13 +12362,13 @@
         <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2434763090196306</v>
+        <v>0.243476309019686</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01467023574678044</v>
+        <v>0.01467023574677377</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7418534552336788</v>
+        <v>0.7418534552335101</v>
       </c>
     </row>
     <row r="57">
@@ -12388,13 +12388,13 @@
         <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1145575004361886</v>
+        <v>0.1145575004362146</v>
       </c>
       <c r="G57" t="n">
         <v>0.007203992523762077</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8782385070399471</v>
+        <v>0.878238507039947</v>
       </c>
     </row>
     <row r="58">
@@ -12414,10 +12414,10 @@
         <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1392691190181015</v>
+        <v>0.1392691190181332</v>
       </c>
       <c r="G58" t="n">
-        <v>0.003962301293705134</v>
+        <v>0.003962301293704233</v>
       </c>
       <c r="H58" t="n">
         <v>0.8567685796882559</v>
@@ -12443,7 +12443,7 @@
         <v>0.03925214454187488</v>
       </c>
       <c r="G59" t="n">
-        <v>0.002685032935932965</v>
+        <v>0.002685032935932355</v>
       </c>
       <c r="H59" t="n">
         <v>0.9580628225222211</v>
@@ -12466,10 +12466,10 @@
         <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>0.01397490004512682</v>
+        <v>0.01397490004513</v>
       </c>
       <c r="G60" t="n">
-        <v>0.002145749326888544</v>
+        <v>0.002145749326888056</v>
       </c>
       <c r="H60" t="n">
         <v>0.9838793506279916</v>
@@ -12492,10 +12492,10 @@
         <v>2</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01311185284808058</v>
+        <v>0.0131118528480776</v>
       </c>
       <c r="G61" t="n">
-        <v>0.001888584251368408</v>
+        <v>0.001888584251367549</v>
       </c>
       <c r="H61" t="n">
         <v>0.9849995629004592</v>
@@ -12521,7 +12521,7 @@
         <v>0.01482363527762251</v>
       </c>
       <c r="G62" t="n">
-        <v>0.001347521953516355</v>
+        <v>0.001347521953515743</v>
       </c>
       <c r="H62" t="n">
         <v>0.9838288427687825</v>
@@ -12544,10 +12544,10 @@
         <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0256643163873676</v>
+        <v>0.02566431638737343</v>
       </c>
       <c r="G63" t="n">
-        <v>0.001684931390580166</v>
+        <v>0.001684931390579782</v>
       </c>
       <c r="H63" t="n">
         <v>0.9726507522219531</v>
@@ -12573,10 +12573,10 @@
         <v>0.06231231617032708</v>
       </c>
       <c r="G64" t="n">
-        <v>0.002913141470329246</v>
+        <v>0.002913141470327259</v>
       </c>
       <c r="H64" t="n">
-        <v>0.934774542359445</v>
+        <v>0.9347745423592324</v>
       </c>
     </row>
     <row r="65">
@@ -12596,10 +12596,10 @@
         <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>0.09684916914582564</v>
+        <v>0.09684916914584765</v>
       </c>
       <c r="G65" t="n">
-        <v>0.005653238482320221</v>
+        <v>0.005653238482315079</v>
       </c>
       <c r="H65" t="n">
         <v>0.8974975923718131</v>
@@ -12625,7 +12625,7 @@
         <v>0.02197036771233849</v>
       </c>
       <c r="G66" t="n">
-        <v>0.00351589349752239</v>
+        <v>0.003515893497519192</v>
       </c>
       <c r="H66" t="n">
         <v>0.9745137387902353</v>
@@ -12651,7 +12651,7 @@
         <v>0.01553281931748821</v>
       </c>
       <c r="G67" t="n">
-        <v>0.001946965938342235</v>
+        <v>0.001946965938340464</v>
       </c>
       <c r="H67" t="n">
         <v>0.9825202147441162</v>
@@ -12677,10 +12677,10 @@
         <v>0.04025003455062792</v>
       </c>
       <c r="G68" t="n">
-        <v>0.001017457420265478</v>
+        <v>0.001017457420264553</v>
       </c>
       <c r="H68" t="n">
-        <v>0.9587325080291069</v>
+        <v>0.9587325080291068</v>
       </c>
     </row>
     <row r="69">
@@ -12703,7 +12703,7 @@
         <v>0.03226112951741725</v>
       </c>
       <c r="G69" t="n">
-        <v>0.001004257439514146</v>
+        <v>0.001004257439513689</v>
       </c>
       <c r="H69" t="n">
         <v>0.966734613043098</v>
@@ -12729,7 +12729,7 @@
         <v>0.01099072862755846</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0008985760405242022</v>
+        <v>0.0008985760405235893</v>
       </c>
       <c r="H70" t="n">
         <v>0.9881106953318355</v>
@@ -12755,7 +12755,7 @@
         <v>0.008851022228271414</v>
       </c>
       <c r="G71" t="n">
-        <v>0.00072836730294081</v>
+        <v>0.0007283673029403131</v>
       </c>
       <c r="H71" t="n">
         <v>0.9904206104687601</v>
@@ -12778,10 +12778,10 @@
         <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>0.01135756951416288</v>
+        <v>0.01135756951416546</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0004394071821869582</v>
+        <v>0.0004394071821866584</v>
       </c>
       <c r="H72" t="n">
         <v>0.9882030233035561</v>
@@ -12804,10 +12804,10 @@
         <v>2</v>
       </c>
       <c r="F73" t="n">
-        <v>0.01458466415686402</v>
+        <v>0.01458466415686734</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0004259812191151791</v>
+        <v>0.0004259812191149854</v>
       </c>
       <c r="H73" t="n">
         <v>0.9849893546239428</v>
@@ -12833,7 +12833,7 @@
         <v>0.02167515208178159</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0003107957648425448</v>
+        <v>0.0003107957648423327</v>
       </c>
       <c r="H74" t="n">
         <v>0.9780140521534672</v>
@@ -12856,10 +12856,10 @@
         <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>0.01144874073844263</v>
+        <v>0.01144874073844523</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0006431298036232313</v>
+        <v>0.0006431298036227925</v>
       </c>
       <c r="H75" t="n">
         <v>0.9879081294580194</v>
@@ -12885,7 +12885,7 @@
         <v>0.01999126949839513</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0007534381646004486</v>
+        <v>0.0007534381646001059</v>
       </c>
       <c r="H76" t="n">
         <v>0.9792552923371055</v>
@@ -12911,7 +12911,7 @@
         <v>0.03605463900609781</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0004660986499148598</v>
+        <v>0.0004660986499145419</v>
       </c>
       <c r="H77" t="n">
         <v>0.9634792623439463</v>
@@ -12937,7 +12937,7 @@
         <v>0.02209774497365756</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0004875067625001201</v>
+        <v>0.0004875067624998984</v>
       </c>
       <c r="H78" t="n">
         <v>0.9774147482638059</v>
@@ -12963,7 +12963,7 @@
         <v>0.01260247731452135</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0007508358759147694</v>
+        <v>0.0007508358759144279</v>
       </c>
       <c r="H79" t="n">
         <v>0.9866466868095356</v>
@@ -12986,10 +12986,10 @@
         <v>2</v>
       </c>
       <c r="F80" t="n">
-        <v>0.01046563706805586</v>
+        <v>0.01046563706805824</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0009184743019829436</v>
+        <v>0.0009184743019827347</v>
       </c>
       <c r="H80" t="n">
         <v>0.9886158886299753</v>
@@ -13012,10 +13012,10 @@
         <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>0.02059044131386036</v>
+        <v>0.02059044131386504</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0008476445084705992</v>
+        <v>0.0008476445084702138</v>
       </c>
       <c r="H81" t="n">
         <v>0.9785619141777195</v>
@@ -13038,10 +13038,10 @@
         <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>0.02335399016759139</v>
+        <v>0.02335399016760201</v>
       </c>
       <c r="G82" t="n">
-        <v>0.001150809181506622</v>
+        <v>0.001150809181506361</v>
       </c>
       <c r="H82" t="n">
         <v>0.9754952006509379</v>
@@ -13064,10 +13064,10 @@
         <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>0.01743946336646914</v>
+        <v>0.0174394633664731</v>
       </c>
       <c r="G83" t="n">
-        <v>0.00167308239538432</v>
+        <v>0.001673082395383559</v>
       </c>
       <c r="H83" t="n">
         <v>0.9808874542380471</v>
@@ -13081,7 +13081,7 @@
         <v>0.03402946422756281</v>
       </c>
       <c r="C84" t="n">
-        <v>0.002718764958117402</v>
+        <v>0.002718764958117403</v>
       </c>
       <c r="D84" t="n">
         <v>0.05513030349324788</v>
@@ -13090,13 +13090,13 @@
         <v>2</v>
       </c>
       <c r="F84" t="n">
-        <v>0.01066048334332052</v>
+        <v>0.01066048334332294</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0009957385640207098</v>
+        <v>0.0009957385640204834</v>
       </c>
       <c r="H84" t="n">
-        <v>0.9883437780926749</v>
+        <v>0.988343778092675</v>
       </c>
     </row>
     <row r="85">
@@ -13104,7 +13104,7 @@
         <v>38717</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.002845288954795244</v>
+        <v>-0.002845288954795243</v>
       </c>
       <c r="C85" t="n">
         <v>0.008921207357914518</v>
@@ -13116,10 +13116,10 @@
         <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>0.01296955279026171</v>
+        <v>0.01296955279025876</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0006576766519210114</v>
+        <v>0.0006576766519207122</v>
       </c>
       <c r="H85" t="n">
         <v>0.9863727705578585</v>
@@ -13142,10 +13142,10 @@
         <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>0.01477819756567306</v>
+        <v>0.01477819756567642</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0002789984849879064</v>
+        <v>0.0002789984849878429</v>
       </c>
       <c r="H86" t="n">
         <v>0.9849428039492889</v>
@@ -13156,7 +13156,7 @@
         <v>38776</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.0006837315003157397</v>
+        <v>-0.0006837315003157393</v>
       </c>
       <c r="C87" t="n">
         <v>-0.004183623699470881</v>
@@ -13168,10 +13168,10 @@
         <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>0.009716276844206376</v>
+        <v>0.009716276844208584</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0005131875405760604</v>
+        <v>0.000513187540575827</v>
       </c>
       <c r="H87" t="n">
         <v>0.9897705356153206</v>
@@ -13194,7 +13194,7 @@
         <v>2</v>
       </c>
       <c r="F88" t="n">
-        <v>0.01407058824231031</v>
+        <v>0.01407058824231671</v>
       </c>
       <c r="G88" t="n">
         <v>0.0005983450367497066</v>
@@ -13223,7 +13223,7 @@
         <v>0.03275931012198034</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0002079886487153064</v>
+        <v>0.0002079886487152119</v>
       </c>
       <c r="H89" t="n">
         <v>0.9670327012293606</v>
@@ -13246,10 +13246,10 @@
         <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>0.03112386352476612</v>
+        <v>0.0311238635247732</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0004923750780552695</v>
+        <v>0.0004923750780549337</v>
       </c>
       <c r="H90" t="n">
         <v>0.9683837613970854</v>
@@ -13272,10 +13272,10 @@
         <v>2</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01586748736356924</v>
+        <v>0.01586748736357285</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0002953605797649753</v>
+        <v>0.0002953605797648411</v>
       </c>
       <c r="H91" t="n">
         <v>0.983837152056556</v>
@@ -13301,7 +13301,7 @@
         <v>0.01241110019097567</v>
       </c>
       <c r="G92" t="n">
-        <v>0.00044321164535409</v>
+        <v>0.0004432116453536869</v>
       </c>
       <c r="H92" t="n">
         <v>0.9871456881637172</v>
@@ -13327,7 +13327,7 @@
         <v>0.01218774743116113</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0004111612410593008</v>
+        <v>0.0004111612410590204</v>
       </c>
       <c r="H93" t="n">
         <v>0.987401091327708</v>
@@ -13350,10 +13350,10 @@
         <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>0.01122525890321516</v>
+        <v>0.01122525890322027</v>
       </c>
       <c r="G94" t="n">
-        <v>0.000344976538912741</v>
+        <v>0.0003449765389125841</v>
       </c>
       <c r="H94" t="n">
         <v>0.9884297645578271</v>
@@ -13376,10 +13376,10 @@
         <v>2</v>
       </c>
       <c r="F95" t="n">
-        <v>0.006984009611045091</v>
+        <v>0.006984009611043502</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0006895605020777278</v>
+        <v>0.0006895605020774142</v>
       </c>
       <c r="H95" t="n">
         <v>0.9923264298868194</v>
@@ -13405,7 +13405,7 @@
         <v>0.009156787474455594</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0008587812740284791</v>
+        <v>0.0008587812740280886</v>
       </c>
       <c r="H96" t="n">
         <v>0.9899844312514888</v>
@@ -13428,10 +13428,10 @@
         <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>0.007240689771373455</v>
+        <v>0.007240689771376748</v>
       </c>
       <c r="G97" t="n">
-        <v>0.001218884039329233</v>
+        <v>0.001218884039328402</v>
       </c>
       <c r="H97" t="n">
         <v>0.9915404261892687</v>
@@ -13454,10 +13454,10 @@
         <v>2</v>
       </c>
       <c r="F98" t="n">
-        <v>0.00861225597511628</v>
+        <v>0.008612255975118239</v>
       </c>
       <c r="G98" t="n">
-        <v>0.001167731590881572</v>
+        <v>0.001167731590881041</v>
       </c>
       <c r="H98" t="n">
         <v>0.990220012434005</v>
@@ -13483,7 +13483,7 @@
         <v>0.02234011196223983</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0009274171705755542</v>
+        <v>0.0009274171705749215</v>
       </c>
       <c r="H99" t="n">
         <v>0.9767324708671784</v>
@@ -13509,10 +13509,10 @@
         <v>0.008580314351327415</v>
       </c>
       <c r="G100" t="n">
-        <v>0.001064328734631523</v>
+        <v>0.001064328734631039</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9903553569140752</v>
+        <v>0.9903553569140751</v>
       </c>
     </row>
     <row r="101">
@@ -13532,10 +13532,10 @@
         <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>0.007281754961527873</v>
+        <v>0.007281754961529529</v>
       </c>
       <c r="G101" t="n">
-        <v>0.001180211565087426</v>
+        <v>0.001180211565086353</v>
       </c>
       <c r="H101" t="n">
         <v>0.9915380334732711</v>
@@ -13558,10 +13558,10 @@
         <v>2</v>
       </c>
       <c r="F102" t="n">
-        <v>0.009879927998871484</v>
+        <v>0.00987992799887373</v>
       </c>
       <c r="G102" t="n">
-        <v>0.001154723227786386</v>
+        <v>0.001154723227785861</v>
       </c>
       <c r="H102" t="n">
         <v>0.9889653487732593</v>
@@ -13584,10 +13584,10 @@
         <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>0.02594741260531237</v>
+        <v>0.02594741260531827</v>
       </c>
       <c r="G103" t="n">
-        <v>0.001066609584084317</v>
+        <v>0.001066609584083589</v>
       </c>
       <c r="H103" t="n">
         <v>0.9729859778104902</v>
@@ -13610,10 +13610,10 @@
         <v>2</v>
       </c>
       <c r="F104" t="n">
-        <v>0.05935167761064485</v>
+        <v>0.05935167761067183</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0005809302064508828</v>
+        <v>0.0005809302064506185</v>
       </c>
       <c r="H104" t="n">
         <v>0.9400673921828946</v>
@@ -13636,10 +13636,10 @@
         <v>2</v>
       </c>
       <c r="F105" t="n">
-        <v>0.04374827924067969</v>
+        <v>0.04374827924068964</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0004063144378974215</v>
+        <v>0.0004063144378971443</v>
       </c>
       <c r="H105" t="n">
         <v>0.9558454063214075</v>
@@ -13653,7 +13653,7 @@
         <v>0.03352305135437444</v>
       </c>
       <c r="C106" t="n">
-        <v>0.000268536980876533</v>
+        <v>0.0002685369808765334</v>
       </c>
       <c r="D106" t="n">
         <v>0.09611736939953514</v>
@@ -13662,10 +13662,10 @@
         <v>2</v>
       </c>
       <c r="F106" t="n">
-        <v>0.07237425510930601</v>
+        <v>0.07237425510932247</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0001070279218847885</v>
+        <v>0.0001070279218847155</v>
       </c>
       <c r="H106" t="n">
         <v>0.9275187169688869</v>
@@ -13679,7 +13679,7 @@
         <v>0.01258704390080084</v>
       </c>
       <c r="C107" t="n">
-        <v>0.007736157572576452</v>
+        <v>0.007736157572576453</v>
       </c>
       <c r="D107" t="n">
         <v>0.06590555952658023</v>
@@ -13691,7 +13691,7 @@
         <v>0.1755883507873448</v>
       </c>
       <c r="G107" t="n">
-        <v>7.565082318725708e-05</v>
+        <v>7.565082318718828e-05</v>
       </c>
       <c r="H107" t="n">
         <v>0.8243359983895501</v>
@@ -13717,10 +13717,10 @@
         <v>0.6195333365032557</v>
       </c>
       <c r="G108" t="n">
-        <v>1.103595347155135e-05</v>
+        <v>1.103595347154382e-05</v>
       </c>
       <c r="H108" t="n">
-        <v>0.3804556275432701</v>
+        <v>0.3804556275433567</v>
       </c>
     </row>
     <row r="109">
@@ -13743,10 +13743,10 @@
         <v>0.6341636136750546</v>
       </c>
       <c r="G109" t="n">
-        <v>3.218375533627599e-05</v>
+        <v>3.218375533626135e-05</v>
       </c>
       <c r="H109" t="n">
-        <v>0.3658042025696268</v>
+        <v>0.3658042025695436</v>
       </c>
     </row>
     <row r="110">
@@ -13769,7 +13769,7 @@
         <v>0.8841548902332073</v>
       </c>
       <c r="G110" t="n">
-        <v>2.843963815386831e-05</v>
+        <v>2.843963815384891e-05</v>
       </c>
       <c r="H110" t="n">
         <v>0.1158166701287094</v>
@@ -13795,10 +13795,10 @@
         <v>0.6066862651892378</v>
       </c>
       <c r="G111" t="n">
-        <v>3.927251073741042e-05</v>
+        <v>3.92725107373747e-05</v>
       </c>
       <c r="H111" t="n">
-        <v>0.3932744623001085</v>
+        <v>0.3932744623000191</v>
       </c>
     </row>
     <row r="112">
@@ -13806,7 +13806,7 @@
         <v>39538</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.006027409667488031</v>
+        <v>-0.006027409667488032</v>
       </c>
       <c r="C112" t="n">
         <v>0.01148223471221401</v>
@@ -13821,7 +13821,7 @@
         <v>0.3456544611799443</v>
       </c>
       <c r="G112" t="n">
-        <v>2.346013683587574e-05</v>
+        <v>2.346013683586507e-05</v>
       </c>
       <c r="H112" t="n">
         <v>0.6543220786832797</v>
@@ -13847,7 +13847,7 @@
         <v>0.2480510497798334</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0001656797437813118</v>
+        <v>0.0001656797437811987</v>
       </c>
       <c r="H113" t="n">
         <v>0.7517832704763383</v>
@@ -13870,10 +13870,10 @@
         <v>2</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3175837467672779</v>
+        <v>0.3175837467673501</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0001705235352990674</v>
+        <v>0.0001705235352990286</v>
       </c>
       <c r="H114" t="n">
         <v>0.682245729697423</v>
@@ -13899,7 +13899,7 @@
         <v>0.9048506530724137</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0002055063218631477</v>
+        <v>0.0002055063218630543</v>
       </c>
       <c r="H115" t="n">
         <v>0.09494384060583159</v>
@@ -13925,10 +13925,10 @@
         <v>0.7622668102200402</v>
       </c>
       <c r="G116" t="n">
-        <v>4.351757273546402e-05</v>
+        <v>4.351757273544423e-05</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2376896722071609</v>
+        <v>0.237689672207269</v>
       </c>
     </row>
     <row r="117">
@@ -13948,13 +13948,13 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.857176310915797</v>
+        <v>0.8571763109156022</v>
       </c>
       <c r="G117" t="n">
-        <v>6.978640639846622e-08</v>
+        <v>6.978640639852969e-08</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1428236192978639</v>
+        <v>0.1428236192979289</v>
       </c>
     </row>
     <row r="118">
@@ -13977,10 +13977,10 @@
         <v>0.9979708323334747</v>
       </c>
       <c r="G118" t="n">
-        <v>9.5962195274243e-08</v>
+        <v>9.596219527448301e-08</v>
       </c>
       <c r="H118" t="n">
-        <v>0.002029071704320614</v>
+        <v>0.002029071704321075</v>
       </c>
     </row>
     <row r="119">
@@ -14003,10 +14003,10 @@
         <v>0.9999999992326138</v>
       </c>
       <c r="G119" t="n">
-        <v>4.941834592286653e-17</v>
+        <v>4.941834592294519e-17</v>
       </c>
       <c r="H119" t="n">
-        <v>7.672999163234883e-10</v>
+        <v>7.672999163236628e-10</v>
       </c>
     </row>
     <row r="120">
@@ -14029,10 +14029,10 @@
         <v>0.9999975933716851</v>
       </c>
       <c r="G120" t="n">
-        <v>7.560719405084809e-11</v>
+        <v>7.560719405091686e-11</v>
       </c>
       <c r="H120" t="n">
-        <v>2.406552677644809e-06</v>
+        <v>2.406552677645356e-06</v>
       </c>
     </row>
     <row r="121">
@@ -14055,7 +14055,7 @@
         <v>0.9952861426893951</v>
       </c>
       <c r="G121" t="n">
-        <v>6.312300330080984e-06</v>
+        <v>6.312300330086725e-06</v>
       </c>
       <c r="H121" t="n">
         <v>0.00470754501023914</v>
@@ -14081,7 +14081,7 @@
         <v>0.9998573727843755</v>
       </c>
       <c r="G122" t="n">
-        <v>5.963199330497759e-05</v>
+        <v>5.963199330495047e-05</v>
       </c>
       <c r="H122" t="n">
         <v>8.299522231479575e-05</v>
@@ -14107,10 +14107,10 @@
         <v>0.9998066395508568</v>
       </c>
       <c r="G123" t="n">
-        <v>6.205089341099058e-05</v>
+        <v>6.205089341097647e-05</v>
       </c>
       <c r="H123" t="n">
-        <v>0.0001313095557411391</v>
+        <v>0.0001313095557410794</v>
       </c>
     </row>
     <row r="124">
@@ -14159,10 +14159,10 @@
         <v>0.7161756432109551</v>
       </c>
       <c r="G125" t="n">
-        <v>3.565285447552459e-05</v>
+        <v>3.565285447550027e-05</v>
       </c>
       <c r="H125" t="n">
-        <v>0.2837887039345217</v>
+        <v>0.2837887039344572</v>
       </c>
     </row>
     <row r="126">
@@ -14185,10 +14185,10 @@
         <v>0.3401067799636339</v>
       </c>
       <c r="G126" t="n">
-        <v>1.184935445695552e-05</v>
+        <v>1.184935445694744e-05</v>
       </c>
       <c r="H126" t="n">
-        <v>0.6598813706819865</v>
+        <v>0.6598813706818365</v>
       </c>
     </row>
     <row r="127">
@@ -14211,10 +14211,10 @@
         <v>0.09907268081809818</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0002463848953102623</v>
+        <v>0.0002463848953100942</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9006809342864981</v>
+        <v>0.9006809342867029</v>
       </c>
     </row>
     <row r="128">
@@ -14234,10 +14234,10 @@
         <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>0.05398477600214974</v>
+        <v>0.05398477600216202</v>
       </c>
       <c r="G128" t="n">
-        <v>0.001258440931520492</v>
+        <v>0.001258440931519633</v>
       </c>
       <c r="H128" t="n">
         <v>0.9447567830662859</v>
@@ -14260,10 +14260,10 @@
         <v>2</v>
       </c>
       <c r="F129" t="n">
-        <v>0.02171996094507955</v>
+        <v>0.02171996094508449</v>
       </c>
       <c r="G129" t="n">
-        <v>0.001349778374246057</v>
+        <v>0.001349778374245136</v>
       </c>
       <c r="H129" t="n">
         <v>0.976930260680572</v>
@@ -14286,10 +14286,10 @@
         <v>2</v>
       </c>
       <c r="F130" t="n">
-        <v>0.02281269216884645</v>
+        <v>0.02281269216886201</v>
       </c>
       <c r="G130" t="n">
-        <v>0.001254222295821249</v>
+        <v>0.001254222295820393</v>
       </c>
       <c r="H130" t="n">
         <v>0.9759330855352697</v>
@@ -14312,10 +14312,10 @@
         <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>0.04891255820823143</v>
+        <v>0.04891255820825368</v>
       </c>
       <c r="G131" t="n">
-        <v>0.001189550131479424</v>
+        <v>0.001189550131478612</v>
       </c>
       <c r="H131" t="n">
         <v>0.9498978916602777</v>
@@ -14341,7 +14341,7 @@
         <v>0.1126576436111737</v>
       </c>
       <c r="G132" t="n">
-        <v>0.000809155486252326</v>
+        <v>0.0008091554862514061</v>
       </c>
       <c r="H132" t="n">
         <v>0.8865332009025017</v>
@@ -14364,10 +14364,10 @@
         <v>2</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1196290436587774</v>
+        <v>0.1196290436588318</v>
       </c>
       <c r="G133" t="n">
-        <v>0.001151560076691048</v>
+        <v>0.001151560076690262</v>
       </c>
       <c r="H133" t="n">
         <v>0.8792193962644239</v>
@@ -14390,10 +14390,10 @@
         <v>2</v>
       </c>
       <c r="F134" t="n">
-        <v>0.128412343497037</v>
+        <v>0.1284123434970662</v>
       </c>
       <c r="G134" t="n">
-        <v>0.0003230959160954572</v>
+        <v>0.0003230959160951633</v>
       </c>
       <c r="H134" t="n">
         <v>0.8712645605868968</v>
@@ -14416,10 +14416,10 @@
         <v>2</v>
       </c>
       <c r="F135" t="n">
-        <v>0.05792263143958883</v>
+        <v>0.057922631439602</v>
       </c>
       <c r="G135" t="n">
-        <v>0.0004035362252151423</v>
+        <v>0.0004035362252149588</v>
       </c>
       <c r="H135" t="n">
         <v>0.9416738323352285</v>
@@ -14442,10 +14442,10 @@
         <v>2</v>
       </c>
       <c r="F136" t="n">
-        <v>0.09164234753132153</v>
+        <v>0.09164234753134237</v>
       </c>
       <c r="G136" t="n">
-        <v>0.0002686122371918976</v>
+        <v>0.0002686122371917755</v>
       </c>
       <c r="H136" t="n">
         <v>0.9080890402314292</v>
@@ -14471,7 +14471,7 @@
         <v>0.2857888398666912</v>
       </c>
       <c r="G137" t="n">
-        <v>1.633554976191431e-05</v>
+        <v>1.633554976190688e-05</v>
       </c>
       <c r="H137" t="n">
         <v>0.714194824583575</v>
@@ -14497,10 +14497,10 @@
         <v>0.9732892747220565</v>
       </c>
       <c r="G138" t="n">
-        <v>3.101193661211657e-06</v>
+        <v>3.101193661208131e-06</v>
       </c>
       <c r="H138" t="n">
-        <v>0.02670762408436953</v>
+        <v>0.02670762408435739</v>
       </c>
     </row>
     <row r="139">
@@ -14523,7 +14523,7 @@
         <v>0.9671155425037832</v>
       </c>
       <c r="G139" t="n">
-        <v>2.591680270957969e-06</v>
+        <v>2.591680270955023e-06</v>
       </c>
       <c r="H139" t="n">
         <v>0.03288186581586764</v>
@@ -14549,7 +14549,7 @@
         <v>0.8695156592676101</v>
       </c>
       <c r="G140" t="n">
-        <v>1.898173326154106e-05</v>
+        <v>1.898173326152811e-05</v>
       </c>
       <c r="H140" t="n">
         <v>0.1304653589990672</v>
@@ -14575,7 +14575,7 @@
         <v>0.8212141940014713</v>
       </c>
       <c r="G141" t="n">
-        <v>3.437439102183918e-05</v>
+        <v>3.437439102182356e-05</v>
       </c>
       <c r="H141" t="n">
         <v>0.1787514316075124</v>
@@ -14601,7 +14601,7 @@
         <v>0.4039588694753503</v>
       </c>
       <c r="G142" t="n">
-        <v>0.0001248263128789107</v>
+        <v>0.0001248263128788539</v>
       </c>
       <c r="H142" t="n">
         <v>0.595916304211796</v>
@@ -14624,10 +14624,10 @@
         <v>2</v>
       </c>
       <c r="F143" t="n">
-        <v>0.07932207037607848</v>
+        <v>0.07932207037609651</v>
       </c>
       <c r="G143" t="n">
-        <v>0.0002892243407254069</v>
+        <v>0.000289224340725341</v>
       </c>
       <c r="H143" t="n">
         <v>0.9203887052831918</v>
@@ -14653,7 +14653,7 @@
         <v>0.02884952887278202</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0004761039052896843</v>
+        <v>0.0004761039052894678</v>
       </c>
       <c r="H144" t="n">
         <v>0.9706743672219812</v>
@@ -14676,10 +14676,10 @@
         <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>0.03488207202962085</v>
+        <v>0.03488207202962878</v>
       </c>
       <c r="G145" t="n">
-        <v>0.0002234376985598436</v>
+        <v>0.000223437698559742</v>
       </c>
       <c r="H145" t="n">
         <v>0.9648944902718789</v>
@@ -14702,10 +14702,10 @@
         <v>2</v>
       </c>
       <c r="F146" t="n">
-        <v>0.01686022628222842</v>
+        <v>0.01686022628223608</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0001612089336322892</v>
+        <v>0.0001612089336321059</v>
       </c>
       <c r="H146" t="n">
         <v>0.9829785647842163</v>
@@ -14731,7 +14731,7 @@
         <v>0.01134055345017393</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0002949004731833719</v>
+        <v>0.0002949004731832378</v>
       </c>
       <c r="H147" t="n">
         <v>0.9883645460765749</v>
@@ -14754,10 +14754,10 @@
         <v>2</v>
       </c>
       <c r="F148" t="n">
-        <v>0.01809371965095938</v>
+        <v>0.01809371965096349</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0004140277685089712</v>
+        <v>0.0004140277685087829</v>
       </c>
       <c r="H148" t="n">
         <v>0.9814922525805283</v>
@@ -14783,7 +14783,7 @@
         <v>0.0637312932438195</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0002512136402779216</v>
+        <v>0.0002512136402776931</v>
       </c>
       <c r="H149" t="n">
         <v>0.9360174931159826</v>
@@ -14806,10 +14806,10 @@
         <v>2</v>
       </c>
       <c r="F150" t="n">
-        <v>0.164197674625086</v>
+        <v>0.1641976746251233</v>
       </c>
       <c r="G150" t="n">
-        <v>9.442180392464847e-05</v>
+        <v>9.442180392458407e-05</v>
       </c>
       <c r="H150" t="n">
         <v>0.8357079035710541</v>
@@ -14835,7 +14835,7 @@
         <v>0.2720761976589574</v>
       </c>
       <c r="G151" t="n">
-        <v>6.563268320620085e-05</v>
+        <v>6.563268320618593e-05</v>
       </c>
       <c r="H151" t="n">
         <v>0.7278581696577546</v>
@@ -14861,10 +14861,10 @@
         <v>0.728215474742989</v>
       </c>
       <c r="G152" t="n">
-        <v>1.893231207224648e-06</v>
+        <v>1.893231207225079e-06</v>
       </c>
       <c r="H152" t="n">
-        <v>0.2717826320257043</v>
+        <v>0.2717826320257661</v>
       </c>
     </row>
     <row r="153">
@@ -14887,7 +14887,7 @@
         <v>0.9954098237195063</v>
       </c>
       <c r="G153" t="n">
-        <v>1.006240856381271e-07</v>
+        <v>1.006240856380585e-07</v>
       </c>
       <c r="H153" t="n">
         <v>0.004590075656307789</v>
@@ -14913,7 +14913,7 @@
         <v>0.9933506915239401</v>
       </c>
       <c r="G154" t="n">
-        <v>3.828230619922052e-10</v>
+        <v>3.82823061991944e-10</v>
       </c>
       <c r="H154" t="n">
         <v>0.006649308093309082</v>
@@ -14939,10 +14939,10 @@
         <v>0.7913257292809189</v>
       </c>
       <c r="G155" t="n">
-        <v>2.051970319879147e-06</v>
+        <v>2.051970319880547e-06</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2086722187487542</v>
+        <v>0.2086722187488016</v>
       </c>
     </row>
     <row r="156">
@@ -14965,7 +14965,7 @@
         <v>0.3567588850425901</v>
       </c>
       <c r="G156" t="n">
-        <v>3.909872351221561e-05</v>
+        <v>3.909872351219783e-05</v>
       </c>
       <c r="H156" t="n">
         <v>0.6432020162338089</v>
@@ -14991,10 +14991,10 @@
         <v>0.2902316736460575</v>
       </c>
       <c r="G157" t="n">
-        <v>3.961946101720437e-06</v>
+        <v>3.961946101719536e-06</v>
       </c>
       <c r="H157" t="n">
-        <v>0.7097643644077707</v>
+        <v>0.709764364407932</v>
       </c>
     </row>
     <row r="158">
@@ -15017,7 +15017,7 @@
         <v>0.1230268751214422</v>
       </c>
       <c r="G158" t="n">
-        <v>8.152478638218403e-05</v>
+        <v>8.152478638214697e-05</v>
       </c>
       <c r="H158" t="n">
         <v>0.8768916000922354</v>
@@ -15043,7 +15043,7 @@
         <v>0.04083592419692861</v>
       </c>
       <c r="G159" t="n">
-        <v>0.0002993168473925655</v>
+        <v>0.0002993168473924294</v>
       </c>
       <c r="H159" t="n">
         <v>0.9588647589555843</v>
@@ -15069,10 +15069,10 @@
         <v>0.04766044947302329</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0003211830334517463</v>
+        <v>0.0003211830334514542</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9520183674935565</v>
+        <v>0.9520183674935566</v>
       </c>
     </row>
     <row r="161">
@@ -15092,10 +15092,10 @@
         <v>2</v>
       </c>
       <c r="F161" t="n">
-        <v>0.1891807217263407</v>
+        <v>0.1891807217263837</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0001211083302736158</v>
+        <v>0.0001211083302735056</v>
       </c>
       <c r="H161" t="n">
         <v>0.810698169943349</v>
@@ -15121,10 +15121,10 @@
         <v>0.4113435506471388</v>
       </c>
       <c r="G162" t="n">
-        <v>5.616665933073245e-06</v>
+        <v>5.616665933068137e-06</v>
       </c>
       <c r="H162" t="n">
-        <v>0.5886508326868612</v>
+        <v>0.5886508326869951</v>
       </c>
     </row>
     <row r="163">
@@ -15147,7 +15147,7 @@
         <v>0.07390417656050188</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0002451353001701711</v>
+        <v>0.0002451353001700595</v>
       </c>
       <c r="H163" t="n">
         <v>0.9258506881392287</v>
@@ -15170,10 +15170,10 @@
         <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>0.02265056224594438</v>
+        <v>0.02265056224594952</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0004657281980778881</v>
+        <v>0.0004657281980776763</v>
       </c>
       <c r="H164" t="n">
         <v>0.9768837095559144</v>
@@ -15199,7 +15199,7 @@
         <v>0.009377809895550895</v>
       </c>
       <c r="G165" t="n">
-        <v>0.0005239122459058014</v>
+        <v>0.0005239122459053249</v>
       </c>
       <c r="H165" t="n">
         <v>0.9900982778584544</v>
@@ -15225,7 +15225,7 @@
         <v>0.007822153215376449</v>
       </c>
       <c r="G166" t="n">
-        <v>0.0005418108033656416</v>
+        <v>0.0005418108033651488</v>
       </c>
       <c r="H166" t="n">
         <v>0.9916360359812488</v>
@@ -15248,10 +15248,10 @@
         <v>2</v>
       </c>
       <c r="F167" t="n">
-        <v>0.01215457876918047</v>
+        <v>0.012154578769186</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0005476767723455538</v>
+        <v>0.0005476767723450557</v>
       </c>
       <c r="H167" t="n">
         <v>0.987297744458555</v>
@@ -15274,10 +15274,10 @@
         <v>2</v>
       </c>
       <c r="F168" t="n">
-        <v>0.009254880447404709</v>
+        <v>0.009254880447408917</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0005528045586216518</v>
+        <v>0.0005528045586212747</v>
       </c>
       <c r="H168" t="n">
         <v>0.9901923149939681</v>
@@ -15300,10 +15300,10 @@
         <v>2</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0068473723112286</v>
+        <v>0.006847372311231714</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0005951137038403102</v>
+        <v>0.000595113703839769</v>
       </c>
       <c r="H169" t="n">
         <v>0.9925575139849795</v>
@@ -15326,10 +15326,10 @@
         <v>2</v>
       </c>
       <c r="F170" t="n">
-        <v>0.008873001797432544</v>
+        <v>0.008873001797434561</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0005014363368894717</v>
+        <v>0.0005014363368891296</v>
       </c>
       <c r="H170" t="n">
         <v>0.9906255618655768</v>
@@ -15352,10 +15352,10 @@
         <v>2</v>
       </c>
       <c r="F171" t="n">
-        <v>0.01375259957390574</v>
+        <v>0.01375259957390887</v>
       </c>
       <c r="G171" t="n">
-        <v>0.0002310570610626913</v>
+        <v>0.0002310570610625862</v>
       </c>
       <c r="H171" t="n">
         <v>0.9860163433649379</v>
@@ -15381,7 +15381,7 @@
         <v>0.01256866017644723</v>
       </c>
       <c r="G172" t="n">
-        <v>0.0003592868914477587</v>
+        <v>0.0003592868914473502</v>
       </c>
       <c r="H172" t="n">
         <v>0.9870720529320729</v>
@@ -15407,7 +15407,7 @@
         <v>0.03242671257667949</v>
       </c>
       <c r="G173" t="n">
-        <v>0.0001044436083138961</v>
+        <v>0.0001044436083137774</v>
       </c>
       <c r="H173" t="n">
         <v>0.9674688438149076</v>
@@ -15433,7 +15433,7 @@
         <v>0.03238660988853388</v>
       </c>
       <c r="G174" t="n">
-        <v>0.0003922318940354309</v>
+        <v>0.0003922318940350741</v>
       </c>
       <c r="H174" t="n">
         <v>0.9672211582175284</v>
@@ -15456,10 +15456,10 @@
         <v>2</v>
       </c>
       <c r="F175" t="n">
-        <v>0.05106713197505332</v>
+        <v>0.05106713197504171</v>
       </c>
       <c r="G175" t="n">
-        <v>0.0001764745601871338</v>
+        <v>0.0001764745601869733</v>
       </c>
       <c r="H175" t="n">
         <v>0.9487563934648596</v>
@@ -15482,10 +15482,10 @@
         <v>2</v>
       </c>
       <c r="F176" t="n">
-        <v>0.03253045027209869</v>
+        <v>0.0325304502720913</v>
       </c>
       <c r="G176" t="n">
-        <v>0.0003776115695018291</v>
+        <v>0.0003776115695016574</v>
       </c>
       <c r="H176" t="n">
         <v>0.9670919381583152</v>
@@ -15508,10 +15508,10 @@
         <v>2</v>
       </c>
       <c r="F177" t="n">
-        <v>0.04701981992484493</v>
+        <v>0.04701981992483425</v>
       </c>
       <c r="G177" t="n">
-        <v>0.001195689912255022</v>
+        <v>0.001195689912254479</v>
       </c>
       <c r="H177" t="n">
         <v>0.9517844901629003</v>
@@ -15534,10 +15534,10 @@
         <v>2</v>
       </c>
       <c r="F178" t="n">
-        <v>0.03152526727487982</v>
+        <v>0.03152526727487265</v>
       </c>
       <c r="G178" t="n">
-        <v>0.000690569763355721</v>
+        <v>0.00069056976335525</v>
       </c>
       <c r="H178" t="n">
         <v>0.9677841629616947</v>
@@ -15560,10 +15560,10 @@
         <v>2</v>
       </c>
       <c r="F179" t="n">
-        <v>0.01837504652430406</v>
+        <v>0.01837504652429988</v>
       </c>
       <c r="G179" t="n">
-        <v>0.0006895420565970257</v>
+        <v>0.0006895420565965554</v>
       </c>
       <c r="H179" t="n">
         <v>0.9809354114190918</v>
@@ -15586,10 +15586,10 @@
         <v>2</v>
       </c>
       <c r="F180" t="n">
-        <v>0.02135209336983498</v>
+        <v>0.02135209336983013</v>
       </c>
       <c r="G180" t="n">
-        <v>0.0001955313130944113</v>
+        <v>0.0001955313130942779</v>
       </c>
       <c r="H180" t="n">
         <v>0.9784523753171456</v>
@@ -15615,7 +15615,7 @@
         <v>0.02020657986744247</v>
       </c>
       <c r="G181" t="n">
-        <v>0.0004722080362885744</v>
+        <v>0.0004722080362882523</v>
       </c>
       <c r="H181" t="n">
         <v>0.9793212120962019</v>
@@ -15638,10 +15638,10 @@
         <v>2</v>
       </c>
       <c r="F182" t="n">
-        <v>0.06903325293141974</v>
+        <v>0.06903325293143543</v>
       </c>
       <c r="G182" t="n">
-        <v>0.0003596650732909582</v>
+        <v>0.0003596650732907129</v>
       </c>
       <c r="H182" t="n">
         <v>0.9306070819952429</v>
@@ -15664,10 +15664,10 @@
         <v>2</v>
       </c>
       <c r="F183" t="n">
-        <v>0.02347181230624713</v>
+        <v>0.02347181230625247</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0004145726568892087</v>
+        <v>0.0004145726568891144</v>
       </c>
       <c r="H183" t="n">
         <v>0.9761136150368678</v>
@@ -15690,10 +15690,10 @@
         <v>2</v>
       </c>
       <c r="F184" t="n">
-        <v>0.009812720437333111</v>
+        <v>0.00981272043733088</v>
       </c>
       <c r="G184" t="n">
-        <v>0.0004551497433269443</v>
+        <v>0.0004551497433266339</v>
       </c>
       <c r="H184" t="n">
         <v>0.9897321298192436</v>
@@ -15716,10 +15716,10 @@
         <v>2</v>
       </c>
       <c r="F185" t="n">
-        <v>0.009856568884525073</v>
+        <v>0.009856568884522831</v>
       </c>
       <c r="G185" t="n">
-        <v>0.000497671256336915</v>
+        <v>0.0004976712563366887</v>
       </c>
       <c r="H185" t="n">
         <v>0.989645759859063</v>
@@ -15742,10 +15742,10 @@
         <v>2</v>
       </c>
       <c r="F186" t="n">
-        <v>0.01639769543614009</v>
+        <v>0.01639769543613637</v>
       </c>
       <c r="G186" t="n">
-        <v>0.0004325987832697611</v>
+        <v>0.0004325987832694661</v>
       </c>
       <c r="H186" t="n">
         <v>0.9831697057805139</v>
@@ -15768,10 +15768,10 @@
         <v>2</v>
       </c>
       <c r="F187" t="n">
-        <v>0.01064007626271147</v>
+        <v>0.01064007626270663</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0004659414411755372</v>
+        <v>0.0004659414411753253</v>
       </c>
       <c r="H187" t="n">
         <v>0.9888939822962181</v>
@@ -15794,10 +15794,10 @@
         <v>2</v>
       </c>
       <c r="F188" t="n">
-        <v>0.01353159817488652</v>
+        <v>0.01353159817488037</v>
       </c>
       <c r="G188" t="n">
-        <v>0.0005969191851420424</v>
+        <v>0.0005969191851416352</v>
       </c>
       <c r="H188" t="n">
         <v>0.985871482639935</v>
@@ -15820,10 +15820,10 @@
         <v>2</v>
       </c>
       <c r="F189" t="n">
-        <v>0.0175658541660553</v>
+        <v>0.0175658541660513</v>
       </c>
       <c r="G189" t="n">
-        <v>0.000940158591337193</v>
+        <v>0.0009401585913367655</v>
       </c>
       <c r="H189" t="n">
         <v>0.98149398724259</v>
@@ -15849,7 +15849,7 @@
         <v>0.01856282568377929</v>
       </c>
       <c r="G190" t="n">
-        <v>0.0005421919823232299</v>
+        <v>0.0005421919823228601</v>
       </c>
       <c r="H190" t="n">
         <v>0.9808949823339369</v>
@@ -15872,10 +15872,10 @@
         <v>2</v>
       </c>
       <c r="F191" t="n">
-        <v>0.0192361422232598</v>
+        <v>0.01923614222325106</v>
       </c>
       <c r="G191" t="n">
-        <v>0.0005364902257021479</v>
+        <v>0.000536490225701782</v>
       </c>
       <c r="H191" t="n">
         <v>0.9802273675511076</v>
@@ -15901,7 +15901,7 @@
         <v>0.02144295139397408</v>
       </c>
       <c r="G192" t="n">
-        <v>0.0006448792389272846</v>
+        <v>0.0006448792389271381</v>
       </c>
       <c r="H192" t="n">
         <v>0.977912169367024</v>
@@ -15924,10 +15924,10 @@
         <v>2</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0512622941467243</v>
+        <v>0.05126229414673595</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0005583076337239457</v>
+        <v>0.0005583076337238187</v>
       </c>
       <c r="H193" t="n">
         <v>0.9481793982195914</v>
@@ -15953,7 +15953,7 @@
         <v>0.2146417094149684</v>
       </c>
       <c r="G194" t="n">
-        <v>0.0003959349070778803</v>
+        <v>0.0003959349070777903</v>
       </c>
       <c r="H194" t="n">
         <v>0.7849623556779654</v>
@@ -15976,10 +15976,10 @@
         <v>2</v>
       </c>
       <c r="F195" t="n">
-        <v>0.08428385292687669</v>
+        <v>0.08428385292685753</v>
       </c>
       <c r="G195" t="n">
-        <v>0.0003785307777592803</v>
+        <v>0.0003785307777590221</v>
       </c>
       <c r="H195" t="n">
         <v>0.9153376162954017</v>
@@ -16002,10 +16002,10 @@
         <v>2</v>
       </c>
       <c r="F196" t="n">
-        <v>0.03556086076329</v>
+        <v>0.03556086076327383</v>
       </c>
       <c r="G196" t="n">
-        <v>0.0003921024054334521</v>
+        <v>0.000392102405433363</v>
       </c>
       <c r="H196" t="n">
         <v>0.9640470368313023</v>
@@ -16028,10 +16028,10 @@
         <v>2</v>
       </c>
       <c r="F197" t="n">
-        <v>0.01118861331819273</v>
+        <v>0.0111886133181851</v>
       </c>
       <c r="G197" t="n">
-        <v>0.0008416626572176909</v>
+        <v>0.0008416626572169255</v>
       </c>
       <c r="H197" t="n">
         <v>0.9879697240246863</v>
@@ -16054,10 +16054,10 @@
         <v>2</v>
       </c>
       <c r="F198" t="n">
-        <v>0.01190474388253124</v>
+        <v>0.01190474388252853</v>
       </c>
       <c r="G198" t="n">
-        <v>0.001132152196675192</v>
+        <v>0.00113215219667442</v>
       </c>
       <c r="H198" t="n">
         <v>0.9869631039208094</v>
@@ -16080,10 +16080,10 @@
         <v>2</v>
       </c>
       <c r="F199" t="n">
-        <v>0.04170916800267736</v>
+        <v>0.04170916800269633</v>
       </c>
       <c r="G199" t="n">
-        <v>0.001426822264725104</v>
+        <v>0.00142682226472478</v>
       </c>
       <c r="H199" t="n">
         <v>0.9568640097326261</v>
@@ -16109,7 +16109,7 @@
         <v>0.110282346343748</v>
       </c>
       <c r="G200" t="n">
-        <v>0.0005055796503496958</v>
+        <v>0.0005055796503493509</v>
       </c>
       <c r="H200" t="n">
         <v>0.8892120740059021</v>
@@ -16132,10 +16132,10 @@
         <v>2</v>
       </c>
       <c r="F201" t="n">
-        <v>0.2594086538814726</v>
+        <v>0.2594086538815316</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0009411823911621501</v>
+        <v>0.0009411823911623642</v>
       </c>
       <c r="H201" t="n">
         <v>0.7396501637273019</v>
@@ -16158,10 +16158,10 @@
         <v>2</v>
       </c>
       <c r="F202" t="n">
-        <v>0.1627550638649944</v>
+        <v>0.1627550638649203</v>
       </c>
       <c r="G202" t="n">
-        <v>0.0003703709257290829</v>
+        <v>0.0003703709257289986</v>
       </c>
       <c r="H202" t="n">
         <v>0.8368745652093249</v>
@@ -16184,10 +16184,10 @@
         <v>2</v>
       </c>
       <c r="F203" t="n">
-        <v>0.1045150781142213</v>
+        <v>0.1045150781141975</v>
       </c>
       <c r="G203" t="n">
-        <v>0.0004080899667814105</v>
+        <v>0.0004080899667812249</v>
       </c>
       <c r="H203" t="n">
         <v>0.8950768319190723</v>
@@ -16210,10 +16210,10 @@
         <v>2</v>
       </c>
       <c r="F204" t="n">
-        <v>0.07116762373545354</v>
+        <v>0.07116762373543736</v>
       </c>
       <c r="G204" t="n">
-        <v>0.0001661967693751028</v>
+        <v>0.0001661967693750273</v>
       </c>
       <c r="H204" t="n">
         <v>0.9286661794952789</v>
@@ -16239,7 +16239,7 @@
         <v>0.1115683398246455</v>
       </c>
       <c r="G205" t="n">
-        <v>0.0003150997250910455</v>
+        <v>0.0003150997250909739</v>
       </c>
       <c r="H205" t="n">
         <v>0.8881165604503004</v>
@@ -16265,7 +16265,7 @@
         <v>0.3115921835495976</v>
       </c>
       <c r="G206" t="n">
-        <v>0.0002151307119743862</v>
+        <v>0.0002151307119742884</v>
       </c>
       <c r="H206" t="n">
         <v>0.688192685738316</v>
@@ -16288,10 +16288,10 @@
         <v>2</v>
       </c>
       <c r="F207" t="n">
-        <v>0.1679459422565393</v>
+        <v>0.1679459422565011</v>
       </c>
       <c r="G207" t="n">
-        <v>0.0002458116787953272</v>
+        <v>0.0002458116787951595</v>
       </c>
       <c r="H207" t="n">
         <v>0.8318082460647073</v>
@@ -16314,10 +16314,10 @@
         <v>2</v>
       </c>
       <c r="F208" t="n">
-        <v>0.06015512141780714</v>
+        <v>0.06015512141777979</v>
       </c>
       <c r="G208" t="n">
-        <v>0.000633500436378617</v>
+        <v>0.0006335004363783289</v>
       </c>
       <c r="H208" t="n">
         <v>0.9392113781457813</v>
@@ -16340,10 +16340,10 @@
         <v>2</v>
       </c>
       <c r="F209" t="n">
-        <v>0.02208396175499108</v>
+        <v>0.02208396175498606</v>
       </c>
       <c r="G209" t="n">
-        <v>0.0005451181829604319</v>
+        <v>0.000545118182960184</v>
       </c>
       <c r="H209" t="n">
         <v>0.9773709200620464</v>
@@ -16369,7 +16369,7 @@
         <v>0.0192338158759392</v>
       </c>
       <c r="G210" t="n">
-        <v>0.0003308157135913254</v>
+        <v>0.000330815713591175</v>
       </c>
       <c r="H210" t="n">
         <v>0.9804353684104413</v>
@@ -16395,10 +16395,10 @@
         <v>0.0367561186160734</v>
       </c>
       <c r="G211" t="n">
-        <v>0.0006600772204464017</v>
+        <v>0.0006600772204462517</v>
       </c>
       <c r="H211" t="n">
-        <v>0.9625838041633668</v>
+        <v>0.9625838041635856</v>
       </c>
     </row>
     <row r="212">
@@ -16418,10 +16418,10 @@
         <v>2</v>
       </c>
       <c r="F212" t="n">
-        <v>0.01163918172893736</v>
+        <v>0.01163918172893471</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0009937241906409623</v>
+        <v>0.0009937241906405104</v>
       </c>
       <c r="H212" t="n">
         <v>0.9873670940804148</v>
@@ -16447,7 +16447,7 @@
         <v>0.008349842993116146</v>
       </c>
       <c r="G213" t="n">
-        <v>0.001187072623954878</v>
+        <v>0.001187072623954338</v>
       </c>
       <c r="H213" t="n">
         <v>0.9904630843829099</v>
@@ -16473,7 +16473,7 @@
         <v>0.009348879664894475</v>
       </c>
       <c r="G214" t="n">
-        <v>0.001534567518837529</v>
+        <v>0.001534567518836831</v>
       </c>
       <c r="H214" t="n">
         <v>0.9891165528163655</v>
@@ -16496,10 +16496,10 @@
         <v>2</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0185212783229707</v>
+        <v>0.01852127832296649</v>
       </c>
       <c r="G215" t="n">
-        <v>0.001988038423130524</v>
+        <v>0.001988038423130072</v>
       </c>
       <c r="H215" t="n">
         <v>0.9794906832538537</v>
@@ -16525,7 +16525,7 @@
         <v>0.03028304946392159</v>
       </c>
       <c r="G216" t="n">
-        <v>0.001689325519282423</v>
+        <v>0.001689325519281654</v>
       </c>
       <c r="H216" t="n">
         <v>0.9680276250166852</v>
@@ -16551,7 +16551,7 @@
         <v>0.009772782295775037</v>
       </c>
       <c r="G217" t="n">
-        <v>0.001225626253361582</v>
+        <v>0.001225626253360746</v>
       </c>
       <c r="H217" t="n">
         <v>0.9890015914508734</v>
@@ -16574,10 +16574,10 @@
         <v>2</v>
       </c>
       <c r="F218" t="n">
-        <v>0.007904014923891985</v>
+        <v>0.007904014923890187</v>
       </c>
       <c r="G218" t="n">
-        <v>0.001090869311352617</v>
+        <v>0.001090869311352121</v>
       </c>
       <c r="H218" t="n">
         <v>0.9910051157647759</v>
@@ -16603,7 +16603,7 @@
         <v>0.007812136715848357</v>
       </c>
       <c r="G219" t="n">
-        <v>0.001222551525910252</v>
+        <v>0.001222551525909696</v>
       </c>
       <c r="H219" t="n">
         <v>0.9909653117583117</v>
@@ -16629,7 +16629,7 @@
         <v>0.007301553614106174</v>
       </c>
       <c r="G220" t="n">
-        <v>0.001102688087155537</v>
+        <v>0.001102688087155286</v>
       </c>
       <c r="H220" t="n">
         <v>0.9915957582988393</v>
@@ -16652,10 +16652,10 @@
         <v>2</v>
       </c>
       <c r="F221" t="n">
-        <v>0.008111250004851221</v>
+        <v>0.008111250004849377</v>
       </c>
       <c r="G221" t="n">
-        <v>0.001017469419108521</v>
+        <v>0.001017469419107827</v>
       </c>
       <c r="H221" t="n">
         <v>0.9908712805761219</v>
@@ -16678,10 +16678,10 @@
         <v>2</v>
       </c>
       <c r="F222" t="n">
-        <v>0.007305310208225242</v>
+        <v>0.007305310208226903</v>
       </c>
       <c r="G222" t="n">
-        <v>0.0009536606852561071</v>
+        <v>0.0009536606852554566</v>
       </c>
       <c r="H222" t="n">
         <v>0.9917410291065543</v>
@@ -16704,10 +16704,10 @@
         <v>2</v>
       </c>
       <c r="F223" t="n">
-        <v>0.006416414433973501</v>
+        <v>0.00641641443397496</v>
       </c>
       <c r="G223" t="n">
-        <v>0.0009706701850237625</v>
+        <v>0.0009706701850233211</v>
       </c>
       <c r="H223" t="n">
         <v>0.9926129153810377</v>
@@ -16733,7 +16733,7 @@
         <v>0.006612688747998363</v>
       </c>
       <c r="G224" t="n">
-        <v>0.001023517568364725</v>
+        <v>0.001023517568364027</v>
       </c>
       <c r="H224" t="n">
         <v>0.9923637936836383</v>
@@ -16759,7 +16759,7 @@
         <v>0.01020764547995273</v>
       </c>
       <c r="G225" t="n">
-        <v>0.001019513758558667</v>
+        <v>0.001019513758558434</v>
       </c>
       <c r="H225" t="n">
         <v>0.988772840761437</v>
@@ -16785,7 +16785,7 @@
         <v>0.006505873573519803</v>
       </c>
       <c r="G226" t="n">
-        <v>0.001059052498284539</v>
+        <v>0.001059052498284298</v>
       </c>
       <c r="H226" t="n">
         <v>0.9924350739280967</v>
@@ -16808,10 +16808,10 @@
         <v>2</v>
       </c>
       <c r="F227" t="n">
-        <v>0.00540412646623225</v>
+        <v>0.005404126466229793</v>
       </c>
       <c r="G227" t="n">
-        <v>0.001070757499767648</v>
+        <v>0.001070757499767404</v>
       </c>
       <c r="H227" t="n">
         <v>0.9935251160339228</v>
@@ -16837,7 +16837,7 @@
         <v>0.005551982037071229</v>
       </c>
       <c r="G228" t="n">
-        <v>0.001100499475056926</v>
+        <v>0.001100499475056175</v>
       </c>
       <c r="H228" t="n">
         <v>0.9933475184878596</v>
@@ -16851,7 +16851,7 @@
         <v>0.01015736928597801</v>
       </c>
       <c r="C229" t="n">
-        <v>0.001216387825317767</v>
+        <v>0.001216387825317766</v>
       </c>
       <c r="D229" t="n">
         <v>0.0206621774602185</v>
@@ -16860,10 +16860,10 @@
         <v>2</v>
       </c>
       <c r="F229" t="n">
-        <v>0.007978716845019091</v>
+        <v>0.007978716845015464</v>
       </c>
       <c r="G229" t="n">
-        <v>0.001081266665745864</v>
+        <v>0.001081266665744635</v>
       </c>
       <c r="H229" t="n">
         <v>0.9909400164893164</v>
@@ -16889,7 +16889,7 @@
         <v>0.01857914748576862</v>
       </c>
       <c r="G230" t="n">
-        <v>0.001023482823774832</v>
+        <v>0.001023482823774366</v>
       </c>
       <c r="H230" t="n">
         <v>0.980397369690439</v>
@@ -16912,10 +16912,10 @@
         <v>2</v>
       </c>
       <c r="F231" t="n">
-        <v>0.03888214815030275</v>
+        <v>0.03888214815029391</v>
       </c>
       <c r="G231" t="n">
-        <v>0.001702981784817234</v>
+        <v>0.001702981784816072</v>
       </c>
       <c r="H231" t="n">
         <v>0.9594148700648653</v>
@@ -16932,7 +16932,7 @@
         <v>0.01121763028466697</v>
       </c>
       <c r="D232" t="n">
-        <v>0.004224764132000604</v>
+        <v>0.004224764132000603</v>
       </c>
       <c r="E232" t="n">
         <v>2</v>
@@ -16941,7 +16941,7 @@
         <v>0.03148467680808879</v>
       </c>
       <c r="G232" t="n">
-        <v>0.001248178217855641</v>
+        <v>0.001248178217854789</v>
       </c>
       <c r="H232" t="n">
         <v>0.967267144974118</v>
@@ -16967,7 +16967,7 @@
         <v>0.01144429689198318</v>
       </c>
       <c r="G233" t="n">
-        <v>0.001341092480966148</v>
+        <v>0.001341092480965538</v>
       </c>
       <c r="H233" t="n">
         <v>0.9872146106269478</v>
@@ -16993,7 +16993,7 @@
         <v>0.009010940347361577</v>
       </c>
       <c r="G234" t="n">
-        <v>0.0009348739935890521</v>
+        <v>0.000934873993588627</v>
       </c>
       <c r="H234" t="n">
         <v>0.9900541856591045</v>
@@ -17004,10 +17004,10 @@
         <v>43281</v>
       </c>
       <c r="B235" t="n">
-        <v>0.004736567679959356</v>
+        <v>0.004736567679959355</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.0008148956246944808</v>
+        <v>-0.000814895624694481</v>
       </c>
       <c r="D235" t="n">
         <v>-0.03739508308922888</v>
@@ -17016,10 +17016,10 @@
         <v>2</v>
       </c>
       <c r="F235" t="n">
-        <v>0.00846923488238341</v>
+        <v>0.008469234882381485</v>
       </c>
       <c r="G235" t="n">
-        <v>0.0006749946302080988</v>
+        <v>0.0006749946302076384</v>
       </c>
       <c r="H235" t="n">
         <v>0.9908557704873066</v>
@@ -17042,10 +17042,10 @@
         <v>2</v>
       </c>
       <c r="F236" t="n">
-        <v>0.01031615517510418</v>
+        <v>0.01031615517510184</v>
       </c>
       <c r="G236" t="n">
-        <v>0.0008464875385516559</v>
+        <v>0.0008464875385510786</v>
       </c>
       <c r="H236" t="n">
         <v>0.988837357286407</v>
@@ -17071,7 +17071,7 @@
         <v>0.03122887467476069</v>
       </c>
       <c r="G237" t="n">
-        <v>0.001052023724572615</v>
+        <v>0.001052023724572137</v>
       </c>
       <c r="H237" t="n">
         <v>0.9677191016005969</v>
@@ -17094,10 +17094,10 @@
         <v>2</v>
       </c>
       <c r="F238" t="n">
-        <v>0.1169836500417442</v>
+        <v>0.1169836500417176</v>
       </c>
       <c r="G238" t="n">
-        <v>0.001402541675476171</v>
+        <v>0.001402541675475214</v>
       </c>
       <c r="H238" t="n">
         <v>0.8816138082828104</v>
@@ -17123,10 +17123,10 @@
         <v>0.6286414313443363</v>
       </c>
       <c r="G239" t="n">
-        <v>0.001774134124928075</v>
+        <v>0.001774134124927268</v>
       </c>
       <c r="H239" t="n">
-        <v>0.3695844345307467</v>
+        <v>0.3695844345306627</v>
       </c>
     </row>
     <row r="240">
@@ -17146,10 +17146,10 @@
         <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0.6090515249670619</v>
+        <v>0.6090515249669234</v>
       </c>
       <c r="G240" t="n">
-        <v>0.0003361188143883968</v>
+        <v>0.000336118814388244</v>
       </c>
       <c r="H240" t="n">
         <v>0.3906123562185826</v>
@@ -17175,7 +17175,7 @@
         <v>0.9485612812789626</v>
       </c>
       <c r="G241" t="n">
-        <v>0.00023942284796914</v>
+        <v>0.0002394228479690312</v>
       </c>
       <c r="H241" t="n">
         <v>0.05119929587299585</v>
@@ -17198,13 +17198,13 @@
         <v>2</v>
       </c>
       <c r="F242" t="n">
-        <v>0.3887539434747788</v>
+        <v>0.3887539434746904</v>
       </c>
       <c r="G242" t="n">
-        <v>0.0002496313327346817</v>
+        <v>0.000249631332734625</v>
       </c>
       <c r="H242" t="n">
-        <v>0.6109964251924463</v>
+        <v>0.6109964251925852</v>
       </c>
     </row>
     <row r="243">
@@ -17250,10 +17250,10 @@
         <v>2</v>
       </c>
       <c r="F244" t="n">
-        <v>0.09230389439968059</v>
+        <v>0.09230389439965961</v>
       </c>
       <c r="G244" t="n">
-        <v>0.0003196342379406749</v>
+        <v>0.0003196342379406022</v>
       </c>
       <c r="H244" t="n">
         <v>0.9073764713624809</v>
@@ -17279,7 +17279,7 @@
         <v>0.1159953800348644</v>
       </c>
       <c r="G245" t="n">
-        <v>0.0002689834206232954</v>
+        <v>0.0002689834206231119</v>
       </c>
       <c r="H245" t="n">
         <v>0.8837356365444478</v>
@@ -17305,7 +17305,7 @@
         <v>0.4358538009725937</v>
       </c>
       <c r="G246" t="n">
-        <v>0.0001626101716203596</v>
+        <v>0.0001626101716202857</v>
       </c>
       <c r="H246" t="n">
         <v>0.5639835888558941</v>
@@ -17331,10 +17331,10 @@
         <v>0.2162449925349835</v>
       </c>
       <c r="G247" t="n">
-        <v>0.0003845984206765254</v>
+        <v>0.0003845984206763505</v>
       </c>
       <c r="H247" t="n">
-        <v>0.7833704090442848</v>
+        <v>0.7833704090442849</v>
       </c>
     </row>
     <row r="248">
@@ -17354,10 +17354,10 @@
         <v>2</v>
       </c>
       <c r="F248" t="n">
-        <v>0.08822672536227093</v>
+        <v>0.08822672536225086</v>
       </c>
       <c r="G248" t="n">
-        <v>0.000495766883064335</v>
+        <v>0.0004957668830641096</v>
       </c>
       <c r="H248" t="n">
         <v>0.9112775077545754</v>
@@ -17383,7 +17383,7 @@
         <v>0.1309986223531719</v>
       </c>
       <c r="G249" t="n">
-        <v>0.0005300042830892071</v>
+        <v>0.0005300042830890865</v>
       </c>
       <c r="H249" t="n">
         <v>0.8684713733636307</v>
@@ -17406,10 +17406,10 @@
         <v>2</v>
       </c>
       <c r="F250" t="n">
-        <v>0.02641329785505631</v>
+        <v>0.0264132978550383</v>
       </c>
       <c r="G250" t="n">
-        <v>0.000580663107607793</v>
+        <v>0.0005806631076072649</v>
       </c>
       <c r="H250" t="n">
         <v>0.9730060390373315</v>
@@ -17432,10 +17432,10 @@
         <v>2</v>
       </c>
       <c r="F251" t="n">
-        <v>0.01142508636557257</v>
+        <v>0.01142508636556997</v>
       </c>
       <c r="G251" t="n">
-        <v>0.0005749602718001295</v>
+        <v>0.000574960271799868</v>
       </c>
       <c r="H251" t="n">
         <v>0.9879999533626255</v>
@@ -17449,7 +17449,7 @@
         <v>0.03445648173694641</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.007765814965729999</v>
+        <v>-0.00776581496573</v>
       </c>
       <c r="D252" t="n">
         <v>-0.03412835173091319</v>
@@ -17458,10 +17458,10 @@
         <v>2</v>
       </c>
       <c r="F252" t="n">
-        <v>0.01969016749616903</v>
+        <v>0.01969016749616455</v>
       </c>
       <c r="G252" t="n">
-        <v>0.0004008130326867989</v>
+        <v>0.0004008130326865256</v>
       </c>
       <c r="H252" t="n">
         <v>0.9799090194711934</v>
@@ -17487,7 +17487,7 @@
         <v>0.08044561525658267</v>
       </c>
       <c r="G253" t="n">
-        <v>0.0001819824543287314</v>
+        <v>0.0001819824543286487</v>
       </c>
       <c r="H253" t="n">
         <v>0.9193724022891462</v>
@@ -17513,7 +17513,7 @@
         <v>0.4816498580939115</v>
       </c>
       <c r="G254" t="n">
-        <v>6.230407213534494e-06</v>
+        <v>6.230407213540161e-06</v>
       </c>
       <c r="H254" t="n">
         <v>0.5183439114989032</v>
@@ -17539,10 +17539,10 @@
         <v>0.9921298827081798</v>
       </c>
       <c r="G255" t="n">
-        <v>6.468559476452106e-09</v>
+        <v>6.468559476466813e-09</v>
       </c>
       <c r="H255" t="n">
-        <v>0.007870110823232936</v>
+        <v>0.007870110823231146</v>
       </c>
     </row>
     <row r="256">
@@ -17556,7 +17556,7 @@
         <v>0.0327494959329138</v>
       </c>
       <c r="D256" t="n">
-        <v>-0.006580482164901778</v>
+        <v>-0.006580482164901779</v>
       </c>
       <c r="E256" t="n">
         <v>0</v>
@@ -17565,10 +17565,10 @@
         <v>0.9999882066537905</v>
       </c>
       <c r="G256" t="n">
-        <v>3.025706619951902e-10</v>
+        <v>3.025706619951214e-10</v>
       </c>
       <c r="H256" t="n">
-        <v>1.179304362290114e-05</v>
+        <v>1.17930436229065e-05</v>
       </c>
     </row>
     <row r="257">
@@ -17588,13 +17588,13 @@
         <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>0.9240666096572768</v>
+        <v>0.9240666096570667</v>
       </c>
       <c r="G257" t="n">
-        <v>8.979478483674445e-06</v>
+        <v>8.979478483680571e-06</v>
       </c>
       <c r="H257" t="n">
-        <v>0.07592441086434414</v>
+        <v>0.0759244108643614</v>
       </c>
     </row>
     <row r="258">
@@ -17614,13 +17614,13 @@
         <v>2</v>
       </c>
       <c r="F258" t="n">
-        <v>0.1906783442057203</v>
+        <v>0.1906783442056769</v>
       </c>
       <c r="G258" t="n">
-        <v>6.187572755642282e-05</v>
+        <v>6.187572755643689e-05</v>
       </c>
       <c r="H258" t="n">
-        <v>0.8092597800666279</v>
+        <v>0.8092597800668119</v>
       </c>
     </row>
     <row r="259">
@@ -17640,10 +17640,10 @@
         <v>2</v>
       </c>
       <c r="F259" t="n">
-        <v>0.05517983635367408</v>
+        <v>0.05517983635362389</v>
       </c>
       <c r="G259" t="n">
-        <v>0.0002905781658465591</v>
+        <v>0.0002905781658464269</v>
       </c>
       <c r="H259" t="n">
         <v>0.944529585480462</v>
@@ -17666,13 +17666,13 @@
         <v>2</v>
       </c>
       <c r="F260" t="n">
-        <v>0.05860847592910993</v>
+        <v>0.05860847592909661</v>
       </c>
       <c r="G260" t="n">
-        <v>0.0003388639599169472</v>
+        <v>0.0003388639599167161</v>
       </c>
       <c r="H260" t="n">
-        <v>0.9410526601109107</v>
+        <v>0.9410526601109106</v>
       </c>
     </row>
     <row r="261">
@@ -17692,10 +17692,10 @@
         <v>2</v>
       </c>
       <c r="F261" t="n">
-        <v>0.06340224163407095</v>
+        <v>0.06340224163405653</v>
       </c>
       <c r="G261" t="n">
-        <v>0.001111381601521142</v>
+        <v>0.00111138160152089</v>
       </c>
       <c r="H261" t="n">
         <v>0.9354863767644123</v>
@@ -17718,10 +17718,10 @@
         <v>2</v>
       </c>
       <c r="F262" t="n">
-        <v>0.1161924366587002</v>
+        <v>0.1161924366586474</v>
       </c>
       <c r="G262" t="n">
-        <v>0.001778285296405024</v>
+        <v>0.001778285296403811</v>
       </c>
       <c r="H262" t="n">
         <v>0.8820292780449156</v>
@@ -17744,13 +17744,13 @@
         <v>2</v>
       </c>
       <c r="F263" t="n">
-        <v>0.1505642444951996</v>
+        <v>0.1505642444951654</v>
       </c>
       <c r="G263" t="n">
-        <v>0.005207729272237334</v>
+        <v>0.00520772927223615</v>
       </c>
       <c r="H263" t="n">
-        <v>0.8442280262324618</v>
+        <v>0.8442280262326538</v>
       </c>
     </row>
     <row r="264">
@@ -17770,13 +17770,13 @@
         <v>2</v>
       </c>
       <c r="F264" t="n">
-        <v>0.2614518760621346</v>
+        <v>0.2614518760620157</v>
       </c>
       <c r="G264" t="n">
-        <v>0.006428403087557936</v>
+        <v>0.006428403087556474</v>
       </c>
       <c r="H264" t="n">
-        <v>0.7321197208502417</v>
+        <v>0.7321197208504082</v>
       </c>
     </row>
     <row r="265">
@@ -17796,10 +17796,10 @@
         <v>2</v>
       </c>
       <c r="F265" t="n">
-        <v>0.06280172565240814</v>
+        <v>0.06280172565235102</v>
       </c>
       <c r="G265" t="n">
-        <v>0.004275922311575253</v>
+        <v>0.004275922311572337</v>
       </c>
       <c r="H265" t="n">
         <v>0.9329223520360325</v>
@@ -17822,10 +17822,10 @@
         <v>2</v>
       </c>
       <c r="F266" t="n">
-        <v>0.02231635464201188</v>
+        <v>0.02231635464199666</v>
       </c>
       <c r="G266" t="n">
-        <v>0.004619986404932926</v>
+        <v>0.004619986404930825</v>
       </c>
       <c r="H266" t="n">
         <v>0.9730636589529701</v>
@@ -17848,10 +17848,10 @@
         <v>2</v>
       </c>
       <c r="F267" t="n">
-        <v>0.01350181022112486</v>
+        <v>0.0135018102211218</v>
       </c>
       <c r="G267" t="n">
-        <v>0.00509665580878017</v>
+        <v>0.005096655808779011</v>
       </c>
       <c r="H267" t="n">
         <v>0.9814015339701723</v>
@@ -17877,7 +17877,7 @@
         <v>0.01092137395396244</v>
       </c>
       <c r="G268" t="n">
-        <v>0.006970971572531317</v>
+        <v>0.006970971572529732</v>
       </c>
       <c r="H268" t="n">
         <v>0.9821076544734743</v>
@@ -17900,10 +17900,10 @@
         <v>2</v>
       </c>
       <c r="F269" t="n">
-        <v>0.01341378469236172</v>
+        <v>0.01341378469236477</v>
       </c>
       <c r="G269" t="n">
-        <v>0.009873533336596511</v>
+        <v>0.009873533336598758</v>
       </c>
       <c r="H269" t="n">
         <v>0.9767126819710555</v>
@@ -17926,10 +17926,10 @@
         <v>2</v>
       </c>
       <c r="F270" t="n">
-        <v>0.01537438322839683</v>
+        <v>0.01537438322839334</v>
       </c>
       <c r="G270" t="n">
-        <v>0.01216857999510921</v>
+        <v>0.01216857999511197</v>
       </c>
       <c r="H270" t="n">
         <v>0.9724570367765498</v>
@@ -17952,7 +17952,7 @@
         <v>2</v>
       </c>
       <c r="F271" t="n">
-        <v>0.01840362179367763</v>
+        <v>0.01840362179367344</v>
       </c>
       <c r="G271" t="n">
         <v>0.01978572743272973</v>
@@ -18033,7 +18033,7 @@
         <v>0.03409788405065999</v>
       </c>
       <c r="G274" t="n">
-        <v>0.3003241705527259</v>
+        <v>0.3003241705526576</v>
       </c>
       <c r="H274" t="n">
         <v>0.6655779453967254</v>
@@ -18114,7 +18114,7 @@
         <v>0.593633199918229</v>
       </c>
       <c r="H277" t="n">
-        <v>0.4043212361032604</v>
+        <v>0.4043212361033524</v>
       </c>
     </row>
     <row r="278">
@@ -18134,13 +18134,13 @@
         <v>1</v>
       </c>
       <c r="F278" t="n">
-        <v>0.00652825939805072</v>
+        <v>0.006528259398049236</v>
       </c>
       <c r="G278" t="n">
         <v>0.9148107039562212</v>
       </c>
       <c r="H278" t="n">
-        <v>0.07866103664571285</v>
+        <v>0.07866103664569497</v>
       </c>
     </row>
     <row r="279">
@@ -18192,7 +18192,7 @@
         <v>0.9673591146401656</v>
       </c>
       <c r="H280" t="n">
-        <v>0.03194016681751614</v>
+        <v>0.03194016681750162</v>
       </c>
     </row>
     <row r="281">
@@ -18212,13 +18212,13 @@
         <v>1</v>
       </c>
       <c r="F281" t="n">
-        <v>0.0008402253817784714</v>
+        <v>0.0008402253817786624</v>
       </c>
       <c r="G281" t="n">
         <v>0.9991035820203877</v>
       </c>
       <c r="H281" t="n">
-        <v>5.619259775425248e-05</v>
+        <v>5.61925977542397e-05</v>
       </c>
     </row>
     <row r="282">
@@ -18238,13 +18238,13 @@
         <v>1</v>
       </c>
       <c r="F282" t="n">
-        <v>9.872069791224545e-05</v>
+        <v>9.87206979123128e-05</v>
       </c>
       <c r="G282" t="n">
         <v>0.9978447861371598</v>
       </c>
       <c r="H282" t="n">
-        <v>0.002056493164849565</v>
+        <v>0.002056493164849097</v>
       </c>
     </row>
     <row r="283">
@@ -18264,13 +18264,13 @@
         <v>1</v>
       </c>
       <c r="F283" t="n">
-        <v>8.875780651337487e-05</v>
+        <v>8.875780651341525e-05</v>
       </c>
       <c r="G283" t="n">
         <v>0.9996184699533956</v>
       </c>
       <c r="H283" t="n">
-        <v>0.0002927722400113659</v>
+        <v>0.0002927722400112993</v>
       </c>
     </row>
     <row r="284">
@@ -18290,13 +18290,13 @@
         <v>1</v>
       </c>
       <c r="F284" t="n">
-        <v>2.031459459394855e-05</v>
+        <v>2.031459459396241e-05</v>
       </c>
       <c r="G284" t="n">
         <v>0.999920796950726</v>
       </c>
       <c r="H284" t="n">
-        <v>5.888845468275875e-05</v>
+        <v>5.888845468274536e-05</v>
       </c>
     </row>
     <row r="285">
@@ -18322,7 +18322,7 @@
         <v>0.9999873263084772</v>
       </c>
       <c r="H285" t="n">
-        <v>1.004880425740064e-05</v>
+        <v>1.00488042573915e-05</v>
       </c>
     </row>
     <row r="286">
@@ -18342,13 +18342,13 @@
         <v>1</v>
       </c>
       <c r="F286" t="n">
-        <v>1.739209236928808e-06</v>
+        <v>1.739209236928017e-06</v>
       </c>
       <c r="G286" t="n">
         <v>0.9999982049241876</v>
       </c>
       <c r="H286" t="n">
-        <v>5.586651948502683e-08</v>
+        <v>5.586651948497602e-08</v>
       </c>
     </row>
     <row r="287">
@@ -18374,7 +18374,7 @@
         <v>0.999256125353481</v>
       </c>
       <c r="H287" t="n">
-        <v>0.0007433642089148194</v>
+        <v>0.0007433642089143123</v>
       </c>
     </row>
     <row r="288">
@@ -18394,13 +18394,13 @@
         <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>6.782433975587701e-06</v>
+        <v>6.782433975583074e-06</v>
       </c>
       <c r="G288" t="n">
         <v>0.9996546144681053</v>
       </c>
       <c r="H288" t="n">
-        <v>0.0003386030978300968</v>
+        <v>0.0003386030978297888</v>
       </c>
     </row>
     <row r="289">
@@ -18420,13 +18420,13 @@
         <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>1.192276855303945e-05</v>
+        <v>1.192276855303403e-05</v>
       </c>
       <c r="G289" t="n">
         <v>0.9998866515329408</v>
       </c>
       <c r="H289" t="n">
-        <v>0.000101425698583589</v>
+        <v>0.0001014256985835429</v>
       </c>
     </row>
     <row r="290">
@@ -18446,13 +18446,13 @@
         <v>1</v>
       </c>
       <c r="F290" t="n">
-        <v>9.013647631614957e-06</v>
+        <v>9.013647631608809e-06</v>
       </c>
       <c r="G290" t="n">
         <v>0.9997330919464044</v>
       </c>
       <c r="H290" t="n">
-        <v>0.0002578944059598084</v>
+        <v>0.0002578944059595738</v>
       </c>
     </row>
     <row r="291">
@@ -18472,13 +18472,13 @@
         <v>1</v>
       </c>
       <c r="F291" t="n">
-        <v>1.438811577138692e-05</v>
+        <v>1.438811577138038e-05</v>
       </c>
       <c r="G291" t="n">
         <v>0.9994220979693929</v>
       </c>
       <c r="H291" t="n">
-        <v>0.0005635139148642174</v>
+        <v>0.0005635139148639613</v>
       </c>
     </row>
     <row r="292">
@@ -18498,13 +18498,13 @@
         <v>1</v>
       </c>
       <c r="F292" t="n">
-        <v>2.142647678835417e-05</v>
+        <v>2.142647678834443e-05</v>
       </c>
       <c r="G292" t="n">
         <v>0.9964490425868522</v>
       </c>
       <c r="H292" t="n">
-        <v>0.003529530936256637</v>
+        <v>0.00352953093625423</v>
       </c>
     </row>
     <row r="293">
@@ -18524,13 +18524,13 @@
         <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>1.966277089501346e-05</v>
+        <v>1.966277089500005e-05</v>
       </c>
       <c r="G293" t="n">
         <v>0.9920919298181827</v>
       </c>
       <c r="H293" t="n">
-        <v>0.007888407410851145</v>
+        <v>0.007888407410845764</v>
       </c>
     </row>
     <row r="294">
@@ -18550,13 +18550,13 @@
         <v>1</v>
       </c>
       <c r="F294" t="n">
-        <v>4.340504212562796e-05</v>
+        <v>4.340504212560822e-05</v>
       </c>
       <c r="G294" t="n">
         <v>0.9907845444182219</v>
       </c>
       <c r="H294" t="n">
-        <v>0.00917205053968775</v>
+        <v>0.009172050539681495</v>
       </c>
     </row>
     <row r="295">
@@ -18576,13 +18576,13 @@
         <v>1</v>
       </c>
       <c r="F295" t="n">
-        <v>5.826075527742044e-05</v>
+        <v>5.82607552773807e-05</v>
       </c>
       <c r="G295" t="n">
         <v>0.9897211316809603</v>
       </c>
       <c r="H295" t="n">
-        <v>0.01022060756366368</v>
+        <v>0.01022060756365671</v>
       </c>
     </row>
     <row r="296">
@@ -18602,13 +18602,13 @@
         <v>1</v>
       </c>
       <c r="F296" t="n">
-        <v>2.330084969759577e-05</v>
+        <v>2.330084969759047e-05</v>
       </c>
       <c r="G296" t="n">
         <v>0.9913363467552797</v>
       </c>
       <c r="H296" t="n">
-        <v>0.008640352394932221</v>
+        <v>0.008640352394926328</v>
       </c>
     </row>
     <row r="297">
@@ -18634,7 +18634,7 @@
         <v>0.9956832043842668</v>
       </c>
       <c r="H297" t="n">
-        <v>0.00428253759973537</v>
+        <v>0.004282537599733423</v>
       </c>
     </row>
     <row r="298">
@@ -18654,13 +18654,13 @@
         <v>1</v>
       </c>
       <c r="F298" t="n">
-        <v>0.0001127514837609199</v>
+        <v>0.000112751483760843</v>
       </c>
       <c r="G298" t="n">
         <v>0.9996542954039619</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0002329531122882792</v>
+        <v>0.0002329531122880144</v>
       </c>
     </row>
     <row r="299">
@@ -18680,13 +18680,13 @@
         <v>1</v>
       </c>
       <c r="F299" t="n">
-        <v>0.0001176285860458359</v>
+        <v>0.0001176285860457556</v>
       </c>
       <c r="G299" t="n">
         <v>0.9996164627993448</v>
       </c>
       <c r="H299" t="n">
-        <v>0.0002659086146926312</v>
+        <v>0.0002659086146923894</v>
       </c>
     </row>
     <row r="300">
@@ -18706,13 +18706,13 @@
         <v>1</v>
       </c>
       <c r="F300" t="n">
-        <v>0.0001537893324507126</v>
+        <v>0.0001537893324506426</v>
       </c>
       <c r="G300" t="n">
         <v>0.9996321052033859</v>
       </c>
       <c r="H300" t="n">
-        <v>0.0002141054641275106</v>
+        <v>0.0002141054641273646</v>
       </c>
     </row>
     <row r="301">
@@ -18732,13 +18732,13 @@
         <v>1</v>
       </c>
       <c r="F301" t="n">
-        <v>0.0001058774692712633</v>
+        <v>0.0001058774692711911</v>
       </c>
       <c r="G301" t="n">
         <v>0.9913493880871225</v>
       </c>
       <c r="H301" t="n">
-        <v>0.008544734443586676</v>
+        <v>0.008544734443580847</v>
       </c>
     </row>
     <row r="302">
@@ -18749,7 +18749,7 @@
         <v>0.01197547558860675</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.006295415534405311</v>
+        <v>-0.00629541553440531</v>
       </c>
       <c r="D302" t="n">
         <v>-0.01612604285629309</v>
@@ -18758,13 +18758,13 @@
         <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>7.195922086081623e-05</v>
+        <v>7.19592208607835e-05</v>
       </c>
       <c r="G302" t="n">
         <v>0.9682044949376508</v>
       </c>
       <c r="H302" t="n">
-        <v>0.03172354584146762</v>
+        <v>0.03172354584144597</v>
       </c>
     </row>
     <row r="303">
@@ -18784,13 +18784,13 @@
         <v>1</v>
       </c>
       <c r="F303" t="n">
-        <v>0.0004734388528815349</v>
+        <v>0.0004734388528813196</v>
       </c>
       <c r="G303" t="n">
         <v>0.955935976539895</v>
       </c>
       <c r="H303" t="n">
-        <v>0.04359058460723277</v>
+        <v>0.04359058460720304</v>
       </c>
     </row>
     <row r="304">
@@ -18810,13 +18810,13 @@
         <v>1</v>
       </c>
       <c r="F304" t="n">
-        <v>0.001851864165615272</v>
+        <v>0.001851864165613588</v>
       </c>
       <c r="G304" t="n">
         <v>0.9508051215075694</v>
       </c>
       <c r="H304" t="n">
-        <v>0.04734301432679605</v>
+        <v>0.047343014326753</v>
       </c>
     </row>
     <row r="305">
@@ -18836,13 +18836,13 @@
         <v>1</v>
       </c>
       <c r="F305" t="n">
-        <v>0.007535661369909291</v>
+        <v>0.007535661369904151</v>
       </c>
       <c r="G305" t="n">
         <v>0.9570536804184639</v>
       </c>
       <c r="H305" t="n">
-        <v>0.0354106582116842</v>
+        <v>0.03541065821166005</v>
       </c>
     </row>
     <row r="306">
@@ -18862,13 +18862,13 @@
         <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>0.002343237214253684</v>
+        <v>0.00234323721425102</v>
       </c>
       <c r="G306" t="n">
         <v>0.8795774961823853</v>
       </c>
       <c r="H306" t="n">
-        <v>0.1180792666034431</v>
+        <v>0.1180792666033894</v>
       </c>
     </row>
     <row r="307">
@@ -18888,13 +18888,13 @@
         <v>1</v>
       </c>
       <c r="F307" t="n">
-        <v>0.001506754404457902</v>
+        <v>0.001506754404457216</v>
       </c>
       <c r="G307" t="n">
-        <v>0.7952963954300999</v>
+        <v>0.7952963954302807</v>
       </c>
       <c r="H307" t="n">
-        <v>0.2031968501653506</v>
+        <v>0.2031968501653044</v>
       </c>
     </row>
     <row r="308">
@@ -18914,13 +18914,13 @@
         <v>1</v>
       </c>
       <c r="F308" t="n">
-        <v>0.003587247153512444</v>
+        <v>0.003587247153509996</v>
       </c>
       <c r="G308" t="n">
         <v>0.7408146382258821</v>
       </c>
       <c r="H308" t="n">
-        <v>0.2555981146207134</v>
+        <v>0.2555981146206553</v>
       </c>
     </row>
     <row r="309">
@@ -18940,13 +18940,13 @@
         <v>1</v>
       </c>
       <c r="F309" t="n">
-        <v>0.002858040266195525</v>
+        <v>0.002858040266194225</v>
       </c>
       <c r="G309" t="n">
         <v>0.7056536675629367</v>
       </c>
       <c r="H309" t="n">
-        <v>0.2914882921708297</v>
+        <v>0.2914882921707634</v>
       </c>
     </row>
     <row r="310">
@@ -18966,13 +18966,13 @@
         <v>1</v>
       </c>
       <c r="F310" t="n">
-        <v>0.006105571531840245</v>
+        <v>0.006105571531837469</v>
       </c>
       <c r="G310" t="n">
         <v>0.6858673569899595</v>
       </c>
       <c r="H310" t="n">
-        <v>0.3080270714782843</v>
+        <v>0.3080270714781443</v>
       </c>
     </row>
     <row r="311">
@@ -18992,13 +18992,13 @@
         <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>0.0219365167051044</v>
+        <v>0.02193651670509941</v>
       </c>
       <c r="G311" t="n">
         <v>0.6791314073777317</v>
       </c>
       <c r="H311" t="n">
-        <v>0.2989320759171454</v>
+        <v>0.2989320759170774</v>
       </c>
     </row>
     <row r="312">
@@ -19018,7 +19018,7 @@
         <v>1</v>
       </c>
       <c r="F312" t="n">
-        <v>0.0177481471541925</v>
+        <v>0.01774814715418443</v>
       </c>
       <c r="G312" t="n">
         <v>0.6011485992137902</v>
@@ -19047,7 +19047,7 @@
         <v>0.02632820192021235</v>
       </c>
       <c r="G313" t="n">
-        <v>0.5518899909026271</v>
+        <v>0.5518899909027526</v>
       </c>
       <c r="H313" t="n">
         <v>0.4217818071771102</v>
@@ -19070,10 +19070,10 @@
         <v>2</v>
       </c>
       <c r="F314" t="n">
-        <v>0.03021843236291301</v>
+        <v>0.03021843236291988</v>
       </c>
       <c r="G314" t="n">
-        <v>0.2743860679499556</v>
+        <v>0.274386067950018</v>
       </c>
       <c r="H314" t="n">
         <v>0.6953954996870592</v>
@@ -19096,10 +19096,10 @@
         <v>2</v>
       </c>
       <c r="F315" t="n">
-        <v>0.1349366788852484</v>
+        <v>0.134936678885279</v>
       </c>
       <c r="G315" t="n">
-        <v>0.1734358921897542</v>
+        <v>0.1734358921897936</v>
       </c>
       <c r="H315" t="n">
         <v>0.6916274289249592</v>
@@ -19113,7 +19113,7 @@
         <v>-0.06138811628823403</v>
       </c>
       <c r="C316" t="n">
-        <v>0.0003471971954322061</v>
+        <v>0.0003471971954322065</v>
       </c>
       <c r="D316" t="n">
         <v>0.08551974980632972</v>
@@ -19125,10 +19125,10 @@
         <v>0.2894440981971224</v>
       </c>
       <c r="G316" t="n">
-        <v>0.1462996594005783</v>
+        <v>0.1462996594006116</v>
       </c>
       <c r="H316" t="n">
-        <v>0.564256242402283</v>
+        <v>0.5642562424021548</v>
       </c>
     </row>
     <row r="317">
@@ -19151,7 +19151,7 @@
         <v>0.09349430802857923</v>
       </c>
       <c r="G317" t="n">
-        <v>0.09137693613195907</v>
+        <v>0.09137693613202141</v>
       </c>
       <c r="H317" t="n">
         <v>0.8151287558395071</v>
@@ -19174,10 +19174,10 @@
         <v>2</v>
       </c>
       <c r="F318" t="n">
-        <v>0.02910959439867274</v>
+        <v>0.02910959439866612</v>
       </c>
       <c r="G318" t="n">
-        <v>0.05962667849350253</v>
+        <v>0.05962667849352965</v>
       </c>
       <c r="H318" t="n">
         <v>0.9112637271078364</v>
@@ -19194,16 +19194,16 @@
         <v>0.01223559560573863</v>
       </c>
       <c r="D319" t="n">
-        <v>0.0008197228885392792</v>
+        <v>0.0008197228885392796</v>
       </c>
       <c r="E319" t="n">
         <v>2</v>
       </c>
       <c r="F319" t="n">
-        <v>0.01546732545285827</v>
+        <v>0.01546732545285124</v>
       </c>
       <c r="G319" t="n">
-        <v>0.04215331500843435</v>
+        <v>0.04215331500844394</v>
       </c>
       <c r="H319" t="n">
         <v>0.9423793595388095</v>
@@ -19229,7 +19229,7 @@
         <v>0.007219993776059615</v>
       </c>
       <c r="G320" t="n">
-        <v>0.0228506563214581</v>
+        <v>0.02285065632146849</v>
       </c>
       <c r="H320" t="n">
         <v>0.9699293499024608</v>
@@ -19255,7 +19255,7 @@
         <v>0.01078605423162199</v>
       </c>
       <c r="G321" t="n">
-        <v>0.01024337718547766</v>
+        <v>0.01024337718548231</v>
       </c>
       <c r="H321" t="n">
         <v>0.9789705685829345</v>
@@ -19278,10 +19278,10 @@
         <v>2</v>
       </c>
       <c r="F322" t="n">
-        <v>0.01697415182414092</v>
+        <v>0.01697415182414477</v>
       </c>
       <c r="G322" t="n">
-        <v>0.002350767932047559</v>
+        <v>0.002350767932048093</v>
       </c>
       <c r="H322" t="n">
         <v>0.9806750802438478</v>
@@ -19344,7 +19344,7 @@
         <v>46022</v>
       </c>
       <c r="B325" t="n">
-        <v>-0.002782332919957095</v>
+        <v>-0.002782332919957094</v>
       </c>
       <c r="C325" t="n">
         <v>-0.009222956945157942</v>
@@ -19359,7 +19359,7 @@
         <v>0.02329956079282212</v>
       </c>
       <c r="G325" t="n">
-        <v>0.00168767695151059</v>
+        <v>0.001687676951509822</v>
       </c>
       <c r="H325" t="n">
         <v>0.9750127622556423</v>
@@ -19382,10 +19382,10 @@
         <v>2</v>
       </c>
       <c r="F326" t="n">
-        <v>0.08023005870476733</v>
+        <v>0.0802300587047491</v>
       </c>
       <c r="G326" t="n">
-        <v>0.001348313015003073</v>
+        <v>0.001348313015001847</v>
       </c>
       <c r="H326" t="n">
         <v>0.9184216282802085</v>
